--- a/.pm-ai-cache/network-source/task-input-newest.xlsx
+++ b/.pm-ai-cache/network-source/task-input-newest.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工程別生産計画問合せ問合せ" sheetId="1" r:id="R868b0e38772e4678"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工程別生産計画問合せ問合せ" sheetId="1" r:id="R80b72b1fb8bd41ac"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -10,7 +10,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5">
   <x:si>
-    <x:t xml:space="preserve">表示基準日 : 2026年05月12日 </x:t>
+    <x:t xml:space="preserve">表示基準日 : 2026年05月13日 </x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">K </x:t>
@@ -578,823 +578,823 @@
         <x:v/>
       </x:c>
       <x:c r="AR5" s="2" t="str">
-        <x:v>04/12(日)</x:v>
+        <x:v>04/13(月)</x:v>
       </x:c>
       <x:c r="AS5" s="2" t="str">
-        <x:v>04/12(日)</x:v>
+        <x:v>04/13(月)</x:v>
       </x:c>
       <x:c r="AT5" s="2" t="str">
-        <x:v>04/12(日)</x:v>
+        <x:v>04/13(月)</x:v>
       </x:c>
       <x:c r="AU5" s="2" t="str">
-        <x:v>04/13(月)</x:v>
+        <x:v>04/14(火)</x:v>
       </x:c>
       <x:c r="AV5" s="2" t="str">
-        <x:v>04/13(月)</x:v>
+        <x:v>04/14(火)</x:v>
       </x:c>
       <x:c r="AW5" s="2" t="str">
-        <x:v>04/13(月)</x:v>
+        <x:v>04/14(火)</x:v>
       </x:c>
       <x:c r="AX5" s="2" t="str">
-        <x:v>04/14(火)</x:v>
+        <x:v>04/15(水)</x:v>
       </x:c>
       <x:c r="AY5" s="2" t="str">
-        <x:v>04/14(火)</x:v>
+        <x:v>04/15(水)</x:v>
       </x:c>
       <x:c r="AZ5" s="2" t="str">
-        <x:v>04/14(火)</x:v>
+        <x:v>04/15(水)</x:v>
       </x:c>
       <x:c r="BA5" s="2" t="str">
-        <x:v>04/15(水)</x:v>
+        <x:v>04/16(木)</x:v>
       </x:c>
       <x:c r="BB5" s="2" t="str">
-        <x:v>04/15(水)</x:v>
+        <x:v>04/16(木)</x:v>
       </x:c>
       <x:c r="BC5" s="2" t="str">
-        <x:v>04/15(水)</x:v>
+        <x:v>04/16(木)</x:v>
       </x:c>
       <x:c r="BD5" s="2" t="str">
-        <x:v>04/16(木)</x:v>
+        <x:v>04/17(金)</x:v>
       </x:c>
       <x:c r="BE5" s="2" t="str">
-        <x:v>04/16(木)</x:v>
+        <x:v>04/17(金)</x:v>
       </x:c>
       <x:c r="BF5" s="2" t="str">
-        <x:v>04/16(木)</x:v>
+        <x:v>04/17(金)</x:v>
       </x:c>
       <x:c r="BG5" s="2" t="str">
-        <x:v>04/17(金)</x:v>
+        <x:v>04/18(土)</x:v>
       </x:c>
       <x:c r="BH5" s="2" t="str">
-        <x:v>04/17(金)</x:v>
+        <x:v>04/18(土)</x:v>
       </x:c>
       <x:c r="BI5" s="2" t="str">
-        <x:v>04/17(金)</x:v>
+        <x:v>04/18(土)</x:v>
       </x:c>
       <x:c r="BJ5" s="2" t="str">
-        <x:v>04/18(土)</x:v>
+        <x:v>04/19(日)</x:v>
       </x:c>
       <x:c r="BK5" s="2" t="str">
-        <x:v>04/18(土)</x:v>
+        <x:v>04/19(日)</x:v>
       </x:c>
       <x:c r="BL5" s="2" t="str">
-        <x:v>04/18(土)</x:v>
+        <x:v>04/19(日)</x:v>
       </x:c>
       <x:c r="BM5" s="2" t="str">
-        <x:v>04/19(日)</x:v>
+        <x:v>04/20(月)</x:v>
       </x:c>
       <x:c r="BN5" s="2" t="str">
-        <x:v>04/19(日)</x:v>
+        <x:v>04/20(月)</x:v>
       </x:c>
       <x:c r="BO5" s="2" t="str">
-        <x:v>04/19(日)</x:v>
+        <x:v>04/20(月)</x:v>
       </x:c>
       <x:c r="BP5" s="2" t="str">
-        <x:v>04/20(月)</x:v>
+        <x:v>04/21(火)</x:v>
       </x:c>
       <x:c r="BQ5" s="2" t="str">
-        <x:v>04/20(月)</x:v>
+        <x:v>04/21(火)</x:v>
       </x:c>
       <x:c r="BR5" s="2" t="str">
-        <x:v>04/20(月)</x:v>
+        <x:v>04/21(火)</x:v>
       </x:c>
       <x:c r="BS5" s="2" t="str">
-        <x:v>04/21(火)</x:v>
+        <x:v>04/22(水)</x:v>
       </x:c>
       <x:c r="BT5" s="2" t="str">
-        <x:v>04/21(火)</x:v>
+        <x:v>04/22(水)</x:v>
       </x:c>
       <x:c r="BU5" s="2" t="str">
-        <x:v>04/21(火)</x:v>
+        <x:v>04/22(水)</x:v>
       </x:c>
       <x:c r="BV5" s="2" t="str">
-        <x:v>04/22(水)</x:v>
+        <x:v>04/23(木)</x:v>
       </x:c>
       <x:c r="BW5" s="2" t="str">
-        <x:v>04/22(水)</x:v>
+        <x:v>04/23(木)</x:v>
       </x:c>
       <x:c r="BX5" s="2" t="str">
-        <x:v>04/22(水)</x:v>
+        <x:v>04/23(木)</x:v>
       </x:c>
       <x:c r="BY5" s="2" t="str">
-        <x:v>04/23(木)</x:v>
+        <x:v>04/24(金)</x:v>
       </x:c>
       <x:c r="BZ5" s="2" t="str">
-        <x:v>04/23(木)</x:v>
+        <x:v>04/24(金)</x:v>
       </x:c>
       <x:c r="CA5" s="2" t="str">
-        <x:v>04/23(木)</x:v>
+        <x:v>04/24(金)</x:v>
       </x:c>
       <x:c r="CB5" s="2" t="str">
-        <x:v>04/24(金)</x:v>
+        <x:v>04/25(土)</x:v>
       </x:c>
       <x:c r="CC5" s="2" t="str">
-        <x:v>04/24(金)</x:v>
+        <x:v>04/25(土)</x:v>
       </x:c>
       <x:c r="CD5" s="2" t="str">
-        <x:v>04/24(金)</x:v>
+        <x:v>04/25(土)</x:v>
       </x:c>
       <x:c r="CE5" s="2" t="str">
-        <x:v>04/25(土)</x:v>
+        <x:v>04/26(日)</x:v>
       </x:c>
       <x:c r="CF5" s="2" t="str">
-        <x:v>04/25(土)</x:v>
+        <x:v>04/26(日)</x:v>
       </x:c>
       <x:c r="CG5" s="2" t="str">
-        <x:v>04/25(土)</x:v>
+        <x:v>04/26(日)</x:v>
       </x:c>
       <x:c r="CH5" s="2" t="str">
-        <x:v>04/26(日)</x:v>
+        <x:v>04/27(月)</x:v>
       </x:c>
       <x:c r="CI5" s="2" t="str">
-        <x:v>04/26(日)</x:v>
+        <x:v>04/27(月)</x:v>
       </x:c>
       <x:c r="CJ5" s="2" t="str">
-        <x:v>04/26(日)</x:v>
+        <x:v>04/27(月)</x:v>
       </x:c>
       <x:c r="CK5" s="2" t="str">
-        <x:v>04/27(月)</x:v>
+        <x:v>04/28(火)</x:v>
       </x:c>
       <x:c r="CL5" s="2" t="str">
-        <x:v>04/27(月)</x:v>
+        <x:v>04/28(火)</x:v>
       </x:c>
       <x:c r="CM5" s="2" t="str">
-        <x:v>04/27(月)</x:v>
+        <x:v>04/28(火)</x:v>
       </x:c>
       <x:c r="CN5" s="2" t="str">
-        <x:v>04/28(火)</x:v>
+        <x:v>04/29(水)</x:v>
       </x:c>
       <x:c r="CO5" s="2" t="str">
-        <x:v>04/28(火)</x:v>
+        <x:v>04/29(水)</x:v>
       </x:c>
       <x:c r="CP5" s="2" t="str">
-        <x:v>04/28(火)</x:v>
+        <x:v>04/29(水)</x:v>
       </x:c>
       <x:c r="CQ5" s="2" t="str">
-        <x:v>04/29(水)</x:v>
+        <x:v>04/30(木)</x:v>
       </x:c>
       <x:c r="CR5" s="2" t="str">
-        <x:v>04/29(水)</x:v>
+        <x:v>04/30(木)</x:v>
       </x:c>
       <x:c r="CS5" s="2" t="str">
-        <x:v>04/29(水)</x:v>
+        <x:v>04/30(木)</x:v>
       </x:c>
       <x:c r="CT5" s="2" t="str">
-        <x:v>04/30(木)</x:v>
+        <x:v>05/01(金)</x:v>
       </x:c>
       <x:c r="CU5" s="2" t="str">
-        <x:v>04/30(木)</x:v>
+        <x:v>05/01(金)</x:v>
       </x:c>
       <x:c r="CV5" s="2" t="str">
-        <x:v>04/30(木)</x:v>
+        <x:v>05/01(金)</x:v>
       </x:c>
       <x:c r="CW5" s="2" t="str">
-        <x:v>05/01(金)</x:v>
+        <x:v>05/02(土)</x:v>
       </x:c>
       <x:c r="CX5" s="2" t="str">
-        <x:v>05/01(金)</x:v>
+        <x:v>05/02(土)</x:v>
       </x:c>
       <x:c r="CY5" s="2" t="str">
-        <x:v>05/01(金)</x:v>
+        <x:v>05/02(土)</x:v>
       </x:c>
       <x:c r="CZ5" s="2" t="str">
-        <x:v>05/02(土)</x:v>
+        <x:v>05/03(日)</x:v>
       </x:c>
       <x:c r="DA5" s="2" t="str">
-        <x:v>05/02(土)</x:v>
+        <x:v>05/03(日)</x:v>
       </x:c>
       <x:c r="DB5" s="2" t="str">
-        <x:v>05/02(土)</x:v>
+        <x:v>05/03(日)</x:v>
       </x:c>
       <x:c r="DC5" s="2" t="str">
-        <x:v>05/03(日)</x:v>
+        <x:v>05/04(月)</x:v>
       </x:c>
       <x:c r="DD5" s="2" t="str">
-        <x:v>05/03(日)</x:v>
+        <x:v>05/04(月)</x:v>
       </x:c>
       <x:c r="DE5" s="2" t="str">
-        <x:v>05/03(日)</x:v>
+        <x:v>05/04(月)</x:v>
       </x:c>
       <x:c r="DF5" s="2" t="str">
-        <x:v>05/04(月)</x:v>
+        <x:v>05/05(火)</x:v>
       </x:c>
       <x:c r="DG5" s="2" t="str">
-        <x:v>05/04(月)</x:v>
+        <x:v>05/05(火)</x:v>
       </x:c>
       <x:c r="DH5" s="2" t="str">
-        <x:v>05/04(月)</x:v>
+        <x:v>05/05(火)</x:v>
       </x:c>
       <x:c r="DI5" s="2" t="str">
-        <x:v>05/05(火)</x:v>
+        <x:v>05/06(水)</x:v>
       </x:c>
       <x:c r="DJ5" s="2" t="str">
-        <x:v>05/05(火)</x:v>
+        <x:v>05/06(水)</x:v>
       </x:c>
       <x:c r="DK5" s="2" t="str">
-        <x:v>05/05(火)</x:v>
+        <x:v>05/06(水)</x:v>
       </x:c>
       <x:c r="DL5" s="2" t="str">
-        <x:v>05/06(水)</x:v>
+        <x:v>05/07(木)</x:v>
       </x:c>
       <x:c r="DM5" s="2" t="str">
-        <x:v>05/06(水)</x:v>
+        <x:v>05/07(木)</x:v>
       </x:c>
       <x:c r="DN5" s="2" t="str">
-        <x:v>05/06(水)</x:v>
+        <x:v>05/07(木)</x:v>
       </x:c>
       <x:c r="DO5" s="2" t="str">
-        <x:v>05/07(木)</x:v>
+        <x:v>05/08(金)</x:v>
       </x:c>
       <x:c r="DP5" s="2" t="str">
-        <x:v>05/07(木)</x:v>
+        <x:v>05/08(金)</x:v>
       </x:c>
       <x:c r="DQ5" s="2" t="str">
-        <x:v>05/07(木)</x:v>
+        <x:v>05/08(金)</x:v>
       </x:c>
       <x:c r="DR5" s="2" t="str">
-        <x:v>05/08(金)</x:v>
+        <x:v>05/09(土)</x:v>
       </x:c>
       <x:c r="DS5" s="2" t="str">
-        <x:v>05/08(金)</x:v>
+        <x:v>05/09(土)</x:v>
       </x:c>
       <x:c r="DT5" s="2" t="str">
-        <x:v>05/08(金)</x:v>
+        <x:v>05/09(土)</x:v>
       </x:c>
       <x:c r="DU5" s="2" t="str">
-        <x:v>05/09(土)</x:v>
+        <x:v>05/10(日)</x:v>
       </x:c>
       <x:c r="DV5" s="2" t="str">
-        <x:v>05/09(土)</x:v>
+        <x:v>05/10(日)</x:v>
       </x:c>
       <x:c r="DW5" s="2" t="str">
-        <x:v>05/09(土)</x:v>
+        <x:v>05/10(日)</x:v>
       </x:c>
       <x:c r="DX5" s="2" t="str">
-        <x:v>05/10(日)</x:v>
+        <x:v>05/11(月)</x:v>
       </x:c>
       <x:c r="DY5" s="2" t="str">
-        <x:v>05/10(日)</x:v>
+        <x:v>05/11(月)</x:v>
       </x:c>
       <x:c r="DZ5" s="2" t="str">
-        <x:v>05/10(日)</x:v>
+        <x:v>05/11(月)</x:v>
       </x:c>
       <x:c r="EA5" s="2" t="str">
-        <x:v>05/11(月)</x:v>
+        <x:v>05/12(火)</x:v>
       </x:c>
       <x:c r="EB5" s="2" t="str">
-        <x:v>05/11(月)</x:v>
+        <x:v>05/12(火)</x:v>
       </x:c>
       <x:c r="EC5" s="2" t="str">
-        <x:v>05/11(月)</x:v>
+        <x:v>05/12(火)</x:v>
       </x:c>
       <x:c r="ED5" s="2" t="str">
-        <x:v>05/12(火)</x:v>
+        <x:v>05/13(水)</x:v>
       </x:c>
       <x:c r="EE5" s="2" t="str">
-        <x:v>05/12(火)</x:v>
+        <x:v>05/13(水)</x:v>
       </x:c>
       <x:c r="EF5" s="2" t="str">
-        <x:v>05/12(火)</x:v>
+        <x:v>05/13(水)</x:v>
       </x:c>
       <x:c r="EG5" s="2" t="str">
-        <x:v>05/13(水)</x:v>
+        <x:v>05/14(木)</x:v>
       </x:c>
       <x:c r="EH5" s="2" t="str">
-        <x:v>05/13(水)</x:v>
+        <x:v>05/14(木)</x:v>
       </x:c>
       <x:c r="EI5" s="2" t="str">
-        <x:v>05/13(水)</x:v>
+        <x:v>05/14(木)</x:v>
       </x:c>
       <x:c r="EJ5" s="2" t="str">
-        <x:v>05/14(木)</x:v>
+        <x:v>05/15(金)</x:v>
       </x:c>
       <x:c r="EK5" s="2" t="str">
-        <x:v>05/14(木)</x:v>
+        <x:v>05/15(金)</x:v>
       </x:c>
       <x:c r="EL5" s="2" t="str">
-        <x:v>05/14(木)</x:v>
+        <x:v>05/15(金)</x:v>
       </x:c>
       <x:c r="EM5" s="2" t="str">
-        <x:v>05/15(金)</x:v>
+        <x:v>05/16(土)</x:v>
       </x:c>
       <x:c r="EN5" s="2" t="str">
-        <x:v>05/15(金)</x:v>
+        <x:v>05/16(土)</x:v>
       </x:c>
       <x:c r="EO5" s="2" t="str">
-        <x:v>05/15(金)</x:v>
+        <x:v>05/16(土)</x:v>
       </x:c>
       <x:c r="EP5" s="2" t="str">
-        <x:v>05/16(土)</x:v>
+        <x:v>05/17(日)</x:v>
       </x:c>
       <x:c r="EQ5" s="2" t="str">
-        <x:v>05/16(土)</x:v>
+        <x:v>05/17(日)</x:v>
       </x:c>
       <x:c r="ER5" s="2" t="str">
-        <x:v>05/16(土)</x:v>
+        <x:v>05/17(日)</x:v>
       </x:c>
       <x:c r="ES5" s="2" t="str">
-        <x:v>05/17(日)</x:v>
+        <x:v>05/18(月)</x:v>
       </x:c>
       <x:c r="ET5" s="2" t="str">
-        <x:v>05/17(日)</x:v>
+        <x:v>05/18(月)</x:v>
       </x:c>
       <x:c r="EU5" s="2" t="str">
-        <x:v>05/17(日)</x:v>
+        <x:v>05/18(月)</x:v>
       </x:c>
       <x:c r="EV5" s="2" t="str">
-        <x:v>05/18(月)</x:v>
+        <x:v>05/19(火)</x:v>
       </x:c>
       <x:c r="EW5" s="2" t="str">
-        <x:v>05/18(月)</x:v>
+        <x:v>05/19(火)</x:v>
       </x:c>
       <x:c r="EX5" s="2" t="str">
-        <x:v>05/18(月)</x:v>
+        <x:v>05/19(火)</x:v>
       </x:c>
       <x:c r="EY5" s="2" t="str">
-        <x:v>05/19(火)</x:v>
+        <x:v>05/20(水)</x:v>
       </x:c>
       <x:c r="EZ5" s="2" t="str">
-        <x:v>05/19(火)</x:v>
+        <x:v>05/20(水)</x:v>
       </x:c>
       <x:c r="FA5" s="2" t="str">
-        <x:v>05/19(火)</x:v>
+        <x:v>05/20(水)</x:v>
       </x:c>
       <x:c r="FB5" s="2" t="str">
-        <x:v>05/20(水)</x:v>
+        <x:v>05/21(木)</x:v>
       </x:c>
       <x:c r="FC5" s="2" t="str">
-        <x:v>05/20(水)</x:v>
+        <x:v>05/21(木)</x:v>
       </x:c>
       <x:c r="FD5" s="2" t="str">
-        <x:v>05/20(水)</x:v>
+        <x:v>05/21(木)</x:v>
       </x:c>
       <x:c r="FE5" s="2" t="str">
-        <x:v>05/21(木)</x:v>
+        <x:v>05/22(金)</x:v>
       </x:c>
       <x:c r="FF5" s="2" t="str">
-        <x:v>05/21(木)</x:v>
+        <x:v>05/22(金)</x:v>
       </x:c>
       <x:c r="FG5" s="2" t="str">
-        <x:v>05/21(木)</x:v>
+        <x:v>05/22(金)</x:v>
       </x:c>
       <x:c r="FH5" s="2" t="str">
-        <x:v>05/22(金)</x:v>
+        <x:v>05/23(土)</x:v>
       </x:c>
       <x:c r="FI5" s="2" t="str">
-        <x:v>05/22(金)</x:v>
+        <x:v>05/23(土)</x:v>
       </x:c>
       <x:c r="FJ5" s="2" t="str">
-        <x:v>05/22(金)</x:v>
+        <x:v>05/23(土)</x:v>
       </x:c>
       <x:c r="FK5" s="2" t="str">
-        <x:v>05/23(土)</x:v>
+        <x:v>05/24(日)</x:v>
       </x:c>
       <x:c r="FL5" s="2" t="str">
-        <x:v>05/23(土)</x:v>
+        <x:v>05/24(日)</x:v>
       </x:c>
       <x:c r="FM5" s="2" t="str">
-        <x:v>05/23(土)</x:v>
+        <x:v>05/24(日)</x:v>
       </x:c>
       <x:c r="FN5" s="2" t="str">
-        <x:v>05/24(日)</x:v>
+        <x:v>05/25(月)</x:v>
       </x:c>
       <x:c r="FO5" s="2" t="str">
-        <x:v>05/24(日)</x:v>
+        <x:v>05/25(月)</x:v>
       </x:c>
       <x:c r="FP5" s="2" t="str">
-        <x:v>05/24(日)</x:v>
+        <x:v>05/25(月)</x:v>
       </x:c>
       <x:c r="FQ5" s="2" t="str">
-        <x:v>05/25(月)</x:v>
+        <x:v>05/26(火)</x:v>
       </x:c>
       <x:c r="FR5" s="2" t="str">
-        <x:v>05/25(月)</x:v>
+        <x:v>05/26(火)</x:v>
       </x:c>
       <x:c r="FS5" s="2" t="str">
-        <x:v>05/25(月)</x:v>
+        <x:v>05/26(火)</x:v>
       </x:c>
       <x:c r="FT5" s="2" t="str">
-        <x:v>05/26(火)</x:v>
+        <x:v>05/27(水)</x:v>
       </x:c>
       <x:c r="FU5" s="2" t="str">
-        <x:v>05/26(火)</x:v>
+        <x:v>05/27(水)</x:v>
       </x:c>
       <x:c r="FV5" s="2" t="str">
-        <x:v>05/26(火)</x:v>
+        <x:v>05/27(水)</x:v>
       </x:c>
       <x:c r="FW5" s="2" t="str">
-        <x:v>05/27(水)</x:v>
+        <x:v>05/28(木)</x:v>
       </x:c>
       <x:c r="FX5" s="2" t="str">
-        <x:v>05/27(水)</x:v>
+        <x:v>05/28(木)</x:v>
       </x:c>
       <x:c r="FY5" s="2" t="str">
-        <x:v>05/27(水)</x:v>
+        <x:v>05/28(木)</x:v>
       </x:c>
       <x:c r="FZ5" s="2" t="str">
-        <x:v>05/28(木)</x:v>
+        <x:v>05/29(金)</x:v>
       </x:c>
       <x:c r="GA5" s="2" t="str">
-        <x:v>05/28(木)</x:v>
+        <x:v>05/29(金)</x:v>
       </x:c>
       <x:c r="GB5" s="2" t="str">
-        <x:v>05/28(木)</x:v>
+        <x:v>05/29(金)</x:v>
       </x:c>
       <x:c r="GC5" s="2" t="str">
-        <x:v>05/29(金)</x:v>
+        <x:v>05/30(土)</x:v>
       </x:c>
       <x:c r="GD5" s="2" t="str">
-        <x:v>05/29(金)</x:v>
+        <x:v>05/30(土)</x:v>
       </x:c>
       <x:c r="GE5" s="2" t="str">
-        <x:v>05/29(金)</x:v>
+        <x:v>05/30(土)</x:v>
       </x:c>
       <x:c r="GF5" s="2" t="str">
-        <x:v>05/30(土)</x:v>
+        <x:v>05/31(日)</x:v>
       </x:c>
       <x:c r="GG5" s="2" t="str">
-        <x:v>05/30(土)</x:v>
+        <x:v>05/31(日)</x:v>
       </x:c>
       <x:c r="GH5" s="2" t="str">
-        <x:v>05/30(土)</x:v>
+        <x:v>05/31(日)</x:v>
       </x:c>
       <x:c r="GI5" s="2" t="str">
-        <x:v>05/31(日)</x:v>
+        <x:v>06/01(月)</x:v>
       </x:c>
       <x:c r="GJ5" s="2" t="str">
-        <x:v>05/31(日)</x:v>
+        <x:v>06/01(月)</x:v>
       </x:c>
       <x:c r="GK5" s="2" t="str">
-        <x:v>05/31(日)</x:v>
+        <x:v>06/01(月)</x:v>
       </x:c>
       <x:c r="GL5" s="2" t="str">
-        <x:v>06/01(月)</x:v>
+        <x:v>06/02(火)</x:v>
       </x:c>
       <x:c r="GM5" s="2" t="str">
-        <x:v>06/01(月)</x:v>
+        <x:v>06/02(火)</x:v>
       </x:c>
       <x:c r="GN5" s="2" t="str">
-        <x:v>06/01(月)</x:v>
+        <x:v>06/02(火)</x:v>
       </x:c>
       <x:c r="GO5" s="2" t="str">
-        <x:v>06/02(火)</x:v>
+        <x:v>06/03(水)</x:v>
       </x:c>
       <x:c r="GP5" s="2" t="str">
-        <x:v>06/02(火)</x:v>
+        <x:v>06/03(水)</x:v>
       </x:c>
       <x:c r="GQ5" s="2" t="str">
-        <x:v>06/02(火)</x:v>
+        <x:v>06/03(水)</x:v>
       </x:c>
       <x:c r="GR5" s="2" t="str">
-        <x:v>06/03(水)</x:v>
+        <x:v>06/04(木)</x:v>
       </x:c>
       <x:c r="GS5" s="2" t="str">
-        <x:v>06/03(水)</x:v>
+        <x:v>06/04(木)</x:v>
       </x:c>
       <x:c r="GT5" s="2" t="str">
-        <x:v>06/03(水)</x:v>
+        <x:v>06/04(木)</x:v>
       </x:c>
       <x:c r="GU5" s="2" t="str">
-        <x:v>06/04(木)</x:v>
+        <x:v>06/05(金)</x:v>
       </x:c>
       <x:c r="GV5" s="2" t="str">
-        <x:v>06/04(木)</x:v>
+        <x:v>06/05(金)</x:v>
       </x:c>
       <x:c r="GW5" s="2" t="str">
-        <x:v>06/04(木)</x:v>
+        <x:v>06/05(金)</x:v>
       </x:c>
       <x:c r="GX5" s="2" t="str">
-        <x:v>06/05(金)</x:v>
+        <x:v>06/06(土)</x:v>
       </x:c>
       <x:c r="GY5" s="2" t="str">
-        <x:v>06/05(金)</x:v>
+        <x:v>06/06(土)</x:v>
       </x:c>
       <x:c r="GZ5" s="2" t="str">
-        <x:v>06/05(金)</x:v>
+        <x:v>06/06(土)</x:v>
       </x:c>
       <x:c r="HA5" s="2" t="str">
-        <x:v>06/06(土)</x:v>
+        <x:v>06/07(日)</x:v>
       </x:c>
       <x:c r="HB5" s="2" t="str">
-        <x:v>06/06(土)</x:v>
+        <x:v>06/07(日)</x:v>
       </x:c>
       <x:c r="HC5" s="2" t="str">
-        <x:v>06/06(土)</x:v>
+        <x:v>06/07(日)</x:v>
       </x:c>
       <x:c r="HD5" s="2" t="str">
-        <x:v>06/07(日)</x:v>
+        <x:v>06/08(月)</x:v>
       </x:c>
       <x:c r="HE5" s="2" t="str">
-        <x:v>06/07(日)</x:v>
+        <x:v>06/08(月)</x:v>
       </x:c>
       <x:c r="HF5" s="2" t="str">
-        <x:v>06/07(日)</x:v>
+        <x:v>06/08(月)</x:v>
       </x:c>
       <x:c r="HG5" s="2" t="str">
-        <x:v>06/08(月)</x:v>
+        <x:v>06/09(火)</x:v>
       </x:c>
       <x:c r="HH5" s="2" t="str">
-        <x:v>06/08(月)</x:v>
+        <x:v>06/09(火)</x:v>
       </x:c>
       <x:c r="HI5" s="2" t="str">
-        <x:v>06/08(月)</x:v>
+        <x:v>06/09(火)</x:v>
       </x:c>
       <x:c r="HJ5" s="2" t="str">
-        <x:v>06/09(火)</x:v>
+        <x:v>06/10(水)</x:v>
       </x:c>
       <x:c r="HK5" s="2" t="str">
-        <x:v>06/09(火)</x:v>
+        <x:v>06/10(水)</x:v>
       </x:c>
       <x:c r="HL5" s="2" t="str">
-        <x:v>06/09(火)</x:v>
+        <x:v>06/10(水)</x:v>
       </x:c>
       <x:c r="HM5" s="2" t="str">
-        <x:v>06/10(水)</x:v>
+        <x:v>06/11(木)</x:v>
       </x:c>
       <x:c r="HN5" s="2" t="str">
-        <x:v>06/10(水)</x:v>
+        <x:v>06/11(木)</x:v>
       </x:c>
       <x:c r="HO5" s="2" t="str">
-        <x:v>06/10(水)</x:v>
+        <x:v>06/11(木)</x:v>
       </x:c>
       <x:c r="HP5" s="2" t="str">
-        <x:v>06/11(木)</x:v>
+        <x:v>06/12(金)</x:v>
       </x:c>
       <x:c r="HQ5" s="2" t="str">
-        <x:v>06/11(木)</x:v>
+        <x:v>06/12(金)</x:v>
       </x:c>
       <x:c r="HR5" s="2" t="str">
-        <x:v>06/11(木)</x:v>
+        <x:v>06/12(金)</x:v>
       </x:c>
       <x:c r="HS5" s="2" t="str">
-        <x:v>06/12(金)</x:v>
+        <x:v>06/13(土)</x:v>
       </x:c>
       <x:c r="HT5" s="2" t="str">
-        <x:v>06/12(金)</x:v>
+        <x:v>06/13(土)</x:v>
       </x:c>
       <x:c r="HU5" s="2" t="str">
-        <x:v>06/12(金)</x:v>
+        <x:v>06/13(土)</x:v>
       </x:c>
       <x:c r="HV5" s="2" t="str">
-        <x:v>06/13(土)</x:v>
+        <x:v>06/14(日)</x:v>
       </x:c>
       <x:c r="HW5" s="2" t="str">
-        <x:v>06/13(土)</x:v>
+        <x:v>06/14(日)</x:v>
       </x:c>
       <x:c r="HX5" s="2" t="str">
-        <x:v>06/13(土)</x:v>
+        <x:v>06/14(日)</x:v>
       </x:c>
       <x:c r="HY5" s="2" t="str">
-        <x:v>06/14(日)</x:v>
+        <x:v>06/15(月)</x:v>
       </x:c>
       <x:c r="HZ5" s="2" t="str">
-        <x:v>06/14(日)</x:v>
+        <x:v>06/15(月)</x:v>
       </x:c>
       <x:c r="IA5" s="2" t="str">
-        <x:v>06/14(日)</x:v>
+        <x:v>06/15(月)</x:v>
       </x:c>
       <x:c r="IB5" s="2" t="str">
-        <x:v>06/15(月)</x:v>
+        <x:v>06/16(火)</x:v>
       </x:c>
       <x:c r="IC5" s="2" t="str">
-        <x:v>06/15(月)</x:v>
+        <x:v>06/16(火)</x:v>
       </x:c>
       <x:c r="ID5" s="2" t="str">
-        <x:v>06/15(月)</x:v>
+        <x:v>06/16(火)</x:v>
       </x:c>
       <x:c r="IE5" s="2" t="str">
-        <x:v>06/16(火)</x:v>
+        <x:v>06/17(水)</x:v>
       </x:c>
       <x:c r="IF5" s="2" t="str">
-        <x:v>06/16(火)</x:v>
+        <x:v>06/17(水)</x:v>
       </x:c>
       <x:c r="IG5" s="2" t="str">
-        <x:v>06/16(火)</x:v>
+        <x:v>06/17(水)</x:v>
       </x:c>
       <x:c r="IH5" s="2" t="str">
-        <x:v>06/17(水)</x:v>
+        <x:v>06/18(木)</x:v>
       </x:c>
       <x:c r="II5" s="2" t="str">
-        <x:v>06/17(水)</x:v>
+        <x:v>06/18(木)</x:v>
       </x:c>
       <x:c r="IJ5" s="2" t="str">
-        <x:v>06/17(水)</x:v>
+        <x:v>06/18(木)</x:v>
       </x:c>
       <x:c r="IK5" s="2" t="str">
-        <x:v>06/18(木)</x:v>
+        <x:v>06/19(金)</x:v>
       </x:c>
       <x:c r="IL5" s="2" t="str">
-        <x:v>06/18(木)</x:v>
+        <x:v>06/19(金)</x:v>
       </x:c>
       <x:c r="IM5" s="2" t="str">
-        <x:v>06/18(木)</x:v>
+        <x:v>06/19(金)</x:v>
       </x:c>
       <x:c r="IN5" s="2" t="str">
-        <x:v>06/19(金)</x:v>
+        <x:v>06/20(土)</x:v>
       </x:c>
       <x:c r="IO5" s="2" t="str">
-        <x:v>06/19(金)</x:v>
+        <x:v>06/20(土)</x:v>
       </x:c>
       <x:c r="IP5" s="2" t="str">
-        <x:v>06/19(金)</x:v>
+        <x:v>06/20(土)</x:v>
       </x:c>
       <x:c r="IQ5" s="2" t="str">
-        <x:v>06/20(土)</x:v>
+        <x:v>06/21(日)</x:v>
       </x:c>
       <x:c r="IR5" s="2" t="str">
-        <x:v>06/20(土)</x:v>
+        <x:v>06/21(日)</x:v>
       </x:c>
       <x:c r="IS5" s="2" t="str">
-        <x:v>06/20(土)</x:v>
+        <x:v>06/21(日)</x:v>
       </x:c>
       <x:c r="IT5" s="2" t="str">
-        <x:v>06/21(日)</x:v>
+        <x:v>06/22(月)</x:v>
       </x:c>
       <x:c r="IU5" s="2" t="str">
-        <x:v>06/21(日)</x:v>
+        <x:v>06/22(月)</x:v>
       </x:c>
       <x:c r="IV5" s="2" t="str">
-        <x:v>06/21(日)</x:v>
+        <x:v>06/22(月)</x:v>
       </x:c>
       <x:c r="IW5" s="2" t="str">
-        <x:v>06/22(月)</x:v>
+        <x:v>06/23(火)</x:v>
       </x:c>
       <x:c r="IX5" s="2" t="str">
-        <x:v>06/22(月)</x:v>
+        <x:v>06/23(火)</x:v>
       </x:c>
       <x:c r="IY5" s="2" t="str">
-        <x:v>06/22(月)</x:v>
+        <x:v>06/23(火)</x:v>
       </x:c>
       <x:c r="IZ5" s="2" t="str">
-        <x:v>06/23(火)</x:v>
+        <x:v>06/24(水)</x:v>
       </x:c>
       <x:c r="JA5" s="2" t="str">
-        <x:v>06/23(火)</x:v>
+        <x:v>06/24(水)</x:v>
       </x:c>
       <x:c r="JB5" s="2" t="str">
-        <x:v>06/23(火)</x:v>
+        <x:v>06/24(水)</x:v>
       </x:c>
       <x:c r="JC5" s="2" t="str">
-        <x:v>06/24(水)</x:v>
+        <x:v>06/25(木)</x:v>
       </x:c>
       <x:c r="JD5" s="2" t="str">
-        <x:v>06/24(水)</x:v>
+        <x:v>06/25(木)</x:v>
       </x:c>
       <x:c r="JE5" s="2" t="str">
-        <x:v>06/24(水)</x:v>
+        <x:v>06/25(木)</x:v>
       </x:c>
       <x:c r="JF5" s="2" t="str">
-        <x:v>06/25(木)</x:v>
+        <x:v>06/26(金)</x:v>
       </x:c>
       <x:c r="JG5" s="2" t="str">
-        <x:v>06/25(木)</x:v>
+        <x:v>06/26(金)</x:v>
       </x:c>
       <x:c r="JH5" s="2" t="str">
-        <x:v>06/25(木)</x:v>
+        <x:v>06/26(金)</x:v>
       </x:c>
       <x:c r="JI5" s="2" t="str">
-        <x:v>06/26(金)</x:v>
+        <x:v>06/27(土)</x:v>
       </x:c>
       <x:c r="JJ5" s="2" t="str">
-        <x:v>06/26(金)</x:v>
+        <x:v>06/27(土)</x:v>
       </x:c>
       <x:c r="JK5" s="2" t="str">
-        <x:v>06/26(金)</x:v>
+        <x:v>06/27(土)</x:v>
       </x:c>
       <x:c r="JL5" s="2" t="str">
-        <x:v>06/27(土)</x:v>
+        <x:v>06/28(日)</x:v>
       </x:c>
       <x:c r="JM5" s="2" t="str">
-        <x:v>06/27(土)</x:v>
+        <x:v>06/28(日)</x:v>
       </x:c>
       <x:c r="JN5" s="2" t="str">
-        <x:v>06/27(土)</x:v>
+        <x:v>06/28(日)</x:v>
       </x:c>
       <x:c r="JO5" s="2" t="str">
-        <x:v>06/28(日)</x:v>
+        <x:v>06/29(月)</x:v>
       </x:c>
       <x:c r="JP5" s="2" t="str">
-        <x:v>06/28(日)</x:v>
+        <x:v>06/29(月)</x:v>
       </x:c>
       <x:c r="JQ5" s="2" t="str">
-        <x:v>06/28(日)</x:v>
+        <x:v>06/29(月)</x:v>
       </x:c>
       <x:c r="JR5" s="2" t="str">
-        <x:v>06/29(月)</x:v>
+        <x:v>06/30(火)</x:v>
       </x:c>
       <x:c r="JS5" s="2" t="str">
-        <x:v>06/29(月)</x:v>
+        <x:v>06/30(火)</x:v>
       </x:c>
       <x:c r="JT5" s="2" t="str">
-        <x:v>06/29(月)</x:v>
+        <x:v>06/30(火)</x:v>
       </x:c>
       <x:c r="JU5" s="2" t="str">
-        <x:v>06/30(火)</x:v>
+        <x:v>07/01(水)</x:v>
       </x:c>
       <x:c r="JV5" s="2" t="str">
-        <x:v>06/30(火)</x:v>
+        <x:v>07/01(水)</x:v>
       </x:c>
       <x:c r="JW5" s="2" t="str">
-        <x:v>06/30(火)</x:v>
+        <x:v>07/01(水)</x:v>
       </x:c>
       <x:c r="JX5" s="2" t="str">
-        <x:v>07/01(水)</x:v>
+        <x:v>07/02(木)</x:v>
       </x:c>
       <x:c r="JY5" s="2" t="str">
-        <x:v>07/01(水)</x:v>
+        <x:v>07/02(木)</x:v>
       </x:c>
       <x:c r="JZ5" s="2" t="str">
-        <x:v>07/01(水)</x:v>
+        <x:v>07/02(木)</x:v>
       </x:c>
       <x:c r="KA5" s="2" t="str">
-        <x:v>07/02(木)</x:v>
+        <x:v>07/03(金)</x:v>
       </x:c>
       <x:c r="KB5" s="2" t="str">
-        <x:v>07/02(木)</x:v>
+        <x:v>07/03(金)</x:v>
       </x:c>
       <x:c r="KC5" s="2" t="str">
-        <x:v>07/02(木)</x:v>
+        <x:v>07/03(金)</x:v>
       </x:c>
       <x:c r="KD5" s="2" t="str">
-        <x:v>07/03(金)</x:v>
+        <x:v>07/04(土)</x:v>
       </x:c>
       <x:c r="KE5" s="2" t="str">
-        <x:v>07/03(金)</x:v>
+        <x:v>07/04(土)</x:v>
       </x:c>
       <x:c r="KF5" s="2" t="str">
-        <x:v>07/03(金)</x:v>
+        <x:v>07/04(土)</x:v>
       </x:c>
       <x:c r="KG5" s="2" t="str">
-        <x:v>07/04(土)</x:v>
+        <x:v>07/05(日)</x:v>
       </x:c>
       <x:c r="KH5" s="2" t="str">
-        <x:v>07/04(土)</x:v>
+        <x:v>07/05(日)</x:v>
       </x:c>
       <x:c r="KI5" s="2" t="str">
-        <x:v>07/04(土)</x:v>
+        <x:v>07/05(日)</x:v>
       </x:c>
       <x:c r="KJ5" s="2" t="str">
-        <x:v>07/05(日)</x:v>
+        <x:v>07/06(月)</x:v>
       </x:c>
       <x:c r="KK5" s="2" t="str">
-        <x:v>07/05(日)</x:v>
+        <x:v>07/06(月)</x:v>
       </x:c>
       <x:c r="KL5" s="2" t="str">
-        <x:v>07/05(日)</x:v>
+        <x:v>07/06(月)</x:v>
       </x:c>
       <x:c r="KM5" s="2" t="str">
-        <x:v>07/06(月)</x:v>
+        <x:v>07/07(火)</x:v>
       </x:c>
       <x:c r="KN5" s="2" t="str">
-        <x:v>07/06(月)</x:v>
+        <x:v>07/07(火)</x:v>
       </x:c>
       <x:c r="KO5" s="2" t="str">
-        <x:v>07/06(月)</x:v>
+        <x:v>07/07(火)</x:v>
       </x:c>
       <x:c r="KP5" s="2" t="str">
-        <x:v>07/07(火)</x:v>
+        <x:v>07/08(水)</x:v>
       </x:c>
       <x:c r="KQ5" s="2" t="str">
-        <x:v>07/07(火)</x:v>
+        <x:v>07/08(水)</x:v>
       </x:c>
       <x:c r="KR5" s="2" t="str">
-        <x:v>07/07(火)</x:v>
+        <x:v>07/08(水)</x:v>
       </x:c>
       <x:c r="KS5" s="2" t="str">
-        <x:v>07/08(水)</x:v>
+        <x:v>07/09(木)</x:v>
       </x:c>
       <x:c r="KT5" s="2" t="str">
-        <x:v>07/08(水)</x:v>
+        <x:v>07/09(木)</x:v>
       </x:c>
       <x:c r="KU5" s="2" t="str">
-        <x:v>07/08(水)</x:v>
+        <x:v>07/09(木)</x:v>
       </x:c>
       <x:c r="KV5" s="2" t="str">
-        <x:v>07/09(木)</x:v>
+        <x:v>07/10(金)</x:v>
       </x:c>
       <x:c r="KW5" s="2" t="str">
-        <x:v>07/09(木)</x:v>
+        <x:v>07/10(金)</x:v>
       </x:c>
       <x:c r="KX5" s="2" t="str">
-        <x:v>07/09(木)</x:v>
+        <x:v>07/10(金)</x:v>
       </x:c>
       <x:c r="KY5" s="2" t="str">
-        <x:v>07/10(金)</x:v>
+        <x:v>07/11(土)</x:v>
       </x:c>
       <x:c r="KZ5" s="2" t="str">
-        <x:v>07/10(金)</x:v>
+        <x:v>07/11(土)</x:v>
       </x:c>
       <x:c r="LA5" s="2" t="str">
-        <x:v>07/10(金)</x:v>
+        <x:v>07/11(土)</x:v>
       </x:c>
       <x:c r="LB5" s="2" t="str">
-        <x:v>07/11(土)</x:v>
+        <x:v>07/12(日)</x:v>
       </x:c>
       <x:c r="LC5" s="2" t="str">
-        <x:v>07/11(土)</x:v>
+        <x:v>07/12(日)</x:v>
       </x:c>
       <x:c r="LD5" s="2" t="str">
-        <x:v>07/11(土)</x:v>
+        <x:v>07/12(日)</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2748,22 +2748,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ED7" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4000.0000</x:v>
       </x:c>
       <x:c r="EE7" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EF7" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4.1400</x:v>
       </x:c>
       <x:c r="EG7" s="6" t="n">
-        <x:v>4000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EH7" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EI7" s="8" t="n">
-        <x:v>4.1400</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ7" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -3689,31 +3689,31 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EA8" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3800.0000</x:v>
       </x:c>
       <x:c r="EB8" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EC8" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3.9300</x:v>
       </x:c>
       <x:c r="ED8" s="6" t="n">
-        <x:v>3800.0000</x:v>
+        <x:v>2200.0000</x:v>
       </x:c>
       <x:c r="EE8" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EF8" s="8" t="n">
-        <x:v>3.9300</x:v>
+        <x:v>2.2700</x:v>
       </x:c>
       <x:c r="EG8" s="6" t="n">
-        <x:v>2200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EH8" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EI8" s="8" t="n">
-        <x:v>2.2700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ8" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -4657,31 +4657,31 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG9" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>7800.0000</x:v>
       </x:c>
       <x:c r="EH9" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EI9" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>8.0600</x:v>
       </x:c>
       <x:c r="EJ9" s="6" t="n">
-        <x:v>7800.0000</x:v>
+        <x:v>1200.0000</x:v>
       </x:c>
       <x:c r="EK9" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EL9" s="8" t="n">
-        <x:v>8.0600</x:v>
+        <x:v>1.2400</x:v>
       </x:c>
       <x:c r="EM9" s="6" t="n">
-        <x:v>1200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN9" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EO9" s="8" t="n">
-        <x:v>1.2400</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP9" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -5616,22 +5616,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ10" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6600.0000</x:v>
       </x:c>
       <x:c r="EK10" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EL10" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6.8200</x:v>
       </x:c>
       <x:c r="EM10" s="6" t="n">
-        <x:v>6600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN10" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EO10" s="8" t="n">
-        <x:v>6.8200</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP10" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -5643,22 +5643,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES10" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2400.0000</x:v>
       </x:c>
       <x:c r="ET10" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EU10" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.4800</x:v>
       </x:c>
       <x:c r="EV10" s="6" t="n">
-        <x:v>2400.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EW10" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EX10" s="8" t="n">
-        <x:v>2.4800</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY10" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -6593,31 +6593,31 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES11" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5000.0000</x:v>
       </x:c>
       <x:c r="ET11" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EU11" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5.1700</x:v>
       </x:c>
       <x:c r="EV11" s="6" t="n">
-        <x:v>5000.0000</x:v>
+        <x:v>1000.0000</x:v>
       </x:c>
       <x:c r="EW11" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EX11" s="8" t="n">
-        <x:v>5.1700</x:v>
+        <x:v>1.0300</x:v>
       </x:c>
       <x:c r="EY11" s="6" t="n">
-        <x:v>1000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EZ11" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FA11" s="8" t="n">
-        <x:v>1.0300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB11" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -7552,22 +7552,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV12" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5100.0000</x:v>
       </x:c>
       <x:c r="EW12" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EX12" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5.2700</x:v>
       </x:c>
       <x:c r="EY12" s="6" t="n">
-        <x:v>5100.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EZ12" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FA12" s="8" t="n">
-        <x:v>5.2700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB12" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -8502,40 +8502,40 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV13" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1200.0000</x:v>
       </x:c>
       <x:c r="EW13" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EX13" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.2400</x:v>
       </x:c>
       <x:c r="EY13" s="6" t="n">
-        <x:v>1200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EZ13" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FA13" s="8" t="n">
-        <x:v>1.2400</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB13" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6800.0000</x:v>
       </x:c>
       <x:c r="FC13" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FD13" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>7.0300</x:v>
       </x:c>
       <x:c r="FE13" s="6" t="n">
-        <x:v>6800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FF13" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FG13" s="8" t="n">
-        <x:v>7.0300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FH13" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -9470,31 +9470,31 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB14" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1000.0000</x:v>
       </x:c>
       <x:c r="FC14" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FD14" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.0300</x:v>
       </x:c>
       <x:c r="FE14" s="6" t="n">
-        <x:v>1000.0000</x:v>
+        <x:v>7000.0000</x:v>
       </x:c>
       <x:c r="FF14" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FG14" s="8" t="n">
-        <x:v>1.0300</x:v>
+        <x:v>7.2400</x:v>
       </x:c>
       <x:c r="FH14" s="6" t="n">
-        <x:v>7000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FI14" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FJ14" s="8" t="n">
-        <x:v>7.2400</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FK14" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -10465,22 +10465,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FQ15" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5000.0000</x:v>
       </x:c>
       <x:c r="FR15" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FS15" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5.1700</x:v>
       </x:c>
       <x:c r="FT15" s="6" t="n">
-        <x:v>5000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FU15" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FV15" s="8" t="n">
-        <x:v>5.1700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FW15" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -11316,22 +11316,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ16" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2100.0000</x:v>
       </x:c>
       <x:c r="EK16" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EL16" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.9400</x:v>
       </x:c>
       <x:c r="EM16" s="6" t="n">
-        <x:v>2100.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN16" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EO16" s="8" t="n">
-        <x:v>1.9400</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP16" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -11343,22 +11343,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES16" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6900.0000</x:v>
       </x:c>
       <x:c r="ET16" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EU16" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6.3700</x:v>
       </x:c>
       <x:c r="EV16" s="6" t="n">
-        <x:v>6900.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EW16" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EX16" s="8" t="n">
-        <x:v>6.3700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY16" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -12311,22 +12311,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY17" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>9000.0000</x:v>
       </x:c>
       <x:c r="EZ17" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="FA17" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>8.3100</x:v>
       </x:c>
       <x:c r="FB17" s="6" t="n">
-        <x:v>9000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FC17" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="FD17" s="8" t="n">
-        <x:v>8.3100</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FE17" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -13306,22 +13306,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FN18" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>9000.0000</x:v>
       </x:c>
       <x:c r="FO18" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="FP18" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>8.3100</x:v>
       </x:c>
       <x:c r="FQ18" s="6" t="n">
-        <x:v>9000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FR18" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="FS18" s="8" t="n">
-        <x:v>8.3100</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FT18" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -14274,22 +14274,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FT19" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>9000.0000</x:v>
       </x:c>
       <x:c r="FU19" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="FV19" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>8.3100</x:v>
       </x:c>
       <x:c r="FW19" s="6" t="n">
-        <x:v>9000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FX19" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="FY19" s="8" t="n">
-        <x:v>8.3100</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FZ19" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -15089,22 +15089,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EA20" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>500.0000</x:v>
       </x:c>
       <x:c r="EB20" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EC20" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.4600</x:v>
       </x:c>
       <x:c r="ED20" s="6" t="n">
-        <x:v>500.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EE20" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EF20" s="8" t="n">
-        <x:v>0.4600</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG20" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -16039,22 +16039,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EA21" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>500.0000</x:v>
       </x:c>
       <x:c r="EB21" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EC21" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.4600</x:v>
       </x:c>
       <x:c r="ED21" s="6" t="n">
-        <x:v>500.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EE21" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EF21" s="8" t="n">
-        <x:v>0.4600</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG21" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -16980,31 +16980,31 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DX22" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4500.0000</x:v>
       </x:c>
       <x:c r="DY22" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="DZ22" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4.1500</x:v>
       </x:c>
       <x:c r="EA22" s="6" t="n">
-        <x:v>4500.0000</x:v>
+        <x:v>1500.0000</x:v>
       </x:c>
       <x:c r="EB22" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EC22" s="8" t="n">
-        <x:v>4.1500</x:v>
+        <x:v>1.3800</x:v>
       </x:c>
       <x:c r="ED22" s="6" t="n">
-        <x:v>1500.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EE22" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EF22" s="8" t="n">
-        <x:v>1.3800</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG22" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -17966,22 +17966,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ23" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4000.0000</x:v>
       </x:c>
       <x:c r="EK23" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EL23" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3.6900</x:v>
       </x:c>
       <x:c r="EM23" s="6" t="n">
-        <x:v>4000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN23" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EO23" s="8" t="n">
-        <x:v>3.6900</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP23" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -18916,22 +18916,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ24" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2000.0000</x:v>
       </x:c>
       <x:c r="EK24" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EL24" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.2200</x:v>
       </x:c>
       <x:c r="EM24" s="6" t="n">
-        <x:v>2000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN24" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EO24" s="8" t="n">
-        <x:v>2.2200</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP24" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -19839,22 +19839,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EA25" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>600.0000</x:v>
       </x:c>
       <x:c r="EB25" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EC25" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.5500</x:v>
       </x:c>
       <x:c r="ED25" s="6" t="n">
-        <x:v>600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EE25" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EF25" s="8" t="n">
-        <x:v>0.5500</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG25" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -19866,22 +19866,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ25" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3600.0000</x:v>
       </x:c>
       <x:c r="EK25" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EL25" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3.3200</x:v>
       </x:c>
       <x:c r="EM25" s="6" t="n">
-        <x:v>3600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN25" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EO25" s="8" t="n">
-        <x:v>3.3200</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP25" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -20807,22 +20807,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG26" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>10.0000</x:v>
       </x:c>
       <x:c r="EH26" s="8" t="n">
         <x:v>10.1000</x:v>
       </x:c>
       <x:c r="EI26" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.0200</x:v>
       </x:c>
       <x:c r="EJ26" s="6" t="n">
-        <x:v>10.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EK26" s="8" t="n">
         <x:v>10.1000</x:v>
       </x:c>
       <x:c r="EL26" s="8" t="n">
-        <x:v>0.0200</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM26" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -21757,22 +21757,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG27" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>193.0000</x:v>
       </x:c>
       <x:c r="EH27" s="8" t="n">
         <x:v>14.9300</x:v>
       </x:c>
       <x:c r="EI27" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.2200</x:v>
       </x:c>
       <x:c r="EJ27" s="6" t="n">
-        <x:v>193.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EK27" s="8" t="n">
         <x:v>14.9300</x:v>
       </x:c>
       <x:c r="EL27" s="8" t="n">
-        <x:v>0.2200</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM27" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -22698,22 +22698,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ED28" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>800.0000</x:v>
       </x:c>
       <x:c r="EE28" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="EF28" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.3200</x:v>
       </x:c>
       <x:c r="EG28" s="6" t="n">
-        <x:v>800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EH28" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="EI28" s="8" t="n">
-        <x:v>1.3200</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ28" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -23639,31 +23639,31 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EA29" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2000.0000</x:v>
       </x:c>
       <x:c r="EB29" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EC29" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.2200</x:v>
       </x:c>
       <x:c r="ED29" s="6" t="n">
-        <x:v>2000.0000</x:v>
+        <x:v>6600.0000</x:v>
       </x:c>
       <x:c r="EE29" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EF29" s="8" t="n">
-        <x:v>2.2200</x:v>
+        <x:v>7.3300</x:v>
       </x:c>
       <x:c r="EG29" s="6" t="n">
-        <x:v>6600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EH29" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EI29" s="8" t="n">
-        <x:v>7.3300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ29" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -24598,22 +24598,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ED30" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>250.0000</x:v>
       </x:c>
       <x:c r="EE30" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EF30" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.2800</x:v>
       </x:c>
       <x:c r="EG30" s="6" t="n">
-        <x:v>250.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EH30" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EI30" s="8" t="n">
-        <x:v>0.2800</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ30" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -25548,22 +25548,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ED31" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>500.0000</x:v>
       </x:c>
       <x:c r="EE31" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EF31" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.5600</x:v>
       </x:c>
       <x:c r="EG31" s="6" t="n">
-        <x:v>500.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EH31" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EI31" s="8" t="n">
-        <x:v>0.5600</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ31" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -26498,22 +26498,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ED32" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>250.0000</x:v>
       </x:c>
       <x:c r="EE32" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EF32" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.2800</x:v>
       </x:c>
       <x:c r="EG32" s="6" t="n">
-        <x:v>250.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EH32" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EI32" s="8" t="n">
-        <x:v>0.2800</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ32" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -27448,22 +27448,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ED33" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>500.0000</x:v>
       </x:c>
       <x:c r="EE33" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EF33" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.5600</x:v>
       </x:c>
       <x:c r="EG33" s="6" t="n">
-        <x:v>500.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EH33" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EI33" s="8" t="n">
-        <x:v>0.5600</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ33" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -28407,22 +28407,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG34" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>8000.0000</x:v>
       </x:c>
       <x:c r="EH34" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EI34" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>8.8900</x:v>
       </x:c>
       <x:c r="EJ34" s="6" t="n">
-        <x:v>8000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EK34" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EL34" s="8" t="n">
-        <x:v>8.8900</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM34" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -29366,22 +29366,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ35" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3000.0000</x:v>
       </x:c>
       <x:c r="EK35" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="EL35" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4.9400</x:v>
       </x:c>
       <x:c r="EM35" s="6" t="n">
-        <x:v>3000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN35" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="EO35" s="8" t="n">
-        <x:v>4.9400</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP35" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -30316,22 +30316,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ36" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3000.0000</x:v>
       </x:c>
       <x:c r="EK36" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="EL36" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4.9400</x:v>
       </x:c>
       <x:c r="EM36" s="6" t="n">
-        <x:v>3000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN36" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="EO36" s="8" t="n">
-        <x:v>4.9400</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP36" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -31266,22 +31266,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ37" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6000.0000</x:v>
       </x:c>
       <x:c r="EK37" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EL37" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6.6700</x:v>
       </x:c>
       <x:c r="EM37" s="6" t="n">
-        <x:v>6000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN37" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EO37" s="8" t="n">
-        <x:v>6.6700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP37" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -32243,22 +32243,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES38" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1400.0000</x:v>
       </x:c>
       <x:c r="ET38" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="EU38" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.3100</x:v>
       </x:c>
       <x:c r="EV38" s="6" t="n">
-        <x:v>1400.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EW38" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="EX38" s="8" t="n">
-        <x:v>2.3100</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY38" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -33193,22 +33193,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES39" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2000.0000</x:v>
       </x:c>
       <x:c r="ET39" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="EU39" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3.2900</x:v>
       </x:c>
       <x:c r="EV39" s="6" t="n">
-        <x:v>2000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EW39" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="EX39" s="8" t="n">
-        <x:v>3.2900</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY39" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -34152,22 +34152,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV40" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>760.0000</x:v>
       </x:c>
       <x:c r="EW40" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="EX40" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.2500</x:v>
       </x:c>
       <x:c r="EY40" s="6" t="n">
-        <x:v>760.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EZ40" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="FA40" s="8" t="n">
-        <x:v>1.2500</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB40" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -35102,7 +35102,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV41" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>800.0000</x:v>
       </x:c>
       <x:c r="EW41" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -35111,7 +35111,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY41" s="6" t="n">
-        <x:v>800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EZ41" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -36124,31 +36124,31 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FT42" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1500.0000</x:v>
       </x:c>
       <x:c r="FU42" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="FV42" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.4700</x:v>
       </x:c>
       <x:c r="FW42" s="6" t="n">
-        <x:v>1500.0000</x:v>
+        <x:v>4500.0000</x:v>
       </x:c>
       <x:c r="FX42" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="FY42" s="8" t="n">
-        <x:v>2.4700</x:v>
+        <x:v>7.4100</x:v>
       </x:c>
       <x:c r="FZ42" s="6" t="n">
-        <x:v>4500.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GA42" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="GB42" s="8" t="n">
-        <x:v>7.4100</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GC42" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -37074,31 +37074,31 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FT43" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3000.0000</x:v>
       </x:c>
       <x:c r="FU43" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FV43" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3.3300</x:v>
       </x:c>
       <x:c r="FW43" s="6" t="n">
-        <x:v>3000.0000</x:v>
+        <x:v>9000.0000</x:v>
       </x:c>
       <x:c r="FX43" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FY43" s="8" t="n">
-        <x:v>3.3300</x:v>
+        <x:v>10.0000</x:v>
       </x:c>
       <x:c r="FZ43" s="6" t="n">
-        <x:v>9000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GA43" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="GB43" s="8" t="n">
-        <x:v>10.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GC43" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -38024,22 +38024,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FT44" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3000.0000</x:v>
       </x:c>
       <x:c r="FU44" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FV44" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.0000</x:v>
       </x:c>
       <x:c r="FW44" s="6" t="n">
-        <x:v>3000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FX44" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FY44" s="8" t="n">
-        <x:v>2.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FZ44" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -38911,22 +38911,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY45" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1400.0000</x:v>
       </x:c>
       <x:c r="EZ45" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FA45" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.9300</x:v>
       </x:c>
       <x:c r="FB45" s="6" t="n">
-        <x:v>1400.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FC45" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FD45" s="8" t="n">
-        <x:v>0.9300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FE45" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -39852,22 +39852,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV46" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6300.0000</x:v>
       </x:c>
       <x:c r="EW46" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EX46" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4.2000</x:v>
       </x:c>
       <x:c r="EY46" s="6" t="n">
-        <x:v>6300.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EZ46" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FA46" s="8" t="n">
-        <x:v>4.2000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB46" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -40811,31 +40811,31 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY47" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>8000.0000</x:v>
       </x:c>
       <x:c r="EZ47" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FA47" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5.3300</x:v>
       </x:c>
       <x:c r="FB47" s="6" t="n">
-        <x:v>8000.0000</x:v>
+        <x:v>1000.0000</x:v>
       </x:c>
       <x:c r="FC47" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FD47" s="8" t="n">
-        <x:v>5.3300</x:v>
+        <x:v>0.6700</x:v>
       </x:c>
       <x:c r="FE47" s="6" t="n">
-        <x:v>1000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FF47" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FG47" s="8" t="n">
-        <x:v>0.6700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FH47" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -41770,22 +41770,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB48" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>9000.0000</x:v>
       </x:c>
       <x:c r="FC48" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FD48" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6.0000</x:v>
       </x:c>
       <x:c r="FE48" s="6" t="n">
-        <x:v>9000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FF48" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FG48" s="8" t="n">
-        <x:v>6.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FH48" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -42702,22 +42702,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV49" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>800.0000</x:v>
       </x:c>
       <x:c r="EW49" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EX49" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.5300</x:v>
       </x:c>
       <x:c r="EY49" s="6" t="n">
-        <x:v>800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EZ49" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FA49" s="8" t="n">
-        <x:v>0.5300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB49" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -43679,22 +43679,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FE50" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>9000.0000</x:v>
       </x:c>
       <x:c r="FF50" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FG50" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6.0000</x:v>
       </x:c>
       <x:c r="FH50" s="6" t="n">
-        <x:v>9000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FI50" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FJ50" s="8" t="n">
-        <x:v>6.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FK50" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -44629,22 +44629,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FE51" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1000.0000</x:v>
       </x:c>
       <x:c r="FF51" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FG51" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.6700</x:v>
       </x:c>
       <x:c r="FH51" s="6" t="n">
-        <x:v>1000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FI51" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FJ51" s="8" t="n">
-        <x:v>0.6700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FK51" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -44656,22 +44656,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FN51" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>8000.0000</x:v>
       </x:c>
       <x:c r="FO51" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FP51" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5.3300</x:v>
       </x:c>
       <x:c r="FQ51" s="6" t="n">
-        <x:v>8000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FR51" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FS51" s="8" t="n">
-        <x:v>5.3300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FT51" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -45606,31 +45606,31 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FN52" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2000.0000</x:v>
       </x:c>
       <x:c r="FO52" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FP52" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.3300</x:v>
       </x:c>
       <x:c r="FQ52" s="6" t="n">
-        <x:v>2000.0000</x:v>
+        <x:v>7000.0000</x:v>
       </x:c>
       <x:c r="FR52" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FS52" s="8" t="n">
-        <x:v>1.3300</x:v>
+        <x:v>4.6700</x:v>
       </x:c>
       <x:c r="FT52" s="6" t="n">
-        <x:v>7000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FU52" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FV52" s="8" t="n">
-        <x:v>4.6700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FW52" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -46583,22 +46583,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FW53" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>7000.0000</x:v>
       </x:c>
       <x:c r="FX53" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FY53" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4.6700</x:v>
       </x:c>
       <x:c r="FZ53" s="6" t="n">
-        <x:v>7000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GA53" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="GB53" s="8" t="n">
-        <x:v>4.6700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GC53" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -47515,31 +47515,31 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FQ54" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3000.0000</x:v>
       </x:c>
       <x:c r="FR54" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FS54" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.0000</x:v>
       </x:c>
       <x:c r="FT54" s="6" t="n">
-        <x:v>3000.0000</x:v>
+        <x:v>6000.0000</x:v>
       </x:c>
       <x:c r="FU54" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FV54" s="8" t="n">
-        <x:v>2.0000</x:v>
+        <x:v>4.0000</x:v>
       </x:c>
       <x:c r="FW54" s="6" t="n">
-        <x:v>6000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FX54" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FY54" s="8" t="n">
-        <x:v>4.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FZ54" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -48357,22 +48357,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG55" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3600.0000</x:v>
       </x:c>
       <x:c r="EH55" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EI55" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4.0000</x:v>
       </x:c>
       <x:c r="EJ55" s="6" t="n">
-        <x:v>3600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EK55" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EL55" s="8" t="n">
-        <x:v>4.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM55" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -49307,22 +49307,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG56" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3600.0000</x:v>
       </x:c>
       <x:c r="EH56" s="8" t="n">
         <x:v>10.0000</x:v>
       </x:c>
       <x:c r="EI56" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6.0000</x:v>
       </x:c>
       <x:c r="EJ56" s="6" t="n">
-        <x:v>3600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EK56" s="8" t="n">
         <x:v>10.0000</x:v>
       </x:c>
       <x:c r="EL56" s="8" t="n">
-        <x:v>6.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM56" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -50293,40 +50293,40 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES57" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3000.0000</x:v>
       </x:c>
       <x:c r="ET57" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="EU57" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5.2600</x:v>
       </x:c>
       <x:c r="EV57" s="6" t="n">
-        <x:v>3000.0000</x:v>
+        <x:v>3900.0000</x:v>
       </x:c>
       <x:c r="EW57" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="EX57" s="8" t="n">
-        <x:v>5.2600</x:v>
+        <x:v>6.8400</x:v>
       </x:c>
       <x:c r="EY57" s="6" t="n">
-        <x:v>3900.0000</x:v>
+        <x:v>2100.0000</x:v>
       </x:c>
       <x:c r="EZ57" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="FA57" s="8" t="n">
-        <x:v>6.8400</x:v>
+        <x:v>3.6800</x:v>
       </x:c>
       <x:c r="FB57" s="6" t="n">
-        <x:v>2100.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FC57" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="FD57" s="8" t="n">
-        <x:v>3.6800</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FE57" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -51261,22 +51261,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY58" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1800.0000</x:v>
       </x:c>
       <x:c r="EZ58" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="FA58" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3.1600</x:v>
       </x:c>
       <x:c r="FB58" s="6" t="n">
-        <x:v>1800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FC58" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="FD58" s="8" t="n">
-        <x:v>3.1600</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FE58" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -51306,31 +51306,31 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FN58" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3900.0000</x:v>
       </x:c>
       <x:c r="FO58" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="FP58" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6.8400</x:v>
       </x:c>
       <x:c r="FQ58" s="6" t="n">
-        <x:v>3900.0000</x:v>
+        <x:v>3300.0000</x:v>
       </x:c>
       <x:c r="FR58" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="FS58" s="8" t="n">
-        <x:v>6.8400</x:v>
+        <x:v>5.7900</x:v>
       </x:c>
       <x:c r="FT58" s="6" t="n">
-        <x:v>3300.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FU58" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="FV58" s="8" t="n">
-        <x:v>5.7900</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FW58" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -52265,22 +52265,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FQ59" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>600.0000</x:v>
       </x:c>
       <x:c r="FR59" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="FS59" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.0500</x:v>
       </x:c>
       <x:c r="FT59" s="6" t="n">
-        <x:v>600.0000</x:v>
+        <x:v>3900.0000</x:v>
       </x:c>
       <x:c r="FU59" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="FV59" s="8" t="n">
-        <x:v>1.0500</x:v>
+        <x:v>6.8400</x:v>
       </x:c>
       <x:c r="FW59" s="6" t="n">
         <x:v>3900.0000</x:v>
@@ -52292,22 +52292,22 @@
         <x:v>6.8400</x:v>
       </x:c>
       <x:c r="FZ59" s="6" t="n">
-        <x:v>3900.0000</x:v>
+        <x:v>600.0000</x:v>
       </x:c>
       <x:c r="GA59" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="GB59" s="8" t="n">
-        <x:v>6.8400</x:v>
+        <x:v>1.0500</x:v>
       </x:c>
       <x:c r="GC59" s="6" t="n">
-        <x:v>600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GD59" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="GE59" s="8" t="n">
-        <x:v>1.0500</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GF59" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -53269,13 +53269,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GI60" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3900.0000</x:v>
       </x:c>
       <x:c r="GJ60" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="GK60" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6.8400</x:v>
       </x:c>
       <x:c r="GL60" s="6" t="n">
         <x:v>3900.0000</x:v>
@@ -53287,22 +53287,22 @@
         <x:v>6.8400</x:v>
       </x:c>
       <x:c r="GO60" s="6" t="n">
-        <x:v>3900.0000</x:v>
+        <x:v>1200.0000</x:v>
       </x:c>
       <x:c r="GP60" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="GQ60" s="8" t="n">
-        <x:v>6.8400</x:v>
+        <x:v>2.1100</x:v>
       </x:c>
       <x:c r="GR60" s="6" t="n">
-        <x:v>1200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GS60" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="GT60" s="8" t="n">
-        <x:v>2.1100</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GU60" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -54039,31 +54039,31 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EA61" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3900.0000</x:v>
       </x:c>
       <x:c r="EB61" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="EC61" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6.8400</x:v>
       </x:c>
       <x:c r="ED61" s="6" t="n">
-        <x:v>3900.0000</x:v>
+        <x:v>2100.0000</x:v>
       </x:c>
       <x:c r="EE61" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="EF61" s="8" t="n">
-        <x:v>6.8400</x:v>
+        <x:v>3.6800</x:v>
       </x:c>
       <x:c r="EG61" s="6" t="n">
-        <x:v>2100.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EH61" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="EI61" s="8" t="n">
-        <x:v>3.6800</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ61" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -54998,31 +54998,31 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ED62" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1800.0000</x:v>
       </x:c>
       <x:c r="EE62" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="EF62" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3.1600</x:v>
       </x:c>
       <x:c r="EG62" s="6" t="n">
-        <x:v>1800.0000</x:v>
+        <x:v>2400.0000</x:v>
       </x:c>
       <x:c r="EH62" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="EI62" s="8" t="n">
-        <x:v>3.1600</x:v>
+        <x:v>4.2100</x:v>
       </x:c>
       <x:c r="EJ62" s="6" t="n">
-        <x:v>2400.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EK62" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="EL62" s="8" t="n">
-        <x:v>4.2100</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM62" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -55930,58 +55930,58 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DX63" s="7" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4500.0000</x:v>
       </x:c>
       <x:c r="DY63" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="DZ63" s="9" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4.1500</x:v>
       </x:c>
       <x:c r="EA63" s="7" t="n">
-        <x:v>4500.0000</x:v>
+        <x:v>12800.0000</x:v>
       </x:c>
       <x:c r="EB63" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="EC63" s="9" t="n">
-        <x:v>4.1500</x:v>
+        <x:v>15.8400</x:v>
       </x:c>
       <x:c r="ED63" s="7" t="n">
-        <x:v>12800.0000</x:v>
+        <x:v>19000.0000</x:v>
       </x:c>
       <x:c r="EE63" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="EF63" s="9" t="n">
-        <x:v>15.8400</x:v>
+        <x:v>23.5800</x:v>
       </x:c>
       <x:c r="EG63" s="7" t="n">
-        <x:v>19000.0000</x:v>
+        <x:v>25603.0000</x:v>
       </x:c>
       <x:c r="EH63" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="EI63" s="9" t="n">
-        <x:v>23.5800</x:v>
+        <x:v>31.4000</x:v>
       </x:c>
       <x:c r="EJ63" s="7" t="n">
-        <x:v>25603.0000</x:v>
+        <x:v>31500.0000</x:v>
       </x:c>
       <x:c r="EK63" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="EL63" s="9" t="n">
-        <x:v>31.4000</x:v>
+        <x:v>35.7800</x:v>
       </x:c>
       <x:c r="EM63" s="7" t="n">
-        <x:v>31500.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN63" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="EO63" s="9" t="n">
-        <x:v>35.7800</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP63" s="7" t="n">
         <x:v>0.0000</x:v>
@@ -55993,58 +55993,58 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES63" s="7" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>20700.0000</x:v>
       </x:c>
       <x:c r="ET63" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="EU63" s="9" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>24.8800</x:v>
       </x:c>
       <x:c r="EV63" s="7" t="n">
-        <x:v>20700.0000</x:v>
+        <x:v>19860.0000</x:v>
       </x:c>
       <x:c r="EW63" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="EX63" s="9" t="n">
-        <x:v>24.8800</x:v>
+        <x:v>20.3600</x:v>
       </x:c>
       <x:c r="EY63" s="7" t="n">
-        <x:v>19860.0000</x:v>
+        <x:v>22300.0000</x:v>
       </x:c>
       <x:c r="EZ63" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FA63" s="9" t="n">
-        <x:v>20.3600</x:v>
+        <x:v>21.4100</x:v>
       </x:c>
       <x:c r="FB63" s="7" t="n">
-        <x:v>22300.0000</x:v>
+        <x:v>17800.0000</x:v>
       </x:c>
       <x:c r="FC63" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FD63" s="9" t="n">
-        <x:v>21.4100</x:v>
+        <x:v>14.7300</x:v>
       </x:c>
       <x:c r="FE63" s="7" t="n">
-        <x:v>17800.0000</x:v>
+        <x:v>17000.0000</x:v>
       </x:c>
       <x:c r="FF63" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FG63" s="9" t="n">
-        <x:v>14.7300</x:v>
+        <x:v>13.9100</x:v>
       </x:c>
       <x:c r="FH63" s="7" t="n">
-        <x:v>17000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FI63" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FJ63" s="9" t="n">
-        <x:v>13.9100</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FK63" s="7" t="n">
         <x:v>0.0000</x:v>
@@ -56056,58 +56056,58 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FN63" s="7" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>22900.0000</x:v>
       </x:c>
       <x:c r="FO63" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FP63" s="9" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>21.8100</x:v>
       </x:c>
       <x:c r="FQ63" s="7" t="n">
-        <x:v>22900.0000</x:v>
+        <x:v>18900.0000</x:v>
       </x:c>
       <x:c r="FR63" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FS63" s="9" t="n">
-        <x:v>21.8100</x:v>
+        <x:v>18.6800</x:v>
       </x:c>
       <x:c r="FT63" s="7" t="n">
-        <x:v>18900.0000</x:v>
+        <x:v>26400.0000</x:v>
       </x:c>
       <x:c r="FU63" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FV63" s="9" t="n">
-        <x:v>18.6800</x:v>
+        <x:v>26.9500</x:v>
       </x:c>
       <x:c r="FW63" s="7" t="n">
-        <x:v>26400.0000</x:v>
+        <x:v>24400.0000</x:v>
       </x:c>
       <x:c r="FX63" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FY63" s="9" t="n">
-        <x:v>26.9500</x:v>
+        <x:v>28.9200</x:v>
       </x:c>
       <x:c r="FZ63" s="7" t="n">
-        <x:v>24400.0000</x:v>
+        <x:v>600.0000</x:v>
       </x:c>
       <x:c r="GA63" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="GB63" s="9" t="n">
-        <x:v>28.9200</x:v>
+        <x:v>1.0500</x:v>
       </x:c>
       <x:c r="GC63" s="7" t="n">
-        <x:v>600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GD63" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="GE63" s="9" t="n">
-        <x:v>1.0500</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GF63" s="7" t="n">
         <x:v>0.0000</x:v>
@@ -56119,13 +56119,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GI63" s="7" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3900.0000</x:v>
       </x:c>
       <x:c r="GJ63" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="GK63" s="9" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6.8400</x:v>
       </x:c>
       <x:c r="GL63" s="7" t="n">
         <x:v>3900.0000</x:v>
@@ -56137,22 +56137,22 @@
         <x:v>6.8400</x:v>
       </x:c>
       <x:c r="GO63" s="7" t="n">
-        <x:v>3900.0000</x:v>
+        <x:v>1200.0000</x:v>
       </x:c>
       <x:c r="GP63" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="GQ63" s="9" t="n">
-        <x:v>6.8400</x:v>
+        <x:v>2.1100</x:v>
       </x:c>
       <x:c r="GR63" s="7" t="n">
-        <x:v>1200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GS63" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="GT63" s="9" t="n">
-        <x:v>2.1100</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GU63" s="7" t="n">
         <x:v>0.0000</x:v>

--- a/.pm-ai-cache/network-source/task-input-newest.xlsx
+++ b/.pm-ai-cache/network-source/task-input-newest.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工程別生産計画問合せ問合せ" sheetId="1" r:id="Rb0e6559bf84f4361"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工程別生産計画問合せ問合せ" sheetId="1" r:id="R029f01c7b6c84e42"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -10,7 +10,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5">
   <x:si>
-    <x:t xml:space="preserve">表示基準日 : 2026年05月19日 </x:t>
+    <x:t xml:space="preserve">表示基準日 : 2026年05月20日 </x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">K </x:t>
@@ -578,823 +578,823 @@
         <x:v/>
       </x:c>
       <x:c r="AR5" s="2" t="str">
-        <x:v>04/19(日)</x:v>
+        <x:v>04/20(月)</x:v>
       </x:c>
       <x:c r="AS5" s="2" t="str">
-        <x:v>04/19(日)</x:v>
+        <x:v>04/20(月)</x:v>
       </x:c>
       <x:c r="AT5" s="2" t="str">
-        <x:v>04/19(日)</x:v>
+        <x:v>04/20(月)</x:v>
       </x:c>
       <x:c r="AU5" s="2" t="str">
-        <x:v>04/20(月)</x:v>
+        <x:v>04/21(火)</x:v>
       </x:c>
       <x:c r="AV5" s="2" t="str">
-        <x:v>04/20(月)</x:v>
+        <x:v>04/21(火)</x:v>
       </x:c>
       <x:c r="AW5" s="2" t="str">
-        <x:v>04/20(月)</x:v>
+        <x:v>04/21(火)</x:v>
       </x:c>
       <x:c r="AX5" s="2" t="str">
-        <x:v>04/21(火)</x:v>
+        <x:v>04/22(水)</x:v>
       </x:c>
       <x:c r="AY5" s="2" t="str">
-        <x:v>04/21(火)</x:v>
+        <x:v>04/22(水)</x:v>
       </x:c>
       <x:c r="AZ5" s="2" t="str">
-        <x:v>04/21(火)</x:v>
+        <x:v>04/22(水)</x:v>
       </x:c>
       <x:c r="BA5" s="2" t="str">
-        <x:v>04/22(水)</x:v>
+        <x:v>04/23(木)</x:v>
       </x:c>
       <x:c r="BB5" s="2" t="str">
-        <x:v>04/22(水)</x:v>
+        <x:v>04/23(木)</x:v>
       </x:c>
       <x:c r="BC5" s="2" t="str">
-        <x:v>04/22(水)</x:v>
+        <x:v>04/23(木)</x:v>
       </x:c>
       <x:c r="BD5" s="2" t="str">
-        <x:v>04/23(木)</x:v>
+        <x:v>04/24(金)</x:v>
       </x:c>
       <x:c r="BE5" s="2" t="str">
-        <x:v>04/23(木)</x:v>
+        <x:v>04/24(金)</x:v>
       </x:c>
       <x:c r="BF5" s="2" t="str">
-        <x:v>04/23(木)</x:v>
+        <x:v>04/24(金)</x:v>
       </x:c>
       <x:c r="BG5" s="2" t="str">
-        <x:v>04/24(金)</x:v>
+        <x:v>04/25(土)</x:v>
       </x:c>
       <x:c r="BH5" s="2" t="str">
-        <x:v>04/24(金)</x:v>
+        <x:v>04/25(土)</x:v>
       </x:c>
       <x:c r="BI5" s="2" t="str">
-        <x:v>04/24(金)</x:v>
+        <x:v>04/25(土)</x:v>
       </x:c>
       <x:c r="BJ5" s="2" t="str">
-        <x:v>04/25(土)</x:v>
+        <x:v>04/26(日)</x:v>
       </x:c>
       <x:c r="BK5" s="2" t="str">
-        <x:v>04/25(土)</x:v>
+        <x:v>04/26(日)</x:v>
       </x:c>
       <x:c r="BL5" s="2" t="str">
-        <x:v>04/25(土)</x:v>
+        <x:v>04/26(日)</x:v>
       </x:c>
       <x:c r="BM5" s="2" t="str">
-        <x:v>04/26(日)</x:v>
+        <x:v>04/27(月)</x:v>
       </x:c>
       <x:c r="BN5" s="2" t="str">
-        <x:v>04/26(日)</x:v>
+        <x:v>04/27(月)</x:v>
       </x:c>
       <x:c r="BO5" s="2" t="str">
-        <x:v>04/26(日)</x:v>
+        <x:v>04/27(月)</x:v>
       </x:c>
       <x:c r="BP5" s="2" t="str">
-        <x:v>04/27(月)</x:v>
+        <x:v>04/28(火)</x:v>
       </x:c>
       <x:c r="BQ5" s="2" t="str">
-        <x:v>04/27(月)</x:v>
+        <x:v>04/28(火)</x:v>
       </x:c>
       <x:c r="BR5" s="2" t="str">
-        <x:v>04/27(月)</x:v>
+        <x:v>04/28(火)</x:v>
       </x:c>
       <x:c r="BS5" s="2" t="str">
-        <x:v>04/28(火)</x:v>
+        <x:v>04/29(水)</x:v>
       </x:c>
       <x:c r="BT5" s="2" t="str">
-        <x:v>04/28(火)</x:v>
+        <x:v>04/29(水)</x:v>
       </x:c>
       <x:c r="BU5" s="2" t="str">
-        <x:v>04/28(火)</x:v>
+        <x:v>04/29(水)</x:v>
       </x:c>
       <x:c r="BV5" s="2" t="str">
-        <x:v>04/29(水)</x:v>
+        <x:v>04/30(木)</x:v>
       </x:c>
       <x:c r="BW5" s="2" t="str">
-        <x:v>04/29(水)</x:v>
+        <x:v>04/30(木)</x:v>
       </x:c>
       <x:c r="BX5" s="2" t="str">
-        <x:v>04/29(水)</x:v>
+        <x:v>04/30(木)</x:v>
       </x:c>
       <x:c r="BY5" s="2" t="str">
-        <x:v>04/30(木)</x:v>
+        <x:v>05/01(金)</x:v>
       </x:c>
       <x:c r="BZ5" s="2" t="str">
-        <x:v>04/30(木)</x:v>
+        <x:v>05/01(金)</x:v>
       </x:c>
       <x:c r="CA5" s="2" t="str">
-        <x:v>04/30(木)</x:v>
+        <x:v>05/01(金)</x:v>
       </x:c>
       <x:c r="CB5" s="2" t="str">
-        <x:v>05/01(金)</x:v>
+        <x:v>05/02(土)</x:v>
       </x:c>
       <x:c r="CC5" s="2" t="str">
-        <x:v>05/01(金)</x:v>
+        <x:v>05/02(土)</x:v>
       </x:c>
       <x:c r="CD5" s="2" t="str">
-        <x:v>05/01(金)</x:v>
+        <x:v>05/02(土)</x:v>
       </x:c>
       <x:c r="CE5" s="2" t="str">
-        <x:v>05/02(土)</x:v>
+        <x:v>05/03(日)</x:v>
       </x:c>
       <x:c r="CF5" s="2" t="str">
-        <x:v>05/02(土)</x:v>
+        <x:v>05/03(日)</x:v>
       </x:c>
       <x:c r="CG5" s="2" t="str">
-        <x:v>05/02(土)</x:v>
+        <x:v>05/03(日)</x:v>
       </x:c>
       <x:c r="CH5" s="2" t="str">
-        <x:v>05/03(日)</x:v>
+        <x:v>05/04(月)</x:v>
       </x:c>
       <x:c r="CI5" s="2" t="str">
-        <x:v>05/03(日)</x:v>
+        <x:v>05/04(月)</x:v>
       </x:c>
       <x:c r="CJ5" s="2" t="str">
-        <x:v>05/03(日)</x:v>
+        <x:v>05/04(月)</x:v>
       </x:c>
       <x:c r="CK5" s="2" t="str">
-        <x:v>05/04(月)</x:v>
+        <x:v>05/05(火)</x:v>
       </x:c>
       <x:c r="CL5" s="2" t="str">
-        <x:v>05/04(月)</x:v>
+        <x:v>05/05(火)</x:v>
       </x:c>
       <x:c r="CM5" s="2" t="str">
-        <x:v>05/04(月)</x:v>
+        <x:v>05/05(火)</x:v>
       </x:c>
       <x:c r="CN5" s="2" t="str">
-        <x:v>05/05(火)</x:v>
+        <x:v>05/06(水)</x:v>
       </x:c>
       <x:c r="CO5" s="2" t="str">
-        <x:v>05/05(火)</x:v>
+        <x:v>05/06(水)</x:v>
       </x:c>
       <x:c r="CP5" s="2" t="str">
-        <x:v>05/05(火)</x:v>
+        <x:v>05/06(水)</x:v>
       </x:c>
       <x:c r="CQ5" s="2" t="str">
-        <x:v>05/06(水)</x:v>
+        <x:v>05/07(木)</x:v>
       </x:c>
       <x:c r="CR5" s="2" t="str">
-        <x:v>05/06(水)</x:v>
+        <x:v>05/07(木)</x:v>
       </x:c>
       <x:c r="CS5" s="2" t="str">
-        <x:v>05/06(水)</x:v>
+        <x:v>05/07(木)</x:v>
       </x:c>
       <x:c r="CT5" s="2" t="str">
-        <x:v>05/07(木)</x:v>
+        <x:v>05/08(金)</x:v>
       </x:c>
       <x:c r="CU5" s="2" t="str">
-        <x:v>05/07(木)</x:v>
+        <x:v>05/08(金)</x:v>
       </x:c>
       <x:c r="CV5" s="2" t="str">
-        <x:v>05/07(木)</x:v>
+        <x:v>05/08(金)</x:v>
       </x:c>
       <x:c r="CW5" s="2" t="str">
-        <x:v>05/08(金)</x:v>
+        <x:v>05/09(土)</x:v>
       </x:c>
       <x:c r="CX5" s="2" t="str">
-        <x:v>05/08(金)</x:v>
+        <x:v>05/09(土)</x:v>
       </x:c>
       <x:c r="CY5" s="2" t="str">
-        <x:v>05/08(金)</x:v>
+        <x:v>05/09(土)</x:v>
       </x:c>
       <x:c r="CZ5" s="2" t="str">
-        <x:v>05/09(土)</x:v>
+        <x:v>05/10(日)</x:v>
       </x:c>
       <x:c r="DA5" s="2" t="str">
-        <x:v>05/09(土)</x:v>
+        <x:v>05/10(日)</x:v>
       </x:c>
       <x:c r="DB5" s="2" t="str">
-        <x:v>05/09(土)</x:v>
+        <x:v>05/10(日)</x:v>
       </x:c>
       <x:c r="DC5" s="2" t="str">
-        <x:v>05/10(日)</x:v>
+        <x:v>05/11(月)</x:v>
       </x:c>
       <x:c r="DD5" s="2" t="str">
-        <x:v>05/10(日)</x:v>
+        <x:v>05/11(月)</x:v>
       </x:c>
       <x:c r="DE5" s="2" t="str">
-        <x:v>05/10(日)</x:v>
+        <x:v>05/11(月)</x:v>
       </x:c>
       <x:c r="DF5" s="2" t="str">
-        <x:v>05/11(月)</x:v>
+        <x:v>05/12(火)</x:v>
       </x:c>
       <x:c r="DG5" s="2" t="str">
-        <x:v>05/11(月)</x:v>
+        <x:v>05/12(火)</x:v>
       </x:c>
       <x:c r="DH5" s="2" t="str">
-        <x:v>05/11(月)</x:v>
+        <x:v>05/12(火)</x:v>
       </x:c>
       <x:c r="DI5" s="2" t="str">
-        <x:v>05/12(火)</x:v>
+        <x:v>05/13(水)</x:v>
       </x:c>
       <x:c r="DJ5" s="2" t="str">
-        <x:v>05/12(火)</x:v>
+        <x:v>05/13(水)</x:v>
       </x:c>
       <x:c r="DK5" s="2" t="str">
-        <x:v>05/12(火)</x:v>
+        <x:v>05/13(水)</x:v>
       </x:c>
       <x:c r="DL5" s="2" t="str">
-        <x:v>05/13(水)</x:v>
+        <x:v>05/14(木)</x:v>
       </x:c>
       <x:c r="DM5" s="2" t="str">
-        <x:v>05/13(水)</x:v>
+        <x:v>05/14(木)</x:v>
       </x:c>
       <x:c r="DN5" s="2" t="str">
-        <x:v>05/13(水)</x:v>
+        <x:v>05/14(木)</x:v>
       </x:c>
       <x:c r="DO5" s="2" t="str">
-        <x:v>05/14(木)</x:v>
+        <x:v>05/15(金)</x:v>
       </x:c>
       <x:c r="DP5" s="2" t="str">
-        <x:v>05/14(木)</x:v>
+        <x:v>05/15(金)</x:v>
       </x:c>
       <x:c r="DQ5" s="2" t="str">
-        <x:v>05/14(木)</x:v>
+        <x:v>05/15(金)</x:v>
       </x:c>
       <x:c r="DR5" s="2" t="str">
-        <x:v>05/15(金)</x:v>
+        <x:v>05/16(土)</x:v>
       </x:c>
       <x:c r="DS5" s="2" t="str">
-        <x:v>05/15(金)</x:v>
+        <x:v>05/16(土)</x:v>
       </x:c>
       <x:c r="DT5" s="2" t="str">
-        <x:v>05/15(金)</x:v>
+        <x:v>05/16(土)</x:v>
       </x:c>
       <x:c r="DU5" s="2" t="str">
-        <x:v>05/16(土)</x:v>
+        <x:v>05/17(日)</x:v>
       </x:c>
       <x:c r="DV5" s="2" t="str">
-        <x:v>05/16(土)</x:v>
+        <x:v>05/17(日)</x:v>
       </x:c>
       <x:c r="DW5" s="2" t="str">
-        <x:v>05/16(土)</x:v>
+        <x:v>05/17(日)</x:v>
       </x:c>
       <x:c r="DX5" s="2" t="str">
-        <x:v>05/17(日)</x:v>
+        <x:v>05/18(月)</x:v>
       </x:c>
       <x:c r="DY5" s="2" t="str">
-        <x:v>05/17(日)</x:v>
+        <x:v>05/18(月)</x:v>
       </x:c>
       <x:c r="DZ5" s="2" t="str">
-        <x:v>05/17(日)</x:v>
+        <x:v>05/18(月)</x:v>
       </x:c>
       <x:c r="EA5" s="2" t="str">
-        <x:v>05/18(月)</x:v>
+        <x:v>05/19(火)</x:v>
       </x:c>
       <x:c r="EB5" s="2" t="str">
-        <x:v>05/18(月)</x:v>
+        <x:v>05/19(火)</x:v>
       </x:c>
       <x:c r="EC5" s="2" t="str">
-        <x:v>05/18(月)</x:v>
+        <x:v>05/19(火)</x:v>
       </x:c>
       <x:c r="ED5" s="2" t="str">
-        <x:v>05/19(火)</x:v>
+        <x:v>05/20(水)</x:v>
       </x:c>
       <x:c r="EE5" s="2" t="str">
-        <x:v>05/19(火)</x:v>
+        <x:v>05/20(水)</x:v>
       </x:c>
       <x:c r="EF5" s="2" t="str">
-        <x:v>05/19(火)</x:v>
+        <x:v>05/20(水)</x:v>
       </x:c>
       <x:c r="EG5" s="2" t="str">
-        <x:v>05/20(水)</x:v>
+        <x:v>05/21(木)</x:v>
       </x:c>
       <x:c r="EH5" s="2" t="str">
-        <x:v>05/20(水)</x:v>
+        <x:v>05/21(木)</x:v>
       </x:c>
       <x:c r="EI5" s="2" t="str">
-        <x:v>05/20(水)</x:v>
+        <x:v>05/21(木)</x:v>
       </x:c>
       <x:c r="EJ5" s="2" t="str">
-        <x:v>05/21(木)</x:v>
+        <x:v>05/22(金)</x:v>
       </x:c>
       <x:c r="EK5" s="2" t="str">
-        <x:v>05/21(木)</x:v>
+        <x:v>05/22(金)</x:v>
       </x:c>
       <x:c r="EL5" s="2" t="str">
-        <x:v>05/21(木)</x:v>
+        <x:v>05/22(金)</x:v>
       </x:c>
       <x:c r="EM5" s="2" t="str">
-        <x:v>05/22(金)</x:v>
+        <x:v>05/23(土)</x:v>
       </x:c>
       <x:c r="EN5" s="2" t="str">
-        <x:v>05/22(金)</x:v>
+        <x:v>05/23(土)</x:v>
       </x:c>
       <x:c r="EO5" s="2" t="str">
-        <x:v>05/22(金)</x:v>
+        <x:v>05/23(土)</x:v>
       </x:c>
       <x:c r="EP5" s="2" t="str">
-        <x:v>05/23(土)</x:v>
+        <x:v>05/24(日)</x:v>
       </x:c>
       <x:c r="EQ5" s="2" t="str">
-        <x:v>05/23(土)</x:v>
+        <x:v>05/24(日)</x:v>
       </x:c>
       <x:c r="ER5" s="2" t="str">
-        <x:v>05/23(土)</x:v>
+        <x:v>05/24(日)</x:v>
       </x:c>
       <x:c r="ES5" s="2" t="str">
-        <x:v>05/24(日)</x:v>
+        <x:v>05/25(月)</x:v>
       </x:c>
       <x:c r="ET5" s="2" t="str">
-        <x:v>05/24(日)</x:v>
+        <x:v>05/25(月)</x:v>
       </x:c>
       <x:c r="EU5" s="2" t="str">
-        <x:v>05/24(日)</x:v>
+        <x:v>05/25(月)</x:v>
       </x:c>
       <x:c r="EV5" s="2" t="str">
-        <x:v>05/25(月)</x:v>
+        <x:v>05/26(火)</x:v>
       </x:c>
       <x:c r="EW5" s="2" t="str">
-        <x:v>05/25(月)</x:v>
+        <x:v>05/26(火)</x:v>
       </x:c>
       <x:c r="EX5" s="2" t="str">
-        <x:v>05/25(月)</x:v>
+        <x:v>05/26(火)</x:v>
       </x:c>
       <x:c r="EY5" s="2" t="str">
-        <x:v>05/26(火)</x:v>
+        <x:v>05/27(水)</x:v>
       </x:c>
       <x:c r="EZ5" s="2" t="str">
-        <x:v>05/26(火)</x:v>
+        <x:v>05/27(水)</x:v>
       </x:c>
       <x:c r="FA5" s="2" t="str">
-        <x:v>05/26(火)</x:v>
+        <x:v>05/27(水)</x:v>
       </x:c>
       <x:c r="FB5" s="2" t="str">
-        <x:v>05/27(水)</x:v>
+        <x:v>05/28(木)</x:v>
       </x:c>
       <x:c r="FC5" s="2" t="str">
-        <x:v>05/27(水)</x:v>
+        <x:v>05/28(木)</x:v>
       </x:c>
       <x:c r="FD5" s="2" t="str">
-        <x:v>05/27(水)</x:v>
+        <x:v>05/28(木)</x:v>
       </x:c>
       <x:c r="FE5" s="2" t="str">
-        <x:v>05/28(木)</x:v>
+        <x:v>05/29(金)</x:v>
       </x:c>
       <x:c r="FF5" s="2" t="str">
-        <x:v>05/28(木)</x:v>
+        <x:v>05/29(金)</x:v>
       </x:c>
       <x:c r="FG5" s="2" t="str">
-        <x:v>05/28(木)</x:v>
+        <x:v>05/29(金)</x:v>
       </x:c>
       <x:c r="FH5" s="2" t="str">
-        <x:v>05/29(金)</x:v>
+        <x:v>05/30(土)</x:v>
       </x:c>
       <x:c r="FI5" s="2" t="str">
-        <x:v>05/29(金)</x:v>
+        <x:v>05/30(土)</x:v>
       </x:c>
       <x:c r="FJ5" s="2" t="str">
-        <x:v>05/29(金)</x:v>
+        <x:v>05/30(土)</x:v>
       </x:c>
       <x:c r="FK5" s="2" t="str">
-        <x:v>05/30(土)</x:v>
+        <x:v>05/31(日)</x:v>
       </x:c>
       <x:c r="FL5" s="2" t="str">
-        <x:v>05/30(土)</x:v>
+        <x:v>05/31(日)</x:v>
       </x:c>
       <x:c r="FM5" s="2" t="str">
-        <x:v>05/30(土)</x:v>
+        <x:v>05/31(日)</x:v>
       </x:c>
       <x:c r="FN5" s="2" t="str">
-        <x:v>05/31(日)</x:v>
+        <x:v>06/01(月)</x:v>
       </x:c>
       <x:c r="FO5" s="2" t="str">
-        <x:v>05/31(日)</x:v>
+        <x:v>06/01(月)</x:v>
       </x:c>
       <x:c r="FP5" s="2" t="str">
-        <x:v>05/31(日)</x:v>
+        <x:v>06/01(月)</x:v>
       </x:c>
       <x:c r="FQ5" s="2" t="str">
-        <x:v>06/01(月)</x:v>
+        <x:v>06/02(火)</x:v>
       </x:c>
       <x:c r="FR5" s="2" t="str">
-        <x:v>06/01(月)</x:v>
+        <x:v>06/02(火)</x:v>
       </x:c>
       <x:c r="FS5" s="2" t="str">
-        <x:v>06/01(月)</x:v>
+        <x:v>06/02(火)</x:v>
       </x:c>
       <x:c r="FT5" s="2" t="str">
-        <x:v>06/02(火)</x:v>
+        <x:v>06/03(水)</x:v>
       </x:c>
       <x:c r="FU5" s="2" t="str">
-        <x:v>06/02(火)</x:v>
+        <x:v>06/03(水)</x:v>
       </x:c>
       <x:c r="FV5" s="2" t="str">
-        <x:v>06/02(火)</x:v>
+        <x:v>06/03(水)</x:v>
       </x:c>
       <x:c r="FW5" s="2" t="str">
-        <x:v>06/03(水)</x:v>
+        <x:v>06/04(木)</x:v>
       </x:c>
       <x:c r="FX5" s="2" t="str">
-        <x:v>06/03(水)</x:v>
+        <x:v>06/04(木)</x:v>
       </x:c>
       <x:c r="FY5" s="2" t="str">
-        <x:v>06/03(水)</x:v>
+        <x:v>06/04(木)</x:v>
       </x:c>
       <x:c r="FZ5" s="2" t="str">
-        <x:v>06/04(木)</x:v>
+        <x:v>06/05(金)</x:v>
       </x:c>
       <x:c r="GA5" s="2" t="str">
-        <x:v>06/04(木)</x:v>
+        <x:v>06/05(金)</x:v>
       </x:c>
       <x:c r="GB5" s="2" t="str">
-        <x:v>06/04(木)</x:v>
+        <x:v>06/05(金)</x:v>
       </x:c>
       <x:c r="GC5" s="2" t="str">
-        <x:v>06/05(金)</x:v>
+        <x:v>06/06(土)</x:v>
       </x:c>
       <x:c r="GD5" s="2" t="str">
-        <x:v>06/05(金)</x:v>
+        <x:v>06/06(土)</x:v>
       </x:c>
       <x:c r="GE5" s="2" t="str">
-        <x:v>06/05(金)</x:v>
+        <x:v>06/06(土)</x:v>
       </x:c>
       <x:c r="GF5" s="2" t="str">
-        <x:v>06/06(土)</x:v>
+        <x:v>06/07(日)</x:v>
       </x:c>
       <x:c r="GG5" s="2" t="str">
-        <x:v>06/06(土)</x:v>
+        <x:v>06/07(日)</x:v>
       </x:c>
       <x:c r="GH5" s="2" t="str">
-        <x:v>06/06(土)</x:v>
+        <x:v>06/07(日)</x:v>
       </x:c>
       <x:c r="GI5" s="2" t="str">
-        <x:v>06/07(日)</x:v>
+        <x:v>06/08(月)</x:v>
       </x:c>
       <x:c r="GJ5" s="2" t="str">
-        <x:v>06/07(日)</x:v>
+        <x:v>06/08(月)</x:v>
       </x:c>
       <x:c r="GK5" s="2" t="str">
-        <x:v>06/07(日)</x:v>
+        <x:v>06/08(月)</x:v>
       </x:c>
       <x:c r="GL5" s="2" t="str">
-        <x:v>06/08(月)</x:v>
+        <x:v>06/09(火)</x:v>
       </x:c>
       <x:c r="GM5" s="2" t="str">
-        <x:v>06/08(月)</x:v>
+        <x:v>06/09(火)</x:v>
       </x:c>
       <x:c r="GN5" s="2" t="str">
-        <x:v>06/08(月)</x:v>
+        <x:v>06/09(火)</x:v>
       </x:c>
       <x:c r="GO5" s="2" t="str">
-        <x:v>06/09(火)</x:v>
+        <x:v>06/10(水)</x:v>
       </x:c>
       <x:c r="GP5" s="2" t="str">
-        <x:v>06/09(火)</x:v>
+        <x:v>06/10(水)</x:v>
       </x:c>
       <x:c r="GQ5" s="2" t="str">
-        <x:v>06/09(火)</x:v>
+        <x:v>06/10(水)</x:v>
       </x:c>
       <x:c r="GR5" s="2" t="str">
-        <x:v>06/10(水)</x:v>
+        <x:v>06/11(木)</x:v>
       </x:c>
       <x:c r="GS5" s="2" t="str">
-        <x:v>06/10(水)</x:v>
+        <x:v>06/11(木)</x:v>
       </x:c>
       <x:c r="GT5" s="2" t="str">
-        <x:v>06/10(水)</x:v>
+        <x:v>06/11(木)</x:v>
       </x:c>
       <x:c r="GU5" s="2" t="str">
-        <x:v>06/11(木)</x:v>
+        <x:v>06/12(金)</x:v>
       </x:c>
       <x:c r="GV5" s="2" t="str">
-        <x:v>06/11(木)</x:v>
+        <x:v>06/12(金)</x:v>
       </x:c>
       <x:c r="GW5" s="2" t="str">
-        <x:v>06/11(木)</x:v>
+        <x:v>06/12(金)</x:v>
       </x:c>
       <x:c r="GX5" s="2" t="str">
-        <x:v>06/12(金)</x:v>
+        <x:v>06/13(土)</x:v>
       </x:c>
       <x:c r="GY5" s="2" t="str">
-        <x:v>06/12(金)</x:v>
+        <x:v>06/13(土)</x:v>
       </x:c>
       <x:c r="GZ5" s="2" t="str">
-        <x:v>06/12(金)</x:v>
+        <x:v>06/13(土)</x:v>
       </x:c>
       <x:c r="HA5" s="2" t="str">
-        <x:v>06/13(土)</x:v>
+        <x:v>06/14(日)</x:v>
       </x:c>
       <x:c r="HB5" s="2" t="str">
-        <x:v>06/13(土)</x:v>
+        <x:v>06/14(日)</x:v>
       </x:c>
       <x:c r="HC5" s="2" t="str">
-        <x:v>06/13(土)</x:v>
+        <x:v>06/14(日)</x:v>
       </x:c>
       <x:c r="HD5" s="2" t="str">
-        <x:v>06/14(日)</x:v>
+        <x:v>06/15(月)</x:v>
       </x:c>
       <x:c r="HE5" s="2" t="str">
-        <x:v>06/14(日)</x:v>
+        <x:v>06/15(月)</x:v>
       </x:c>
       <x:c r="HF5" s="2" t="str">
-        <x:v>06/14(日)</x:v>
+        <x:v>06/15(月)</x:v>
       </x:c>
       <x:c r="HG5" s="2" t="str">
-        <x:v>06/15(月)</x:v>
+        <x:v>06/16(火)</x:v>
       </x:c>
       <x:c r="HH5" s="2" t="str">
-        <x:v>06/15(月)</x:v>
+        <x:v>06/16(火)</x:v>
       </x:c>
       <x:c r="HI5" s="2" t="str">
-        <x:v>06/15(月)</x:v>
+        <x:v>06/16(火)</x:v>
       </x:c>
       <x:c r="HJ5" s="2" t="str">
-        <x:v>06/16(火)</x:v>
+        <x:v>06/17(水)</x:v>
       </x:c>
       <x:c r="HK5" s="2" t="str">
-        <x:v>06/16(火)</x:v>
+        <x:v>06/17(水)</x:v>
       </x:c>
       <x:c r="HL5" s="2" t="str">
-        <x:v>06/16(火)</x:v>
+        <x:v>06/17(水)</x:v>
       </x:c>
       <x:c r="HM5" s="2" t="str">
-        <x:v>06/17(水)</x:v>
+        <x:v>06/18(木)</x:v>
       </x:c>
       <x:c r="HN5" s="2" t="str">
-        <x:v>06/17(水)</x:v>
+        <x:v>06/18(木)</x:v>
       </x:c>
       <x:c r="HO5" s="2" t="str">
-        <x:v>06/17(水)</x:v>
+        <x:v>06/18(木)</x:v>
       </x:c>
       <x:c r="HP5" s="2" t="str">
-        <x:v>06/18(木)</x:v>
+        <x:v>06/19(金)</x:v>
       </x:c>
       <x:c r="HQ5" s="2" t="str">
-        <x:v>06/18(木)</x:v>
+        <x:v>06/19(金)</x:v>
       </x:c>
       <x:c r="HR5" s="2" t="str">
-        <x:v>06/18(木)</x:v>
+        <x:v>06/19(金)</x:v>
       </x:c>
       <x:c r="HS5" s="2" t="str">
-        <x:v>06/19(金)</x:v>
+        <x:v>06/20(土)</x:v>
       </x:c>
       <x:c r="HT5" s="2" t="str">
-        <x:v>06/19(金)</x:v>
+        <x:v>06/20(土)</x:v>
       </x:c>
       <x:c r="HU5" s="2" t="str">
-        <x:v>06/19(金)</x:v>
+        <x:v>06/20(土)</x:v>
       </x:c>
       <x:c r="HV5" s="2" t="str">
-        <x:v>06/20(土)</x:v>
+        <x:v>06/21(日)</x:v>
       </x:c>
       <x:c r="HW5" s="2" t="str">
-        <x:v>06/20(土)</x:v>
+        <x:v>06/21(日)</x:v>
       </x:c>
       <x:c r="HX5" s="2" t="str">
-        <x:v>06/20(土)</x:v>
+        <x:v>06/21(日)</x:v>
       </x:c>
       <x:c r="HY5" s="2" t="str">
-        <x:v>06/21(日)</x:v>
+        <x:v>06/22(月)</x:v>
       </x:c>
       <x:c r="HZ5" s="2" t="str">
-        <x:v>06/21(日)</x:v>
+        <x:v>06/22(月)</x:v>
       </x:c>
       <x:c r="IA5" s="2" t="str">
-        <x:v>06/21(日)</x:v>
+        <x:v>06/22(月)</x:v>
       </x:c>
       <x:c r="IB5" s="2" t="str">
-        <x:v>06/22(月)</x:v>
+        <x:v>06/23(火)</x:v>
       </x:c>
       <x:c r="IC5" s="2" t="str">
-        <x:v>06/22(月)</x:v>
+        <x:v>06/23(火)</x:v>
       </x:c>
       <x:c r="ID5" s="2" t="str">
-        <x:v>06/22(月)</x:v>
+        <x:v>06/23(火)</x:v>
       </x:c>
       <x:c r="IE5" s="2" t="str">
-        <x:v>06/23(火)</x:v>
+        <x:v>06/24(水)</x:v>
       </x:c>
       <x:c r="IF5" s="2" t="str">
-        <x:v>06/23(火)</x:v>
+        <x:v>06/24(水)</x:v>
       </x:c>
       <x:c r="IG5" s="2" t="str">
-        <x:v>06/23(火)</x:v>
+        <x:v>06/24(水)</x:v>
       </x:c>
       <x:c r="IH5" s="2" t="str">
-        <x:v>06/24(水)</x:v>
+        <x:v>06/25(木)</x:v>
       </x:c>
       <x:c r="II5" s="2" t="str">
-        <x:v>06/24(水)</x:v>
+        <x:v>06/25(木)</x:v>
       </x:c>
       <x:c r="IJ5" s="2" t="str">
-        <x:v>06/24(水)</x:v>
+        <x:v>06/25(木)</x:v>
       </x:c>
       <x:c r="IK5" s="2" t="str">
-        <x:v>06/25(木)</x:v>
+        <x:v>06/26(金)</x:v>
       </x:c>
       <x:c r="IL5" s="2" t="str">
-        <x:v>06/25(木)</x:v>
+        <x:v>06/26(金)</x:v>
       </x:c>
       <x:c r="IM5" s="2" t="str">
-        <x:v>06/25(木)</x:v>
+        <x:v>06/26(金)</x:v>
       </x:c>
       <x:c r="IN5" s="2" t="str">
-        <x:v>06/26(金)</x:v>
+        <x:v>06/27(土)</x:v>
       </x:c>
       <x:c r="IO5" s="2" t="str">
-        <x:v>06/26(金)</x:v>
+        <x:v>06/27(土)</x:v>
       </x:c>
       <x:c r="IP5" s="2" t="str">
-        <x:v>06/26(金)</x:v>
+        <x:v>06/27(土)</x:v>
       </x:c>
       <x:c r="IQ5" s="2" t="str">
-        <x:v>06/27(土)</x:v>
+        <x:v>06/28(日)</x:v>
       </x:c>
       <x:c r="IR5" s="2" t="str">
-        <x:v>06/27(土)</x:v>
+        <x:v>06/28(日)</x:v>
       </x:c>
       <x:c r="IS5" s="2" t="str">
-        <x:v>06/27(土)</x:v>
+        <x:v>06/28(日)</x:v>
       </x:c>
       <x:c r="IT5" s="2" t="str">
-        <x:v>06/28(日)</x:v>
+        <x:v>06/29(月)</x:v>
       </x:c>
       <x:c r="IU5" s="2" t="str">
-        <x:v>06/28(日)</x:v>
+        <x:v>06/29(月)</x:v>
       </x:c>
       <x:c r="IV5" s="2" t="str">
-        <x:v>06/28(日)</x:v>
+        <x:v>06/29(月)</x:v>
       </x:c>
       <x:c r="IW5" s="2" t="str">
-        <x:v>06/29(月)</x:v>
+        <x:v>06/30(火)</x:v>
       </x:c>
       <x:c r="IX5" s="2" t="str">
-        <x:v>06/29(月)</x:v>
+        <x:v>06/30(火)</x:v>
       </x:c>
       <x:c r="IY5" s="2" t="str">
-        <x:v>06/29(月)</x:v>
+        <x:v>06/30(火)</x:v>
       </x:c>
       <x:c r="IZ5" s="2" t="str">
-        <x:v>06/30(火)</x:v>
+        <x:v>07/01(水)</x:v>
       </x:c>
       <x:c r="JA5" s="2" t="str">
-        <x:v>06/30(火)</x:v>
+        <x:v>07/01(水)</x:v>
       </x:c>
       <x:c r="JB5" s="2" t="str">
-        <x:v>06/30(火)</x:v>
+        <x:v>07/01(水)</x:v>
       </x:c>
       <x:c r="JC5" s="2" t="str">
-        <x:v>07/01(水)</x:v>
+        <x:v>07/02(木)</x:v>
       </x:c>
       <x:c r="JD5" s="2" t="str">
-        <x:v>07/01(水)</x:v>
+        <x:v>07/02(木)</x:v>
       </x:c>
       <x:c r="JE5" s="2" t="str">
-        <x:v>07/01(水)</x:v>
+        <x:v>07/02(木)</x:v>
       </x:c>
       <x:c r="JF5" s="2" t="str">
-        <x:v>07/02(木)</x:v>
+        <x:v>07/03(金)</x:v>
       </x:c>
       <x:c r="JG5" s="2" t="str">
-        <x:v>07/02(木)</x:v>
+        <x:v>07/03(金)</x:v>
       </x:c>
       <x:c r="JH5" s="2" t="str">
-        <x:v>07/02(木)</x:v>
+        <x:v>07/03(金)</x:v>
       </x:c>
       <x:c r="JI5" s="2" t="str">
-        <x:v>07/03(金)</x:v>
+        <x:v>07/04(土)</x:v>
       </x:c>
       <x:c r="JJ5" s="2" t="str">
-        <x:v>07/03(金)</x:v>
+        <x:v>07/04(土)</x:v>
       </x:c>
       <x:c r="JK5" s="2" t="str">
-        <x:v>07/03(金)</x:v>
+        <x:v>07/04(土)</x:v>
       </x:c>
       <x:c r="JL5" s="2" t="str">
-        <x:v>07/04(土)</x:v>
+        <x:v>07/05(日)</x:v>
       </x:c>
       <x:c r="JM5" s="2" t="str">
-        <x:v>07/04(土)</x:v>
+        <x:v>07/05(日)</x:v>
       </x:c>
       <x:c r="JN5" s="2" t="str">
-        <x:v>07/04(土)</x:v>
+        <x:v>07/05(日)</x:v>
       </x:c>
       <x:c r="JO5" s="2" t="str">
-        <x:v>07/05(日)</x:v>
+        <x:v>07/06(月)</x:v>
       </x:c>
       <x:c r="JP5" s="2" t="str">
-        <x:v>07/05(日)</x:v>
+        <x:v>07/06(月)</x:v>
       </x:c>
       <x:c r="JQ5" s="2" t="str">
-        <x:v>07/05(日)</x:v>
+        <x:v>07/06(月)</x:v>
       </x:c>
       <x:c r="JR5" s="2" t="str">
-        <x:v>07/06(月)</x:v>
+        <x:v>07/07(火)</x:v>
       </x:c>
       <x:c r="JS5" s="2" t="str">
-        <x:v>07/06(月)</x:v>
+        <x:v>07/07(火)</x:v>
       </x:c>
       <x:c r="JT5" s="2" t="str">
-        <x:v>07/06(月)</x:v>
+        <x:v>07/07(火)</x:v>
       </x:c>
       <x:c r="JU5" s="2" t="str">
-        <x:v>07/07(火)</x:v>
+        <x:v>07/08(水)</x:v>
       </x:c>
       <x:c r="JV5" s="2" t="str">
-        <x:v>07/07(火)</x:v>
+        <x:v>07/08(水)</x:v>
       </x:c>
       <x:c r="JW5" s="2" t="str">
-        <x:v>07/07(火)</x:v>
+        <x:v>07/08(水)</x:v>
       </x:c>
       <x:c r="JX5" s="2" t="str">
-        <x:v>07/08(水)</x:v>
+        <x:v>07/09(木)</x:v>
       </x:c>
       <x:c r="JY5" s="2" t="str">
-        <x:v>07/08(水)</x:v>
+        <x:v>07/09(木)</x:v>
       </x:c>
       <x:c r="JZ5" s="2" t="str">
-        <x:v>07/08(水)</x:v>
+        <x:v>07/09(木)</x:v>
       </x:c>
       <x:c r="KA5" s="2" t="str">
-        <x:v>07/09(木)</x:v>
+        <x:v>07/10(金)</x:v>
       </x:c>
       <x:c r="KB5" s="2" t="str">
-        <x:v>07/09(木)</x:v>
+        <x:v>07/10(金)</x:v>
       </x:c>
       <x:c r="KC5" s="2" t="str">
-        <x:v>07/09(木)</x:v>
+        <x:v>07/10(金)</x:v>
       </x:c>
       <x:c r="KD5" s="2" t="str">
-        <x:v>07/10(金)</x:v>
+        <x:v>07/11(土)</x:v>
       </x:c>
       <x:c r="KE5" s="2" t="str">
-        <x:v>07/10(金)</x:v>
+        <x:v>07/11(土)</x:v>
       </x:c>
       <x:c r="KF5" s="2" t="str">
-        <x:v>07/10(金)</x:v>
+        <x:v>07/11(土)</x:v>
       </x:c>
       <x:c r="KG5" s="2" t="str">
-        <x:v>07/11(土)</x:v>
+        <x:v>07/12(日)</x:v>
       </x:c>
       <x:c r="KH5" s="2" t="str">
-        <x:v>07/11(土)</x:v>
+        <x:v>07/12(日)</x:v>
       </x:c>
       <x:c r="KI5" s="2" t="str">
-        <x:v>07/11(土)</x:v>
+        <x:v>07/12(日)</x:v>
       </x:c>
       <x:c r="KJ5" s="2" t="str">
-        <x:v>07/12(日)</x:v>
+        <x:v>07/13(月)</x:v>
       </x:c>
       <x:c r="KK5" s="2" t="str">
-        <x:v>07/12(日)</x:v>
+        <x:v>07/13(月)</x:v>
       </x:c>
       <x:c r="KL5" s="2" t="str">
-        <x:v>07/12(日)</x:v>
+        <x:v>07/13(月)</x:v>
       </x:c>
       <x:c r="KM5" s="2" t="str">
-        <x:v>07/13(月)</x:v>
+        <x:v>07/14(火)</x:v>
       </x:c>
       <x:c r="KN5" s="2" t="str">
-        <x:v>07/13(月)</x:v>
+        <x:v>07/14(火)</x:v>
       </x:c>
       <x:c r="KO5" s="2" t="str">
-        <x:v>07/13(月)</x:v>
+        <x:v>07/14(火)</x:v>
       </x:c>
       <x:c r="KP5" s="2" t="str">
-        <x:v>07/14(火)</x:v>
+        <x:v>07/15(水)</x:v>
       </x:c>
       <x:c r="KQ5" s="2" t="str">
-        <x:v>07/14(火)</x:v>
+        <x:v>07/15(水)</x:v>
       </x:c>
       <x:c r="KR5" s="2" t="str">
-        <x:v>07/14(火)</x:v>
+        <x:v>07/15(水)</x:v>
       </x:c>
       <x:c r="KS5" s="2" t="str">
-        <x:v>07/15(水)</x:v>
+        <x:v>07/16(木)</x:v>
       </x:c>
       <x:c r="KT5" s="2" t="str">
-        <x:v>07/15(水)</x:v>
+        <x:v>07/16(木)</x:v>
       </x:c>
       <x:c r="KU5" s="2" t="str">
-        <x:v>07/15(水)</x:v>
+        <x:v>07/16(木)</x:v>
       </x:c>
       <x:c r="KV5" s="2" t="str">
-        <x:v>07/16(木)</x:v>
+        <x:v>07/17(金)</x:v>
       </x:c>
       <x:c r="KW5" s="2" t="str">
-        <x:v>07/16(木)</x:v>
+        <x:v>07/17(金)</x:v>
       </x:c>
       <x:c r="KX5" s="2" t="str">
-        <x:v>07/16(木)</x:v>
+        <x:v>07/17(金)</x:v>
       </x:c>
       <x:c r="KY5" s="2" t="str">
-        <x:v>07/17(金)</x:v>
+        <x:v>07/18(土)</x:v>
       </x:c>
       <x:c r="KZ5" s="2" t="str">
-        <x:v>07/17(金)</x:v>
+        <x:v>07/18(土)</x:v>
       </x:c>
       <x:c r="LA5" s="2" t="str">
-        <x:v>07/17(金)</x:v>
+        <x:v>07/18(土)</x:v>
       </x:c>
       <x:c r="LB5" s="2" t="str">
-        <x:v>07/18(土)</x:v>
+        <x:v>07/19(日)</x:v>
       </x:c>
       <x:c r="LC5" s="2" t="str">
-        <x:v>07/18(土)</x:v>
+        <x:v>07/19(日)</x:v>
       </x:c>
       <x:c r="LD5" s="2" t="str">
-        <x:v>07/18(土)</x:v>
+        <x:v>07/19(日)</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2739,40 +2739,40 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EA7" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2000.0000</x:v>
       </x:c>
       <x:c r="EB7" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EC7" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.0700</x:v>
       </x:c>
       <x:c r="ED7" s="6" t="n">
-        <x:v>2000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EE7" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EF7" s="8" t="n">
-        <x:v>2.0700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG7" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6000.0000</x:v>
       </x:c>
       <x:c r="EH7" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EI7" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6.2000</x:v>
       </x:c>
       <x:c r="EJ7" s="6" t="n">
-        <x:v>6000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EK7" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EL7" s="8" t="n">
-        <x:v>6.2000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM7" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -3716,22 +3716,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ8" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>200.0000</x:v>
       </x:c>
       <x:c r="EK8" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EL8" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.2100</x:v>
       </x:c>
       <x:c r="EM8" s="6" t="n">
-        <x:v>200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN8" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EO8" s="8" t="n">
-        <x:v>0.2100</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP8" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -4666,22 +4666,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ9" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6000.0000</x:v>
       </x:c>
       <x:c r="EK9" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EL9" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6.2000</x:v>
       </x:c>
       <x:c r="EM9" s="6" t="n">
-        <x:v>6000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN9" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EO9" s="8" t="n">
-        <x:v>6.2000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP9" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -4702,22 +4702,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV9" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2000.0000</x:v>
       </x:c>
       <x:c r="EW9" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EX9" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.0700</x:v>
       </x:c>
       <x:c r="EY9" s="6" t="n">
-        <x:v>2000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EZ9" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FA9" s="8" t="n">
-        <x:v>2.0700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB9" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -5652,22 +5652,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV10" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>400.0000</x:v>
       </x:c>
       <x:c r="EW10" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EX10" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.4100</x:v>
       </x:c>
       <x:c r="EY10" s="6" t="n">
-        <x:v>400.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EZ10" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FA10" s="8" t="n">
-        <x:v>0.4100</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB10" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -6602,22 +6602,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV11" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5000.0000</x:v>
       </x:c>
       <x:c r="EW11" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EX11" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5.1700</x:v>
       </x:c>
       <x:c r="EY11" s="6" t="n">
-        <x:v>5000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EZ11" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FA11" s="8" t="n">
-        <x:v>5.1700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB11" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -7624,22 +7624,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FT12" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1155.0000</x:v>
       </x:c>
       <x:c r="FU12" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FV12" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.1900</x:v>
       </x:c>
       <x:c r="FW12" s="6" t="n">
-        <x:v>1155.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FX12" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FY12" s="8" t="n">
-        <x:v>1.1900</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FZ12" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -8529,22 +8529,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FE13" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>9000.0000</x:v>
       </x:c>
       <x:c r="FF13" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="FG13" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>8.3100</x:v>
       </x:c>
       <x:c r="FH13" s="6" t="n">
-        <x:v>9000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FI13" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="FJ13" s="8" t="n">
-        <x:v>8.3100</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FK13" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -9470,22 +9470,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB14" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6000.0000</x:v>
       </x:c>
       <x:c r="FC14" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="FD14" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5.5400</x:v>
       </x:c>
       <x:c r="FE14" s="6" t="n">
-        <x:v>6000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FF14" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="FG14" s="8" t="n">
-        <x:v>5.5400</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FH14" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -9997,7 +9997,7 @@
         <x:v>400.0000</x:v>
       </x:c>
       <x:c r="Q15" s="8" t="n">
-        <x:v>80.0000</x:v>
+        <x:v>397.0000</x:v>
       </x:c>
       <x:c r="R15" s="1" t="str">
         <x:v>分割,スリット,EC</x:v>
@@ -10063,7 +10063,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AM15" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>20.0000</x:v>
       </x:c>
       <x:c r="AN15" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -10348,22 +10348,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ED15" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>20.0000</x:v>
       </x:c>
       <x:c r="EE15" s="8" t="n">
         <x:v>18.0200</x:v>
       </x:c>
       <x:c r="EF15" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.0200</x:v>
       </x:c>
       <x:c r="EG15" s="6" t="n">
-        <x:v>20.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EH15" s="8" t="n">
         <x:v>18.0200</x:v>
       </x:c>
       <x:c r="EI15" s="8" t="n">
-        <x:v>0.0200</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ15" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -11013,7 +11013,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AM16" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1500.0000</x:v>
       </x:c>
       <x:c r="AN16" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -11298,22 +11298,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ED16" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1500.0000</x:v>
       </x:c>
       <x:c r="EE16" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EF16" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.3800</x:v>
       </x:c>
       <x:c r="EG16" s="6" t="n">
-        <x:v>1500.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EH16" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EI16" s="8" t="n">
-        <x:v>1.3800</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ16" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -12203,22 +12203,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DO17" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4200.0000</x:v>
       </x:c>
       <x:c r="DP17" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="DQ17" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3.8800</x:v>
       </x:c>
       <x:c r="DR17" s="6" t="n">
-        <x:v>4200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DS17" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="DT17" s="8" t="n">
-        <x:v>3.8800</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DU17" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -12230,22 +12230,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DX17" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3900.0000</x:v>
       </x:c>
       <x:c r="DY17" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="DZ17" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3.6000</x:v>
       </x:c>
       <x:c r="EA17" s="6" t="n">
-        <x:v>3900.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EB17" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EC17" s="8" t="n">
-        <x:v>3.6000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ED17" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -12913,7 +12913,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AM18" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>800.0000</x:v>
       </x:c>
       <x:c r="AN18" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -13198,22 +13198,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ED18" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>800.0000</x:v>
       </x:c>
       <x:c r="EE18" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EF18" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.7400</x:v>
       </x:c>
       <x:c r="EG18" s="6" t="n">
-        <x:v>800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EH18" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EI18" s="8" t="n">
-        <x:v>0.7400</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ18" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -13863,7 +13863,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AM19" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1000.0000</x:v>
       </x:c>
       <x:c r="AN19" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -14148,22 +14148,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ED19" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1000.0000</x:v>
       </x:c>
       <x:c r="EE19" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EF19" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.9200</x:v>
       </x:c>
       <x:c r="EG19" s="6" t="n">
-        <x:v>1000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EH19" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EI19" s="8" t="n">
-        <x:v>0.9200</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ19" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -15143,22 +15143,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES20" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>250.0000</x:v>
       </x:c>
       <x:c r="ET20" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EU20" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.2300</x:v>
       </x:c>
       <x:c r="EV20" s="6" t="n">
-        <x:v>250.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EW20" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EX20" s="8" t="n">
-        <x:v>0.2300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY20" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -16093,22 +16093,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES21" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>400.0000</x:v>
       </x:c>
       <x:c r="ET21" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EU21" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.3700</x:v>
       </x:c>
       <x:c r="EV21" s="6" t="n">
-        <x:v>400.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EW21" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EX21" s="8" t="n">
-        <x:v>0.3700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY21" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -17043,22 +17043,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES22" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>500.0000</x:v>
       </x:c>
       <x:c r="ET22" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EU22" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.4600</x:v>
       </x:c>
       <x:c r="EV22" s="6" t="n">
-        <x:v>500.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EW22" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EX22" s="8" t="n">
-        <x:v>0.4600</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY22" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -17663,7 +17663,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AM23" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2700.0000</x:v>
       </x:c>
       <x:c r="AN23" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -17948,22 +17948,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ED23" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2700.0000</x:v>
       </x:c>
       <x:c r="EE23" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EF23" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.4900</x:v>
       </x:c>
       <x:c r="EG23" s="6" t="n">
-        <x:v>2700.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EH23" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EI23" s="8" t="n">
-        <x:v>2.4900</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ23" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -18613,7 +18613,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AM24" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>7200.0000</x:v>
       </x:c>
       <x:c r="AN24" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -18898,22 +18898,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ED24" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1500.0000</x:v>
       </x:c>
       <x:c r="EE24" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EF24" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.3800</x:v>
       </x:c>
       <x:c r="EG24" s="6" t="n">
-        <x:v>1500.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EH24" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EI24" s="8" t="n">
-        <x:v>1.3800</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ24" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -18943,22 +18943,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES24" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5700.0000</x:v>
       </x:c>
       <x:c r="ET24" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EU24" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5.2600</x:v>
       </x:c>
       <x:c r="EV24" s="6" t="n">
-        <x:v>5700.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EW24" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EX24" s="8" t="n">
-        <x:v>5.2600</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY24" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -19920,22 +19920,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB25" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>20.0000</x:v>
       </x:c>
       <x:c r="FC25" s="8" t="n">
         <x:v>18.0200</x:v>
       </x:c>
       <x:c r="FD25" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.0200</x:v>
       </x:c>
       <x:c r="FE25" s="6" t="n">
-        <x:v>20.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FF25" s="8" t="n">
         <x:v>18.0200</x:v>
       </x:c>
       <x:c r="FG25" s="8" t="n">
-        <x:v>0.0200</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FH25" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -20870,22 +20870,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB26" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4000.0000</x:v>
       </x:c>
       <x:c r="FC26" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="FD26" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3.6900</x:v>
       </x:c>
       <x:c r="FE26" s="6" t="n">
-        <x:v>4000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FF26" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="FG26" s="8" t="n">
-        <x:v>3.6900</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FH26" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -21820,22 +21820,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB27" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>20.0000</x:v>
       </x:c>
       <x:c r="FC27" s="8" t="n">
         <x:v>18.0200</x:v>
       </x:c>
       <x:c r="FD27" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.0200</x:v>
       </x:c>
       <x:c r="FE27" s="6" t="n">
-        <x:v>20.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FF27" s="8" t="n">
         <x:v>18.0200</x:v>
       </x:c>
       <x:c r="FG27" s="8" t="n">
-        <x:v>0.0200</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FH27" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -22770,22 +22770,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB28" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>20.0000</x:v>
       </x:c>
       <x:c r="FC28" s="8" t="n">
         <x:v>18.0200</x:v>
       </x:c>
       <x:c r="FD28" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.0200</x:v>
       </x:c>
       <x:c r="FE28" s="6" t="n">
-        <x:v>20.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FF28" s="8" t="n">
         <x:v>18.0200</x:v>
       </x:c>
       <x:c r="FG28" s="8" t="n">
-        <x:v>0.0200</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FH28" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -23675,22 +23675,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM29" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6000.0000</x:v>
       </x:c>
       <x:c r="EN29" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="EO29" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>9.8800</x:v>
       </x:c>
       <x:c r="EP29" s="6" t="n">
-        <x:v>6000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EQ29" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="ER29" s="8" t="n">
-        <x:v>9.8800</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES29" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -24247,7 +24247,7 @@
         <x:v>400.0000</x:v>
       </x:c>
       <x:c r="Q30" s="8" t="n">
-        <x:v>80.0000</x:v>
+        <x:v>397.0000</x:v>
       </x:c>
       <x:c r="R30" s="1" t="str">
         <x:v>分割,スリット,EC</x:v>
@@ -24589,22 +24589,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EA30" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>60.0000</x:v>
       </x:c>
       <x:c r="EB30" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="EC30" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.1000</x:v>
       </x:c>
       <x:c r="ED30" s="6" t="n">
-        <x:v>60.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EE30" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="EF30" s="8" t="n">
-        <x:v>0.1000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG30" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -25539,22 +25539,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EA31" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1400.0000</x:v>
       </x:c>
       <x:c r="EB31" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="EC31" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.3100</x:v>
       </x:c>
       <x:c r="ED31" s="6" t="n">
-        <x:v>1400.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EE31" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="EF31" s="8" t="n">
-        <x:v>2.3100</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG31" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -26147,7 +26147,7 @@
         <x:v>400.0000</x:v>
       </x:c>
       <x:c r="Q32" s="8" t="n">
-        <x:v>80.0000</x:v>
+        <x:v>397.0000</x:v>
       </x:c>
       <x:c r="R32" s="1" t="str">
         <x:v>分割,スリット,EC</x:v>
@@ -26231,7 +26231,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AS32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="AT32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26240,7 +26240,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AV32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="AW32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26249,7 +26249,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AY32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="AZ32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26258,7 +26258,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BB32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="BC32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26267,7 +26267,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BE32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="BF32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26276,7 +26276,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BH32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="BI32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26285,7 +26285,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BK32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="BL32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26294,7 +26294,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BN32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="BO32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26303,7 +26303,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BQ32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="BR32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26312,7 +26312,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BT32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="BU32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26321,7 +26321,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BW32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="BX32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26330,7 +26330,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BZ32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="CA32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26339,7 +26339,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CC32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="CD32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26348,7 +26348,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CF32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="CG32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26357,7 +26357,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CI32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="CJ32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26366,7 +26366,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CL32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="CM32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26375,7 +26375,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CO32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="CP32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26384,7 +26384,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CR32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="CS32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26393,7 +26393,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CU32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="CV32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26402,7 +26402,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CX32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="CY32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26411,7 +26411,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DA32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="DB32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26420,7 +26420,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DD32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="DE32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26429,7 +26429,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DG32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="DH32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26438,7 +26438,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DJ32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="DK32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26447,7 +26447,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DM32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="DN32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26456,7 +26456,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DP32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="DQ32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26465,7 +26465,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DS32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="DT32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26474,7 +26474,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DV32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="DW32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26483,34 +26483,34 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DY32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="DZ32" s="8" t="n">
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EA32" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>400.0000</x:v>
       </x:c>
       <x:c r="EB32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EC32" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.4400</x:v>
       </x:c>
       <x:c r="ED32" s="6" t="n">
-        <x:v>400.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EE32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EF32" s="8" t="n">
-        <x:v>0.4400</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG32" s="6" t="n">
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EH32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EI32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26519,7 +26519,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EK32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EL32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26528,7 +26528,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EO32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26537,7 +26537,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EQ32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="ER32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26546,7 +26546,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ET32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EU32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26555,7 +26555,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EW32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EX32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26564,7 +26564,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EZ32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FA32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26573,7 +26573,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FC32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FD32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26582,7 +26582,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FF32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FG32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26591,7 +26591,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FI32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FJ32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26600,7 +26600,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FL32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FM32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26609,7 +26609,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FO32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FP32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26618,7 +26618,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FR32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FS32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26627,7 +26627,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FU32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FV32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26636,7 +26636,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FX32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FY32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26645,7 +26645,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GA32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="GB32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26654,7 +26654,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GD32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="GE32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26663,7 +26663,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GG32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="GH32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26672,7 +26672,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GJ32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="GK32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26681,7 +26681,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GM32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="GN32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26690,7 +26690,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GP32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="GQ32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26699,7 +26699,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GS32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="GT32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26708,7 +26708,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GV32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="GW32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26717,7 +26717,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GY32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="GZ32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26726,7 +26726,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HB32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="HC32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26735,7 +26735,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HE32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="HF32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26744,7 +26744,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HH32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="HI32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26753,7 +26753,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HK32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="HL32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26762,7 +26762,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HN32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="HO32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26771,7 +26771,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HQ32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="HR32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26780,7 +26780,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HT32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="HU32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26789,7 +26789,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HW32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="HX32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26798,7 +26798,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HZ32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="IA32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26807,7 +26807,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="IC32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="ID32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26816,7 +26816,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="IF32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="IG32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26825,7 +26825,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="II32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="IJ32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26834,7 +26834,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="IL32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="IM32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26843,7 +26843,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="IO32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="IP32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26852,7 +26852,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="IR32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="IS32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26861,7 +26861,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="IU32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="IV32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26870,7 +26870,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="IX32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="IY32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26879,7 +26879,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JA32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="JB32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26888,7 +26888,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JD32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="JE32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26897,7 +26897,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JG32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="JH32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26906,7 +26906,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JJ32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="JK32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26915,7 +26915,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JM32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="JN32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26924,7 +26924,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JP32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="JQ32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26933,7 +26933,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JS32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="JT32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26942,7 +26942,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JV32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="JW32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26951,7 +26951,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JY32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="JZ32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26960,7 +26960,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KB32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="KC32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26969,7 +26969,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KE32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="KF32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26978,7 +26978,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KH32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="KI32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26987,7 +26987,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KK32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="KL32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -26996,7 +26996,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KN32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="KO32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -27005,7 +27005,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KQ32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="KR32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -27014,7 +27014,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KT32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="KU32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -27023,7 +27023,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KW32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="KX32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -27032,7 +27032,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KZ32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="LA32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -27041,7 +27041,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="LC32" s="8" t="n">
-        <x:v>15.0100</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="LD32" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -27160,10 +27160,10 @@
         <x:v>760.0000</x:v>
       </x:c>
       <x:c r="AL33" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>200.0000</x:v>
       </x:c>
       <x:c r="AM33" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>560.0000</x:v>
       </x:c>
       <x:c r="AN33" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -27448,22 +27448,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ED33" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>760.0000</x:v>
       </x:c>
       <x:c r="EE33" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="EF33" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.2500</x:v>
       </x:c>
       <x:c r="EG33" s="6" t="n">
-        <x:v>760.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EH33" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="EI33" s="8" t="n">
-        <x:v>1.2500</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ33" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -28113,7 +28113,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AM34" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1000.0000</x:v>
       </x:c>
       <x:c r="AN34" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -28398,22 +28398,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ED34" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1000.0000</x:v>
       </x:c>
       <x:c r="EE34" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EF34" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.1100</x:v>
       </x:c>
       <x:c r="EG34" s="6" t="n">
-        <x:v>1000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EH34" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EI34" s="8" t="n">
-        <x:v>1.1100</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ34" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -29366,22 +29366,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ35" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>800.0000</x:v>
       </x:c>
       <x:c r="EK35" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EL35" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.8900</x:v>
       </x:c>
       <x:c r="EM35" s="6" t="n">
-        <x:v>800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN35" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EO35" s="8" t="n">
-        <x:v>0.8900</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP35" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -30013,7 +30013,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AM36" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>800.0000</x:v>
       </x:c>
       <x:c r="AN36" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -30298,7 +30298,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ED36" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>800.0000</x:v>
       </x:c>
       <x:c r="EE36" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -30307,7 +30307,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG36" s="6" t="n">
-        <x:v>800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EH36" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -31248,22 +31248,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ED37" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>250.0000</x:v>
       </x:c>
       <x:c r="EE37" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="EF37" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.4100</x:v>
       </x:c>
       <x:c r="EG37" s="6" t="n">
-        <x:v>250.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EH37" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="EI37" s="8" t="n">
-        <x:v>0.4100</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ37" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -32198,22 +32198,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ED38" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>400.0000</x:v>
       </x:c>
       <x:c r="EE38" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="EF38" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.6600</x:v>
       </x:c>
       <x:c r="EG38" s="6" t="n">
-        <x:v>400.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EH38" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="EI38" s="8" t="n">
-        <x:v>0.6600</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ38" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -33148,22 +33148,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ED39" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>500.0000</x:v>
       </x:c>
       <x:c r="EE39" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="EF39" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.8200</x:v>
       </x:c>
       <x:c r="EG39" s="6" t="n">
-        <x:v>500.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EH39" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="EI39" s="8" t="n">
-        <x:v>0.8200</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ39" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -34116,22 +34116,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ40" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1000.0000</x:v>
       </x:c>
       <x:c r="EK40" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EL40" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.1100</x:v>
       </x:c>
       <x:c r="EM40" s="6" t="n">
-        <x:v>1000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN40" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EO40" s="8" t="n">
-        <x:v>1.1100</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP40" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -35093,22 +35093,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES41" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>250.0000</x:v>
       </x:c>
       <x:c r="ET41" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EU41" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.2800</x:v>
       </x:c>
       <x:c r="EV41" s="6" t="n">
-        <x:v>250.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EW41" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EX41" s="8" t="n">
-        <x:v>0.2800</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY41" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -35998,22 +35998,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ED42" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>400.0000</x:v>
       </x:c>
       <x:c r="EE42" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EF42" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.4400</x:v>
       </x:c>
       <x:c r="EG42" s="6" t="n">
-        <x:v>400.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EH42" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EI42" s="8" t="n">
-        <x:v>0.4400</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ42" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -37011,22 +37011,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY43" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1600.0000</x:v>
       </x:c>
       <x:c r="EZ43" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FA43" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.7800</x:v>
       </x:c>
       <x:c r="FB43" s="6" t="n">
-        <x:v>1600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FC43" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FD43" s="8" t="n">
-        <x:v>1.7800</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FE43" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -38015,22 +38015,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FQ44" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2000.0000</x:v>
       </x:c>
       <x:c r="FR44" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="FS44" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3.2900</x:v>
       </x:c>
       <x:c r="FT44" s="6" t="n">
-        <x:v>2000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FU44" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="FV44" s="8" t="n">
-        <x:v>3.2900</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FW44" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -38866,22 +38866,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ45" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>20.0000</x:v>
       </x:c>
       <x:c r="EK45" s="8" t="n">
         <x:v>10.1000</x:v>
       </x:c>
       <x:c r="EL45" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.0300</x:v>
       </x:c>
       <x:c r="EM45" s="6" t="n">
-        <x:v>20.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN45" s="8" t="n">
         <x:v>10.1000</x:v>
       </x:c>
       <x:c r="EO45" s="8" t="n">
-        <x:v>0.0300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP45" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -39861,31 +39861,31 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY46" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1500.0000</x:v>
       </x:c>
       <x:c r="EZ46" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="FA46" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.4700</x:v>
       </x:c>
       <x:c r="FB46" s="6" t="n">
-        <x:v>1500.0000</x:v>
+        <x:v>4500.0000</x:v>
       </x:c>
       <x:c r="FC46" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="FD46" s="8" t="n">
-        <x:v>2.4700</x:v>
+        <x:v>7.4100</x:v>
       </x:c>
       <x:c r="FE46" s="6" t="n">
-        <x:v>4500.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FF46" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="FG46" s="8" t="n">
-        <x:v>7.4100</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FH46" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -40766,22 +40766,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ47" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>91.0000</x:v>
       </x:c>
       <x:c r="EK47" s="8" t="n">
         <x:v>15.0300</x:v>
       </x:c>
       <x:c r="EL47" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.1000</x:v>
       </x:c>
       <x:c r="EM47" s="6" t="n">
-        <x:v>91.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN47" s="8" t="n">
         <x:v>15.0300</x:v>
       </x:c>
       <x:c r="EO47" s="8" t="n">
-        <x:v>0.1000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP47" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -41716,22 +41716,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ48" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>180.0000</x:v>
       </x:c>
       <x:c r="EK48" s="8" t="n">
         <x:v>15.0400</x:v>
       </x:c>
       <x:c r="EL48" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.2000</x:v>
       </x:c>
       <x:c r="EM48" s="6" t="n">
-        <x:v>180.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN48" s="8" t="n">
         <x:v>15.0400</x:v>
       </x:c>
       <x:c r="EO48" s="8" t="n">
-        <x:v>0.2000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP48" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -42666,22 +42666,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ49" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>271.0000</x:v>
       </x:c>
       <x:c r="EK49" s="8" t="n">
         <x:v>15.0400</x:v>
       </x:c>
       <x:c r="EL49" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.3000</x:v>
       </x:c>
       <x:c r="EM49" s="6" t="n">
-        <x:v>271.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN49" s="8" t="n">
         <x:v>15.0400</x:v>
       </x:c>
       <x:c r="EO49" s="8" t="n">
-        <x:v>0.3000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP49" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -43661,31 +43661,31 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY50" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3000.0000</x:v>
       </x:c>
       <x:c r="EZ50" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FA50" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3.3300</x:v>
       </x:c>
       <x:c r="FB50" s="6" t="n">
-        <x:v>3000.0000</x:v>
+        <x:v>9000.0000</x:v>
       </x:c>
       <x:c r="FC50" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FD50" s="8" t="n">
-        <x:v>3.3300</x:v>
+        <x:v>10.0000</x:v>
       </x:c>
       <x:c r="FE50" s="6" t="n">
-        <x:v>9000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FF50" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FG50" s="8" t="n">
-        <x:v>10.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FH50" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -44260,7 +44260,7 @@
         <x:v>1400.0000</x:v>
       </x:c>
       <x:c r="AL51" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1400.0000</x:v>
       </x:c>
       <x:c r="AM51" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -44548,22 +44548,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ED51" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1400.0000</x:v>
       </x:c>
       <x:c r="EE51" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EF51" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.9300</x:v>
       </x:c>
       <x:c r="EG51" s="6" t="n">
-        <x:v>1400.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EH51" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EI51" s="8" t="n">
-        <x:v>0.9300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ51" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -45498,22 +45498,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ED52" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6300.0000</x:v>
       </x:c>
       <x:c r="EE52" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EF52" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4.2000</x:v>
       </x:c>
       <x:c r="EG52" s="6" t="n">
-        <x:v>6300.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EH52" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EI52" s="8" t="n">
-        <x:v>4.2000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ52" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -46439,22 +46439,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EA53" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>9000.0000</x:v>
       </x:c>
       <x:c r="EB53" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EC53" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6.0000</x:v>
       </x:c>
       <x:c r="ED53" s="6" t="n">
-        <x:v>9000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EE53" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EF53" s="8" t="n">
-        <x:v>6.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG53" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -47113,7 +47113,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AM54" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>9000.0000</x:v>
       </x:c>
       <x:c r="AN54" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -47398,31 +47398,31 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ED54" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1000.0000</x:v>
       </x:c>
       <x:c r="EE54" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EF54" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.6700</x:v>
       </x:c>
       <x:c r="EG54" s="6" t="n">
-        <x:v>1000.0000</x:v>
+        <x:v>8000.0000</x:v>
       </x:c>
       <x:c r="EH54" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EI54" s="8" t="n">
-        <x:v>0.6700</x:v>
+        <x:v>5.3300</x:v>
       </x:c>
       <x:c r="EJ54" s="6" t="n">
-        <x:v>8000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EK54" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EL54" s="8" t="n">
-        <x:v>5.3300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM54" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -48339,22 +48339,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EA55" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>800.0000</x:v>
       </x:c>
       <x:c r="EB55" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EC55" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.5300</x:v>
       </x:c>
       <x:c r="ED55" s="6" t="n">
-        <x:v>800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EE55" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EF55" s="8" t="n">
-        <x:v>0.5300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG55" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -49307,31 +49307,31 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG56" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3000.0000</x:v>
       </x:c>
       <x:c r="EH56" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EI56" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.0000</x:v>
       </x:c>
       <x:c r="EJ56" s="6" t="n">
-        <x:v>3000.0000</x:v>
+        <x:v>6000.0000</x:v>
       </x:c>
       <x:c r="EK56" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EL56" s="8" t="n">
-        <x:v>2.0000</x:v>
+        <x:v>4.0000</x:v>
       </x:c>
       <x:c r="EM56" s="6" t="n">
-        <x:v>6000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN56" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EO56" s="8" t="n">
-        <x:v>4.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP56" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -50266,22 +50266,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ57" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4000.0000</x:v>
       </x:c>
       <x:c r="EK57" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EL57" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.6700</x:v>
       </x:c>
       <x:c r="EM57" s="6" t="n">
-        <x:v>4000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN57" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EO57" s="8" t="n">
-        <x:v>2.6700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP57" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -50293,22 +50293,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES57" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5000.0000</x:v>
       </x:c>
       <x:c r="ET57" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EU57" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3.3300</x:v>
       </x:c>
       <x:c r="EV57" s="6" t="n">
-        <x:v>5000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EW57" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EX57" s="8" t="n">
-        <x:v>3.3300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY57" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -51252,22 +51252,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV58" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3000.0000</x:v>
       </x:c>
       <x:c r="EW58" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EX58" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.0000</x:v>
       </x:c>
       <x:c r="EY58" s="6" t="n">
-        <x:v>3000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EZ58" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FA58" s="8" t="n">
-        <x:v>2.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB58" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -52193,31 +52193,31 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES59" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6000.0000</x:v>
       </x:c>
       <x:c r="ET59" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EU59" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4.0000</x:v>
       </x:c>
       <x:c r="EV59" s="6" t="n">
-        <x:v>6000.0000</x:v>
+        <x:v>3000.0000</x:v>
       </x:c>
       <x:c r="EW59" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EX59" s="8" t="n">
-        <x:v>4.0000</x:v>
+        <x:v>2.0000</x:v>
       </x:c>
       <x:c r="EY59" s="6" t="n">
-        <x:v>3000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EZ59" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FA59" s="8" t="n">
-        <x:v>2.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB59" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -53170,22 +53170,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB60" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1600.0000</x:v>
       </x:c>
       <x:c r="FC60" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FD60" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.0700</x:v>
       </x:c>
       <x:c r="FE60" s="6" t="n">
-        <x:v>1600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FF60" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FG60" s="8" t="n">
-        <x:v>1.0700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FH60" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -54120,31 +54120,31 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB61" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5000.0000</x:v>
       </x:c>
       <x:c r="FC61" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FD61" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3.3300</x:v>
       </x:c>
       <x:c r="FE61" s="6" t="n">
-        <x:v>5000.0000</x:v>
+        <x:v>2000.0000</x:v>
       </x:c>
       <x:c r="FF61" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FG61" s="8" t="n">
-        <x:v>3.3300</x:v>
+        <x:v>1.3300</x:v>
       </x:c>
       <x:c r="FH61" s="6" t="n">
-        <x:v>2000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FI61" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FJ61" s="8" t="n">
-        <x:v>1.3300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FK61" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -55052,40 +55052,40 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV62" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5000.0000</x:v>
       </x:c>
       <x:c r="EW62" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EX62" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3.3300</x:v>
       </x:c>
       <x:c r="EY62" s="6" t="n">
-        <x:v>5000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EZ62" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FA62" s="8" t="n">
-        <x:v>3.3300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB62" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4000.0000</x:v>
       </x:c>
       <x:c r="FC62" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FD62" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.6700</x:v>
       </x:c>
       <x:c r="FE62" s="6" t="n">
-        <x:v>4000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FF62" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FG62" s="8" t="n">
-        <x:v>2.6700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FH62" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -56011,22 +56011,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY63" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2700.0000</x:v>
       </x:c>
       <x:c r="EZ63" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="FA63" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4.7400</x:v>
       </x:c>
       <x:c r="FB63" s="6" t="n">
-        <x:v>2700.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FC63" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="FD63" s="8" t="n">
-        <x:v>4.7400</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FE63" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -56056,22 +56056,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FN63" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3300.0000</x:v>
       </x:c>
       <x:c r="FO63" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="FP63" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5.7900</x:v>
       </x:c>
       <x:c r="FQ63" s="6" t="n">
-        <x:v>3300.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FR63" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="FS63" s="8" t="n">
-        <x:v>5.7900</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FT63" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -57015,13 +57015,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FQ64" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3600.0000</x:v>
       </x:c>
       <x:c r="FR64" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="FS64" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6.3200</x:v>
       </x:c>
       <x:c r="FT64" s="6" t="n">
         <x:v>3600.0000</x:v>
@@ -57033,31 +57033,31 @@
         <x:v>6.3200</x:v>
       </x:c>
       <x:c r="FW64" s="6" t="n">
-        <x:v>3600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FX64" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="FY64" s="8" t="n">
-        <x:v>6.3200</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FZ64" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1800.0000</x:v>
       </x:c>
       <x:c r="GA64" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="GB64" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3.1600</x:v>
       </x:c>
       <x:c r="GC64" s="6" t="n">
-        <x:v>1800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GD64" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="GE64" s="8" t="n">
-        <x:v>3.1600</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GF64" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -57551,7 +57551,7 @@
         <x:v>46160</x:v>
       </x:c>
       <x:c r="AI65" s="4" t="n">
-        <x:v>46162</x:v>
+        <x:v>46163</x:v>
       </x:c>
       <x:c r="AJ65" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -57830,31 +57830,31 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DX65" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4200.0000</x:v>
       </x:c>
       <x:c r="DY65" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="DZ65" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>7.3700</x:v>
       </x:c>
       <x:c r="EA65" s="6" t="n">
-        <x:v>4200.0000</x:v>
+        <x:v>2700.0000</x:v>
       </x:c>
       <x:c r="EB65" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="EC65" s="8" t="n">
-        <x:v>7.3700</x:v>
+        <x:v>4.7400</x:v>
       </x:c>
       <x:c r="ED65" s="6" t="n">
-        <x:v>2700.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EE65" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="EF65" s="8" t="n">
-        <x:v>4.7400</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG65" s="6" t="n">
         <x:v>1200.0000</x:v>
@@ -58807,22 +58807,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG66" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2700.0000</x:v>
       </x:c>
       <x:c r="EH66" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="EI66" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4.7400</x:v>
       </x:c>
       <x:c r="EJ66" s="6" t="n">
-        <x:v>2700.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EK66" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="EL66" s="8" t="n">
-        <x:v>4.7400</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM66" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -59793,13 +59793,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES67" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3600.0000</x:v>
       </x:c>
       <x:c r="ET67" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="EU67" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6.3200</x:v>
       </x:c>
       <x:c r="EV67" s="6" t="n">
         <x:v>3600.0000</x:v>
@@ -59811,13 +59811,13 @@
         <x:v>6.3200</x:v>
       </x:c>
       <x:c r="EY67" s="6" t="n">
-        <x:v>3600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EZ67" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="FA67" s="8" t="n">
-        <x:v>6.3200</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB67" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -60833,22 +60833,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FW68" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2310.0000</x:v>
       </x:c>
       <x:c r="FX68" s="8" t="n">
         <x:v>20.0000</x:v>
       </x:c>
       <x:c r="FY68" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.9300</x:v>
       </x:c>
       <x:c r="FZ68" s="6" t="n">
-        <x:v>2310.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GA68" s="8" t="n">
         <x:v>20.0000</x:v>
       </x:c>
       <x:c r="GB68" s="8" t="n">
-        <x:v>1.9300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GC68" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -61783,22 +61783,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FW69" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1400.0000</x:v>
       </x:c>
       <x:c r="FX69" s="8" t="n">
         <x:v>20.0000</x:v>
       </x:c>
       <x:c r="FY69" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.1700</x:v>
       </x:c>
       <x:c r="FZ69" s="6" t="n">
-        <x:v>1400.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GA69" s="8" t="n">
         <x:v>20.0000</x:v>
       </x:c>
       <x:c r="GB69" s="8" t="n">
-        <x:v>1.1700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GC69" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -62553,22 +62553,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DO70" s="7" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4200.0000</x:v>
       </x:c>
       <x:c r="DP70" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="DQ70" s="9" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3.8800</x:v>
       </x:c>
       <x:c r="DR70" s="7" t="n">
-        <x:v>4200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DS70" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="DT70" s="9" t="n">
-        <x:v>3.8800</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DU70" s="7" t="n">
         <x:v>0.0000</x:v>
@@ -62580,121 +62580,121 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DX70" s="7" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>8100.0000</x:v>
       </x:c>
       <x:c r="DY70" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="DZ70" s="9" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>10.9700</x:v>
       </x:c>
       <x:c r="EA70" s="7" t="n">
-        <x:v>8100.0000</x:v>
+        <x:v>16360.0000</x:v>
       </x:c>
       <x:c r="EB70" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="EC70" s="9" t="n">
-        <x:v>10.9700</x:v>
+        <x:v>16.1900</x:v>
       </x:c>
       <x:c r="ED70" s="7" t="n">
-        <x:v>16360.0000</x:v>
+        <x:v>20330.0000</x:v>
       </x:c>
       <x:c r="EE70" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="EF70" s="9" t="n">
-        <x:v>16.1900</x:v>
+        <x:v>17.4200</x:v>
       </x:c>
       <x:c r="EG70" s="7" t="n">
-        <x:v>21530.0000</x:v>
+        <x:v>20900.0000</x:v>
       </x:c>
       <x:c r="EH70" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="EI70" s="9" t="n">
-        <x:v>19.5300</x:v>
+        <x:v>20.3800</x:v>
       </x:c>
       <x:c r="EJ70" s="7" t="n">
-        <x:v>19700.0000</x:v>
+        <x:v>18562.0000</x:v>
       </x:c>
       <x:c r="EK70" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="EL70" s="9" t="n">
-        <x:v>18.2700</x:v>
+        <x:v>15.7100</x:v>
       </x:c>
       <x:c r="EM70" s="7" t="n">
-        <x:v>18562.0000</x:v>
+        <x:v>6000.0000</x:v>
       </x:c>
       <x:c r="EN70" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="EO70" s="9" t="n">
-        <x:v>15.7100</x:v>
+        <x:v>9.8800</x:v>
       </x:c>
       <x:c r="EP70" s="7" t="n">
-        <x:v>6000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EQ70" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="ER70" s="9" t="n">
-        <x:v>9.8800</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES70" s="7" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>21700.0000</x:v>
       </x:c>
       <x:c r="ET70" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="EU70" s="9" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>20.2500</x:v>
       </x:c>
       <x:c r="EV70" s="7" t="n">
-        <x:v>21700.0000</x:v>
+        <x:v>22000.0000</x:v>
       </x:c>
       <x:c r="EW70" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="EX70" s="9" t="n">
-        <x:v>20.2500</x:v>
+        <x:v>21.3000</x:v>
       </x:c>
       <x:c r="EY70" s="7" t="n">
-        <x:v>22000.0000</x:v>
+        <x:v>8800.0000</x:v>
       </x:c>
       <x:c r="EZ70" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FA70" s="9" t="n">
-        <x:v>21.3000</x:v>
+        <x:v>12.3200</x:v>
       </x:c>
       <x:c r="FB70" s="7" t="n">
-        <x:v>8800.0000</x:v>
+        <x:v>34160.0000</x:v>
       </x:c>
       <x:c r="FC70" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FD70" s="9" t="n">
-        <x:v>12.3200</x:v>
+        <x:v>33.7700</x:v>
       </x:c>
       <x:c r="FE70" s="7" t="n">
-        <x:v>34160.0000</x:v>
+        <x:v>11000.0000</x:v>
       </x:c>
       <x:c r="FF70" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FG70" s="9" t="n">
-        <x:v>33.7700</x:v>
+        <x:v>9.6400</x:v>
       </x:c>
       <x:c r="FH70" s="7" t="n">
-        <x:v>11000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FI70" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FJ70" s="9" t="n">
-        <x:v>9.6400</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FK70" s="7" t="n">
         <x:v>0.0000</x:v>
@@ -62706,58 +62706,58 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FN70" s="7" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3300.0000</x:v>
       </x:c>
       <x:c r="FO70" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FP70" s="9" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5.7900</x:v>
       </x:c>
       <x:c r="FQ70" s="7" t="n">
-        <x:v>3300.0000</x:v>
+        <x:v>5600.0000</x:v>
       </x:c>
       <x:c r="FR70" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FS70" s="9" t="n">
-        <x:v>5.7900</x:v>
+        <x:v>9.6100</x:v>
       </x:c>
       <x:c r="FT70" s="7" t="n">
-        <x:v>5600.0000</x:v>
+        <x:v>4755.0000</x:v>
       </x:c>
       <x:c r="FU70" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FV70" s="9" t="n">
-        <x:v>9.6100</x:v>
+        <x:v>7.5100</x:v>
       </x:c>
       <x:c r="FW70" s="7" t="n">
-        <x:v>4755.0000</x:v>
+        <x:v>3710.0000</x:v>
       </x:c>
       <x:c r="FX70" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FY70" s="9" t="n">
-        <x:v>7.5100</x:v>
+        <x:v>3.1000</x:v>
       </x:c>
       <x:c r="FZ70" s="7" t="n">
-        <x:v>3710.0000</x:v>
+        <x:v>1800.0000</x:v>
       </x:c>
       <x:c r="GA70" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="GB70" s="9" t="n">
-        <x:v>3.1000</x:v>
+        <x:v>3.1600</x:v>
       </x:c>
       <x:c r="GC70" s="7" t="n">
-        <x:v>1800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GD70" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="GE70" s="9" t="n">
-        <x:v>3.1600</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GF70" s="7" t="n">
         <x:v>0.0000</x:v>

--- a/.pm-ai-cache/network-source/task-input-newest.xlsx
+++ b/.pm-ai-cache/network-source/task-input-newest.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工程別生産計画問合せ問合せ" sheetId="1" r:id="R0b8a1475993f4827"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工程別生産計画問合せ問合せ" sheetId="1" r:id="R4fcf3930dfe7443a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -10,7 +10,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7">
   <x:si>
-    <x:t xml:space="preserve">表示基準日 : 2026年05月23日 </x:t>
+    <x:t xml:space="preserve">表示基準日 : 2026年05月25日 </x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">K </x:t>
@@ -584,823 +584,823 @@
         <x:v/>
       </x:c>
       <x:c r="AR5" s="2" t="str">
-        <x:v>04/23(木)</x:v>
+        <x:v>04/25(土)</x:v>
       </x:c>
       <x:c r="AS5" s="2" t="str">
-        <x:v>04/23(木)</x:v>
+        <x:v>04/25(土)</x:v>
       </x:c>
       <x:c r="AT5" s="2" t="str">
-        <x:v>04/23(木)</x:v>
+        <x:v>04/25(土)</x:v>
       </x:c>
       <x:c r="AU5" s="2" t="str">
-        <x:v>04/24(金)</x:v>
+        <x:v>04/26(日)</x:v>
       </x:c>
       <x:c r="AV5" s="2" t="str">
-        <x:v>04/24(金)</x:v>
+        <x:v>04/26(日)</x:v>
       </x:c>
       <x:c r="AW5" s="2" t="str">
-        <x:v>04/24(金)</x:v>
+        <x:v>04/26(日)</x:v>
       </x:c>
       <x:c r="AX5" s="2" t="str">
-        <x:v>04/25(土)</x:v>
+        <x:v>04/27(月)</x:v>
       </x:c>
       <x:c r="AY5" s="2" t="str">
-        <x:v>04/25(土)</x:v>
+        <x:v>04/27(月)</x:v>
       </x:c>
       <x:c r="AZ5" s="2" t="str">
-        <x:v>04/25(土)</x:v>
+        <x:v>04/27(月)</x:v>
       </x:c>
       <x:c r="BA5" s="2" t="str">
-        <x:v>04/26(日)</x:v>
+        <x:v>04/28(火)</x:v>
       </x:c>
       <x:c r="BB5" s="2" t="str">
-        <x:v>04/26(日)</x:v>
+        <x:v>04/28(火)</x:v>
       </x:c>
       <x:c r="BC5" s="2" t="str">
-        <x:v>04/26(日)</x:v>
+        <x:v>04/28(火)</x:v>
       </x:c>
       <x:c r="BD5" s="2" t="str">
-        <x:v>04/27(月)</x:v>
+        <x:v>04/29(水)</x:v>
       </x:c>
       <x:c r="BE5" s="2" t="str">
-        <x:v>04/27(月)</x:v>
+        <x:v>04/29(水)</x:v>
       </x:c>
       <x:c r="BF5" s="2" t="str">
-        <x:v>04/27(月)</x:v>
+        <x:v>04/29(水)</x:v>
       </x:c>
       <x:c r="BG5" s="2" t="str">
-        <x:v>04/28(火)</x:v>
+        <x:v>04/30(木)</x:v>
       </x:c>
       <x:c r="BH5" s="2" t="str">
-        <x:v>04/28(火)</x:v>
+        <x:v>04/30(木)</x:v>
       </x:c>
       <x:c r="BI5" s="2" t="str">
-        <x:v>04/28(火)</x:v>
+        <x:v>04/30(木)</x:v>
       </x:c>
       <x:c r="BJ5" s="2" t="str">
-        <x:v>04/29(水)</x:v>
+        <x:v>05/01(金)</x:v>
       </x:c>
       <x:c r="BK5" s="2" t="str">
-        <x:v>04/29(水)</x:v>
+        <x:v>05/01(金)</x:v>
       </x:c>
       <x:c r="BL5" s="2" t="str">
-        <x:v>04/29(水)</x:v>
+        <x:v>05/01(金)</x:v>
       </x:c>
       <x:c r="BM5" s="2" t="str">
-        <x:v>04/30(木)</x:v>
+        <x:v>05/02(土)</x:v>
       </x:c>
       <x:c r="BN5" s="2" t="str">
-        <x:v>04/30(木)</x:v>
+        <x:v>05/02(土)</x:v>
       </x:c>
       <x:c r="BO5" s="2" t="str">
-        <x:v>04/30(木)</x:v>
+        <x:v>05/02(土)</x:v>
       </x:c>
       <x:c r="BP5" s="2" t="str">
-        <x:v>05/01(金)</x:v>
+        <x:v>05/03(日)</x:v>
       </x:c>
       <x:c r="BQ5" s="2" t="str">
-        <x:v>05/01(金)</x:v>
+        <x:v>05/03(日)</x:v>
       </x:c>
       <x:c r="BR5" s="2" t="str">
-        <x:v>05/01(金)</x:v>
+        <x:v>05/03(日)</x:v>
       </x:c>
       <x:c r="BS5" s="2" t="str">
-        <x:v>05/02(土)</x:v>
+        <x:v>05/04(月)</x:v>
       </x:c>
       <x:c r="BT5" s="2" t="str">
-        <x:v>05/02(土)</x:v>
+        <x:v>05/04(月)</x:v>
       </x:c>
       <x:c r="BU5" s="2" t="str">
-        <x:v>05/02(土)</x:v>
+        <x:v>05/04(月)</x:v>
       </x:c>
       <x:c r="BV5" s="2" t="str">
-        <x:v>05/03(日)</x:v>
+        <x:v>05/05(火)</x:v>
       </x:c>
       <x:c r="BW5" s="2" t="str">
-        <x:v>05/03(日)</x:v>
+        <x:v>05/05(火)</x:v>
       </x:c>
       <x:c r="BX5" s="2" t="str">
-        <x:v>05/03(日)</x:v>
+        <x:v>05/05(火)</x:v>
       </x:c>
       <x:c r="BY5" s="2" t="str">
-        <x:v>05/04(月)</x:v>
+        <x:v>05/06(水)</x:v>
       </x:c>
       <x:c r="BZ5" s="2" t="str">
-        <x:v>05/04(月)</x:v>
+        <x:v>05/06(水)</x:v>
       </x:c>
       <x:c r="CA5" s="2" t="str">
-        <x:v>05/04(月)</x:v>
+        <x:v>05/06(水)</x:v>
       </x:c>
       <x:c r="CB5" s="2" t="str">
-        <x:v>05/05(火)</x:v>
+        <x:v>05/07(木)</x:v>
       </x:c>
       <x:c r="CC5" s="2" t="str">
-        <x:v>05/05(火)</x:v>
+        <x:v>05/07(木)</x:v>
       </x:c>
       <x:c r="CD5" s="2" t="str">
-        <x:v>05/05(火)</x:v>
+        <x:v>05/07(木)</x:v>
       </x:c>
       <x:c r="CE5" s="2" t="str">
-        <x:v>05/06(水)</x:v>
+        <x:v>05/08(金)</x:v>
       </x:c>
       <x:c r="CF5" s="2" t="str">
-        <x:v>05/06(水)</x:v>
+        <x:v>05/08(金)</x:v>
       </x:c>
       <x:c r="CG5" s="2" t="str">
-        <x:v>05/06(水)</x:v>
+        <x:v>05/08(金)</x:v>
       </x:c>
       <x:c r="CH5" s="2" t="str">
-        <x:v>05/07(木)</x:v>
+        <x:v>05/09(土)</x:v>
       </x:c>
       <x:c r="CI5" s="2" t="str">
-        <x:v>05/07(木)</x:v>
+        <x:v>05/09(土)</x:v>
       </x:c>
       <x:c r="CJ5" s="2" t="str">
-        <x:v>05/07(木)</x:v>
+        <x:v>05/09(土)</x:v>
       </x:c>
       <x:c r="CK5" s="2" t="str">
-        <x:v>05/08(金)</x:v>
+        <x:v>05/10(日)</x:v>
       </x:c>
       <x:c r="CL5" s="2" t="str">
-        <x:v>05/08(金)</x:v>
+        <x:v>05/10(日)</x:v>
       </x:c>
       <x:c r="CM5" s="2" t="str">
-        <x:v>05/08(金)</x:v>
+        <x:v>05/10(日)</x:v>
       </x:c>
       <x:c r="CN5" s="2" t="str">
-        <x:v>05/09(土)</x:v>
+        <x:v>05/11(月)</x:v>
       </x:c>
       <x:c r="CO5" s="2" t="str">
-        <x:v>05/09(土)</x:v>
+        <x:v>05/11(月)</x:v>
       </x:c>
       <x:c r="CP5" s="2" t="str">
-        <x:v>05/09(土)</x:v>
+        <x:v>05/11(月)</x:v>
       </x:c>
       <x:c r="CQ5" s="2" t="str">
-        <x:v>05/10(日)</x:v>
+        <x:v>05/12(火)</x:v>
       </x:c>
       <x:c r="CR5" s="2" t="str">
-        <x:v>05/10(日)</x:v>
+        <x:v>05/12(火)</x:v>
       </x:c>
       <x:c r="CS5" s="2" t="str">
-        <x:v>05/10(日)</x:v>
+        <x:v>05/12(火)</x:v>
       </x:c>
       <x:c r="CT5" s="2" t="str">
-        <x:v>05/11(月)</x:v>
+        <x:v>05/13(水)</x:v>
       </x:c>
       <x:c r="CU5" s="2" t="str">
-        <x:v>05/11(月)</x:v>
+        <x:v>05/13(水)</x:v>
       </x:c>
       <x:c r="CV5" s="2" t="str">
-        <x:v>05/11(月)</x:v>
+        <x:v>05/13(水)</x:v>
       </x:c>
       <x:c r="CW5" s="2" t="str">
-        <x:v>05/12(火)</x:v>
+        <x:v>05/14(木)</x:v>
       </x:c>
       <x:c r="CX5" s="2" t="str">
-        <x:v>05/12(火)</x:v>
+        <x:v>05/14(木)</x:v>
       </x:c>
       <x:c r="CY5" s="2" t="str">
-        <x:v>05/12(火)</x:v>
+        <x:v>05/14(木)</x:v>
       </x:c>
       <x:c r="CZ5" s="2" t="str">
-        <x:v>05/13(水)</x:v>
+        <x:v>05/15(金)</x:v>
       </x:c>
       <x:c r="DA5" s="2" t="str">
-        <x:v>05/13(水)</x:v>
+        <x:v>05/15(金)</x:v>
       </x:c>
       <x:c r="DB5" s="2" t="str">
-        <x:v>05/13(水)</x:v>
+        <x:v>05/15(金)</x:v>
       </x:c>
       <x:c r="DC5" s="2" t="str">
-        <x:v>05/14(木)</x:v>
+        <x:v>05/16(土)</x:v>
       </x:c>
       <x:c r="DD5" s="2" t="str">
-        <x:v>05/14(木)</x:v>
+        <x:v>05/16(土)</x:v>
       </x:c>
       <x:c r="DE5" s="2" t="str">
-        <x:v>05/14(木)</x:v>
+        <x:v>05/16(土)</x:v>
       </x:c>
       <x:c r="DF5" s="2" t="str">
-        <x:v>05/15(金)</x:v>
+        <x:v>05/17(日)</x:v>
       </x:c>
       <x:c r="DG5" s="2" t="str">
-        <x:v>05/15(金)</x:v>
+        <x:v>05/17(日)</x:v>
       </x:c>
       <x:c r="DH5" s="2" t="str">
-        <x:v>05/15(金)</x:v>
+        <x:v>05/17(日)</x:v>
       </x:c>
       <x:c r="DI5" s="2" t="str">
-        <x:v>05/16(土)</x:v>
+        <x:v>05/18(月)</x:v>
       </x:c>
       <x:c r="DJ5" s="2" t="str">
-        <x:v>05/16(土)</x:v>
+        <x:v>05/18(月)</x:v>
       </x:c>
       <x:c r="DK5" s="2" t="str">
-        <x:v>05/16(土)</x:v>
+        <x:v>05/18(月)</x:v>
       </x:c>
       <x:c r="DL5" s="2" t="str">
-        <x:v>05/17(日)</x:v>
+        <x:v>05/19(火)</x:v>
       </x:c>
       <x:c r="DM5" s="2" t="str">
-        <x:v>05/17(日)</x:v>
+        <x:v>05/19(火)</x:v>
       </x:c>
       <x:c r="DN5" s="2" t="str">
-        <x:v>05/17(日)</x:v>
+        <x:v>05/19(火)</x:v>
       </x:c>
       <x:c r="DO5" s="2" t="str">
-        <x:v>05/18(月)</x:v>
+        <x:v>05/20(水)</x:v>
       </x:c>
       <x:c r="DP5" s="2" t="str">
-        <x:v>05/18(月)</x:v>
+        <x:v>05/20(水)</x:v>
       </x:c>
       <x:c r="DQ5" s="2" t="str">
-        <x:v>05/18(月)</x:v>
+        <x:v>05/20(水)</x:v>
       </x:c>
       <x:c r="DR5" s="2" t="str">
-        <x:v>05/19(火)</x:v>
+        <x:v>05/21(木)</x:v>
       </x:c>
       <x:c r="DS5" s="2" t="str">
-        <x:v>05/19(火)</x:v>
+        <x:v>05/21(木)</x:v>
       </x:c>
       <x:c r="DT5" s="2" t="str">
-        <x:v>05/19(火)</x:v>
+        <x:v>05/21(木)</x:v>
       </x:c>
       <x:c r="DU5" s="2" t="str">
-        <x:v>05/20(水)</x:v>
+        <x:v>05/22(金)</x:v>
       </x:c>
       <x:c r="DV5" s="2" t="str">
-        <x:v>05/20(水)</x:v>
+        <x:v>05/22(金)</x:v>
       </x:c>
       <x:c r="DW5" s="2" t="str">
-        <x:v>05/20(水)</x:v>
+        <x:v>05/22(金)</x:v>
       </x:c>
       <x:c r="DX5" s="2" t="str">
-        <x:v>05/21(木)</x:v>
+        <x:v>05/23(土)</x:v>
       </x:c>
       <x:c r="DY5" s="2" t="str">
-        <x:v>05/21(木)</x:v>
+        <x:v>05/23(土)</x:v>
       </x:c>
       <x:c r="DZ5" s="2" t="str">
-        <x:v>05/21(木)</x:v>
+        <x:v>05/23(土)</x:v>
       </x:c>
       <x:c r="EA5" s="2" t="str">
-        <x:v>05/22(金)</x:v>
+        <x:v>05/24(日)</x:v>
       </x:c>
       <x:c r="EB5" s="2" t="str">
-        <x:v>05/22(金)</x:v>
+        <x:v>05/24(日)</x:v>
       </x:c>
       <x:c r="EC5" s="2" t="str">
-        <x:v>05/22(金)</x:v>
+        <x:v>05/24(日)</x:v>
       </x:c>
       <x:c r="ED5" s="2" t="str">
-        <x:v>05/23(土)</x:v>
+        <x:v>05/25(月)</x:v>
       </x:c>
       <x:c r="EE5" s="2" t="str">
-        <x:v>05/23(土)</x:v>
+        <x:v>05/25(月)</x:v>
       </x:c>
       <x:c r="EF5" s="2" t="str">
-        <x:v>05/23(土)</x:v>
+        <x:v>05/25(月)</x:v>
       </x:c>
       <x:c r="EG5" s="2" t="str">
-        <x:v>05/24(日)</x:v>
+        <x:v>05/26(火)</x:v>
       </x:c>
       <x:c r="EH5" s="2" t="str">
-        <x:v>05/24(日)</x:v>
+        <x:v>05/26(火)</x:v>
       </x:c>
       <x:c r="EI5" s="2" t="str">
-        <x:v>05/24(日)</x:v>
+        <x:v>05/26(火)</x:v>
       </x:c>
       <x:c r="EJ5" s="2" t="str">
-        <x:v>05/25(月)</x:v>
+        <x:v>05/27(水)</x:v>
       </x:c>
       <x:c r="EK5" s="2" t="str">
-        <x:v>05/25(月)</x:v>
+        <x:v>05/27(水)</x:v>
       </x:c>
       <x:c r="EL5" s="2" t="str">
-        <x:v>05/25(月)</x:v>
+        <x:v>05/27(水)</x:v>
       </x:c>
       <x:c r="EM5" s="2" t="str">
-        <x:v>05/26(火)</x:v>
+        <x:v>05/28(木)</x:v>
       </x:c>
       <x:c r="EN5" s="2" t="str">
-        <x:v>05/26(火)</x:v>
+        <x:v>05/28(木)</x:v>
       </x:c>
       <x:c r="EO5" s="2" t="str">
-        <x:v>05/26(火)</x:v>
+        <x:v>05/28(木)</x:v>
       </x:c>
       <x:c r="EP5" s="2" t="str">
-        <x:v>05/27(水)</x:v>
+        <x:v>05/29(金)</x:v>
       </x:c>
       <x:c r="EQ5" s="2" t="str">
-        <x:v>05/27(水)</x:v>
+        <x:v>05/29(金)</x:v>
       </x:c>
       <x:c r="ER5" s="2" t="str">
-        <x:v>05/27(水)</x:v>
+        <x:v>05/29(金)</x:v>
       </x:c>
       <x:c r="ES5" s="2" t="str">
-        <x:v>05/28(木)</x:v>
+        <x:v>05/30(土)</x:v>
       </x:c>
       <x:c r="ET5" s="2" t="str">
-        <x:v>05/28(木)</x:v>
+        <x:v>05/30(土)</x:v>
       </x:c>
       <x:c r="EU5" s="2" t="str">
-        <x:v>05/28(木)</x:v>
+        <x:v>05/30(土)</x:v>
       </x:c>
       <x:c r="EV5" s="2" t="str">
-        <x:v>05/29(金)</x:v>
+        <x:v>05/31(日)</x:v>
       </x:c>
       <x:c r="EW5" s="2" t="str">
-        <x:v>05/29(金)</x:v>
+        <x:v>05/31(日)</x:v>
       </x:c>
       <x:c r="EX5" s="2" t="str">
-        <x:v>05/29(金)</x:v>
+        <x:v>05/31(日)</x:v>
       </x:c>
       <x:c r="EY5" s="2" t="str">
-        <x:v>05/30(土)</x:v>
+        <x:v>06/01(月)</x:v>
       </x:c>
       <x:c r="EZ5" s="2" t="str">
-        <x:v>05/30(土)</x:v>
+        <x:v>06/01(月)</x:v>
       </x:c>
       <x:c r="FA5" s="2" t="str">
-        <x:v>05/30(土)</x:v>
+        <x:v>06/01(月)</x:v>
       </x:c>
       <x:c r="FB5" s="2" t="str">
-        <x:v>05/31(日)</x:v>
+        <x:v>06/02(火)</x:v>
       </x:c>
       <x:c r="FC5" s="2" t="str">
-        <x:v>05/31(日)</x:v>
+        <x:v>06/02(火)</x:v>
       </x:c>
       <x:c r="FD5" s="2" t="str">
-        <x:v>05/31(日)</x:v>
+        <x:v>06/02(火)</x:v>
       </x:c>
       <x:c r="FE5" s="2" t="str">
-        <x:v>06/01(月)</x:v>
+        <x:v>06/03(水)</x:v>
       </x:c>
       <x:c r="FF5" s="2" t="str">
-        <x:v>06/01(月)</x:v>
+        <x:v>06/03(水)</x:v>
       </x:c>
       <x:c r="FG5" s="2" t="str">
-        <x:v>06/01(月)</x:v>
+        <x:v>06/03(水)</x:v>
       </x:c>
       <x:c r="FH5" s="2" t="str">
-        <x:v>06/02(火)</x:v>
+        <x:v>06/04(木)</x:v>
       </x:c>
       <x:c r="FI5" s="2" t="str">
-        <x:v>06/02(火)</x:v>
+        <x:v>06/04(木)</x:v>
       </x:c>
       <x:c r="FJ5" s="2" t="str">
-        <x:v>06/02(火)</x:v>
+        <x:v>06/04(木)</x:v>
       </x:c>
       <x:c r="FK5" s="2" t="str">
-        <x:v>06/03(水)</x:v>
+        <x:v>06/05(金)</x:v>
       </x:c>
       <x:c r="FL5" s="2" t="str">
-        <x:v>06/03(水)</x:v>
+        <x:v>06/05(金)</x:v>
       </x:c>
       <x:c r="FM5" s="2" t="str">
-        <x:v>06/03(水)</x:v>
+        <x:v>06/05(金)</x:v>
       </x:c>
       <x:c r="FN5" s="2" t="str">
-        <x:v>06/04(木)</x:v>
+        <x:v>06/06(土)</x:v>
       </x:c>
       <x:c r="FO5" s="2" t="str">
-        <x:v>06/04(木)</x:v>
+        <x:v>06/06(土)</x:v>
       </x:c>
       <x:c r="FP5" s="2" t="str">
-        <x:v>06/04(木)</x:v>
+        <x:v>06/06(土)</x:v>
       </x:c>
       <x:c r="FQ5" s="2" t="str">
-        <x:v>06/05(金)</x:v>
+        <x:v>06/07(日)</x:v>
       </x:c>
       <x:c r="FR5" s="2" t="str">
-        <x:v>06/05(金)</x:v>
+        <x:v>06/07(日)</x:v>
       </x:c>
       <x:c r="FS5" s="2" t="str">
-        <x:v>06/05(金)</x:v>
+        <x:v>06/07(日)</x:v>
       </x:c>
       <x:c r="FT5" s="2" t="str">
-        <x:v>06/06(土)</x:v>
+        <x:v>06/08(月)</x:v>
       </x:c>
       <x:c r="FU5" s="2" t="str">
-        <x:v>06/06(土)</x:v>
+        <x:v>06/08(月)</x:v>
       </x:c>
       <x:c r="FV5" s="2" t="str">
-        <x:v>06/06(土)</x:v>
+        <x:v>06/08(月)</x:v>
       </x:c>
       <x:c r="FW5" s="2" t="str">
-        <x:v>06/07(日)</x:v>
+        <x:v>06/09(火)</x:v>
       </x:c>
       <x:c r="FX5" s="2" t="str">
-        <x:v>06/07(日)</x:v>
+        <x:v>06/09(火)</x:v>
       </x:c>
       <x:c r="FY5" s="2" t="str">
-        <x:v>06/07(日)</x:v>
+        <x:v>06/09(火)</x:v>
       </x:c>
       <x:c r="FZ5" s="2" t="str">
-        <x:v>06/08(月)</x:v>
+        <x:v>06/10(水)</x:v>
       </x:c>
       <x:c r="GA5" s="2" t="str">
-        <x:v>06/08(月)</x:v>
+        <x:v>06/10(水)</x:v>
       </x:c>
       <x:c r="GB5" s="2" t="str">
-        <x:v>06/08(月)</x:v>
+        <x:v>06/10(水)</x:v>
       </x:c>
       <x:c r="GC5" s="2" t="str">
-        <x:v>06/09(火)</x:v>
+        <x:v>06/11(木)</x:v>
       </x:c>
       <x:c r="GD5" s="2" t="str">
-        <x:v>06/09(火)</x:v>
+        <x:v>06/11(木)</x:v>
       </x:c>
       <x:c r="GE5" s="2" t="str">
-        <x:v>06/09(火)</x:v>
+        <x:v>06/11(木)</x:v>
       </x:c>
       <x:c r="GF5" s="2" t="str">
-        <x:v>06/10(水)</x:v>
+        <x:v>06/12(金)</x:v>
       </x:c>
       <x:c r="GG5" s="2" t="str">
-        <x:v>06/10(水)</x:v>
+        <x:v>06/12(金)</x:v>
       </x:c>
       <x:c r="GH5" s="2" t="str">
-        <x:v>06/10(水)</x:v>
+        <x:v>06/12(金)</x:v>
       </x:c>
       <x:c r="GI5" s="2" t="str">
-        <x:v>06/11(木)</x:v>
+        <x:v>06/13(土)</x:v>
       </x:c>
       <x:c r="GJ5" s="2" t="str">
-        <x:v>06/11(木)</x:v>
+        <x:v>06/13(土)</x:v>
       </x:c>
       <x:c r="GK5" s="2" t="str">
-        <x:v>06/11(木)</x:v>
+        <x:v>06/13(土)</x:v>
       </x:c>
       <x:c r="GL5" s="2" t="str">
-        <x:v>06/12(金)</x:v>
+        <x:v>06/14(日)</x:v>
       </x:c>
       <x:c r="GM5" s="2" t="str">
-        <x:v>06/12(金)</x:v>
+        <x:v>06/14(日)</x:v>
       </x:c>
       <x:c r="GN5" s="2" t="str">
-        <x:v>06/12(金)</x:v>
+        <x:v>06/14(日)</x:v>
       </x:c>
       <x:c r="GO5" s="2" t="str">
-        <x:v>06/13(土)</x:v>
+        <x:v>06/15(月)</x:v>
       </x:c>
       <x:c r="GP5" s="2" t="str">
-        <x:v>06/13(土)</x:v>
+        <x:v>06/15(月)</x:v>
       </x:c>
       <x:c r="GQ5" s="2" t="str">
-        <x:v>06/13(土)</x:v>
+        <x:v>06/15(月)</x:v>
       </x:c>
       <x:c r="GR5" s="2" t="str">
-        <x:v>06/14(日)</x:v>
+        <x:v>06/16(火)</x:v>
       </x:c>
       <x:c r="GS5" s="2" t="str">
-        <x:v>06/14(日)</x:v>
+        <x:v>06/16(火)</x:v>
       </x:c>
       <x:c r="GT5" s="2" t="str">
-        <x:v>06/14(日)</x:v>
+        <x:v>06/16(火)</x:v>
       </x:c>
       <x:c r="GU5" s="2" t="str">
-        <x:v>06/15(月)</x:v>
+        <x:v>06/17(水)</x:v>
       </x:c>
       <x:c r="GV5" s="2" t="str">
-        <x:v>06/15(月)</x:v>
+        <x:v>06/17(水)</x:v>
       </x:c>
       <x:c r="GW5" s="2" t="str">
-        <x:v>06/15(月)</x:v>
+        <x:v>06/17(水)</x:v>
       </x:c>
       <x:c r="GX5" s="2" t="str">
-        <x:v>06/16(火)</x:v>
+        <x:v>06/18(木)</x:v>
       </x:c>
       <x:c r="GY5" s="2" t="str">
-        <x:v>06/16(火)</x:v>
+        <x:v>06/18(木)</x:v>
       </x:c>
       <x:c r="GZ5" s="2" t="str">
-        <x:v>06/16(火)</x:v>
+        <x:v>06/18(木)</x:v>
       </x:c>
       <x:c r="HA5" s="2" t="str">
-        <x:v>06/17(水)</x:v>
+        <x:v>06/19(金)</x:v>
       </x:c>
       <x:c r="HB5" s="2" t="str">
-        <x:v>06/17(水)</x:v>
+        <x:v>06/19(金)</x:v>
       </x:c>
       <x:c r="HC5" s="2" t="str">
-        <x:v>06/17(水)</x:v>
+        <x:v>06/19(金)</x:v>
       </x:c>
       <x:c r="HD5" s="2" t="str">
-        <x:v>06/18(木)</x:v>
+        <x:v>06/20(土)</x:v>
       </x:c>
       <x:c r="HE5" s="2" t="str">
-        <x:v>06/18(木)</x:v>
+        <x:v>06/20(土)</x:v>
       </x:c>
       <x:c r="HF5" s="2" t="str">
-        <x:v>06/18(木)</x:v>
+        <x:v>06/20(土)</x:v>
       </x:c>
       <x:c r="HG5" s="2" t="str">
-        <x:v>06/19(金)</x:v>
+        <x:v>06/21(日)</x:v>
       </x:c>
       <x:c r="HH5" s="2" t="str">
-        <x:v>06/19(金)</x:v>
+        <x:v>06/21(日)</x:v>
       </x:c>
       <x:c r="HI5" s="2" t="str">
-        <x:v>06/19(金)</x:v>
+        <x:v>06/21(日)</x:v>
       </x:c>
       <x:c r="HJ5" s="2" t="str">
-        <x:v>06/20(土)</x:v>
+        <x:v>06/22(月)</x:v>
       </x:c>
       <x:c r="HK5" s="2" t="str">
-        <x:v>06/20(土)</x:v>
+        <x:v>06/22(月)</x:v>
       </x:c>
       <x:c r="HL5" s="2" t="str">
-        <x:v>06/20(土)</x:v>
+        <x:v>06/22(月)</x:v>
       </x:c>
       <x:c r="HM5" s="2" t="str">
-        <x:v>06/21(日)</x:v>
+        <x:v>06/23(火)</x:v>
       </x:c>
       <x:c r="HN5" s="2" t="str">
-        <x:v>06/21(日)</x:v>
+        <x:v>06/23(火)</x:v>
       </x:c>
       <x:c r="HO5" s="2" t="str">
-        <x:v>06/21(日)</x:v>
+        <x:v>06/23(火)</x:v>
       </x:c>
       <x:c r="HP5" s="2" t="str">
-        <x:v>06/22(月)</x:v>
+        <x:v>06/24(水)</x:v>
       </x:c>
       <x:c r="HQ5" s="2" t="str">
-        <x:v>06/22(月)</x:v>
+        <x:v>06/24(水)</x:v>
       </x:c>
       <x:c r="HR5" s="2" t="str">
-        <x:v>06/22(月)</x:v>
+        <x:v>06/24(水)</x:v>
       </x:c>
       <x:c r="HS5" s="2" t="str">
-        <x:v>06/23(火)</x:v>
+        <x:v>06/25(木)</x:v>
       </x:c>
       <x:c r="HT5" s="2" t="str">
-        <x:v>06/23(火)</x:v>
+        <x:v>06/25(木)</x:v>
       </x:c>
       <x:c r="HU5" s="2" t="str">
-        <x:v>06/23(火)</x:v>
+        <x:v>06/25(木)</x:v>
       </x:c>
       <x:c r="HV5" s="2" t="str">
-        <x:v>06/24(水)</x:v>
+        <x:v>06/26(金)</x:v>
       </x:c>
       <x:c r="HW5" s="2" t="str">
-        <x:v>06/24(水)</x:v>
+        <x:v>06/26(金)</x:v>
       </x:c>
       <x:c r="HX5" s="2" t="str">
-        <x:v>06/24(水)</x:v>
+        <x:v>06/26(金)</x:v>
       </x:c>
       <x:c r="HY5" s="2" t="str">
-        <x:v>06/25(木)</x:v>
+        <x:v>06/27(土)</x:v>
       </x:c>
       <x:c r="HZ5" s="2" t="str">
-        <x:v>06/25(木)</x:v>
+        <x:v>06/27(土)</x:v>
       </x:c>
       <x:c r="IA5" s="2" t="str">
-        <x:v>06/25(木)</x:v>
+        <x:v>06/27(土)</x:v>
       </x:c>
       <x:c r="IB5" s="2" t="str">
-        <x:v>06/26(金)</x:v>
+        <x:v>06/28(日)</x:v>
       </x:c>
       <x:c r="IC5" s="2" t="str">
-        <x:v>06/26(金)</x:v>
+        <x:v>06/28(日)</x:v>
       </x:c>
       <x:c r="ID5" s="2" t="str">
-        <x:v>06/26(金)</x:v>
+        <x:v>06/28(日)</x:v>
       </x:c>
       <x:c r="IE5" s="2" t="str">
-        <x:v>06/27(土)</x:v>
+        <x:v>06/29(月)</x:v>
       </x:c>
       <x:c r="IF5" s="2" t="str">
-        <x:v>06/27(土)</x:v>
+        <x:v>06/29(月)</x:v>
       </x:c>
       <x:c r="IG5" s="2" t="str">
-        <x:v>06/27(土)</x:v>
+        <x:v>06/29(月)</x:v>
       </x:c>
       <x:c r="IH5" s="2" t="str">
-        <x:v>06/28(日)</x:v>
+        <x:v>06/30(火)</x:v>
       </x:c>
       <x:c r="II5" s="2" t="str">
-        <x:v>06/28(日)</x:v>
+        <x:v>06/30(火)</x:v>
       </x:c>
       <x:c r="IJ5" s="2" t="str">
-        <x:v>06/28(日)</x:v>
+        <x:v>06/30(火)</x:v>
       </x:c>
       <x:c r="IK5" s="2" t="str">
-        <x:v>06/29(月)</x:v>
+        <x:v>07/01(水)</x:v>
       </x:c>
       <x:c r="IL5" s="2" t="str">
-        <x:v>06/29(月)</x:v>
+        <x:v>07/01(水)</x:v>
       </x:c>
       <x:c r="IM5" s="2" t="str">
-        <x:v>06/29(月)</x:v>
+        <x:v>07/01(水)</x:v>
       </x:c>
       <x:c r="IN5" s="2" t="str">
-        <x:v>06/30(火)</x:v>
+        <x:v>07/02(木)</x:v>
       </x:c>
       <x:c r="IO5" s="2" t="str">
-        <x:v>06/30(火)</x:v>
+        <x:v>07/02(木)</x:v>
       </x:c>
       <x:c r="IP5" s="2" t="str">
-        <x:v>06/30(火)</x:v>
+        <x:v>07/02(木)</x:v>
       </x:c>
       <x:c r="IQ5" s="2" t="str">
-        <x:v>07/01(水)</x:v>
+        <x:v>07/03(金)</x:v>
       </x:c>
       <x:c r="IR5" s="2" t="str">
-        <x:v>07/01(水)</x:v>
+        <x:v>07/03(金)</x:v>
       </x:c>
       <x:c r="IS5" s="2" t="str">
-        <x:v>07/01(水)</x:v>
+        <x:v>07/03(金)</x:v>
       </x:c>
       <x:c r="IT5" s="2" t="str">
-        <x:v>07/02(木)</x:v>
+        <x:v>07/04(土)</x:v>
       </x:c>
       <x:c r="IU5" s="2" t="str">
-        <x:v>07/02(木)</x:v>
+        <x:v>07/04(土)</x:v>
       </x:c>
       <x:c r="IV5" s="2" t="str">
-        <x:v>07/02(木)</x:v>
+        <x:v>07/04(土)</x:v>
       </x:c>
       <x:c r="IW5" s="2" t="str">
-        <x:v>07/03(金)</x:v>
+        <x:v>07/05(日)</x:v>
       </x:c>
       <x:c r="IX5" s="2" t="str">
-        <x:v>07/03(金)</x:v>
+        <x:v>07/05(日)</x:v>
       </x:c>
       <x:c r="IY5" s="2" t="str">
-        <x:v>07/03(金)</x:v>
+        <x:v>07/05(日)</x:v>
       </x:c>
       <x:c r="IZ5" s="2" t="str">
-        <x:v>07/04(土)</x:v>
+        <x:v>07/06(月)</x:v>
       </x:c>
       <x:c r="JA5" s="2" t="str">
-        <x:v>07/04(土)</x:v>
+        <x:v>07/06(月)</x:v>
       </x:c>
       <x:c r="JB5" s="2" t="str">
-        <x:v>07/04(土)</x:v>
+        <x:v>07/06(月)</x:v>
       </x:c>
       <x:c r="JC5" s="2" t="str">
-        <x:v>07/05(日)</x:v>
+        <x:v>07/07(火)</x:v>
       </x:c>
       <x:c r="JD5" s="2" t="str">
-        <x:v>07/05(日)</x:v>
+        <x:v>07/07(火)</x:v>
       </x:c>
       <x:c r="JE5" s="2" t="str">
-        <x:v>07/05(日)</x:v>
+        <x:v>07/07(火)</x:v>
       </x:c>
       <x:c r="JF5" s="2" t="str">
-        <x:v>07/06(月)</x:v>
+        <x:v>07/08(水)</x:v>
       </x:c>
       <x:c r="JG5" s="2" t="str">
-        <x:v>07/06(月)</x:v>
+        <x:v>07/08(水)</x:v>
       </x:c>
       <x:c r="JH5" s="2" t="str">
-        <x:v>07/06(月)</x:v>
+        <x:v>07/08(水)</x:v>
       </x:c>
       <x:c r="JI5" s="2" t="str">
-        <x:v>07/07(火)</x:v>
+        <x:v>07/09(木)</x:v>
       </x:c>
       <x:c r="JJ5" s="2" t="str">
-        <x:v>07/07(火)</x:v>
+        <x:v>07/09(木)</x:v>
       </x:c>
       <x:c r="JK5" s="2" t="str">
-        <x:v>07/07(火)</x:v>
+        <x:v>07/09(木)</x:v>
       </x:c>
       <x:c r="JL5" s="2" t="str">
-        <x:v>07/08(水)</x:v>
+        <x:v>07/10(金)</x:v>
       </x:c>
       <x:c r="JM5" s="2" t="str">
-        <x:v>07/08(水)</x:v>
+        <x:v>07/10(金)</x:v>
       </x:c>
       <x:c r="JN5" s="2" t="str">
-        <x:v>07/08(水)</x:v>
+        <x:v>07/10(金)</x:v>
       </x:c>
       <x:c r="JO5" s="2" t="str">
-        <x:v>07/09(木)</x:v>
+        <x:v>07/11(土)</x:v>
       </x:c>
       <x:c r="JP5" s="2" t="str">
-        <x:v>07/09(木)</x:v>
+        <x:v>07/11(土)</x:v>
       </x:c>
       <x:c r="JQ5" s="2" t="str">
-        <x:v>07/09(木)</x:v>
+        <x:v>07/11(土)</x:v>
       </x:c>
       <x:c r="JR5" s="2" t="str">
-        <x:v>07/10(金)</x:v>
+        <x:v>07/12(日)</x:v>
       </x:c>
       <x:c r="JS5" s="2" t="str">
-        <x:v>07/10(金)</x:v>
+        <x:v>07/12(日)</x:v>
       </x:c>
       <x:c r="JT5" s="2" t="str">
-        <x:v>07/10(金)</x:v>
+        <x:v>07/12(日)</x:v>
       </x:c>
       <x:c r="JU5" s="2" t="str">
-        <x:v>07/11(土)</x:v>
+        <x:v>07/13(月)</x:v>
       </x:c>
       <x:c r="JV5" s="2" t="str">
-        <x:v>07/11(土)</x:v>
+        <x:v>07/13(月)</x:v>
       </x:c>
       <x:c r="JW5" s="2" t="str">
-        <x:v>07/11(土)</x:v>
+        <x:v>07/13(月)</x:v>
       </x:c>
       <x:c r="JX5" s="2" t="str">
-        <x:v>07/12(日)</x:v>
+        <x:v>07/14(火)</x:v>
       </x:c>
       <x:c r="JY5" s="2" t="str">
-        <x:v>07/12(日)</x:v>
+        <x:v>07/14(火)</x:v>
       </x:c>
       <x:c r="JZ5" s="2" t="str">
-        <x:v>07/12(日)</x:v>
+        <x:v>07/14(火)</x:v>
       </x:c>
       <x:c r="KA5" s="2" t="str">
-        <x:v>07/13(月)</x:v>
+        <x:v>07/15(水)</x:v>
       </x:c>
       <x:c r="KB5" s="2" t="str">
-        <x:v>07/13(月)</x:v>
+        <x:v>07/15(水)</x:v>
       </x:c>
       <x:c r="KC5" s="2" t="str">
-        <x:v>07/13(月)</x:v>
+        <x:v>07/15(水)</x:v>
       </x:c>
       <x:c r="KD5" s="2" t="str">
-        <x:v>07/14(火)</x:v>
+        <x:v>07/16(木)</x:v>
       </x:c>
       <x:c r="KE5" s="2" t="str">
-        <x:v>07/14(火)</x:v>
+        <x:v>07/16(木)</x:v>
       </x:c>
       <x:c r="KF5" s="2" t="str">
-        <x:v>07/14(火)</x:v>
+        <x:v>07/16(木)</x:v>
       </x:c>
       <x:c r="KG5" s="2" t="str">
-        <x:v>07/15(水)</x:v>
+        <x:v>07/17(金)</x:v>
       </x:c>
       <x:c r="KH5" s="2" t="str">
-        <x:v>07/15(水)</x:v>
+        <x:v>07/17(金)</x:v>
       </x:c>
       <x:c r="KI5" s="2" t="str">
-        <x:v>07/15(水)</x:v>
+        <x:v>07/17(金)</x:v>
       </x:c>
       <x:c r="KJ5" s="2" t="str">
-        <x:v>07/16(木)</x:v>
+        <x:v>07/18(土)</x:v>
       </x:c>
       <x:c r="KK5" s="2" t="str">
-        <x:v>07/16(木)</x:v>
+        <x:v>07/18(土)</x:v>
       </x:c>
       <x:c r="KL5" s="2" t="str">
-        <x:v>07/16(木)</x:v>
+        <x:v>07/18(土)</x:v>
       </x:c>
       <x:c r="KM5" s="2" t="str">
-        <x:v>07/17(金)</x:v>
+        <x:v>07/19(日)</x:v>
       </x:c>
       <x:c r="KN5" s="2" t="str">
-        <x:v>07/17(金)</x:v>
+        <x:v>07/19(日)</x:v>
       </x:c>
       <x:c r="KO5" s="2" t="str">
-        <x:v>07/17(金)</x:v>
+        <x:v>07/19(日)</x:v>
       </x:c>
       <x:c r="KP5" s="2" t="str">
-        <x:v>07/18(土)</x:v>
+        <x:v>07/20(月)</x:v>
       </x:c>
       <x:c r="KQ5" s="2" t="str">
-        <x:v>07/18(土)</x:v>
+        <x:v>07/20(月)</x:v>
       </x:c>
       <x:c r="KR5" s="2" t="str">
-        <x:v>07/18(土)</x:v>
+        <x:v>07/20(月)</x:v>
       </x:c>
       <x:c r="KS5" s="2" t="str">
-        <x:v>07/19(日)</x:v>
+        <x:v>07/21(火)</x:v>
       </x:c>
       <x:c r="KT5" s="2" t="str">
-        <x:v>07/19(日)</x:v>
+        <x:v>07/21(火)</x:v>
       </x:c>
       <x:c r="KU5" s="2" t="str">
-        <x:v>07/19(日)</x:v>
+        <x:v>07/21(火)</x:v>
       </x:c>
       <x:c r="KV5" s="2" t="str">
-        <x:v>07/20(月)</x:v>
+        <x:v>07/22(水)</x:v>
       </x:c>
       <x:c r="KW5" s="2" t="str">
-        <x:v>07/20(月)</x:v>
+        <x:v>07/22(水)</x:v>
       </x:c>
       <x:c r="KX5" s="2" t="str">
-        <x:v>07/20(月)</x:v>
+        <x:v>07/22(水)</x:v>
       </x:c>
       <x:c r="KY5" s="2" t="str">
-        <x:v>07/21(火)</x:v>
+        <x:v>07/23(木)</x:v>
       </x:c>
       <x:c r="KZ5" s="2" t="str">
-        <x:v>07/21(火)</x:v>
+        <x:v>07/23(木)</x:v>
       </x:c>
       <x:c r="LA5" s="2" t="str">
-        <x:v>07/21(火)</x:v>
+        <x:v>07/23(木)</x:v>
       </x:c>
       <x:c r="LB5" s="2" t="str">
-        <x:v>07/22(水)</x:v>
+        <x:v>07/24(金)</x:v>
       </x:c>
       <x:c r="LC5" s="2" t="str">
-        <x:v>07/22(水)</x:v>
+        <x:v>07/24(金)</x:v>
       </x:c>
       <x:c r="LD5" s="2" t="str">
-        <x:v>07/22(水)</x:v>
+        <x:v>07/24(金)</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2826,13 +2826,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB7" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2000.0000</x:v>
       </x:c>
       <x:c r="FC7" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FD7" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.0700</x:v>
       </x:c>
       <x:c r="FE7" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -2844,13 +2844,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FH7" s="6" t="n">
-        <x:v>2000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FI7" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FJ7" s="8" t="n">
-        <x:v>2.0700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FK7" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -3677,13 +3677,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DU8" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5400.0000</x:v>
       </x:c>
       <x:c r="DV8" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="DW8" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5.5800</x:v>
       </x:c>
       <x:c r="DX8" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -3695,13 +3695,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EA8" s="6" t="n">
-        <x:v>5400.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EB8" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EC8" s="8" t="n">
-        <x:v>5.5800</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ED8" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -3713,13 +3713,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG8" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2600.0000</x:v>
       </x:c>
       <x:c r="EH8" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EI8" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.6900</x:v>
       </x:c>
       <x:c r="EJ8" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -3731,13 +3731,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM8" s="6" t="n">
-        <x:v>2600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN8" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EO8" s="8" t="n">
-        <x:v>2.6900</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP8" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -4663,13 +4663,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG9" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>400.0000</x:v>
       </x:c>
       <x:c r="EH9" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EI9" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.4100</x:v>
       </x:c>
       <x:c r="EJ9" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -4681,13 +4681,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM9" s="6" t="n">
-        <x:v>400.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN9" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EO9" s="8" t="n">
-        <x:v>0.4100</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP9" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -5613,13 +5613,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG10" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5000.0000</x:v>
       </x:c>
       <x:c r="EH10" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EI10" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5.1700</x:v>
       </x:c>
       <x:c r="EJ10" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -5631,13 +5631,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM10" s="6" t="n">
-        <x:v>5000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN10" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EO10" s="8" t="n">
-        <x:v>5.1700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP10" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -6626,13 +6626,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB11" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2400.0000</x:v>
       </x:c>
       <x:c r="FC11" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FD11" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.4800</x:v>
       </x:c>
       <x:c r="FE11" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -6644,13 +6644,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FH11" s="6" t="n">
-        <x:v>2400.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FI11" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FJ11" s="8" t="n">
-        <x:v>2.4800</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FK11" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -7576,13 +7576,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB12" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1155.0000</x:v>
       </x:c>
       <x:c r="FC12" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FD12" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.1900</x:v>
       </x:c>
       <x:c r="FE12" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -7594,13 +7594,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FH12" s="6" t="n">
-        <x:v>1155.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FI12" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FJ12" s="8" t="n">
-        <x:v>1.1900</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FK12" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -8535,13 +8535,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FE13" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2800.0000</x:v>
       </x:c>
       <x:c r="FF13" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FG13" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.8900</x:v>
       </x:c>
       <x:c r="FH13" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -8553,13 +8553,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FK13" s="6" t="n">
-        <x:v>2800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FL13" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FM13" s="8" t="n">
-        <x:v>2.8900</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FN13" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -9467,40 +9467,40 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY14" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4500.0000</x:v>
       </x:c>
       <x:c r="EZ14" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="FA14" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4.1500</x:v>
       </x:c>
       <x:c r="FB14" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4500.0000</x:v>
       </x:c>
       <x:c r="FC14" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="FD14" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4.1500</x:v>
       </x:c>
       <x:c r="FE14" s="6" t="n">
-        <x:v>4500.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FF14" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="FG14" s="8" t="n">
-        <x:v>4.1500</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FH14" s="6" t="n">
-        <x:v>4500.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FI14" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="FJ14" s="8" t="n">
-        <x:v>4.1500</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FK14" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -10354,13 +10354,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ED15" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>250.0000</x:v>
       </x:c>
       <x:c r="EE15" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EF15" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.2300</x:v>
       </x:c>
       <x:c r="EG15" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -10372,13 +10372,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ15" s="6" t="n">
-        <x:v>250.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EK15" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EL15" s="8" t="n">
-        <x:v>0.2300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM15" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -11304,13 +11304,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ED16" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>400.0000</x:v>
       </x:c>
       <x:c r="EE16" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EF16" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.3700</x:v>
       </x:c>
       <x:c r="EG16" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -11322,13 +11322,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ16" s="6" t="n">
-        <x:v>400.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EK16" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EL16" s="8" t="n">
-        <x:v>0.3700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM16" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -12254,13 +12254,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ED17" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>500.0000</x:v>
       </x:c>
       <x:c r="EE17" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EF17" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.4600</x:v>
       </x:c>
       <x:c r="EG17" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -12272,13 +12272,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ17" s="6" t="n">
-        <x:v>500.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EK17" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EL17" s="8" t="n">
-        <x:v>0.4600</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM17" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -13159,13 +13159,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DO18" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2700.0000</x:v>
       </x:c>
       <x:c r="DP18" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="DQ18" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.4900</x:v>
       </x:c>
       <x:c r="DR18" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -13177,13 +13177,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DU18" s="6" t="n">
-        <x:v>2700.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DV18" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="DW18" s="8" t="n">
-        <x:v>2.4900</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DX18" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -14109,13 +14109,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DO19" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1500.0000</x:v>
       </x:c>
       <x:c r="DP19" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="DQ19" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.3800</x:v>
       </x:c>
       <x:c r="DR19" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -14127,13 +14127,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DU19" s="6" t="n">
-        <x:v>1500.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DV19" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="DW19" s="8" t="n">
-        <x:v>1.3800</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DX19" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -14154,13 +14154,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ED19" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5700.0000</x:v>
       </x:c>
       <x:c r="EE19" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EF19" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5.2600</x:v>
       </x:c>
       <x:c r="EG19" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -14172,13 +14172,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ19" s="6" t="n">
-        <x:v>5700.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EK19" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EL19" s="8" t="n">
-        <x:v>5.2600</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM19" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -15131,13 +15131,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM20" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>20.0000</x:v>
       </x:c>
       <x:c r="EN20" s="8" t="n">
         <x:v>18.0200</x:v>
       </x:c>
       <x:c r="EO20" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.0200</x:v>
       </x:c>
       <x:c r="EP20" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -15149,13 +15149,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES20" s="6" t="n">
-        <x:v>20.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ET20" s="8" t="n">
         <x:v>18.0200</x:v>
       </x:c>
       <x:c r="EU20" s="8" t="n">
-        <x:v>0.0200</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV20" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -16081,13 +16081,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM21" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4000.0000</x:v>
       </x:c>
       <x:c r="EN21" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EO21" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3.6900</x:v>
       </x:c>
       <x:c r="EP21" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -16099,13 +16099,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES21" s="6" t="n">
-        <x:v>4000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ET21" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EU21" s="8" t="n">
-        <x:v>3.6900</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV21" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -17031,13 +17031,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM22" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>20.0000</x:v>
       </x:c>
       <x:c r="EN22" s="8" t="n">
         <x:v>18.0200</x:v>
       </x:c>
       <x:c r="EO22" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.0200</x:v>
       </x:c>
       <x:c r="EP22" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -17049,13 +17049,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES22" s="6" t="n">
-        <x:v>20.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ET22" s="8" t="n">
         <x:v>18.0200</x:v>
       </x:c>
       <x:c r="EU22" s="8" t="n">
-        <x:v>0.0200</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV22" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -17981,13 +17981,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM23" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>20.0000</x:v>
       </x:c>
       <x:c r="EN23" s="8" t="n">
         <x:v>18.0200</x:v>
       </x:c>
       <x:c r="EO23" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.0200</x:v>
       </x:c>
       <x:c r="EP23" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -17999,13 +17999,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES23" s="6" t="n">
-        <x:v>20.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ET23" s="8" t="n">
         <x:v>18.0200</x:v>
       </x:c>
       <x:c r="EU23" s="8" t="n">
-        <x:v>0.0200</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV23" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -18868,13 +18868,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DR24" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>250.0000</x:v>
       </x:c>
       <x:c r="DS24" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="DT24" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.4100</x:v>
       </x:c>
       <x:c r="DU24" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -18886,13 +18886,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DX24" s="6" t="n">
-        <x:v>250.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DY24" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="DZ24" s="8" t="n">
-        <x:v>0.4100</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EA24" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -19818,13 +19818,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DR25" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>250.0000</x:v>
       </x:c>
       <x:c r="DS25" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="DT25" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.4100</x:v>
       </x:c>
       <x:c r="DU25" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -19836,32 +19836,32 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DX25" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="DY25" s="8" t="n">
+        <x:v>10.1200</x:v>
+      </x:c>
+      <x:c r="DZ25" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="EA25" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="EB25" s="8" t="n">
+        <x:v>10.1200</x:v>
+      </x:c>
+      <x:c r="EC25" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="ED25" s="6" t="n">
         <x:v>250.0000</x:v>
       </x:c>
-      <x:c r="DY25" s="8" t="n">
-        <x:v>10.1200</x:v>
-      </x:c>
-      <x:c r="DZ25" s="8" t="n">
+      <x:c r="EE25" s="8" t="n">
+        <x:v>10.1200</x:v>
+      </x:c>
+      <x:c r="EF25" s="8" t="n">
         <x:v>0.4100</x:v>
       </x:c>
-      <x:c r="EA25" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="EB25" s="8" t="n">
-        <x:v>10.1200</x:v>
-      </x:c>
-      <x:c r="EC25" s="8" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="ED25" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="EE25" s="8" t="n">
-        <x:v>10.1200</x:v>
-      </x:c>
-      <x:c r="EF25" s="8" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
       <x:c r="EG25" s="6" t="n">
         <x:v>0.0000</x:v>
       </x:c>
@@ -19872,13 +19872,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ25" s="6" t="n">
-        <x:v>250.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EK25" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="EL25" s="8" t="n">
-        <x:v>0.4100</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM25" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -20768,13 +20768,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DR26" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>400.0000</x:v>
       </x:c>
       <x:c r="DS26" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="DT26" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.6600</x:v>
       </x:c>
       <x:c r="DU26" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -20786,13 +20786,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DX26" s="6" t="n">
-        <x:v>400.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DY26" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="DZ26" s="8" t="n">
-        <x:v>0.6600</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EA26" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -21754,13 +21754,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ED27" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>250.0000</x:v>
       </x:c>
       <x:c r="EE27" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EF27" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.2800</x:v>
       </x:c>
       <x:c r="EG27" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -21772,13 +21772,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ27" s="6" t="n">
-        <x:v>250.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EK27" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EL27" s="8" t="n">
-        <x:v>0.2800</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM27" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -22668,13 +22668,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DR28" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>400.0000</x:v>
       </x:c>
       <x:c r="DS28" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="DT28" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.4400</x:v>
       </x:c>
       <x:c r="DU28" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -22686,13 +22686,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DX28" s="6" t="n">
-        <x:v>400.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DY28" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="DZ28" s="8" t="n">
-        <x:v>0.4400</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EA28" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -23672,13 +23672,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ29" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1600.0000</x:v>
       </x:c>
       <x:c r="EK29" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EL29" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.7800</x:v>
       </x:c>
       <x:c r="EM29" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -23690,13 +23690,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP29" s="6" t="n">
-        <x:v>1600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EQ29" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="ER29" s="8" t="n">
-        <x:v>1.7800</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES29" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -24640,13 +24640,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP30" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1943.0000</x:v>
       </x:c>
       <x:c r="EQ30" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="ER30" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3.2000</x:v>
       </x:c>
       <x:c r="ES30" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -24658,13 +24658,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV30" s="6" t="n">
-        <x:v>1943.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EW30" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="EX30" s="8" t="n">
-        <x:v>3.2000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY30" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -25554,13 +25554,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ED31" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2250.0000</x:v>
       </x:c>
       <x:c r="EE31" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="EF31" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3.7100</x:v>
       </x:c>
       <x:c r="EG31" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -25572,13 +25572,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ31" s="6" t="n">
-        <x:v>2250.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EK31" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="EL31" s="8" t="n">
-        <x:v>3.7100</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM31" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -26504,13 +26504,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ED32" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>20.0000</x:v>
       </x:c>
       <x:c r="EE32" s="8" t="n">
         <x:v>10.1000</x:v>
       </x:c>
       <x:c r="EF32" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.0300</x:v>
       </x:c>
       <x:c r="EG32" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -26522,13 +26522,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ32" s="6" t="n">
-        <x:v>20.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EK32" s="8" t="n">
         <x:v>10.1000</x:v>
       </x:c>
       <x:c r="EL32" s="8" t="n">
-        <x:v>0.0300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM32" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -27454,13 +27454,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ED33" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2000.0000</x:v>
       </x:c>
       <x:c r="EE33" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="EF33" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3.2900</x:v>
       </x:c>
       <x:c r="EG33" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -27472,13 +27472,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ33" s="6" t="n">
-        <x:v>2000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EK33" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="EL33" s="8" t="n">
-        <x:v>3.2900</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM33" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -28422,40 +28422,40 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ34" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3900.0000</x:v>
       </x:c>
       <x:c r="EK34" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="EL34" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6.4200</x:v>
       </x:c>
       <x:c r="EM34" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2100.0000</x:v>
       </x:c>
       <x:c r="EN34" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="EO34" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3.4600</x:v>
       </x:c>
       <x:c r="EP34" s="6" t="n">
-        <x:v>3900.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EQ34" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="ER34" s="8" t="n">
-        <x:v>6.4200</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES34" s="6" t="n">
-        <x:v>2100.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ET34" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="EU34" s="8" t="n">
-        <x:v>3.4600</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV34" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -29354,13 +29354,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ED35" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>91.0000</x:v>
       </x:c>
       <x:c r="EE35" s="8" t="n">
         <x:v>15.0300</x:v>
       </x:c>
       <x:c r="EF35" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.1000</x:v>
       </x:c>
       <x:c r="EG35" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -29372,13 +29372,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ35" s="6" t="n">
-        <x:v>91.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EK35" s="8" t="n">
         <x:v>15.0300</x:v>
       </x:c>
       <x:c r="EL35" s="8" t="n">
-        <x:v>0.1000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM35" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -30304,13 +30304,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ED36" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>180.0000</x:v>
       </x:c>
       <x:c r="EE36" s="8" t="n">
         <x:v>15.0400</x:v>
       </x:c>
       <x:c r="EF36" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.2000</x:v>
       </x:c>
       <x:c r="EG36" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -30322,13 +30322,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ36" s="6" t="n">
-        <x:v>180.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EK36" s="8" t="n">
         <x:v>15.0400</x:v>
       </x:c>
       <x:c r="EL36" s="8" t="n">
-        <x:v>0.2000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM36" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -31254,13 +31254,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ED37" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>271.0000</x:v>
       </x:c>
       <x:c r="EE37" s="8" t="n">
         <x:v>15.0400</x:v>
       </x:c>
       <x:c r="EF37" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.3000</x:v>
       </x:c>
       <x:c r="EG37" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -31272,13 +31272,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ37" s="6" t="n">
-        <x:v>271.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EK37" s="8" t="n">
         <x:v>15.0400</x:v>
       </x:c>
       <x:c r="EL37" s="8" t="n">
-        <x:v>0.3000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM37" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -32222,40 +32222,40 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ38" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>7800.0000</x:v>
       </x:c>
       <x:c r="EK38" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EL38" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>8.6700</x:v>
       </x:c>
       <x:c r="EM38" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4200.0000</x:v>
       </x:c>
       <x:c r="EN38" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EO38" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4.6700</x:v>
       </x:c>
       <x:c r="EP38" s="6" t="n">
-        <x:v>7800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EQ38" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="ER38" s="8" t="n">
-        <x:v>8.6700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES38" s="6" t="n">
-        <x:v>4200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ET38" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EU38" s="8" t="n">
-        <x:v>4.6700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV38" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -33190,7 +33190,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP39" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2000.0000</x:v>
       </x:c>
       <x:c r="EQ39" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -33208,7 +33208,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV39" s="6" t="n">
-        <x:v>2000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EW39" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -34167,13 +34167,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY40" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>950.0000</x:v>
       </x:c>
       <x:c r="EZ40" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="FA40" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.5600</x:v>
       </x:c>
       <x:c r="FB40" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -34185,13 +34185,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FE40" s="6" t="n">
-        <x:v>950.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FF40" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="FG40" s="8" t="n">
-        <x:v>1.5600</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FH40" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -35117,7 +35117,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY41" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1000.0000</x:v>
       </x:c>
       <x:c r="EZ41" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -35135,7 +35135,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FE41" s="6" t="n">
-        <x:v>1000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FF41" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -36067,40 +36067,40 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY42" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1940.0000</x:v>
       </x:c>
       <x:c r="EZ42" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="FA42" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3.1900</x:v>
       </x:c>
       <x:c r="FB42" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1940.0000</x:v>
       </x:c>
       <x:c r="FC42" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="FD42" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3.1900</x:v>
       </x:c>
       <x:c r="FE42" s="6" t="n">
-        <x:v>1940.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FF42" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="FG42" s="8" t="n">
-        <x:v>3.1900</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FH42" s="6" t="n">
-        <x:v>1940.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FI42" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="FJ42" s="8" t="n">
-        <x:v>3.1900</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FK42" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -37017,7 +37017,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY43" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2000.0000</x:v>
       </x:c>
       <x:c r="EZ43" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -37026,7 +37026,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB43" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2000.0000</x:v>
       </x:c>
       <x:c r="FC43" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -37035,7 +37035,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FE43" s="6" t="n">
-        <x:v>2000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FF43" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -37044,7 +37044,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FH43" s="6" t="n">
-        <x:v>2000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FI43" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -37985,22 +37985,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FE44" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4200.0000</x:v>
       </x:c>
       <x:c r="FF44" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="FG44" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6.9200</x:v>
       </x:c>
       <x:c r="FH44" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4200.0000</x:v>
       </x:c>
       <x:c r="FI44" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="FJ44" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6.9200</x:v>
       </x:c>
       <x:c r="FK44" s="6" t="n">
         <x:v>4200.0000</x:v>
@@ -38012,40 +38012,40 @@
         <x:v>6.9200</x:v>
       </x:c>
       <x:c r="FN44" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="FO44" s="8" t="n">
+        <x:v>10.1200</x:v>
+      </x:c>
+      <x:c r="FP44" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="FQ44" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="FR44" s="8" t="n">
+        <x:v>10.1200</x:v>
+      </x:c>
+      <x:c r="FS44" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="FT44" s="6" t="n">
         <x:v>4200.0000</x:v>
       </x:c>
-      <x:c r="FO44" s="8" t="n">
-        <x:v>10.1200</x:v>
-      </x:c>
-      <x:c r="FP44" s="8" t="n">
+      <x:c r="FU44" s="8" t="n">
+        <x:v>10.1200</x:v>
+      </x:c>
+      <x:c r="FV44" s="8" t="n">
         <x:v>6.9200</x:v>
       </x:c>
-      <x:c r="FQ44" s="6" t="n">
+      <x:c r="FW44" s="6" t="n">
         <x:v>4200.0000</x:v>
       </x:c>
-      <x:c r="FR44" s="8" t="n">
-        <x:v>10.1200</x:v>
-      </x:c>
-      <x:c r="FS44" s="8" t="n">
+      <x:c r="FX44" s="8" t="n">
+        <x:v>10.1200</x:v>
+      </x:c>
+      <x:c r="FY44" s="8" t="n">
         <x:v>6.9200</x:v>
-      </x:c>
-      <x:c r="FT44" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="FU44" s="8" t="n">
-        <x:v>10.1200</x:v>
-      </x:c>
-      <x:c r="FV44" s="8" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="FW44" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="FX44" s="8" t="n">
-        <x:v>10.1200</x:v>
-      </x:c>
-      <x:c r="FY44" s="8" t="n">
-        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FZ44" s="6" t="n">
         <x:v>4200.0000</x:v>
@@ -38066,22 +38066,22 @@
         <x:v>6.9200</x:v>
       </x:c>
       <x:c r="GF44" s="6" t="n">
-        <x:v>4200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GG44" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="GH44" s="8" t="n">
-        <x:v>6.9200</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GI44" s="6" t="n">
-        <x:v>4200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GJ44" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="GK44" s="8" t="n">
-        <x:v>6.9200</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GL44" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -38818,49 +38818,49 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DR45" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1400.0000</x:v>
       </x:c>
       <x:c r="DS45" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="DT45" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.9300</x:v>
       </x:c>
       <x:c r="DU45" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1600.0000</x:v>
       </x:c>
       <x:c r="DV45" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="DW45" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.0700</x:v>
       </x:c>
       <x:c r="DX45" s="6" t="n">
-        <x:v>1400.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DY45" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="DZ45" s="8" t="n">
-        <x:v>0.9300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EA45" s="6" t="n">
-        <x:v>1600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EB45" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EC45" s="8" t="n">
-        <x:v>1.0700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ED45" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6000.0000</x:v>
       </x:c>
       <x:c r="EE45" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EF45" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4.0000</x:v>
       </x:c>
       <x:c r="EG45" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -38872,13 +38872,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ45" s="6" t="n">
-        <x:v>6000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EK45" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EL45" s="8" t="n">
-        <x:v>4.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM45" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -39822,13 +39822,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ46" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3000.0000</x:v>
       </x:c>
       <x:c r="EK46" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EL46" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.0000</x:v>
       </x:c>
       <x:c r="EM46" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -39840,13 +39840,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP46" s="6" t="n">
-        <x:v>3000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EQ46" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="ER46" s="8" t="n">
-        <x:v>2.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES46" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -40754,40 +40754,40 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ED47" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5000.0000</x:v>
       </x:c>
       <x:c r="EE47" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EF47" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3.3300</x:v>
       </x:c>
       <x:c r="EG47" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4000.0000</x:v>
       </x:c>
       <x:c r="EH47" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EI47" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.6700</x:v>
       </x:c>
       <x:c r="EJ47" s="6" t="n">
-        <x:v>5000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EK47" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EL47" s="8" t="n">
-        <x:v>3.3300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM47" s="6" t="n">
-        <x:v>4000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN47" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EO47" s="8" t="n">
-        <x:v>2.6700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP47" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -41722,13 +41722,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ48" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1600.0000</x:v>
       </x:c>
       <x:c r="EK48" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EL48" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.0700</x:v>
       </x:c>
       <x:c r="EM48" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -41740,13 +41740,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP48" s="6" t="n">
-        <x:v>1600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EQ48" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="ER48" s="8" t="n">
-        <x:v>1.0700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES48" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -42681,13 +42681,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM49" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2000.0000</x:v>
       </x:c>
       <x:c r="EN49" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EO49" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.3300</x:v>
       </x:c>
       <x:c r="EP49" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -42699,13 +42699,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES49" s="6" t="n">
-        <x:v>2000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ET49" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EU49" s="8" t="n">
-        <x:v>1.3300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV49" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -43631,13 +43631,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM50" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2000.0000</x:v>
       </x:c>
       <x:c r="EN50" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EO50" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.3300</x:v>
       </x:c>
       <x:c r="EP50" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -43649,13 +43649,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES50" s="6" t="n">
-        <x:v>2000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ET50" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EU50" s="8" t="n">
-        <x:v>1.3300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV50" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -44572,40 +44572,40 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ51" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5000.0000</x:v>
       </x:c>
       <x:c r="EK51" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EL51" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3.3300</x:v>
       </x:c>
       <x:c r="EM51" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2000.0000</x:v>
       </x:c>
       <x:c r="EN51" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EO51" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.3300</x:v>
       </x:c>
       <x:c r="EP51" s="6" t="n">
-        <x:v>5000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EQ51" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="ER51" s="8" t="n">
-        <x:v>3.3300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES51" s="6" t="n">
-        <x:v>2000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ET51" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EU51" s="8" t="n">
-        <x:v>1.3300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV51" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -45513,40 +45513,40 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG52" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>7000.0000</x:v>
       </x:c>
       <x:c r="EH52" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EI52" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4.6700</x:v>
       </x:c>
       <x:c r="EJ52" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2000.0000</x:v>
       </x:c>
       <x:c r="EK52" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EL52" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.3300</x:v>
       </x:c>
       <x:c r="EM52" s="6" t="n">
-        <x:v>7000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN52" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EO52" s="8" t="n">
-        <x:v>4.6700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP52" s="6" t="n">
-        <x:v>2000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EQ52" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="ER52" s="8" t="n">
-        <x:v>1.3300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES52" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -46517,13 +46517,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY53" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2000.0000</x:v>
       </x:c>
       <x:c r="EZ53" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="FA53" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.8500</x:v>
       </x:c>
       <x:c r="FB53" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -46535,13 +46535,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FE53" s="6" t="n">
-        <x:v>2000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FF53" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="FG53" s="8" t="n">
-        <x:v>1.8500</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FH53" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -47467,13 +47467,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY54" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1000.0000</x:v>
       </x:c>
       <x:c r="EZ54" s="8" t="n">
         <x:v>25.0100</x:v>
       </x:c>
       <x:c r="FA54" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.6700</x:v>
       </x:c>
       <x:c r="FB54" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -47485,13 +47485,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FE54" s="6" t="n">
-        <x:v>1000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FF54" s="8" t="n">
         <x:v>25.0100</x:v>
       </x:c>
       <x:c r="FG54" s="8" t="n">
-        <x:v>0.6700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FH54" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -48417,7 +48417,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY55" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2000.0000</x:v>
       </x:c>
       <x:c r="EZ55" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -48435,7 +48435,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FE55" s="6" t="n">
-        <x:v>2000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FF55" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -49367,13 +49367,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY56" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3995.0000</x:v>
       </x:c>
       <x:c r="EZ56" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FA56" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.6600</x:v>
       </x:c>
       <x:c r="FB56" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -49385,13 +49385,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FE56" s="6" t="n">
-        <x:v>3995.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FF56" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FG56" s="8" t="n">
-        <x:v>2.6600</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FH56" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -50389,13 +50389,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FW57" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3200.0000</x:v>
       </x:c>
       <x:c r="FX57" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FY57" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.1300</x:v>
       </x:c>
       <x:c r="FZ57" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -50407,13 +50407,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GC57" s="6" t="n">
-        <x:v>3200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GD57" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="GE57" s="8" t="n">
-        <x:v>2.1300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GF57" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -51339,13 +51339,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FW58" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>200.0000</x:v>
       </x:c>
       <x:c r="FX58" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FY58" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.1300</x:v>
       </x:c>
       <x:c r="FZ58" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -51357,13 +51357,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GC58" s="6" t="n">
-        <x:v>200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GD58" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="GE58" s="8" t="n">
-        <x:v>0.1300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GF58" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -52289,13 +52289,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FW59" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1600.0000</x:v>
       </x:c>
       <x:c r="FX59" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FY59" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.0700</x:v>
       </x:c>
       <x:c r="FZ59" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -52307,13 +52307,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GC59" s="6" t="n">
-        <x:v>1600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GD59" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="GE59" s="8" t="n">
-        <x:v>1.0700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GF59" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -53239,13 +53239,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FW60" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3800.0000</x:v>
       </x:c>
       <x:c r="FX60" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FY60" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.5300</x:v>
       </x:c>
       <x:c r="FZ60" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -53257,13 +53257,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GC60" s="6" t="n">
-        <x:v>3800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GD60" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="GE60" s="8" t="n">
-        <x:v>2.5300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GF60" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -54189,13 +54189,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FW61" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>600.0000</x:v>
       </x:c>
       <x:c r="FX61" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FY61" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.4000</x:v>
       </x:c>
       <x:c r="FZ61" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -54207,13 +54207,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GC61" s="6" t="n">
-        <x:v>600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GD61" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="GE61" s="8" t="n">
-        <x:v>0.4000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GF61" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -55139,13 +55139,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FW62" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>800.0000</x:v>
       </x:c>
       <x:c r="FX62" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FY62" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.5300</x:v>
       </x:c>
       <x:c r="FZ62" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -55157,13 +55157,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GC62" s="6" t="n">
-        <x:v>800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GD62" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="GE62" s="8" t="n">
-        <x:v>0.5300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GF62" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -56044,13 +56044,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FH63" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>200.0000</x:v>
       </x:c>
       <x:c r="FI63" s="8" t="n">
         <x:v>10.0000</x:v>
       </x:c>
       <x:c r="FJ63" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.3300</x:v>
       </x:c>
       <x:c r="FK63" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -56062,13 +56062,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FN63" s="6" t="n">
-        <x:v>200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FO63" s="8" t="n">
         <x:v>10.0000</x:v>
       </x:c>
       <x:c r="FP63" s="8" t="n">
-        <x:v>0.3300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FQ63" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -56994,13 +56994,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FH64" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>800.0000</x:v>
       </x:c>
       <x:c r="FI64" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FJ64" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.8900</x:v>
       </x:c>
       <x:c r="FK64" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -57012,13 +57012,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FN64" s="6" t="n">
-        <x:v>800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FO64" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FP64" s="8" t="n">
-        <x:v>0.8900</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FQ64" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -57944,13 +57944,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FH65" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>800.0000</x:v>
       </x:c>
       <x:c r="FI65" s="8" t="n">
         <x:v>10.0000</x:v>
       </x:c>
       <x:c r="FJ65" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.3300</x:v>
       </x:c>
       <x:c r="FK65" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -57962,13 +57962,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FN65" s="6" t="n">
-        <x:v>800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FO65" s="8" t="n">
         <x:v>10.0000</x:v>
       </x:c>
       <x:c r="FP65" s="8" t="n">
-        <x:v>1.3300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FQ65" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -58894,13 +58894,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FH66" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>200.0000</x:v>
       </x:c>
       <x:c r="FI66" s="8" t="n">
         <x:v>10.0000</x:v>
       </x:c>
       <x:c r="FJ66" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.3300</x:v>
       </x:c>
       <x:c r="FK66" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -58912,13 +58912,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FN66" s="6" t="n">
-        <x:v>200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FO66" s="8" t="n">
         <x:v>10.0000</x:v>
       </x:c>
       <x:c r="FP66" s="8" t="n">
-        <x:v>0.3300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FQ66" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -59844,13 +59844,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FH67" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1200.0000</x:v>
       </x:c>
       <x:c r="FI67" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FJ67" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.3300</x:v>
       </x:c>
       <x:c r="FK67" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -59862,13 +59862,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FN67" s="6" t="n">
-        <x:v>1200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FO67" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FP67" s="8" t="n">
-        <x:v>1.3300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FQ67" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -60794,13 +60794,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FH68" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1200.0000</x:v>
       </x:c>
       <x:c r="FI68" s="8" t="n">
         <x:v>10.0000</x:v>
       </x:c>
       <x:c r="FJ68" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.0000</x:v>
       </x:c>
       <x:c r="FK68" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -60812,13 +60812,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FN68" s="6" t="n">
-        <x:v>1200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FO68" s="8" t="n">
         <x:v>10.0000</x:v>
       </x:c>
       <x:c r="FP68" s="8" t="n">
-        <x:v>2.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FQ68" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -61717,49 +61717,49 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY69" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2400.0000</x:v>
       </x:c>
       <x:c r="EZ69" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="FA69" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4.2100</x:v>
       </x:c>
       <x:c r="FB69" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3300.0000</x:v>
       </x:c>
       <x:c r="FC69" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="FD69" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5.7900</x:v>
       </x:c>
       <x:c r="FE69" s="6" t="n">
-        <x:v>2400.0000</x:v>
+        <x:v>3300.0000</x:v>
       </x:c>
       <x:c r="FF69" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="FG69" s="8" t="n">
-        <x:v>4.2100</x:v>
+        <x:v>5.7900</x:v>
       </x:c>
       <x:c r="FH69" s="6" t="n">
-        <x:v>3300.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FI69" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="FJ69" s="8" t="n">
-        <x:v>5.7900</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FK69" s="6" t="n">
-        <x:v>3300.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FL69" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="FM69" s="8" t="n">
-        <x:v>5.7900</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FN69" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -62568,13 +62568,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DR70" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2100.0000</x:v>
       </x:c>
       <x:c r="DS70" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="DT70" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3.6800</x:v>
       </x:c>
       <x:c r="DU70" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -62586,13 +62586,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DX70" s="6" t="n">
-        <x:v>2100.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DY70" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="DZ70" s="8" t="n">
-        <x:v>3.6800</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EA70" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -62613,13 +62613,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG70" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>600.0000</x:v>
       </x:c>
       <x:c r="EH70" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="EI70" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.0500</x:v>
       </x:c>
       <x:c r="EJ70" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -62631,13 +62631,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM70" s="6" t="n">
-        <x:v>600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN70" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="EO70" s="8" t="n">
-        <x:v>1.0500</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP70" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -63563,40 +63563,40 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG71" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3300.0000</x:v>
       </x:c>
       <x:c r="EH71" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="EI71" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5.7900</x:v>
       </x:c>
       <x:c r="EJ71" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3900.0000</x:v>
       </x:c>
       <x:c r="EK71" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="EL71" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6.8400</x:v>
       </x:c>
       <x:c r="EM71" s="6" t="n">
-        <x:v>3300.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN71" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="EO71" s="8" t="n">
-        <x:v>5.7900</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP71" s="6" t="n">
-        <x:v>3900.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EQ71" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="ER71" s="8" t="n">
-        <x:v>6.8400</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES71" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -64594,13 +64594,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FH72" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2310.0000</x:v>
       </x:c>
       <x:c r="FI72" s="8" t="n">
         <x:v>20.0000</x:v>
       </x:c>
       <x:c r="FJ72" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.9300</x:v>
       </x:c>
       <x:c r="FK72" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -64612,13 +64612,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FN72" s="6" t="n">
-        <x:v>2310.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FO72" s="8" t="n">
         <x:v>20.0000</x:v>
       </x:c>
       <x:c r="FP72" s="8" t="n">
-        <x:v>1.9300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FQ72" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -65544,13 +65544,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FH73" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1400.0000</x:v>
       </x:c>
       <x:c r="FI73" s="8" t="n">
         <x:v>20.0000</x:v>
       </x:c>
       <x:c r="FJ73" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.1700</x:v>
       </x:c>
       <x:c r="FK73" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -65562,13 +65562,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FN73" s="6" t="n">
-        <x:v>1400.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FO73" s="8" t="n">
         <x:v>20.0000</x:v>
       </x:c>
       <x:c r="FP73" s="8" t="n">
-        <x:v>1.1700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FQ73" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -66530,13 +66530,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FT74" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3200.0000</x:v>
       </x:c>
       <x:c r="FU74" s="8" t="n">
         <x:v>20.0000</x:v>
       </x:c>
       <x:c r="FV74" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.6700</x:v>
       </x:c>
       <x:c r="FW74" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -66548,13 +66548,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FZ74" s="6" t="n">
-        <x:v>3200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GA74" s="8" t="n">
         <x:v>20.0000</x:v>
       </x:c>
       <x:c r="GB74" s="8" t="n">
-        <x:v>2.6700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GC74" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -67480,13 +67480,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FT75" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1600.0000</x:v>
       </x:c>
       <x:c r="FU75" s="8" t="n">
         <x:v>20.0000</x:v>
       </x:c>
       <x:c r="FV75" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.3300</x:v>
       </x:c>
       <x:c r="FW75" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -67498,13 +67498,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FZ75" s="6" t="n">
-        <x:v>1600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GA75" s="8" t="n">
         <x:v>20.0000</x:v>
       </x:c>
       <x:c r="GB75" s="8" t="n">
-        <x:v>1.3300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GC75" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -68394,13 +68394,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FH76" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>600.0000</x:v>
       </x:c>
       <x:c r="FI76" s="8" t="n">
         <x:v>20.0000</x:v>
       </x:c>
       <x:c r="FJ76" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.5000</x:v>
       </x:c>
       <x:c r="FK76" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -68412,13 +68412,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FN76" s="6" t="n">
-        <x:v>600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FO76" s="8" t="n">
         <x:v>20.0000</x:v>
       </x:c>
       <x:c r="FP76" s="8" t="n">
-        <x:v>0.5000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FQ76" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -69209,229 +69209,229 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DO77" s="7" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4200.0000</x:v>
       </x:c>
       <x:c r="DP77" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="DQ77" s="9" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3.8700</x:v>
       </x:c>
       <x:c r="DR77" s="7" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4800.0000</x:v>
       </x:c>
       <x:c r="DS77" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="DT77" s="9" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6.5300</x:v>
       </x:c>
       <x:c r="DU77" s="7" t="n">
-        <x:v>4200.0000</x:v>
+        <x:v>7000.0000</x:v>
       </x:c>
       <x:c r="DV77" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="DW77" s="9" t="n">
-        <x:v>3.8700</x:v>
+        <x:v>6.6500</x:v>
       </x:c>
       <x:c r="DX77" s="7" t="n">
-        <x:v>4800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DY77" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="DZ77" s="9" t="n">
-        <x:v>6.5300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EA77" s="7" t="n">
-        <x:v>7000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EB77" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="EC77" s="9" t="n">
-        <x:v>6.6500</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ED77" s="7" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>23162.0000</x:v>
       </x:c>
       <x:c r="EE77" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="EF77" s="9" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>21.9700</x:v>
       </x:c>
       <x:c r="EG77" s="7" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>22900.0000</x:v>
       </x:c>
       <x:c r="EH77" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="EI77" s="9" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>22.4500</x:v>
       </x:c>
       <x:c r="EJ77" s="7" t="n">
-        <x:v>23162.0000</x:v>
+        <x:v>28800.0000</x:v>
       </x:c>
       <x:c r="EK77" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="EL77" s="9" t="n">
-        <x:v>21.9700</x:v>
+        <x:v>31.4400</x:v>
       </x:c>
       <x:c r="EM77" s="7" t="n">
-        <x:v>22900.0000</x:v>
+        <x:v>16360.0000</x:v>
       </x:c>
       <x:c r="EN77" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="EO77" s="9" t="n">
-        <x:v>22.4500</x:v>
+        <x:v>15.8700</x:v>
       </x:c>
       <x:c r="EP77" s="7" t="n">
-        <x:v>28800.0000</x:v>
+        <x:v>3943.0000</x:v>
       </x:c>
       <x:c r="EQ77" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="ER77" s="9" t="n">
-        <x:v>31.4400</x:v>
+        <x:v>3.2000</x:v>
       </x:c>
       <x:c r="ES77" s="7" t="n">
-        <x:v>16360.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ET77" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="EU77" s="9" t="n">
-        <x:v>15.8700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV77" s="7" t="n">
-        <x:v>3943.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EW77" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="EX77" s="9" t="n">
-        <x:v>3.2000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY77" s="7" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>21785.0000</x:v>
       </x:c>
       <x:c r="EZ77" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FA77" s="9" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>18.2900</x:v>
       </x:c>
       <x:c r="FB77" s="7" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>17295.0000</x:v>
       </x:c>
       <x:c r="FC77" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FD77" s="9" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>18.8700</x:v>
       </x:c>
       <x:c r="FE77" s="7" t="n">
-        <x:v>21785.0000</x:v>
+        <x:v>10300.0000</x:v>
       </x:c>
       <x:c r="FF77" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FG77" s="9" t="n">
-        <x:v>18.2900</x:v>
+        <x:v>15.6000</x:v>
       </x:c>
       <x:c r="FH77" s="7" t="n">
-        <x:v>17295.0000</x:v>
+        <x:v>12910.0000</x:v>
       </x:c>
       <x:c r="FI77" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FJ77" s="9" t="n">
-        <x:v>18.8700</x:v>
+        <x:v>16.7300</x:v>
       </x:c>
       <x:c r="FK77" s="7" t="n">
-        <x:v>10300.0000</x:v>
+        <x:v>4200.0000</x:v>
       </x:c>
       <x:c r="FL77" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FM77" s="9" t="n">
-        <x:v>15.6000</x:v>
+        <x:v>6.9200</x:v>
       </x:c>
       <x:c r="FN77" s="7" t="n">
-        <x:v>12910.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FO77" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FP77" s="9" t="n">
-        <x:v>16.7300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FQ77" s="7" t="n">
-        <x:v>4200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FR77" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FS77" s="9" t="n">
-        <x:v>6.9200</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FT77" s="7" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>9000.0000</x:v>
       </x:c>
       <x:c r="FU77" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FV77" s="9" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>10.9200</x:v>
       </x:c>
       <x:c r="FW77" s="7" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>14400.0000</x:v>
       </x:c>
       <x:c r="FX77" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FY77" s="9" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>13.7100</x:v>
       </x:c>
       <x:c r="FZ77" s="7" t="n">
-        <x:v>9000.0000</x:v>
+        <x:v>4200.0000</x:v>
       </x:c>
       <x:c r="GA77" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="GB77" s="9" t="n">
-        <x:v>10.9200</x:v>
+        <x:v>6.9200</x:v>
       </x:c>
       <x:c r="GC77" s="7" t="n">
-        <x:v>14400.0000</x:v>
+        <x:v>4200.0000</x:v>
       </x:c>
       <x:c r="GD77" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="GE77" s="9" t="n">
-        <x:v>13.7100</x:v>
+        <x:v>6.9200</x:v>
       </x:c>
       <x:c r="GF77" s="7" t="n">
-        <x:v>4200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GG77" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="GH77" s="9" t="n">
-        <x:v>6.9200</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GI77" s="7" t="n">
-        <x:v>4200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GJ77" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="GK77" s="9" t="n">
-        <x:v>6.9200</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GL77" s="7" t="n">
         <x:v>0.0000</x:v>

--- a/.pm-ai-cache/network-source/task-input-newest.xlsx
+++ b/.pm-ai-cache/network-source/task-input-newest.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工程別生産計画問合せ問合せ" sheetId="1" r:id="Rc5426f1cee3449dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工程別生産計画問合せ問合せ" sheetId="1" r:id="R8535f5ddcb1a405a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -10,7 +10,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6">
   <x:si>
-    <x:t xml:space="preserve">表示基準日 : 2026年06月05日 </x:t>
+    <x:t xml:space="preserve">表示基準日 : 2026年06月07日 </x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">S </x:t>
@@ -581,823 +581,823 @@
         <x:v/>
       </x:c>
       <x:c r="AR5" s="2" t="str">
-        <x:v>05/06(水)</x:v>
+        <x:v>05/08(金)</x:v>
       </x:c>
       <x:c r="AS5" s="2" t="str">
-        <x:v>05/06(水)</x:v>
+        <x:v>05/08(金)</x:v>
       </x:c>
       <x:c r="AT5" s="2" t="str">
-        <x:v>05/06(水)</x:v>
+        <x:v>05/08(金)</x:v>
       </x:c>
       <x:c r="AU5" s="2" t="str">
-        <x:v>05/07(木)</x:v>
+        <x:v>05/09(土)</x:v>
       </x:c>
       <x:c r="AV5" s="2" t="str">
-        <x:v>05/07(木)</x:v>
+        <x:v>05/09(土)</x:v>
       </x:c>
       <x:c r="AW5" s="2" t="str">
-        <x:v>05/07(木)</x:v>
+        <x:v>05/09(土)</x:v>
       </x:c>
       <x:c r="AX5" s="2" t="str">
-        <x:v>05/08(金)</x:v>
+        <x:v>05/10(日)</x:v>
       </x:c>
       <x:c r="AY5" s="2" t="str">
-        <x:v>05/08(金)</x:v>
+        <x:v>05/10(日)</x:v>
       </x:c>
       <x:c r="AZ5" s="2" t="str">
-        <x:v>05/08(金)</x:v>
+        <x:v>05/10(日)</x:v>
       </x:c>
       <x:c r="BA5" s="2" t="str">
-        <x:v>05/09(土)</x:v>
+        <x:v>05/11(月)</x:v>
       </x:c>
       <x:c r="BB5" s="2" t="str">
-        <x:v>05/09(土)</x:v>
+        <x:v>05/11(月)</x:v>
       </x:c>
       <x:c r="BC5" s="2" t="str">
-        <x:v>05/09(土)</x:v>
+        <x:v>05/11(月)</x:v>
       </x:c>
       <x:c r="BD5" s="2" t="str">
-        <x:v>05/10(日)</x:v>
+        <x:v>05/12(火)</x:v>
       </x:c>
       <x:c r="BE5" s="2" t="str">
-        <x:v>05/10(日)</x:v>
+        <x:v>05/12(火)</x:v>
       </x:c>
       <x:c r="BF5" s="2" t="str">
-        <x:v>05/10(日)</x:v>
+        <x:v>05/12(火)</x:v>
       </x:c>
       <x:c r="BG5" s="2" t="str">
-        <x:v>05/11(月)</x:v>
+        <x:v>05/13(水)</x:v>
       </x:c>
       <x:c r="BH5" s="2" t="str">
-        <x:v>05/11(月)</x:v>
+        <x:v>05/13(水)</x:v>
       </x:c>
       <x:c r="BI5" s="2" t="str">
-        <x:v>05/11(月)</x:v>
+        <x:v>05/13(水)</x:v>
       </x:c>
       <x:c r="BJ5" s="2" t="str">
-        <x:v>05/12(火)</x:v>
+        <x:v>05/14(木)</x:v>
       </x:c>
       <x:c r="BK5" s="2" t="str">
-        <x:v>05/12(火)</x:v>
+        <x:v>05/14(木)</x:v>
       </x:c>
       <x:c r="BL5" s="2" t="str">
-        <x:v>05/12(火)</x:v>
+        <x:v>05/14(木)</x:v>
       </x:c>
       <x:c r="BM5" s="2" t="str">
-        <x:v>05/13(水)</x:v>
+        <x:v>05/15(金)</x:v>
       </x:c>
       <x:c r="BN5" s="2" t="str">
-        <x:v>05/13(水)</x:v>
+        <x:v>05/15(金)</x:v>
       </x:c>
       <x:c r="BO5" s="2" t="str">
-        <x:v>05/13(水)</x:v>
+        <x:v>05/15(金)</x:v>
       </x:c>
       <x:c r="BP5" s="2" t="str">
-        <x:v>05/14(木)</x:v>
+        <x:v>05/16(土)</x:v>
       </x:c>
       <x:c r="BQ5" s="2" t="str">
-        <x:v>05/14(木)</x:v>
+        <x:v>05/16(土)</x:v>
       </x:c>
       <x:c r="BR5" s="2" t="str">
-        <x:v>05/14(木)</x:v>
+        <x:v>05/16(土)</x:v>
       </x:c>
       <x:c r="BS5" s="2" t="str">
-        <x:v>05/15(金)</x:v>
+        <x:v>05/17(日)</x:v>
       </x:c>
       <x:c r="BT5" s="2" t="str">
-        <x:v>05/15(金)</x:v>
+        <x:v>05/17(日)</x:v>
       </x:c>
       <x:c r="BU5" s="2" t="str">
-        <x:v>05/15(金)</x:v>
+        <x:v>05/17(日)</x:v>
       </x:c>
       <x:c r="BV5" s="2" t="str">
-        <x:v>05/16(土)</x:v>
+        <x:v>05/18(月)</x:v>
       </x:c>
       <x:c r="BW5" s="2" t="str">
-        <x:v>05/16(土)</x:v>
+        <x:v>05/18(月)</x:v>
       </x:c>
       <x:c r="BX5" s="2" t="str">
-        <x:v>05/16(土)</x:v>
+        <x:v>05/18(月)</x:v>
       </x:c>
       <x:c r="BY5" s="2" t="str">
-        <x:v>05/17(日)</x:v>
+        <x:v>05/19(火)</x:v>
       </x:c>
       <x:c r="BZ5" s="2" t="str">
-        <x:v>05/17(日)</x:v>
+        <x:v>05/19(火)</x:v>
       </x:c>
       <x:c r="CA5" s="2" t="str">
-        <x:v>05/17(日)</x:v>
+        <x:v>05/19(火)</x:v>
       </x:c>
       <x:c r="CB5" s="2" t="str">
-        <x:v>05/18(月)</x:v>
+        <x:v>05/20(水)</x:v>
       </x:c>
       <x:c r="CC5" s="2" t="str">
-        <x:v>05/18(月)</x:v>
+        <x:v>05/20(水)</x:v>
       </x:c>
       <x:c r="CD5" s="2" t="str">
-        <x:v>05/18(月)</x:v>
+        <x:v>05/20(水)</x:v>
       </x:c>
       <x:c r="CE5" s="2" t="str">
-        <x:v>05/19(火)</x:v>
+        <x:v>05/21(木)</x:v>
       </x:c>
       <x:c r="CF5" s="2" t="str">
-        <x:v>05/19(火)</x:v>
+        <x:v>05/21(木)</x:v>
       </x:c>
       <x:c r="CG5" s="2" t="str">
-        <x:v>05/19(火)</x:v>
+        <x:v>05/21(木)</x:v>
       </x:c>
       <x:c r="CH5" s="2" t="str">
-        <x:v>05/20(水)</x:v>
+        <x:v>05/22(金)</x:v>
       </x:c>
       <x:c r="CI5" s="2" t="str">
-        <x:v>05/20(水)</x:v>
+        <x:v>05/22(金)</x:v>
       </x:c>
       <x:c r="CJ5" s="2" t="str">
-        <x:v>05/20(水)</x:v>
+        <x:v>05/22(金)</x:v>
       </x:c>
       <x:c r="CK5" s="2" t="str">
-        <x:v>05/21(木)</x:v>
+        <x:v>05/23(土)</x:v>
       </x:c>
       <x:c r="CL5" s="2" t="str">
-        <x:v>05/21(木)</x:v>
+        <x:v>05/23(土)</x:v>
       </x:c>
       <x:c r="CM5" s="2" t="str">
-        <x:v>05/21(木)</x:v>
+        <x:v>05/23(土)</x:v>
       </x:c>
       <x:c r="CN5" s="2" t="str">
-        <x:v>05/22(金)</x:v>
+        <x:v>05/24(日)</x:v>
       </x:c>
       <x:c r="CO5" s="2" t="str">
-        <x:v>05/22(金)</x:v>
+        <x:v>05/24(日)</x:v>
       </x:c>
       <x:c r="CP5" s="2" t="str">
-        <x:v>05/22(金)</x:v>
+        <x:v>05/24(日)</x:v>
       </x:c>
       <x:c r="CQ5" s="2" t="str">
-        <x:v>05/23(土)</x:v>
+        <x:v>05/25(月)</x:v>
       </x:c>
       <x:c r="CR5" s="2" t="str">
-        <x:v>05/23(土)</x:v>
+        <x:v>05/25(月)</x:v>
       </x:c>
       <x:c r="CS5" s="2" t="str">
-        <x:v>05/23(土)</x:v>
+        <x:v>05/25(月)</x:v>
       </x:c>
       <x:c r="CT5" s="2" t="str">
-        <x:v>05/24(日)</x:v>
+        <x:v>05/26(火)</x:v>
       </x:c>
       <x:c r="CU5" s="2" t="str">
-        <x:v>05/24(日)</x:v>
+        <x:v>05/26(火)</x:v>
       </x:c>
       <x:c r="CV5" s="2" t="str">
-        <x:v>05/24(日)</x:v>
+        <x:v>05/26(火)</x:v>
       </x:c>
       <x:c r="CW5" s="2" t="str">
-        <x:v>05/25(月)</x:v>
+        <x:v>05/27(水)</x:v>
       </x:c>
       <x:c r="CX5" s="2" t="str">
-        <x:v>05/25(月)</x:v>
+        <x:v>05/27(水)</x:v>
       </x:c>
       <x:c r="CY5" s="2" t="str">
-        <x:v>05/25(月)</x:v>
+        <x:v>05/27(水)</x:v>
       </x:c>
       <x:c r="CZ5" s="2" t="str">
-        <x:v>05/26(火)</x:v>
+        <x:v>05/28(木)</x:v>
       </x:c>
       <x:c r="DA5" s="2" t="str">
-        <x:v>05/26(火)</x:v>
+        <x:v>05/28(木)</x:v>
       </x:c>
       <x:c r="DB5" s="2" t="str">
-        <x:v>05/26(火)</x:v>
+        <x:v>05/28(木)</x:v>
       </x:c>
       <x:c r="DC5" s="2" t="str">
-        <x:v>05/27(水)</x:v>
+        <x:v>05/29(金)</x:v>
       </x:c>
       <x:c r="DD5" s="2" t="str">
-        <x:v>05/27(水)</x:v>
+        <x:v>05/29(金)</x:v>
       </x:c>
       <x:c r="DE5" s="2" t="str">
-        <x:v>05/27(水)</x:v>
+        <x:v>05/29(金)</x:v>
       </x:c>
       <x:c r="DF5" s="2" t="str">
-        <x:v>05/28(木)</x:v>
+        <x:v>05/30(土)</x:v>
       </x:c>
       <x:c r="DG5" s="2" t="str">
-        <x:v>05/28(木)</x:v>
+        <x:v>05/30(土)</x:v>
       </x:c>
       <x:c r="DH5" s="2" t="str">
-        <x:v>05/28(木)</x:v>
+        <x:v>05/30(土)</x:v>
       </x:c>
       <x:c r="DI5" s="2" t="str">
-        <x:v>05/29(金)</x:v>
+        <x:v>05/31(日)</x:v>
       </x:c>
       <x:c r="DJ5" s="2" t="str">
-        <x:v>05/29(金)</x:v>
+        <x:v>05/31(日)</x:v>
       </x:c>
       <x:c r="DK5" s="2" t="str">
-        <x:v>05/29(金)</x:v>
+        <x:v>05/31(日)</x:v>
       </x:c>
       <x:c r="DL5" s="2" t="str">
-        <x:v>05/30(土)</x:v>
+        <x:v>06/01(月)</x:v>
       </x:c>
       <x:c r="DM5" s="2" t="str">
-        <x:v>05/30(土)</x:v>
+        <x:v>06/01(月)</x:v>
       </x:c>
       <x:c r="DN5" s="2" t="str">
-        <x:v>05/30(土)</x:v>
+        <x:v>06/01(月)</x:v>
       </x:c>
       <x:c r="DO5" s="2" t="str">
-        <x:v>05/31(日)</x:v>
+        <x:v>06/02(火)</x:v>
       </x:c>
       <x:c r="DP5" s="2" t="str">
-        <x:v>05/31(日)</x:v>
+        <x:v>06/02(火)</x:v>
       </x:c>
       <x:c r="DQ5" s="2" t="str">
-        <x:v>05/31(日)</x:v>
+        <x:v>06/02(火)</x:v>
       </x:c>
       <x:c r="DR5" s="2" t="str">
-        <x:v>06/01(月)</x:v>
+        <x:v>06/03(水)</x:v>
       </x:c>
       <x:c r="DS5" s="2" t="str">
-        <x:v>06/01(月)</x:v>
+        <x:v>06/03(水)</x:v>
       </x:c>
       <x:c r="DT5" s="2" t="str">
-        <x:v>06/01(月)</x:v>
+        <x:v>06/03(水)</x:v>
       </x:c>
       <x:c r="DU5" s="2" t="str">
-        <x:v>06/02(火)</x:v>
+        <x:v>06/04(木)</x:v>
       </x:c>
       <x:c r="DV5" s="2" t="str">
-        <x:v>06/02(火)</x:v>
+        <x:v>06/04(木)</x:v>
       </x:c>
       <x:c r="DW5" s="2" t="str">
-        <x:v>06/02(火)</x:v>
+        <x:v>06/04(木)</x:v>
       </x:c>
       <x:c r="DX5" s="2" t="str">
-        <x:v>06/03(水)</x:v>
+        <x:v>06/05(金)</x:v>
       </x:c>
       <x:c r="DY5" s="2" t="str">
-        <x:v>06/03(水)</x:v>
+        <x:v>06/05(金)</x:v>
       </x:c>
       <x:c r="DZ5" s="2" t="str">
-        <x:v>06/03(水)</x:v>
+        <x:v>06/05(金)</x:v>
       </x:c>
       <x:c r="EA5" s="2" t="str">
-        <x:v>06/04(木)</x:v>
+        <x:v>06/06(土)</x:v>
       </x:c>
       <x:c r="EB5" s="2" t="str">
-        <x:v>06/04(木)</x:v>
+        <x:v>06/06(土)</x:v>
       </x:c>
       <x:c r="EC5" s="2" t="str">
-        <x:v>06/04(木)</x:v>
+        <x:v>06/06(土)</x:v>
       </x:c>
       <x:c r="ED5" s="2" t="str">
-        <x:v>06/05(金)</x:v>
+        <x:v>06/07(日)</x:v>
       </x:c>
       <x:c r="EE5" s="2" t="str">
-        <x:v>06/05(金)</x:v>
+        <x:v>06/07(日)</x:v>
       </x:c>
       <x:c r="EF5" s="2" t="str">
-        <x:v>06/05(金)</x:v>
+        <x:v>06/07(日)</x:v>
       </x:c>
       <x:c r="EG5" s="2" t="str">
-        <x:v>06/06(土)</x:v>
+        <x:v>06/08(月)</x:v>
       </x:c>
       <x:c r="EH5" s="2" t="str">
-        <x:v>06/06(土)</x:v>
+        <x:v>06/08(月)</x:v>
       </x:c>
       <x:c r="EI5" s="2" t="str">
-        <x:v>06/06(土)</x:v>
+        <x:v>06/08(月)</x:v>
       </x:c>
       <x:c r="EJ5" s="2" t="str">
-        <x:v>06/07(日)</x:v>
+        <x:v>06/09(火)</x:v>
       </x:c>
       <x:c r="EK5" s="2" t="str">
-        <x:v>06/07(日)</x:v>
+        <x:v>06/09(火)</x:v>
       </x:c>
       <x:c r="EL5" s="2" t="str">
-        <x:v>06/07(日)</x:v>
+        <x:v>06/09(火)</x:v>
       </x:c>
       <x:c r="EM5" s="2" t="str">
-        <x:v>06/08(月)</x:v>
+        <x:v>06/10(水)</x:v>
       </x:c>
       <x:c r="EN5" s="2" t="str">
-        <x:v>06/08(月)</x:v>
+        <x:v>06/10(水)</x:v>
       </x:c>
       <x:c r="EO5" s="2" t="str">
-        <x:v>06/08(月)</x:v>
+        <x:v>06/10(水)</x:v>
       </x:c>
       <x:c r="EP5" s="2" t="str">
-        <x:v>06/09(火)</x:v>
+        <x:v>06/11(木)</x:v>
       </x:c>
       <x:c r="EQ5" s="2" t="str">
-        <x:v>06/09(火)</x:v>
+        <x:v>06/11(木)</x:v>
       </x:c>
       <x:c r="ER5" s="2" t="str">
-        <x:v>06/09(火)</x:v>
+        <x:v>06/11(木)</x:v>
       </x:c>
       <x:c r="ES5" s="2" t="str">
-        <x:v>06/10(水)</x:v>
+        <x:v>06/12(金)</x:v>
       </x:c>
       <x:c r="ET5" s="2" t="str">
-        <x:v>06/10(水)</x:v>
+        <x:v>06/12(金)</x:v>
       </x:c>
       <x:c r="EU5" s="2" t="str">
-        <x:v>06/10(水)</x:v>
+        <x:v>06/12(金)</x:v>
       </x:c>
       <x:c r="EV5" s="2" t="str">
-        <x:v>06/11(木)</x:v>
+        <x:v>06/13(土)</x:v>
       </x:c>
       <x:c r="EW5" s="2" t="str">
-        <x:v>06/11(木)</x:v>
+        <x:v>06/13(土)</x:v>
       </x:c>
       <x:c r="EX5" s="2" t="str">
-        <x:v>06/11(木)</x:v>
+        <x:v>06/13(土)</x:v>
       </x:c>
       <x:c r="EY5" s="2" t="str">
-        <x:v>06/12(金)</x:v>
+        <x:v>06/14(日)</x:v>
       </x:c>
       <x:c r="EZ5" s="2" t="str">
-        <x:v>06/12(金)</x:v>
+        <x:v>06/14(日)</x:v>
       </x:c>
       <x:c r="FA5" s="2" t="str">
-        <x:v>06/12(金)</x:v>
+        <x:v>06/14(日)</x:v>
       </x:c>
       <x:c r="FB5" s="2" t="str">
-        <x:v>06/13(土)</x:v>
+        <x:v>06/15(月)</x:v>
       </x:c>
       <x:c r="FC5" s="2" t="str">
-        <x:v>06/13(土)</x:v>
+        <x:v>06/15(月)</x:v>
       </x:c>
       <x:c r="FD5" s="2" t="str">
-        <x:v>06/13(土)</x:v>
+        <x:v>06/15(月)</x:v>
       </x:c>
       <x:c r="FE5" s="2" t="str">
-        <x:v>06/14(日)</x:v>
+        <x:v>06/16(火)</x:v>
       </x:c>
       <x:c r="FF5" s="2" t="str">
-        <x:v>06/14(日)</x:v>
+        <x:v>06/16(火)</x:v>
       </x:c>
       <x:c r="FG5" s="2" t="str">
-        <x:v>06/14(日)</x:v>
+        <x:v>06/16(火)</x:v>
       </x:c>
       <x:c r="FH5" s="2" t="str">
-        <x:v>06/15(月)</x:v>
+        <x:v>06/17(水)</x:v>
       </x:c>
       <x:c r="FI5" s="2" t="str">
-        <x:v>06/15(月)</x:v>
+        <x:v>06/17(水)</x:v>
       </x:c>
       <x:c r="FJ5" s="2" t="str">
-        <x:v>06/15(月)</x:v>
+        <x:v>06/17(水)</x:v>
       </x:c>
       <x:c r="FK5" s="2" t="str">
-        <x:v>06/16(火)</x:v>
+        <x:v>06/18(木)</x:v>
       </x:c>
       <x:c r="FL5" s="2" t="str">
-        <x:v>06/16(火)</x:v>
+        <x:v>06/18(木)</x:v>
       </x:c>
       <x:c r="FM5" s="2" t="str">
-        <x:v>06/16(火)</x:v>
+        <x:v>06/18(木)</x:v>
       </x:c>
       <x:c r="FN5" s="2" t="str">
-        <x:v>06/17(水)</x:v>
+        <x:v>06/19(金)</x:v>
       </x:c>
       <x:c r="FO5" s="2" t="str">
-        <x:v>06/17(水)</x:v>
+        <x:v>06/19(金)</x:v>
       </x:c>
       <x:c r="FP5" s="2" t="str">
-        <x:v>06/17(水)</x:v>
+        <x:v>06/19(金)</x:v>
       </x:c>
       <x:c r="FQ5" s="2" t="str">
-        <x:v>06/18(木)</x:v>
+        <x:v>06/20(土)</x:v>
       </x:c>
       <x:c r="FR5" s="2" t="str">
-        <x:v>06/18(木)</x:v>
+        <x:v>06/20(土)</x:v>
       </x:c>
       <x:c r="FS5" s="2" t="str">
-        <x:v>06/18(木)</x:v>
+        <x:v>06/20(土)</x:v>
       </x:c>
       <x:c r="FT5" s="2" t="str">
-        <x:v>06/19(金)</x:v>
+        <x:v>06/21(日)</x:v>
       </x:c>
       <x:c r="FU5" s="2" t="str">
-        <x:v>06/19(金)</x:v>
+        <x:v>06/21(日)</x:v>
       </x:c>
       <x:c r="FV5" s="2" t="str">
-        <x:v>06/19(金)</x:v>
+        <x:v>06/21(日)</x:v>
       </x:c>
       <x:c r="FW5" s="2" t="str">
-        <x:v>06/20(土)</x:v>
+        <x:v>06/22(月)</x:v>
       </x:c>
       <x:c r="FX5" s="2" t="str">
-        <x:v>06/20(土)</x:v>
+        <x:v>06/22(月)</x:v>
       </x:c>
       <x:c r="FY5" s="2" t="str">
-        <x:v>06/20(土)</x:v>
+        <x:v>06/22(月)</x:v>
       </x:c>
       <x:c r="FZ5" s="2" t="str">
-        <x:v>06/21(日)</x:v>
+        <x:v>06/23(火)</x:v>
       </x:c>
       <x:c r="GA5" s="2" t="str">
-        <x:v>06/21(日)</x:v>
+        <x:v>06/23(火)</x:v>
       </x:c>
       <x:c r="GB5" s="2" t="str">
-        <x:v>06/21(日)</x:v>
+        <x:v>06/23(火)</x:v>
       </x:c>
       <x:c r="GC5" s="2" t="str">
-        <x:v>06/22(月)</x:v>
+        <x:v>06/24(水)</x:v>
       </x:c>
       <x:c r="GD5" s="2" t="str">
-        <x:v>06/22(月)</x:v>
+        <x:v>06/24(水)</x:v>
       </x:c>
       <x:c r="GE5" s="2" t="str">
-        <x:v>06/22(月)</x:v>
+        <x:v>06/24(水)</x:v>
       </x:c>
       <x:c r="GF5" s="2" t="str">
-        <x:v>06/23(火)</x:v>
+        <x:v>06/25(木)</x:v>
       </x:c>
       <x:c r="GG5" s="2" t="str">
-        <x:v>06/23(火)</x:v>
+        <x:v>06/25(木)</x:v>
       </x:c>
       <x:c r="GH5" s="2" t="str">
-        <x:v>06/23(火)</x:v>
+        <x:v>06/25(木)</x:v>
       </x:c>
       <x:c r="GI5" s="2" t="str">
-        <x:v>06/24(水)</x:v>
+        <x:v>06/26(金)</x:v>
       </x:c>
       <x:c r="GJ5" s="2" t="str">
-        <x:v>06/24(水)</x:v>
+        <x:v>06/26(金)</x:v>
       </x:c>
       <x:c r="GK5" s="2" t="str">
-        <x:v>06/24(水)</x:v>
+        <x:v>06/26(金)</x:v>
       </x:c>
       <x:c r="GL5" s="2" t="str">
-        <x:v>06/25(木)</x:v>
+        <x:v>06/27(土)</x:v>
       </x:c>
       <x:c r="GM5" s="2" t="str">
-        <x:v>06/25(木)</x:v>
+        <x:v>06/27(土)</x:v>
       </x:c>
       <x:c r="GN5" s="2" t="str">
-        <x:v>06/25(木)</x:v>
+        <x:v>06/27(土)</x:v>
       </x:c>
       <x:c r="GO5" s="2" t="str">
-        <x:v>06/26(金)</x:v>
+        <x:v>06/28(日)</x:v>
       </x:c>
       <x:c r="GP5" s="2" t="str">
-        <x:v>06/26(金)</x:v>
+        <x:v>06/28(日)</x:v>
       </x:c>
       <x:c r="GQ5" s="2" t="str">
-        <x:v>06/26(金)</x:v>
+        <x:v>06/28(日)</x:v>
       </x:c>
       <x:c r="GR5" s="2" t="str">
-        <x:v>06/27(土)</x:v>
+        <x:v>06/29(月)</x:v>
       </x:c>
       <x:c r="GS5" s="2" t="str">
-        <x:v>06/27(土)</x:v>
+        <x:v>06/29(月)</x:v>
       </x:c>
       <x:c r="GT5" s="2" t="str">
-        <x:v>06/27(土)</x:v>
+        <x:v>06/29(月)</x:v>
       </x:c>
       <x:c r="GU5" s="2" t="str">
-        <x:v>06/28(日)</x:v>
+        <x:v>06/30(火)</x:v>
       </x:c>
       <x:c r="GV5" s="2" t="str">
-        <x:v>06/28(日)</x:v>
+        <x:v>06/30(火)</x:v>
       </x:c>
       <x:c r="GW5" s="2" t="str">
-        <x:v>06/28(日)</x:v>
+        <x:v>06/30(火)</x:v>
       </x:c>
       <x:c r="GX5" s="2" t="str">
-        <x:v>06/29(月)</x:v>
+        <x:v>07/01(水)</x:v>
       </x:c>
       <x:c r="GY5" s="2" t="str">
-        <x:v>06/29(月)</x:v>
+        <x:v>07/01(水)</x:v>
       </x:c>
       <x:c r="GZ5" s="2" t="str">
-        <x:v>06/29(月)</x:v>
+        <x:v>07/01(水)</x:v>
       </x:c>
       <x:c r="HA5" s="2" t="str">
-        <x:v>06/30(火)</x:v>
+        <x:v>07/02(木)</x:v>
       </x:c>
       <x:c r="HB5" s="2" t="str">
-        <x:v>06/30(火)</x:v>
+        <x:v>07/02(木)</x:v>
       </x:c>
       <x:c r="HC5" s="2" t="str">
-        <x:v>06/30(火)</x:v>
+        <x:v>07/02(木)</x:v>
       </x:c>
       <x:c r="HD5" s="2" t="str">
-        <x:v>07/01(水)</x:v>
+        <x:v>07/03(金)</x:v>
       </x:c>
       <x:c r="HE5" s="2" t="str">
-        <x:v>07/01(水)</x:v>
+        <x:v>07/03(金)</x:v>
       </x:c>
       <x:c r="HF5" s="2" t="str">
-        <x:v>07/01(水)</x:v>
+        <x:v>07/03(金)</x:v>
       </x:c>
       <x:c r="HG5" s="2" t="str">
-        <x:v>07/02(木)</x:v>
+        <x:v>07/04(土)</x:v>
       </x:c>
       <x:c r="HH5" s="2" t="str">
-        <x:v>07/02(木)</x:v>
+        <x:v>07/04(土)</x:v>
       </x:c>
       <x:c r="HI5" s="2" t="str">
-        <x:v>07/02(木)</x:v>
+        <x:v>07/04(土)</x:v>
       </x:c>
       <x:c r="HJ5" s="2" t="str">
-        <x:v>07/03(金)</x:v>
+        <x:v>07/05(日)</x:v>
       </x:c>
       <x:c r="HK5" s="2" t="str">
-        <x:v>07/03(金)</x:v>
+        <x:v>07/05(日)</x:v>
       </x:c>
       <x:c r="HL5" s="2" t="str">
-        <x:v>07/03(金)</x:v>
+        <x:v>07/05(日)</x:v>
       </x:c>
       <x:c r="HM5" s="2" t="str">
-        <x:v>07/04(土)</x:v>
+        <x:v>07/06(月)</x:v>
       </x:c>
       <x:c r="HN5" s="2" t="str">
-        <x:v>07/04(土)</x:v>
+        <x:v>07/06(月)</x:v>
       </x:c>
       <x:c r="HO5" s="2" t="str">
-        <x:v>07/04(土)</x:v>
+        <x:v>07/06(月)</x:v>
       </x:c>
       <x:c r="HP5" s="2" t="str">
-        <x:v>07/05(日)</x:v>
+        <x:v>07/07(火)</x:v>
       </x:c>
       <x:c r="HQ5" s="2" t="str">
-        <x:v>07/05(日)</x:v>
+        <x:v>07/07(火)</x:v>
       </x:c>
       <x:c r="HR5" s="2" t="str">
-        <x:v>07/05(日)</x:v>
+        <x:v>07/07(火)</x:v>
       </x:c>
       <x:c r="HS5" s="2" t="str">
-        <x:v>07/06(月)</x:v>
+        <x:v>07/08(水)</x:v>
       </x:c>
       <x:c r="HT5" s="2" t="str">
-        <x:v>07/06(月)</x:v>
+        <x:v>07/08(水)</x:v>
       </x:c>
       <x:c r="HU5" s="2" t="str">
-        <x:v>07/06(月)</x:v>
+        <x:v>07/08(水)</x:v>
       </x:c>
       <x:c r="HV5" s="2" t="str">
-        <x:v>07/07(火)</x:v>
+        <x:v>07/09(木)</x:v>
       </x:c>
       <x:c r="HW5" s="2" t="str">
-        <x:v>07/07(火)</x:v>
+        <x:v>07/09(木)</x:v>
       </x:c>
       <x:c r="HX5" s="2" t="str">
-        <x:v>07/07(火)</x:v>
+        <x:v>07/09(木)</x:v>
       </x:c>
       <x:c r="HY5" s="2" t="str">
-        <x:v>07/08(水)</x:v>
+        <x:v>07/10(金)</x:v>
       </x:c>
       <x:c r="HZ5" s="2" t="str">
-        <x:v>07/08(水)</x:v>
+        <x:v>07/10(金)</x:v>
       </x:c>
       <x:c r="IA5" s="2" t="str">
-        <x:v>07/08(水)</x:v>
+        <x:v>07/10(金)</x:v>
       </x:c>
       <x:c r="IB5" s="2" t="str">
-        <x:v>07/09(木)</x:v>
+        <x:v>07/11(土)</x:v>
       </x:c>
       <x:c r="IC5" s="2" t="str">
-        <x:v>07/09(木)</x:v>
+        <x:v>07/11(土)</x:v>
       </x:c>
       <x:c r="ID5" s="2" t="str">
-        <x:v>07/09(木)</x:v>
+        <x:v>07/11(土)</x:v>
       </x:c>
       <x:c r="IE5" s="2" t="str">
-        <x:v>07/10(金)</x:v>
+        <x:v>07/12(日)</x:v>
       </x:c>
       <x:c r="IF5" s="2" t="str">
-        <x:v>07/10(金)</x:v>
+        <x:v>07/12(日)</x:v>
       </x:c>
       <x:c r="IG5" s="2" t="str">
-        <x:v>07/10(金)</x:v>
+        <x:v>07/12(日)</x:v>
       </x:c>
       <x:c r="IH5" s="2" t="str">
-        <x:v>07/11(土)</x:v>
+        <x:v>07/13(月)</x:v>
       </x:c>
       <x:c r="II5" s="2" t="str">
-        <x:v>07/11(土)</x:v>
+        <x:v>07/13(月)</x:v>
       </x:c>
       <x:c r="IJ5" s="2" t="str">
-        <x:v>07/11(土)</x:v>
+        <x:v>07/13(月)</x:v>
       </x:c>
       <x:c r="IK5" s="2" t="str">
-        <x:v>07/12(日)</x:v>
+        <x:v>07/14(火)</x:v>
       </x:c>
       <x:c r="IL5" s="2" t="str">
-        <x:v>07/12(日)</x:v>
+        <x:v>07/14(火)</x:v>
       </x:c>
       <x:c r="IM5" s="2" t="str">
-        <x:v>07/12(日)</x:v>
+        <x:v>07/14(火)</x:v>
       </x:c>
       <x:c r="IN5" s="2" t="str">
-        <x:v>07/13(月)</x:v>
+        <x:v>07/15(水)</x:v>
       </x:c>
       <x:c r="IO5" s="2" t="str">
-        <x:v>07/13(月)</x:v>
+        <x:v>07/15(水)</x:v>
       </x:c>
       <x:c r="IP5" s="2" t="str">
-        <x:v>07/13(月)</x:v>
+        <x:v>07/15(水)</x:v>
       </x:c>
       <x:c r="IQ5" s="2" t="str">
-        <x:v>07/14(火)</x:v>
+        <x:v>07/16(木)</x:v>
       </x:c>
       <x:c r="IR5" s="2" t="str">
-        <x:v>07/14(火)</x:v>
+        <x:v>07/16(木)</x:v>
       </x:c>
       <x:c r="IS5" s="2" t="str">
-        <x:v>07/14(火)</x:v>
+        <x:v>07/16(木)</x:v>
       </x:c>
       <x:c r="IT5" s="2" t="str">
-        <x:v>07/15(水)</x:v>
+        <x:v>07/17(金)</x:v>
       </x:c>
       <x:c r="IU5" s="2" t="str">
-        <x:v>07/15(水)</x:v>
+        <x:v>07/17(金)</x:v>
       </x:c>
       <x:c r="IV5" s="2" t="str">
-        <x:v>07/15(水)</x:v>
+        <x:v>07/17(金)</x:v>
       </x:c>
       <x:c r="IW5" s="2" t="str">
-        <x:v>07/16(木)</x:v>
+        <x:v>07/18(土)</x:v>
       </x:c>
       <x:c r="IX5" s="2" t="str">
-        <x:v>07/16(木)</x:v>
+        <x:v>07/18(土)</x:v>
       </x:c>
       <x:c r="IY5" s="2" t="str">
-        <x:v>07/16(木)</x:v>
+        <x:v>07/18(土)</x:v>
       </x:c>
       <x:c r="IZ5" s="2" t="str">
-        <x:v>07/17(金)</x:v>
+        <x:v>07/19(日)</x:v>
       </x:c>
       <x:c r="JA5" s="2" t="str">
-        <x:v>07/17(金)</x:v>
+        <x:v>07/19(日)</x:v>
       </x:c>
       <x:c r="JB5" s="2" t="str">
-        <x:v>07/17(金)</x:v>
+        <x:v>07/19(日)</x:v>
       </x:c>
       <x:c r="JC5" s="2" t="str">
-        <x:v>07/18(土)</x:v>
+        <x:v>07/20(月)</x:v>
       </x:c>
       <x:c r="JD5" s="2" t="str">
-        <x:v>07/18(土)</x:v>
+        <x:v>07/20(月)</x:v>
       </x:c>
       <x:c r="JE5" s="2" t="str">
-        <x:v>07/18(土)</x:v>
+        <x:v>07/20(月)</x:v>
       </x:c>
       <x:c r="JF5" s="2" t="str">
-        <x:v>07/19(日)</x:v>
+        <x:v>07/21(火)</x:v>
       </x:c>
       <x:c r="JG5" s="2" t="str">
-        <x:v>07/19(日)</x:v>
+        <x:v>07/21(火)</x:v>
       </x:c>
       <x:c r="JH5" s="2" t="str">
-        <x:v>07/19(日)</x:v>
+        <x:v>07/21(火)</x:v>
       </x:c>
       <x:c r="JI5" s="2" t="str">
-        <x:v>07/20(月)</x:v>
+        <x:v>07/22(水)</x:v>
       </x:c>
       <x:c r="JJ5" s="2" t="str">
-        <x:v>07/20(月)</x:v>
+        <x:v>07/22(水)</x:v>
       </x:c>
       <x:c r="JK5" s="2" t="str">
-        <x:v>07/20(月)</x:v>
+        <x:v>07/22(水)</x:v>
       </x:c>
       <x:c r="JL5" s="2" t="str">
-        <x:v>07/21(火)</x:v>
+        <x:v>07/23(木)</x:v>
       </x:c>
       <x:c r="JM5" s="2" t="str">
-        <x:v>07/21(火)</x:v>
+        <x:v>07/23(木)</x:v>
       </x:c>
       <x:c r="JN5" s="2" t="str">
-        <x:v>07/21(火)</x:v>
+        <x:v>07/23(木)</x:v>
       </x:c>
       <x:c r="JO5" s="2" t="str">
-        <x:v>07/22(水)</x:v>
+        <x:v>07/24(金)</x:v>
       </x:c>
       <x:c r="JP5" s="2" t="str">
-        <x:v>07/22(水)</x:v>
+        <x:v>07/24(金)</x:v>
       </x:c>
       <x:c r="JQ5" s="2" t="str">
-        <x:v>07/22(水)</x:v>
+        <x:v>07/24(金)</x:v>
       </x:c>
       <x:c r="JR5" s="2" t="str">
-        <x:v>07/23(木)</x:v>
+        <x:v>07/25(土)</x:v>
       </x:c>
       <x:c r="JS5" s="2" t="str">
-        <x:v>07/23(木)</x:v>
+        <x:v>07/25(土)</x:v>
       </x:c>
       <x:c r="JT5" s="2" t="str">
-        <x:v>07/23(木)</x:v>
+        <x:v>07/25(土)</x:v>
       </x:c>
       <x:c r="JU5" s="2" t="str">
-        <x:v>07/24(金)</x:v>
+        <x:v>07/26(日)</x:v>
       </x:c>
       <x:c r="JV5" s="2" t="str">
-        <x:v>07/24(金)</x:v>
+        <x:v>07/26(日)</x:v>
       </x:c>
       <x:c r="JW5" s="2" t="str">
-        <x:v>07/24(金)</x:v>
+        <x:v>07/26(日)</x:v>
       </x:c>
       <x:c r="JX5" s="2" t="str">
-        <x:v>07/25(土)</x:v>
+        <x:v>07/27(月)</x:v>
       </x:c>
       <x:c r="JY5" s="2" t="str">
-        <x:v>07/25(土)</x:v>
+        <x:v>07/27(月)</x:v>
       </x:c>
       <x:c r="JZ5" s="2" t="str">
-        <x:v>07/25(土)</x:v>
+        <x:v>07/27(月)</x:v>
       </x:c>
       <x:c r="KA5" s="2" t="str">
-        <x:v>07/26(日)</x:v>
+        <x:v>07/28(火)</x:v>
       </x:c>
       <x:c r="KB5" s="2" t="str">
-        <x:v>07/26(日)</x:v>
+        <x:v>07/28(火)</x:v>
       </x:c>
       <x:c r="KC5" s="2" t="str">
-        <x:v>07/26(日)</x:v>
+        <x:v>07/28(火)</x:v>
       </x:c>
       <x:c r="KD5" s="2" t="str">
-        <x:v>07/27(月)</x:v>
+        <x:v>07/29(水)</x:v>
       </x:c>
       <x:c r="KE5" s="2" t="str">
-        <x:v>07/27(月)</x:v>
+        <x:v>07/29(水)</x:v>
       </x:c>
       <x:c r="KF5" s="2" t="str">
-        <x:v>07/27(月)</x:v>
+        <x:v>07/29(水)</x:v>
       </x:c>
       <x:c r="KG5" s="2" t="str">
-        <x:v>07/28(火)</x:v>
+        <x:v>07/30(木)</x:v>
       </x:c>
       <x:c r="KH5" s="2" t="str">
-        <x:v>07/28(火)</x:v>
+        <x:v>07/30(木)</x:v>
       </x:c>
       <x:c r="KI5" s="2" t="str">
-        <x:v>07/28(火)</x:v>
+        <x:v>07/30(木)</x:v>
       </x:c>
       <x:c r="KJ5" s="2" t="str">
-        <x:v>07/29(水)</x:v>
+        <x:v>07/31(金)</x:v>
       </x:c>
       <x:c r="KK5" s="2" t="str">
-        <x:v>07/29(水)</x:v>
+        <x:v>07/31(金)</x:v>
       </x:c>
       <x:c r="KL5" s="2" t="str">
-        <x:v>07/29(水)</x:v>
+        <x:v>07/31(金)</x:v>
       </x:c>
       <x:c r="KM5" s="2" t="str">
-        <x:v>07/30(木)</x:v>
+        <x:v>08/01(土)</x:v>
       </x:c>
       <x:c r="KN5" s="2" t="str">
-        <x:v>07/30(木)</x:v>
+        <x:v>08/01(土)</x:v>
       </x:c>
       <x:c r="KO5" s="2" t="str">
-        <x:v>07/30(木)</x:v>
+        <x:v>08/01(土)</x:v>
       </x:c>
       <x:c r="KP5" s="2" t="str">
-        <x:v>07/31(金)</x:v>
+        <x:v>08/02(日)</x:v>
       </x:c>
       <x:c r="KQ5" s="2" t="str">
-        <x:v>07/31(金)</x:v>
+        <x:v>08/02(日)</x:v>
       </x:c>
       <x:c r="KR5" s="2" t="str">
-        <x:v>07/31(金)</x:v>
+        <x:v>08/02(日)</x:v>
       </x:c>
       <x:c r="KS5" s="2" t="str">
-        <x:v>08/01(土)</x:v>
+        <x:v>08/03(月)</x:v>
       </x:c>
       <x:c r="KT5" s="2" t="str">
-        <x:v>08/01(土)</x:v>
+        <x:v>08/03(月)</x:v>
       </x:c>
       <x:c r="KU5" s="2" t="str">
-        <x:v>08/01(土)</x:v>
+        <x:v>08/03(月)</x:v>
       </x:c>
       <x:c r="KV5" s="2" t="str">
-        <x:v>08/02(日)</x:v>
+        <x:v>08/04(火)</x:v>
       </x:c>
       <x:c r="KW5" s="2" t="str">
-        <x:v>08/02(日)</x:v>
+        <x:v>08/04(火)</x:v>
       </x:c>
       <x:c r="KX5" s="2" t="str">
-        <x:v>08/02(日)</x:v>
+        <x:v>08/04(火)</x:v>
       </x:c>
       <x:c r="KY5" s="2" t="str">
-        <x:v>08/03(月)</x:v>
+        <x:v>08/05(水)</x:v>
       </x:c>
       <x:c r="KZ5" s="2" t="str">
-        <x:v>08/03(月)</x:v>
+        <x:v>08/05(水)</x:v>
       </x:c>
       <x:c r="LA5" s="2" t="str">
-        <x:v>08/03(月)</x:v>
+        <x:v>08/05(水)</x:v>
       </x:c>
       <x:c r="LB5" s="2" t="str">
-        <x:v>08/04(火)</x:v>
+        <x:v>08/06(木)</x:v>
       </x:c>
       <x:c r="LC5" s="2" t="str">
-        <x:v>08/04(火)</x:v>
+        <x:v>08/06(木)</x:v>
       </x:c>
       <x:c r="LD5" s="2" t="str">
-        <x:v>08/04(火)</x:v>
+        <x:v>08/06(木)</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2724,13 +2724,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DU7" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>100.0000</x:v>
       </x:c>
       <x:c r="DV7" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="DW7" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.1000</x:v>
       </x:c>
       <x:c r="DX7" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -2742,32 +2742,32 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EA7" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="EB7" s="8" t="n">
+        <x:v>16.1200</x:v>
+      </x:c>
+      <x:c r="EC7" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="ED7" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="EE7" s="8" t="n">
+        <x:v>16.1200</x:v>
+      </x:c>
+      <x:c r="EF7" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="EG7" s="6" t="n">
         <x:v>100.0000</x:v>
       </x:c>
-      <x:c r="EB7" s="8" t="n">
-        <x:v>16.1200</x:v>
-      </x:c>
-      <x:c r="EC7" s="8" t="n">
+      <x:c r="EH7" s="8" t="n">
+        <x:v>16.1200</x:v>
+      </x:c>
+      <x:c r="EI7" s="8" t="n">
         <x:v>0.1000</x:v>
       </x:c>
-      <x:c r="ED7" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="EE7" s="8" t="n">
-        <x:v>16.1200</x:v>
-      </x:c>
-      <x:c r="EF7" s="8" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="EG7" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="EH7" s="8" t="n">
-        <x:v>16.1200</x:v>
-      </x:c>
-      <x:c r="EI7" s="8" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
       <x:c r="EJ7" s="6" t="n">
         <x:v>0.0000</x:v>
       </x:c>
@@ -2778,13 +2778,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM7" s="6" t="n">
-        <x:v>100.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN7" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EO7" s="8" t="n">
-        <x:v>0.1000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP7" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -3674,13 +3674,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DU8" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>100.0000</x:v>
       </x:c>
       <x:c r="DV8" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="DW8" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.1100</x:v>
       </x:c>
       <x:c r="DX8" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -3692,32 +3692,32 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EA8" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="EB8" s="8" t="n">
+        <x:v>15.0000</x:v>
+      </x:c>
+      <x:c r="EC8" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="ED8" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="EE8" s="8" t="n">
+        <x:v>15.0000</x:v>
+      </x:c>
+      <x:c r="EF8" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="EG8" s="6" t="n">
         <x:v>100.0000</x:v>
       </x:c>
-      <x:c r="EB8" s="8" t="n">
-        <x:v>15.0000</x:v>
-      </x:c>
-      <x:c r="EC8" s="8" t="n">
+      <x:c r="EH8" s="8" t="n">
+        <x:v>15.0000</x:v>
+      </x:c>
+      <x:c r="EI8" s="8" t="n">
         <x:v>0.1100</x:v>
       </x:c>
-      <x:c r="ED8" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="EE8" s="8" t="n">
-        <x:v>15.0000</x:v>
-      </x:c>
-      <x:c r="EF8" s="8" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="EG8" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="EH8" s="8" t="n">
-        <x:v>15.0000</x:v>
-      </x:c>
-      <x:c r="EI8" s="8" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
       <x:c r="EJ8" s="6" t="n">
         <x:v>0.0000</x:v>
       </x:c>
@@ -3728,13 +3728,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM8" s="6" t="n">
-        <x:v>100.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN8" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EO8" s="8" t="n">
-        <x:v>0.1100</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP8" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -4660,13 +4660,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG9" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>150.0000</x:v>
       </x:c>
       <x:c r="EH9" s="8" t="n">
         <x:v>16.1100</x:v>
       </x:c>
       <x:c r="EI9" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.1600</x:v>
       </x:c>
       <x:c r="EJ9" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -4678,13 +4678,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM9" s="6" t="n">
-        <x:v>150.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN9" s="8" t="n">
         <x:v>16.1100</x:v>
       </x:c>
       <x:c r="EO9" s="8" t="n">
-        <x:v>0.1600</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP9" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -5610,13 +5610,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG10" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>150.0000</x:v>
       </x:c>
       <x:c r="EH10" s="8" t="n">
         <x:v>16.1100</x:v>
       </x:c>
       <x:c r="EI10" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.1600</x:v>
       </x:c>
       <x:c r="EJ10" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -5628,13 +5628,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM10" s="6" t="n">
-        <x:v>150.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN10" s="8" t="n">
         <x:v>16.1100</x:v>
       </x:c>
       <x:c r="EO10" s="8" t="n">
-        <x:v>0.1600</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP10" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -6560,13 +6560,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG11" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1200.0000</x:v>
       </x:c>
       <x:c r="EH11" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EI11" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.2400</x:v>
       </x:c>
       <x:c r="EJ11" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -6578,13 +6578,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM11" s="6" t="n">
-        <x:v>1200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN11" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EO11" s="8" t="n">
-        <x:v>1.2400</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP11" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -7510,13 +7510,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG12" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>100.0000</x:v>
       </x:c>
       <x:c r="EH12" s="8" t="n">
         <x:v>16.1300</x:v>
       </x:c>
       <x:c r="EI12" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.1000</x:v>
       </x:c>
       <x:c r="EJ12" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -7528,13 +7528,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM12" s="6" t="n">
-        <x:v>100.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN12" s="8" t="n">
         <x:v>16.1300</x:v>
       </x:c>
       <x:c r="EO12" s="8" t="n">
-        <x:v>0.1000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP12" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -8460,13 +8460,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG13" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>300.0000</x:v>
       </x:c>
       <x:c r="EH13" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EI13" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.3100</x:v>
       </x:c>
       <x:c r="EJ13" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -8478,13 +8478,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM13" s="6" t="n">
-        <x:v>300.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN13" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EO13" s="8" t="n">
-        <x:v>0.3100</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP13" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -9410,40 +9410,40 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG14" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>600.0000</x:v>
       </x:c>
       <x:c r="EH14" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EI14" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.6200</x:v>
       </x:c>
       <x:c r="EJ14" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>7500.0000</x:v>
       </x:c>
       <x:c r="EK14" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EL14" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>7.7500</x:v>
       </x:c>
       <x:c r="EM14" s="6" t="n">
-        <x:v>600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN14" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EO14" s="8" t="n">
-        <x:v>0.6200</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP14" s="6" t="n">
-        <x:v>7500.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EQ14" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="ER14" s="8" t="n">
-        <x:v>7.7500</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES14" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -10360,13 +10360,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG15" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1200.0000</x:v>
       </x:c>
       <x:c r="EH15" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EI15" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.2400</x:v>
       </x:c>
       <x:c r="EJ15" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -10378,13 +10378,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM15" s="6" t="n">
-        <x:v>1200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN15" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EO15" s="8" t="n">
-        <x:v>1.2400</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP15" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -11328,40 +11328,40 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM16" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>7500.0000</x:v>
       </x:c>
       <x:c r="EN16" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EO16" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>7.7500</x:v>
       </x:c>
       <x:c r="EP16" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>600.0000</x:v>
       </x:c>
       <x:c r="EQ16" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="ER16" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.6200</x:v>
       </x:c>
       <x:c r="ES16" s="6" t="n">
-        <x:v>7500.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ET16" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EU16" s="8" t="n">
-        <x:v>7.7500</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV16" s="6" t="n">
-        <x:v>600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EW16" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EX16" s="8" t="n">
-        <x:v>0.6200</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY16" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -12287,40 +12287,40 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP17" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6900.0000</x:v>
       </x:c>
       <x:c r="EQ17" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="ER17" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>7.1300</x:v>
       </x:c>
       <x:c r="ES17" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1200.0000</x:v>
       </x:c>
       <x:c r="ET17" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EU17" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.2400</x:v>
       </x:c>
       <x:c r="EV17" s="6" t="n">
-        <x:v>6900.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EW17" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EX17" s="8" t="n">
-        <x:v>7.1300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY17" s="6" t="n">
-        <x:v>1200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EZ17" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FA17" s="8" t="n">
-        <x:v>1.2400</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB17" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -13246,13 +13246,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES18" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6000.0000</x:v>
       </x:c>
       <x:c r="ET18" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EU18" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6.2000</x:v>
       </x:c>
       <x:c r="EV18" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -13264,22 +13264,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY18" s="6" t="n">
-        <x:v>6000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EZ18" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FA18" s="8" t="n">
-        <x:v>6.2000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB18" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2100.0000</x:v>
       </x:c>
       <x:c r="FC18" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FD18" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.1700</x:v>
       </x:c>
       <x:c r="FE18" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -13291,13 +13291,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FH18" s="6" t="n">
-        <x:v>2100.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FI18" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FJ18" s="8" t="n">
-        <x:v>2.1700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FK18" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -14223,40 +14223,40 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB19" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5400.0000</x:v>
       </x:c>
       <x:c r="FC19" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FD19" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5.5800</x:v>
       </x:c>
       <x:c r="FE19" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2700.0000</x:v>
       </x:c>
       <x:c r="FF19" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FG19" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.7900</x:v>
       </x:c>
       <x:c r="FH19" s="6" t="n">
-        <x:v>5400.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FI19" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FJ19" s="8" t="n">
-        <x:v>5.5800</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FK19" s="6" t="n">
-        <x:v>2700.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FL19" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FM19" s="8" t="n">
-        <x:v>2.7900</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FN19" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -15191,13 +15191,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FH20" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>630.0000</x:v>
       </x:c>
       <x:c r="FI20" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FJ20" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.6500</x:v>
       </x:c>
       <x:c r="FK20" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -15209,13 +15209,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FN20" s="6" t="n">
-        <x:v>630.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FO20" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FP20" s="8" t="n">
-        <x:v>0.6500</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FQ20" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -16132,40 +16132,40 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FE21" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4800.0000</x:v>
       </x:c>
       <x:c r="FF21" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FG21" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4.9600</x:v>
       </x:c>
       <x:c r="FH21" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3300.0000</x:v>
       </x:c>
       <x:c r="FI21" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FJ21" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3.4100</x:v>
       </x:c>
       <x:c r="FK21" s="6" t="n">
-        <x:v>4800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FL21" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FM21" s="8" t="n">
-        <x:v>4.9600</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FN21" s="6" t="n">
-        <x:v>3300.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FO21" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FP21" s="8" t="n">
-        <x:v>3.4100</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FQ21" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -17145,13 +17145,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FZ22" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6000.0000</x:v>
       </x:c>
       <x:c r="GA22" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="GB22" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6.2000</x:v>
       </x:c>
       <x:c r="GC22" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -17163,13 +17163,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GF22" s="6" t="n">
-        <x:v>6000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GG22" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="GH22" s="8" t="n">
-        <x:v>6.2000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GI22" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -18113,40 +18113,40 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GF23" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6400.0000</x:v>
       </x:c>
       <x:c r="GG23" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="GH23" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6.6200</x:v>
       </x:c>
       <x:c r="GI23" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3600.0000</x:v>
       </x:c>
       <x:c r="GJ23" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="GK23" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3.7200</x:v>
       </x:c>
       <x:c r="GL23" s="6" t="n">
-        <x:v>6400.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GM23" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="GN23" s="8" t="n">
-        <x:v>6.6200</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GO23" s="6" t="n">
-        <x:v>3600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GP23" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="GQ23" s="8" t="n">
-        <x:v>3.7200</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GR23" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -19072,40 +19072,40 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GI24" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3200.0000</x:v>
       </x:c>
       <x:c r="GJ24" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="GK24" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3.3100</x:v>
       </x:c>
       <x:c r="GL24" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6800.0000</x:v>
       </x:c>
       <x:c r="GM24" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="GN24" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>7.0300</x:v>
       </x:c>
       <x:c r="GO24" s="6" t="n">
-        <x:v>3200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GP24" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="GQ24" s="8" t="n">
-        <x:v>3.3100</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GR24" s="6" t="n">
-        <x:v>6800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GS24" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="GT24" s="8" t="n">
-        <x:v>7.0300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GU24" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -20067,40 +20067,40 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GX25" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4200.0000</x:v>
       </x:c>
       <x:c r="GY25" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="GZ25" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4.3400</x:v>
       </x:c>
       <x:c r="HA25" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5800.0000</x:v>
       </x:c>
       <x:c r="HB25" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="HC25" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6.0000</x:v>
       </x:c>
       <x:c r="HD25" s="6" t="n">
-        <x:v>4200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HE25" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="HF25" s="8" t="n">
-        <x:v>4.3400</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HG25" s="6" t="n">
-        <x:v>5800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HH25" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="HI25" s="8" t="n">
-        <x:v>6.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HJ25" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -21026,49 +21026,49 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HA26" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1000.0000</x:v>
       </x:c>
       <x:c r="HB26" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="HC26" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.0300</x:v>
       </x:c>
       <x:c r="HD26" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6800.0000</x:v>
       </x:c>
       <x:c r="HE26" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="HF26" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>7.0300</x:v>
       </x:c>
       <x:c r="HG26" s="6" t="n">
-        <x:v>1000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HH26" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="HI26" s="8" t="n">
-        <x:v>1.0300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HJ26" s="6" t="n">
-        <x:v>6800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HK26" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="HL26" s="8" t="n">
-        <x:v>7.0300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HM26" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2200.0000</x:v>
       </x:c>
       <x:c r="HN26" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="HO26" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.2700</x:v>
       </x:c>
       <x:c r="HP26" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -21080,13 +21080,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HS26" s="6" t="n">
-        <x:v>2200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HT26" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="HU26" s="8" t="n">
-        <x:v>2.2700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HV26" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -21760,13 +21760,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG27" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1400.0000</x:v>
       </x:c>
       <x:c r="EH27" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EI27" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.2900</x:v>
       </x:c>
       <x:c r="EJ27" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -21778,13 +21778,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM27" s="6" t="n">
-        <x:v>1400.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN27" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EO27" s="8" t="n">
-        <x:v>1.2900</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP27" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -22710,13 +22710,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG28" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2400.0000</x:v>
       </x:c>
       <x:c r="EH28" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EI28" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.2100</x:v>
       </x:c>
       <x:c r="EJ28" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -22728,13 +22728,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM28" s="6" t="n">
-        <x:v>2400.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN28" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EO28" s="8" t="n">
-        <x:v>2.2100</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP28" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -23633,13 +23633,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DX29" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5700.0000</x:v>
       </x:c>
       <x:c r="DY29" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="DZ29" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5.2600</x:v>
       </x:c>
       <x:c r="EA29" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -23651,13 +23651,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ED29" s="6" t="n">
-        <x:v>5700.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EE29" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EF29" s="8" t="n">
-        <x:v>5.2600</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG29" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -24637,13 +24637,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP30" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5000.0000</x:v>
       </x:c>
       <x:c r="EQ30" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="ER30" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4.6100</x:v>
       </x:c>
       <x:c r="ES30" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -24655,13 +24655,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV30" s="6" t="n">
-        <x:v>5000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EW30" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EX30" s="8" t="n">
-        <x:v>4.6100</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY30" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -25560,13 +25560,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG31" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2400.0000</x:v>
       </x:c>
       <x:c r="EH31" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EI31" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.2100</x:v>
       </x:c>
       <x:c r="EJ31" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -25578,13 +25578,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM31" s="6" t="n">
-        <x:v>2400.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN31" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EO31" s="8" t="n">
-        <x:v>2.2100</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP31" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -26537,13 +26537,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP32" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>400.0000</x:v>
       </x:c>
       <x:c r="EQ32" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="ER32" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.3700</x:v>
       </x:c>
       <x:c r="ES32" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -26555,13 +26555,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV32" s="6" t="n">
-        <x:v>400.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EW32" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EX32" s="8" t="n">
-        <x:v>0.3700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY32" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -27487,13 +27487,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP33" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>500.0000</x:v>
       </x:c>
       <x:c r="EQ33" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="ER33" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.4600</x:v>
       </x:c>
       <x:c r="ES33" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -27505,13 +27505,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV33" s="6" t="n">
-        <x:v>500.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EW33" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EX33" s="8" t="n">
-        <x:v>0.4600</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY33" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -28473,13 +28473,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB34" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1000.0000</x:v>
       </x:c>
       <x:c r="FC34" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="FD34" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.9200</x:v>
       </x:c>
       <x:c r="FE34" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -28491,13 +28491,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FH34" s="6" t="n">
-        <x:v>1000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FI34" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="FJ34" s="8" t="n">
-        <x:v>0.9200</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FK34" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -29423,13 +29423,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB35" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1500.0000</x:v>
       </x:c>
       <x:c r="FC35" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="FD35" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.3800</x:v>
       </x:c>
       <x:c r="FE35" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -29441,13 +29441,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FH35" s="6" t="n">
-        <x:v>1500.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FI35" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="FJ35" s="8" t="n">
-        <x:v>1.3800</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FK35" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -30310,13 +30310,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG36" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1000.0000</x:v>
       </x:c>
       <x:c r="EH36" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EI36" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.9200</x:v>
       </x:c>
       <x:c r="EJ36" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -30328,13 +30328,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM36" s="6" t="n">
-        <x:v>1000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN36" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EO36" s="8" t="n">
-        <x:v>0.9200</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP36" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -31350,13 +31350,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FK37" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2000.0000</x:v>
       </x:c>
       <x:c r="FL37" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="FM37" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.8500</x:v>
       </x:c>
       <x:c r="FN37" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -31368,13 +31368,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FQ37" s="6" t="n">
-        <x:v>2000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FR37" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="FS37" s="8" t="n">
-        <x:v>1.8500</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FT37" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -32282,13 +32282,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FE38" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6000.0000</x:v>
       </x:c>
       <x:c r="FF38" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="FG38" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5.5400</x:v>
       </x:c>
       <x:c r="FH38" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -32300,13 +32300,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FK38" s="6" t="n">
-        <x:v>6000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FL38" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="FM38" s="8" t="n">
-        <x:v>5.5400</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FN38" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -33241,40 +33241,40 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FH39" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1200.0000</x:v>
       </x:c>
       <x:c r="FI39" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="FJ39" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.1100</x:v>
       </x:c>
       <x:c r="FK39" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4800.0000</x:v>
       </x:c>
       <x:c r="FL39" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="FM39" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4.4300</x:v>
       </x:c>
       <x:c r="FN39" s="6" t="n">
-        <x:v>1200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FO39" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="FP39" s="8" t="n">
-        <x:v>1.1100</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FQ39" s="6" t="n">
-        <x:v>4800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FR39" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="FS39" s="8" t="n">
-        <x:v>4.4300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FT39" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -34182,40 +34182,40 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FE40" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2100.0000</x:v>
       </x:c>
       <x:c r="FF40" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="FG40" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.9400</x:v>
       </x:c>
       <x:c r="FH40" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6900.0000</x:v>
       </x:c>
       <x:c r="FI40" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="FJ40" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6.3700</x:v>
       </x:c>
       <x:c r="FK40" s="6" t="n">
-        <x:v>2100.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FL40" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="FM40" s="8" t="n">
-        <x:v>1.9400</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FN40" s="6" t="n">
-        <x:v>6900.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FO40" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="FP40" s="8" t="n">
-        <x:v>6.3700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FQ40" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -35060,13 +35060,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG41" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>600.0000</x:v>
       </x:c>
       <x:c r="EH41" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EI41" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.6700</x:v>
       </x:c>
       <x:c r="EJ41" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -35078,13 +35078,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM41" s="6" t="n">
-        <x:v>600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN41" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EO41" s="8" t="n">
-        <x:v>0.6700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP41" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -36019,13 +36019,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ42" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>400.0000</x:v>
       </x:c>
       <x:c r="EK42" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EL42" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.4400</x:v>
       </x:c>
       <x:c r="EM42" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -36037,13 +36037,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP42" s="6" t="n">
-        <x:v>400.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EQ42" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="ER42" s="8" t="n">
-        <x:v>0.4400</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES42" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -36915,58 +36915,58 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DR43" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>7500.0000</x:v>
       </x:c>
       <x:c r="DS43" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="DT43" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>12.3500</x:v>
       </x:c>
       <x:c r="DU43" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>9600.0000</x:v>
       </x:c>
       <x:c r="DV43" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="DW43" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>15.8100</x:v>
       </x:c>
       <x:c r="DX43" s="6" t="n">
-        <x:v>7500.0000</x:v>
+        <x:v>6900.0000</x:v>
       </x:c>
       <x:c r="DY43" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="DZ43" s="8" t="n">
-        <x:v>12.3500</x:v>
+        <x:v>11.3600</x:v>
       </x:c>
       <x:c r="EA43" s="6" t="n">
-        <x:v>9600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EB43" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="EC43" s="8" t="n">
-        <x:v>15.8100</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ED43" s="6" t="n">
-        <x:v>6900.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EE43" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="EF43" s="8" t="n">
-        <x:v>11.3600</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG43" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5400.0000</x:v>
       </x:c>
       <x:c r="EH43" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="EI43" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>8.8900</x:v>
       </x:c>
       <x:c r="EJ43" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -36978,13 +36978,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM43" s="6" t="n">
-        <x:v>5400.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN43" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="EO43" s="8" t="n">
-        <x:v>8.8900</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP43" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -37937,13 +37937,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP44" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>475.0000</x:v>
       </x:c>
       <x:c r="EQ44" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="ER44" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.7800</x:v>
       </x:c>
       <x:c r="ES44" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -37955,13 +37955,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV44" s="6" t="n">
-        <x:v>475.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EW44" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="EX44" s="8" t="n">
-        <x:v>0.7800</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY44" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -38860,40 +38860,40 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG45" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1500.0000</x:v>
       </x:c>
       <x:c r="EH45" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="EI45" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.4700</x:v>
       </x:c>
       <x:c r="EJ45" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4500.0000</x:v>
       </x:c>
       <x:c r="EK45" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="EL45" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>7.4100</x:v>
       </x:c>
       <x:c r="EM45" s="6" t="n">
-        <x:v>1500.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN45" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="EO45" s="8" t="n">
-        <x:v>2.4700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP45" s="6" t="n">
-        <x:v>4500.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EQ45" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="ER45" s="8" t="n">
-        <x:v>7.4100</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES45" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -39828,13 +39828,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM46" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>400.0000</x:v>
       </x:c>
       <x:c r="EN46" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EO46" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.4400</x:v>
       </x:c>
       <x:c r="EP46" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -39846,13 +39846,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES46" s="6" t="n">
-        <x:v>400.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ET46" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EU46" s="8" t="n">
-        <x:v>0.4400</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV46" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -40760,40 +40760,40 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG47" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3000.0000</x:v>
       </x:c>
       <x:c r="EH47" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EI47" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3.3300</x:v>
       </x:c>
       <x:c r="EJ47" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>9000.0000</x:v>
       </x:c>
       <x:c r="EK47" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EL47" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>10.0000</x:v>
       </x:c>
       <x:c r="EM47" s="6" t="n">
-        <x:v>3000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN47" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EO47" s="8" t="n">
-        <x:v>3.3300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP47" s="6" t="n">
-        <x:v>9000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EQ47" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="ER47" s="8" t="n">
-        <x:v>10.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES47" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -41737,7 +41737,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP48" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>500.0000</x:v>
       </x:c>
       <x:c r="EQ48" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -41755,7 +41755,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV48" s="6" t="n">
-        <x:v>500.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EW48" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -42678,13 +42678,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM49" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>500.0000</x:v>
       </x:c>
       <x:c r="EN49" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="EO49" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.8200</x:v>
       </x:c>
       <x:c r="EP49" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -42696,13 +42696,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES49" s="6" t="n">
-        <x:v>500.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ET49" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="EU49" s="8" t="n">
-        <x:v>0.8200</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV49" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -43637,13 +43637,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP50" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1500.0000</x:v>
       </x:c>
       <x:c r="EQ50" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="ER50" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.4700</x:v>
       </x:c>
       <x:c r="ES50" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -43655,13 +43655,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV50" s="6" t="n">
-        <x:v>1500.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EW50" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="EX50" s="8" t="n">
-        <x:v>2.4700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY50" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -44578,40 +44578,40 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM51" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1800.0000</x:v>
       </x:c>
       <x:c r="EN51" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="EO51" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.9600</x:v>
       </x:c>
       <x:c r="EP51" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3600.0000</x:v>
       </x:c>
       <x:c r="EQ51" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="ER51" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5.9300</x:v>
       </x:c>
       <x:c r="ES51" s="6" t="n">
-        <x:v>1800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ET51" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="EU51" s="8" t="n">
-        <x:v>2.9600</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV51" s="6" t="n">
-        <x:v>3600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EW51" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="EX51" s="8" t="n">
-        <x:v>5.9300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY51" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -45528,40 +45528,40 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM52" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3600.0000</x:v>
       </x:c>
       <x:c r="EN52" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EO52" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4.0000</x:v>
       </x:c>
       <x:c r="EP52" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>7200.0000</x:v>
       </x:c>
       <x:c r="EQ52" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="ER52" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>8.0000</x:v>
       </x:c>
       <x:c r="ES52" s="6" t="n">
-        <x:v>3600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ET52" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EU52" s="8" t="n">
-        <x:v>4.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV52" s="6" t="n">
-        <x:v>7200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EW52" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EX52" s="8" t="n">
-        <x:v>8.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY52" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -46496,13 +46496,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES53" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>10000.0000</x:v>
       </x:c>
       <x:c r="ET53" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EU53" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>11.1100</x:v>
       </x:c>
       <x:c r="EV53" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -46514,13 +46514,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY53" s="6" t="n">
-        <x:v>10000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EZ53" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FA53" s="8" t="n">
-        <x:v>11.1100</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB53" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -47473,40 +47473,40 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB54" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>7200.0000</x:v>
       </x:c>
       <x:c r="FC54" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="FD54" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>11.8600</x:v>
       </x:c>
       <x:c r="FE54" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2400.0000</x:v>
       </x:c>
       <x:c r="FF54" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="FG54" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3.9500</x:v>
       </x:c>
       <x:c r="FH54" s="6" t="n">
-        <x:v>7200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FI54" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="FJ54" s="8" t="n">
-        <x:v>11.8600</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FK54" s="6" t="n">
-        <x:v>2400.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FL54" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="FM54" s="8" t="n">
-        <x:v>3.9500</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FN54" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -48450,13 +48450,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FK55" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4600.0000</x:v>
       </x:c>
       <x:c r="FL55" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FM55" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5.1100</x:v>
       </x:c>
       <x:c r="FN55" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -48468,13 +48468,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FQ55" s="6" t="n">
-        <x:v>4600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FR55" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FS55" s="8" t="n">
-        <x:v>5.1100</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FT55" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -49400,13 +49400,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FK56" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1800.0000</x:v>
       </x:c>
       <x:c r="FL56" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FM56" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.0000</x:v>
       </x:c>
       <x:c r="FN56" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -49418,13 +49418,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FQ56" s="6" t="n">
-        <x:v>1800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FR56" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FS56" s="8" t="n">
-        <x:v>2.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FT56" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -50341,13 +50341,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FH57" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6600.0000</x:v>
       </x:c>
       <x:c r="FI57" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FJ57" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>7.3300</x:v>
       </x:c>
       <x:c r="FK57" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -50359,13 +50359,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FN57" s="6" t="n">
-        <x:v>6600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FO57" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FP57" s="8" t="n">
-        <x:v>7.3300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FQ57" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -51309,13 +51309,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FN58" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5000.0000</x:v>
       </x:c>
       <x:c r="FO58" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="FP58" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>8.2300</x:v>
       </x:c>
       <x:c r="FQ58" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -51327,13 +51327,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FT58" s="6" t="n">
-        <x:v>5000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FU58" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="FV58" s="8" t="n">
-        <x:v>8.2300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FW58" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -52187,13 +52187,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP59" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>950.0000</x:v>
       </x:c>
       <x:c r="EQ59" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="ER59" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.5600</x:v>
       </x:c>
       <x:c r="ES59" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -52205,13 +52205,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV59" s="6" t="n">
-        <x:v>950.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EW59" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="EX59" s="8" t="n">
-        <x:v>1.5600</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY59" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -53137,7 +53137,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP60" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1000.0000</x:v>
       </x:c>
       <x:c r="EQ60" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -53155,7 +53155,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV60" s="6" t="n">
-        <x:v>1000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EW60" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -54186,13 +54186,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FW61" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2000.0000</x:v>
       </x:c>
       <x:c r="FX61" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FY61" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.2200</x:v>
       </x:c>
       <x:c r="FZ61" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -54204,13 +54204,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GC61" s="6" t="n">
-        <x:v>2000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GD61" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="GE61" s="8" t="n">
-        <x:v>2.2200</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GF61" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -55082,40 +55082,40 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FE62" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4500.0000</x:v>
       </x:c>
       <x:c r="FF62" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="FG62" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>7.4100</x:v>
       </x:c>
       <x:c r="FH62" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1500.0000</x:v>
       </x:c>
       <x:c r="FI62" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="FJ62" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.4700</x:v>
       </x:c>
       <x:c r="FK62" s="6" t="n">
-        <x:v>4500.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FL62" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="FM62" s="8" t="n">
-        <x:v>7.4100</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FN62" s="6" t="n">
-        <x:v>1500.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FO62" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="FP62" s="8" t="n">
-        <x:v>2.4700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FQ62" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -55969,13 +55969,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ63" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>200.0000</x:v>
       </x:c>
       <x:c r="EK63" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EL63" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.1300</x:v>
       </x:c>
       <x:c r="EM63" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -55987,13 +55987,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP63" s="6" t="n">
-        <x:v>200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EQ63" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="ER63" s="8" t="n">
-        <x:v>0.1300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES63" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -56919,13 +56919,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ64" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3200.0000</x:v>
       </x:c>
       <x:c r="EK64" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EL64" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.1300</x:v>
       </x:c>
       <x:c r="EM64" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -56937,13 +56937,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP64" s="6" t="n">
-        <x:v>3200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EQ64" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="ER64" s="8" t="n">
-        <x:v>2.1300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES64" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -57869,13 +57869,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ65" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>200.0000</x:v>
       </x:c>
       <x:c r="EK65" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EL65" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.1300</x:v>
       </x:c>
       <x:c r="EM65" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -57887,13 +57887,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP65" s="6" t="n">
-        <x:v>200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EQ65" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="ER65" s="8" t="n">
-        <x:v>0.1300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES65" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -58819,13 +58819,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ66" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3800.0000</x:v>
       </x:c>
       <x:c r="EK66" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EL66" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.5300</x:v>
       </x:c>
       <x:c r="EM66" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -58837,13 +58837,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP66" s="6" t="n">
-        <x:v>3800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EQ66" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="ER66" s="8" t="n">
-        <x:v>2.5300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES66" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -59769,13 +59769,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ67" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1600.0000</x:v>
       </x:c>
       <x:c r="EK67" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EL67" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.0700</x:v>
       </x:c>
       <x:c r="EM67" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -59787,13 +59787,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP67" s="6" t="n">
-        <x:v>1600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EQ67" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="ER67" s="8" t="n">
-        <x:v>1.0700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES67" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -60719,13 +60719,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ68" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>600.0000</x:v>
       </x:c>
       <x:c r="EK68" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EL68" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.4000</x:v>
       </x:c>
       <x:c r="EM68" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -60737,13 +60737,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP68" s="6" t="n">
-        <x:v>600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EQ68" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="ER68" s="8" t="n">
-        <x:v>0.4000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES68" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -61669,13 +61669,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ69" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>800.0000</x:v>
       </x:c>
       <x:c r="EK69" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EL69" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.5300</x:v>
       </x:c>
       <x:c r="EM69" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -61687,13 +61687,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP69" s="6" t="n">
-        <x:v>800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EQ69" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="ER69" s="8" t="n">
-        <x:v>0.5300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES69" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -62637,13 +62637,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP70" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>500.0000</x:v>
       </x:c>
       <x:c r="EQ70" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="ER70" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.3300</x:v>
       </x:c>
       <x:c r="ES70" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -62655,13 +62655,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV70" s="6" t="n">
-        <x:v>500.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EW70" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EX70" s="8" t="n">
-        <x:v>0.3300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY70" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -63587,13 +63587,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP71" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1000.0000</x:v>
       </x:c>
       <x:c r="EQ71" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="ER71" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.6700</x:v>
       </x:c>
       <x:c r="ES71" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -63605,13 +63605,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV71" s="6" t="n">
-        <x:v>1000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EW71" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EX71" s="8" t="n">
-        <x:v>0.6700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY71" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -64510,13 +64510,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG72" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3200.0000</x:v>
       </x:c>
       <x:c r="EH72" s="8" t="n">
         <x:v>20.0000</x:v>
       </x:c>
       <x:c r="EI72" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.6700</x:v>
       </x:c>
       <x:c r="EJ72" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -64528,13 +64528,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM72" s="6" t="n">
-        <x:v>3200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN72" s="8" t="n">
         <x:v>20.0000</x:v>
       </x:c>
       <x:c r="EO72" s="8" t="n">
-        <x:v>2.6700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP72" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -65460,13 +65460,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG73" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1600.0000</x:v>
       </x:c>
       <x:c r="EH73" s="8" t="n">
         <x:v>20.0000</x:v>
       </x:c>
       <x:c r="EI73" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.3300</x:v>
       </x:c>
       <x:c r="EJ73" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -65478,13 +65478,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM73" s="6" t="n">
-        <x:v>1600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN73" s="8" t="n">
         <x:v>20.0000</x:v>
       </x:c>
       <x:c r="EO73" s="8" t="n">
-        <x:v>1.3300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP73" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -66410,13 +66410,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG74" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>600.0000</x:v>
       </x:c>
       <x:c r="EH74" s="8" t="n">
         <x:v>20.0000</x:v>
       </x:c>
       <x:c r="EI74" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.5000</x:v>
       </x:c>
       <x:c r="EJ74" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -66428,13 +66428,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM74" s="6" t="n">
-        <x:v>600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN74" s="8" t="n">
         <x:v>20.0000</x:v>
       </x:c>
       <x:c r="EO74" s="8" t="n">
-        <x:v>0.5000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP74" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -67333,13 +67333,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DX75" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2700.0000</x:v>
       </x:c>
       <x:c r="DY75" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="DZ75" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4.7400</x:v>
       </x:c>
       <x:c r="EA75" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -67351,13 +67351,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ED75" s="6" t="n">
-        <x:v>2700.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EE75" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="EF75" s="8" t="n">
-        <x:v>4.7400</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG75" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -67378,13 +67378,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM75" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3000.0000</x:v>
       </x:c>
       <x:c r="EN75" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="EO75" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5.2600</x:v>
       </x:c>
       <x:c r="EP75" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -67396,13 +67396,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES75" s="6" t="n">
-        <x:v>3000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ET75" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="EU75" s="8" t="n">
-        <x:v>5.2600</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV75" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -68382,40 +68382,40 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FE76" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3600.0000</x:v>
       </x:c>
       <x:c r="FF76" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="FG76" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6.3200</x:v>
       </x:c>
       <x:c r="FH76" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2400.0000</x:v>
       </x:c>
       <x:c r="FI76" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="FJ76" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4.2100</x:v>
       </x:c>
       <x:c r="FK76" s="6" t="n">
-        <x:v>3600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FL76" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="FM76" s="8" t="n">
-        <x:v>6.3200</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FN76" s="6" t="n">
-        <x:v>2400.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FO76" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="FP76" s="8" t="n">
-        <x:v>4.2100</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FQ76" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -69359,13 +69359,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FN77" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1260.0000</x:v>
       </x:c>
       <x:c r="FO77" s="8" t="n">
         <x:v>20.0000</x:v>
       </x:c>
       <x:c r="FP77" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.0500</x:v>
       </x:c>
       <x:c r="FQ77" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -69377,13 +69377,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FT77" s="6" t="n">
-        <x:v>1260.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FU77" s="8" t="n">
         <x:v>20.0000</x:v>
       </x:c>
       <x:c r="FV77" s="8" t="n">
-        <x:v>1.0500</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FW77" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -70345,40 +70345,40 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FZ78" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3000.0000</x:v>
       </x:c>
       <x:c r="GA78" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="GB78" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5.2600</x:v>
       </x:c>
       <x:c r="GC78" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3000.0000</x:v>
       </x:c>
       <x:c r="GD78" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="GE78" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5.2600</x:v>
       </x:c>
       <x:c r="GF78" s="6" t="n">
-        <x:v>3000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GG78" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="GH78" s="8" t="n">
-        <x:v>5.2600</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GI78" s="6" t="n">
-        <x:v>3000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GJ78" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="GK78" s="8" t="n">
-        <x:v>5.2600</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GL78" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -71241,40 +71241,40 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FH79" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1200.0000</x:v>
       </x:c>
       <x:c r="FI79" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="FJ79" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.1100</x:v>
       </x:c>
       <x:c r="FK79" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3600.0000</x:v>
       </x:c>
       <x:c r="FL79" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="FM79" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6.3200</x:v>
       </x:c>
       <x:c r="FN79" s="6" t="n">
-        <x:v>1200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FO79" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="FP79" s="8" t="n">
-        <x:v>2.1100</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FQ79" s="6" t="n">
-        <x:v>3600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FR79" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="FS79" s="8" t="n">
-        <x:v>6.3200</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FT79" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -71286,40 +71286,40 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FW79" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3600.0000</x:v>
       </x:c>
       <x:c r="FX79" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="FY79" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6.3200</x:v>
       </x:c>
       <x:c r="FZ79" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>600.0000</x:v>
       </x:c>
       <x:c r="GA79" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="GB79" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.0500</x:v>
       </x:c>
       <x:c r="GC79" s="6" t="n">
-        <x:v>3600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GD79" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="GE79" s="8" t="n">
-        <x:v>6.3200</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GF79" s="6" t="n">
-        <x:v>600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GG79" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="GH79" s="8" t="n">
-        <x:v>1.0500</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GI79" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -72065,247 +72065,247 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DR80" s="7" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>7500.0000</x:v>
       </x:c>
       <x:c r="DS80" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="DT80" s="9" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>12.3500</x:v>
       </x:c>
       <x:c r="DU80" s="7" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>9800.0000</x:v>
       </x:c>
       <x:c r="DV80" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="DW80" s="9" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>16.0200</x:v>
       </x:c>
       <x:c r="DX80" s="7" t="n">
-        <x:v>7500.0000</x:v>
+        <x:v>15300.0000</x:v>
       </x:c>
       <x:c r="DY80" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="DZ80" s="9" t="n">
-        <x:v>12.3500</x:v>
+        <x:v>21.3600</x:v>
       </x:c>
       <x:c r="EA80" s="7" t="n">
-        <x:v>9800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EB80" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="EC80" s="9" t="n">
-        <x:v>16.0200</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ED80" s="7" t="n">
-        <x:v>15300.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EE80" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="EF80" s="9" t="n">
-        <x:v>21.3600</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG80" s="7" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>27000.0000</x:v>
       </x:c>
       <x:c r="EH80" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="EI80" s="9" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>30.5300</x:v>
       </x:c>
       <x:c r="EJ80" s="7" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>31800.0000</x:v>
       </x:c>
       <x:c r="EK80" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="EL80" s="9" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>32.5200</x:v>
       </x:c>
       <x:c r="EM80" s="7" t="n">
-        <x:v>27000.0000</x:v>
+        <x:v>16800.0000</x:v>
       </x:c>
       <x:c r="EN80" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="EO80" s="9" t="n">
-        <x:v>30.5300</x:v>
+        <x:v>21.2300</x:v>
       </x:c>
       <x:c r="EP80" s="7" t="n">
-        <x:v>31800.0000</x:v>
+        <x:v>30125.0000</x:v>
       </x:c>
       <x:c r="EQ80" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="ER80" s="9" t="n">
-        <x:v>32.5200</x:v>
+        <x:v>32.9300</x:v>
       </x:c>
       <x:c r="ES80" s="7" t="n">
-        <x:v>16800.0000</x:v>
+        <x:v>17200.0000</x:v>
       </x:c>
       <x:c r="ET80" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="EU80" s="9" t="n">
-        <x:v>21.2300</x:v>
+        <x:v>18.5500</x:v>
       </x:c>
       <x:c r="EV80" s="7" t="n">
-        <x:v>30125.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EW80" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="EX80" s="9" t="n">
-        <x:v>32.9300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY80" s="7" t="n">
-        <x:v>17200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EZ80" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FA80" s="9" t="n">
-        <x:v>18.5500</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB80" s="7" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>17200.0000</x:v>
       </x:c>
       <x:c r="FC80" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FD80" s="9" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>21.9100</x:v>
       </x:c>
       <x:c r="FE80" s="7" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>26100.0000</x:v>
       </x:c>
       <x:c r="FF80" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FG80" s="9" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>32.9100</x:v>
       </x:c>
       <x:c r="FH80" s="7" t="n">
-        <x:v>17200.0000</x:v>
+        <x:v>23730.0000</x:v>
       </x:c>
       <x:c r="FI80" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FJ80" s="9" t="n">
-        <x:v>21.9100</x:v>
+        <x:v>27.6600</x:v>
       </x:c>
       <x:c r="FK80" s="7" t="n">
-        <x:v>26100.0000</x:v>
+        <x:v>16800.0000</x:v>
       </x:c>
       <x:c r="FL80" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FM80" s="9" t="n">
-        <x:v>32.9100</x:v>
+        <x:v>19.7100</x:v>
       </x:c>
       <x:c r="FN80" s="7" t="n">
-        <x:v>23730.0000</x:v>
+        <x:v>6260.0000</x:v>
       </x:c>
       <x:c r="FO80" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FP80" s="9" t="n">
-        <x:v>27.6600</x:v>
+        <x:v>9.2800</x:v>
       </x:c>
       <x:c r="FQ80" s="7" t="n">
-        <x:v>16800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FR80" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FS80" s="9" t="n">
-        <x:v>19.7100</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FT80" s="7" t="n">
-        <x:v>6260.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FU80" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FV80" s="9" t="n">
-        <x:v>9.2800</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FW80" s="7" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5600.0000</x:v>
       </x:c>
       <x:c r="FX80" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FY80" s="9" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>8.5400</x:v>
       </x:c>
       <x:c r="FZ80" s="7" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>9600.0000</x:v>
       </x:c>
       <x:c r="GA80" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="GB80" s="9" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>12.5100</x:v>
       </x:c>
       <x:c r="GC80" s="7" t="n">
-        <x:v>5600.0000</x:v>
+        <x:v>3000.0000</x:v>
       </x:c>
       <x:c r="GD80" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="GE80" s="9" t="n">
-        <x:v>8.5400</x:v>
+        <x:v>5.2600</x:v>
       </x:c>
       <x:c r="GF80" s="7" t="n">
-        <x:v>9600.0000</x:v>
+        <x:v>6400.0000</x:v>
       </x:c>
       <x:c r="GG80" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="GH80" s="9" t="n">
-        <x:v>12.5100</x:v>
+        <x:v>6.6200</x:v>
       </x:c>
       <x:c r="GI80" s="7" t="n">
-        <x:v>3000.0000</x:v>
+        <x:v>6800.0000</x:v>
       </x:c>
       <x:c r="GJ80" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="GK80" s="9" t="n">
-        <x:v>5.2600</x:v>
+        <x:v>7.0300</x:v>
       </x:c>
       <x:c r="GL80" s="7" t="n">
-        <x:v>6400.0000</x:v>
+        <x:v>6800.0000</x:v>
       </x:c>
       <x:c r="GM80" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="GN80" s="9" t="n">
-        <x:v>6.6200</x:v>
+        <x:v>7.0300</x:v>
       </x:c>
       <x:c r="GO80" s="7" t="n">
-        <x:v>6800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GP80" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="GQ80" s="9" t="n">
-        <x:v>7.0300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GR80" s="7" t="n">
-        <x:v>6800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GS80" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="GT80" s="9" t="n">
-        <x:v>7.0300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GU80" s="7" t="n">
         <x:v>0.0000</x:v>
@@ -72317,58 +72317,58 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GX80" s="7" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4200.0000</x:v>
       </x:c>
       <x:c r="GY80" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="GZ80" s="9" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4.3400</x:v>
       </x:c>
       <x:c r="HA80" s="7" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6800.0000</x:v>
       </x:c>
       <x:c r="HB80" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="HC80" s="9" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>7.0300</x:v>
       </x:c>
       <x:c r="HD80" s="7" t="n">
-        <x:v>4200.0000</x:v>
+        <x:v>6800.0000</x:v>
       </x:c>
       <x:c r="HE80" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="HF80" s="9" t="n">
-        <x:v>4.3400</x:v>
+        <x:v>7.0300</x:v>
       </x:c>
       <x:c r="HG80" s="7" t="n">
-        <x:v>6800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HH80" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="HI80" s="9" t="n">
-        <x:v>7.0300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HJ80" s="7" t="n">
-        <x:v>6800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HK80" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="HL80" s="9" t="n">
-        <x:v>7.0300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HM80" s="7" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2200.0000</x:v>
       </x:c>
       <x:c r="HN80" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="HO80" s="9" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.2700</x:v>
       </x:c>
       <x:c r="HP80" s="7" t="n">
         <x:v>0.0000</x:v>
@@ -72380,13 +72380,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HS80" s="7" t="n">
-        <x:v>2200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HT80" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="HU80" s="9" t="n">
-        <x:v>2.2700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HV80" s="7" t="n">
         <x:v>0.0000</x:v>

--- a/.pm-ai-cache/network-source/task-input-newest.xlsx
+++ b/.pm-ai-cache/network-source/task-input-newest.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工程別生産計画問合せ問合せ" sheetId="1" r:id="Rb05d2629aa4049ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工程別生産計画問合せ問合せ" sheetId="1" r:id="Ra96e1b666ede4b40"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/.pm-ai-cache/network-source/task-input-newest.xlsx
+++ b/.pm-ai-cache/network-source/task-input-newest.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工程別生産計画問合せ問合せ" sheetId="1" r:id="R82f3b605fb62407e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工程別生産計画問合せ問合せ" sheetId="1" r:id="R3a0cb7ac10ed422e"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/.pm-ai-cache/network-source/task-input-newest.xlsx
+++ b/.pm-ai-cache/network-source/task-input-newest.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工程別生産計画問合せ問合せ" sheetId="1" r:id="R12725e8d0c074da7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工程別生産計画問合せ問合せ" sheetId="1" r:id="R73a2a23cd30b4e38"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -46070,7 +46070,7 @@
         <x:v>SEC</x:v>
       </x:c>
       <x:c r="G53" s="1" t="str">
-        <x:v>001</x:v>
+        <x:v>003</x:v>
       </x:c>
       <x:c r="H53" s="4" t="n">
         <x:v>46210</x:v>
@@ -46112,7 +46112,7 @@
         <x:v>自動車材料事業部</x:v>
       </x:c>
       <x:c r="U53" s="1" t="str">
-        <x:v>00075341</x:v>
+        <x:v>00075366</x:v>
       </x:c>
       <x:c r="V53" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -46151,16 +46151,16 @@
         <x:v/>
       </x:c>
       <x:c r="AH53" s="4" t="n">
-        <x:v>46218</x:v>
+        <x:v>46228</x:v>
       </x:c>
       <x:c r="AI53" s="4" t="n">
-        <x:v>46218</x:v>
+        <x:v>46228</x:v>
       </x:c>
       <x:c r="AJ53" s="1" t="str">
         <x:v>0:未完</x:v>
       </x:c>
       <x:c r="AK53" s="6" t="n">
-        <x:v>3200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AL53" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -46514,103 +46514,103 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY53" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="EZ53" s="8" t="n">
+        <x:v>25.0000</x:v>
+      </x:c>
+      <x:c r="FA53" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="FB53" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="FC53" s="8" t="n">
+        <x:v>25.0000</x:v>
+      </x:c>
+      <x:c r="FD53" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="FE53" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="FF53" s="8" t="n">
+        <x:v>25.0000</x:v>
+      </x:c>
+      <x:c r="FG53" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="FH53" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="FI53" s="8" t="n">
+        <x:v>25.0000</x:v>
+      </x:c>
+      <x:c r="FJ53" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="FK53" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="FL53" s="8" t="n">
+        <x:v>25.0000</x:v>
+      </x:c>
+      <x:c r="FM53" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="FN53" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="FO53" s="8" t="n">
+        <x:v>25.0000</x:v>
+      </x:c>
+      <x:c r="FP53" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="FQ53" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="FR53" s="8" t="n">
+        <x:v>25.0000</x:v>
+      </x:c>
+      <x:c r="FS53" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="FT53" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="FU53" s="8" t="n">
+        <x:v>25.0000</x:v>
+      </x:c>
+      <x:c r="FV53" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="FW53" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="FX53" s="8" t="n">
+        <x:v>25.0000</x:v>
+      </x:c>
+      <x:c r="FY53" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="FZ53" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="GA53" s="8" t="n">
+        <x:v>25.0000</x:v>
+      </x:c>
+      <x:c r="GB53" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="GC53" s="6" t="n">
         <x:v>3200.0000</x:v>
       </x:c>
-      <x:c r="EZ53" s="8" t="n">
-        <x:v>25.0000</x:v>
-      </x:c>
-      <x:c r="FA53" s="8" t="n">
+      <x:c r="GD53" s="8" t="n">
+        <x:v>25.0000</x:v>
+      </x:c>
+      <x:c r="GE53" s="8" t="n">
         <x:v>2.1300</x:v>
-      </x:c>
-      <x:c r="FB53" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="FC53" s="8" t="n">
-        <x:v>25.0000</x:v>
-      </x:c>
-      <x:c r="FD53" s="8" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="FE53" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="FF53" s="8" t="n">
-        <x:v>25.0000</x:v>
-      </x:c>
-      <x:c r="FG53" s="8" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="FH53" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="FI53" s="8" t="n">
-        <x:v>25.0000</x:v>
-      </x:c>
-      <x:c r="FJ53" s="8" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="FK53" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="FL53" s="8" t="n">
-        <x:v>25.0000</x:v>
-      </x:c>
-      <x:c r="FM53" s="8" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="FN53" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="FO53" s="8" t="n">
-        <x:v>25.0000</x:v>
-      </x:c>
-      <x:c r="FP53" s="8" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="FQ53" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="FR53" s="8" t="n">
-        <x:v>25.0000</x:v>
-      </x:c>
-      <x:c r="FS53" s="8" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="FT53" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="FU53" s="8" t="n">
-        <x:v>25.0000</x:v>
-      </x:c>
-      <x:c r="FV53" s="8" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="FW53" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="FX53" s="8" t="n">
-        <x:v>25.0000</x:v>
-      </x:c>
-      <x:c r="FY53" s="8" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="FZ53" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="GA53" s="8" t="n">
-        <x:v>25.0000</x:v>
-      </x:c>
-      <x:c r="GB53" s="8" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="GC53" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="GD53" s="8" t="n">
-        <x:v>25.0000</x:v>
-      </x:c>
-      <x:c r="GE53" s="8" t="n">
-        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GF53" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -47020,7 +47020,7 @@
         <x:v>SEC</x:v>
       </x:c>
       <x:c r="G54" s="1" t="str">
-        <x:v>003</x:v>
+        <x:v>005</x:v>
       </x:c>
       <x:c r="H54" s="4" t="n">
         <x:v>46210</x:v>
@@ -47104,7 +47104,7 @@
         <x:v>46227</x:v>
       </x:c>
       <x:c r="AI54" s="4" t="n">
-        <x:v>46230</x:v>
+        <x:v>46228</x:v>
       </x:c>
       <x:c r="AJ54" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -47554,13 +47554,13 @@
         <x:v>0.6700</x:v>
       </x:c>
       <x:c r="GC54" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2000.0000</x:v>
       </x:c>
       <x:c r="GD54" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="GE54" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.3300</x:v>
       </x:c>
       <x:c r="GF54" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -47572,13 +47572,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GI54" s="6" t="n">
-        <x:v>2000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GJ54" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="GK54" s="8" t="n">
-        <x:v>1.3300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GL54" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -49870,7 +49870,7 @@
         <x:v>SEC</x:v>
       </x:c>
       <x:c r="G57" s="1" t="str">
-        <x:v>014</x:v>
+        <x:v>013</x:v>
       </x:c>
       <x:c r="H57" s="4" t="n">
         <x:v>46199</x:v>
@@ -49951,10 +49951,10 @@
         <x:v/>
       </x:c>
       <x:c r="AH57" s="4" t="n">
+        <x:v>46212</x:v>
+      </x:c>
+      <x:c r="AI57" s="4" t="n">
         <x:v>46213</x:v>
-      </x:c>
-      <x:c r="AI57" s="4" t="n">
-        <x:v>46217</x:v>
       </x:c>
       <x:c r="AJ57" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -50260,22 +50260,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG57" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5000.0000</x:v>
       </x:c>
       <x:c r="EH57" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EI57" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3.3300</x:v>
       </x:c>
       <x:c r="EJ57" s="6" t="n">
-        <x:v>6000.0000</x:v>
+        <x:v>5000.0000</x:v>
       </x:c>
       <x:c r="EK57" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EL57" s="8" t="n">
-        <x:v>4.0000</x:v>
+        <x:v>3.3300</x:v>
       </x:c>
       <x:c r="EM57" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -50305,13 +50305,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV57" s="6" t="n">
-        <x:v>4000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EW57" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EX57" s="8" t="n">
-        <x:v>2.6700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY57" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -68310,22 +68310,22 @@
         <x:v>2.0800</x:v>
       </x:c>
       <x:c r="EG76" s="7" t="n">
-        <x:v>15200.0000</x:v>
+        <x:v>20200.0000</x:v>
       </x:c>
       <x:c r="EH76" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="EI76" s="9" t="n">
-        <x:v>18.7900</x:v>
+        <x:v>22.1200</x:v>
       </x:c>
       <x:c r="EJ76" s="7" t="n">
-        <x:v>16800.0000</x:v>
+        <x:v>15800.0000</x:v>
       </x:c>
       <x:c r="EK76" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="EL76" s="9" t="n">
-        <x:v>18.5400</x:v>
+        <x:v>17.8700</x:v>
       </x:c>
       <x:c r="EM76" s="7" t="n">
         <x:v>0.0000</x:v>
@@ -68355,22 +68355,22 @@
         <x:v>21.4500</x:v>
       </x:c>
       <x:c r="EV76" s="7" t="n">
-        <x:v>9100.0000</x:v>
+        <x:v>5100.0000</x:v>
       </x:c>
       <x:c r="EW76" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="EX76" s="9" t="n">
-        <x:v>8.8800</x:v>
+        <x:v>6.2100</x:v>
       </x:c>
       <x:c r="EY76" s="7" t="n">
-        <x:v>14800.0000</x:v>
+        <x:v>11600.0000</x:v>
       </x:c>
       <x:c r="EZ76" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FA76" s="9" t="n">
-        <x:v>16.4700</x:v>
+        <x:v>14.3400</x:v>
       </x:c>
       <x:c r="FB76" s="7" t="n">
         <x:v>18100.0000</x:v>
@@ -68454,13 +68454,13 @@
         <x:v>17.9200</x:v>
       </x:c>
       <x:c r="GC76" s="7" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5200.0000</x:v>
       </x:c>
       <x:c r="GD76" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="GE76" s="9" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3.4600</x:v>
       </x:c>
       <x:c r="GF76" s="7" t="n">
         <x:v>0.0000</x:v>
@@ -68472,13 +68472,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GI76" s="7" t="n">
-        <x:v>7550.0000</x:v>
+        <x:v>5550.0000</x:v>
       </x:c>
       <x:c r="GJ76" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="GK76" s="9" t="n">
-        <x:v>7.0600</x:v>
+        <x:v>5.7300</x:v>
       </x:c>
       <x:c r="GL76" s="7" t="n">
         <x:v>0.0000</x:v>

--- a/.pm-ai-cache/network-source/task-input-newest.xlsx
+++ b/.pm-ai-cache/network-source/task-input-newest.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工程別生産計画問合せ問合せ" sheetId="1" r:id="R73a2a23cd30b4e38"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工程別生産計画問合せ問合せ" sheetId="1" r:id="Rda1820ea73e14e9f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -10,7 +10,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6">
   <x:si>
-    <x:t xml:space="preserve">表示基準日 : 2026年07月08日 </x:t>
+    <x:t xml:space="preserve">表示基準日 : 2026年07月09日 </x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">S </x:t>
@@ -581,823 +581,823 @@
         <x:v/>
       </x:c>
       <x:c r="AR5" s="2" t="str">
-        <x:v>06/08(月)</x:v>
+        <x:v>06/09(火)</x:v>
       </x:c>
       <x:c r="AS5" s="2" t="str">
-        <x:v>06/08(月)</x:v>
+        <x:v>06/09(火)</x:v>
       </x:c>
       <x:c r="AT5" s="2" t="str">
-        <x:v>06/08(月)</x:v>
+        <x:v>06/09(火)</x:v>
       </x:c>
       <x:c r="AU5" s="2" t="str">
-        <x:v>06/09(火)</x:v>
+        <x:v>06/10(水)</x:v>
       </x:c>
       <x:c r="AV5" s="2" t="str">
-        <x:v>06/09(火)</x:v>
+        <x:v>06/10(水)</x:v>
       </x:c>
       <x:c r="AW5" s="2" t="str">
-        <x:v>06/09(火)</x:v>
+        <x:v>06/10(水)</x:v>
       </x:c>
       <x:c r="AX5" s="2" t="str">
-        <x:v>06/10(水)</x:v>
+        <x:v>06/11(木)</x:v>
       </x:c>
       <x:c r="AY5" s="2" t="str">
-        <x:v>06/10(水)</x:v>
+        <x:v>06/11(木)</x:v>
       </x:c>
       <x:c r="AZ5" s="2" t="str">
-        <x:v>06/10(水)</x:v>
+        <x:v>06/11(木)</x:v>
       </x:c>
       <x:c r="BA5" s="2" t="str">
-        <x:v>06/11(木)</x:v>
+        <x:v>06/12(金)</x:v>
       </x:c>
       <x:c r="BB5" s="2" t="str">
-        <x:v>06/11(木)</x:v>
+        <x:v>06/12(金)</x:v>
       </x:c>
       <x:c r="BC5" s="2" t="str">
-        <x:v>06/11(木)</x:v>
+        <x:v>06/12(金)</x:v>
       </x:c>
       <x:c r="BD5" s="2" t="str">
-        <x:v>06/12(金)</x:v>
+        <x:v>06/13(土)</x:v>
       </x:c>
       <x:c r="BE5" s="2" t="str">
-        <x:v>06/12(金)</x:v>
+        <x:v>06/13(土)</x:v>
       </x:c>
       <x:c r="BF5" s="2" t="str">
-        <x:v>06/12(金)</x:v>
+        <x:v>06/13(土)</x:v>
       </x:c>
       <x:c r="BG5" s="2" t="str">
-        <x:v>06/13(土)</x:v>
+        <x:v>06/14(日)</x:v>
       </x:c>
       <x:c r="BH5" s="2" t="str">
-        <x:v>06/13(土)</x:v>
+        <x:v>06/14(日)</x:v>
       </x:c>
       <x:c r="BI5" s="2" t="str">
-        <x:v>06/13(土)</x:v>
+        <x:v>06/14(日)</x:v>
       </x:c>
       <x:c r="BJ5" s="2" t="str">
-        <x:v>06/14(日)</x:v>
+        <x:v>06/15(月)</x:v>
       </x:c>
       <x:c r="BK5" s="2" t="str">
-        <x:v>06/14(日)</x:v>
+        <x:v>06/15(月)</x:v>
       </x:c>
       <x:c r="BL5" s="2" t="str">
-        <x:v>06/14(日)</x:v>
+        <x:v>06/15(月)</x:v>
       </x:c>
       <x:c r="BM5" s="2" t="str">
-        <x:v>06/15(月)</x:v>
+        <x:v>06/16(火)</x:v>
       </x:c>
       <x:c r="BN5" s="2" t="str">
-        <x:v>06/15(月)</x:v>
+        <x:v>06/16(火)</x:v>
       </x:c>
       <x:c r="BO5" s="2" t="str">
-        <x:v>06/15(月)</x:v>
+        <x:v>06/16(火)</x:v>
       </x:c>
       <x:c r="BP5" s="2" t="str">
-        <x:v>06/16(火)</x:v>
+        <x:v>06/17(水)</x:v>
       </x:c>
       <x:c r="BQ5" s="2" t="str">
-        <x:v>06/16(火)</x:v>
+        <x:v>06/17(水)</x:v>
       </x:c>
       <x:c r="BR5" s="2" t="str">
-        <x:v>06/16(火)</x:v>
+        <x:v>06/17(水)</x:v>
       </x:c>
       <x:c r="BS5" s="2" t="str">
-        <x:v>06/17(水)</x:v>
+        <x:v>06/18(木)</x:v>
       </x:c>
       <x:c r="BT5" s="2" t="str">
-        <x:v>06/17(水)</x:v>
+        <x:v>06/18(木)</x:v>
       </x:c>
       <x:c r="BU5" s="2" t="str">
-        <x:v>06/17(水)</x:v>
+        <x:v>06/18(木)</x:v>
       </x:c>
       <x:c r="BV5" s="2" t="str">
-        <x:v>06/18(木)</x:v>
+        <x:v>06/19(金)</x:v>
       </x:c>
       <x:c r="BW5" s="2" t="str">
-        <x:v>06/18(木)</x:v>
+        <x:v>06/19(金)</x:v>
       </x:c>
       <x:c r="BX5" s="2" t="str">
-        <x:v>06/18(木)</x:v>
+        <x:v>06/19(金)</x:v>
       </x:c>
       <x:c r="BY5" s="2" t="str">
-        <x:v>06/19(金)</x:v>
+        <x:v>06/20(土)</x:v>
       </x:c>
       <x:c r="BZ5" s="2" t="str">
-        <x:v>06/19(金)</x:v>
+        <x:v>06/20(土)</x:v>
       </x:c>
       <x:c r="CA5" s="2" t="str">
-        <x:v>06/19(金)</x:v>
+        <x:v>06/20(土)</x:v>
       </x:c>
       <x:c r="CB5" s="2" t="str">
-        <x:v>06/20(土)</x:v>
+        <x:v>06/21(日)</x:v>
       </x:c>
       <x:c r="CC5" s="2" t="str">
-        <x:v>06/20(土)</x:v>
+        <x:v>06/21(日)</x:v>
       </x:c>
       <x:c r="CD5" s="2" t="str">
-        <x:v>06/20(土)</x:v>
+        <x:v>06/21(日)</x:v>
       </x:c>
       <x:c r="CE5" s="2" t="str">
-        <x:v>06/21(日)</x:v>
+        <x:v>06/22(月)</x:v>
       </x:c>
       <x:c r="CF5" s="2" t="str">
-        <x:v>06/21(日)</x:v>
+        <x:v>06/22(月)</x:v>
       </x:c>
       <x:c r="CG5" s="2" t="str">
-        <x:v>06/21(日)</x:v>
+        <x:v>06/22(月)</x:v>
       </x:c>
       <x:c r="CH5" s="2" t="str">
-        <x:v>06/22(月)</x:v>
+        <x:v>06/23(火)</x:v>
       </x:c>
       <x:c r="CI5" s="2" t="str">
-        <x:v>06/22(月)</x:v>
+        <x:v>06/23(火)</x:v>
       </x:c>
       <x:c r="CJ5" s="2" t="str">
-        <x:v>06/22(月)</x:v>
+        <x:v>06/23(火)</x:v>
       </x:c>
       <x:c r="CK5" s="2" t="str">
-        <x:v>06/23(火)</x:v>
+        <x:v>06/24(水)</x:v>
       </x:c>
       <x:c r="CL5" s="2" t="str">
-        <x:v>06/23(火)</x:v>
+        <x:v>06/24(水)</x:v>
       </x:c>
       <x:c r="CM5" s="2" t="str">
-        <x:v>06/23(火)</x:v>
+        <x:v>06/24(水)</x:v>
       </x:c>
       <x:c r="CN5" s="2" t="str">
-        <x:v>06/24(水)</x:v>
+        <x:v>06/25(木)</x:v>
       </x:c>
       <x:c r="CO5" s="2" t="str">
-        <x:v>06/24(水)</x:v>
+        <x:v>06/25(木)</x:v>
       </x:c>
       <x:c r="CP5" s="2" t="str">
-        <x:v>06/24(水)</x:v>
+        <x:v>06/25(木)</x:v>
       </x:c>
       <x:c r="CQ5" s="2" t="str">
-        <x:v>06/25(木)</x:v>
+        <x:v>06/26(金)</x:v>
       </x:c>
       <x:c r="CR5" s="2" t="str">
-        <x:v>06/25(木)</x:v>
+        <x:v>06/26(金)</x:v>
       </x:c>
       <x:c r="CS5" s="2" t="str">
-        <x:v>06/25(木)</x:v>
+        <x:v>06/26(金)</x:v>
       </x:c>
       <x:c r="CT5" s="2" t="str">
-        <x:v>06/26(金)</x:v>
+        <x:v>06/27(土)</x:v>
       </x:c>
       <x:c r="CU5" s="2" t="str">
-        <x:v>06/26(金)</x:v>
+        <x:v>06/27(土)</x:v>
       </x:c>
       <x:c r="CV5" s="2" t="str">
-        <x:v>06/26(金)</x:v>
+        <x:v>06/27(土)</x:v>
       </x:c>
       <x:c r="CW5" s="2" t="str">
-        <x:v>06/27(土)</x:v>
+        <x:v>06/28(日)</x:v>
       </x:c>
       <x:c r="CX5" s="2" t="str">
-        <x:v>06/27(土)</x:v>
+        <x:v>06/28(日)</x:v>
       </x:c>
       <x:c r="CY5" s="2" t="str">
-        <x:v>06/27(土)</x:v>
+        <x:v>06/28(日)</x:v>
       </x:c>
       <x:c r="CZ5" s="2" t="str">
-        <x:v>06/28(日)</x:v>
+        <x:v>06/29(月)</x:v>
       </x:c>
       <x:c r="DA5" s="2" t="str">
-        <x:v>06/28(日)</x:v>
+        <x:v>06/29(月)</x:v>
       </x:c>
       <x:c r="DB5" s="2" t="str">
-        <x:v>06/28(日)</x:v>
+        <x:v>06/29(月)</x:v>
       </x:c>
       <x:c r="DC5" s="2" t="str">
-        <x:v>06/29(月)</x:v>
+        <x:v>06/30(火)</x:v>
       </x:c>
       <x:c r="DD5" s="2" t="str">
-        <x:v>06/29(月)</x:v>
+        <x:v>06/30(火)</x:v>
       </x:c>
       <x:c r="DE5" s="2" t="str">
-        <x:v>06/29(月)</x:v>
+        <x:v>06/30(火)</x:v>
       </x:c>
       <x:c r="DF5" s="2" t="str">
-        <x:v>06/30(火)</x:v>
+        <x:v>07/01(水)</x:v>
       </x:c>
       <x:c r="DG5" s="2" t="str">
-        <x:v>06/30(火)</x:v>
+        <x:v>07/01(水)</x:v>
       </x:c>
       <x:c r="DH5" s="2" t="str">
-        <x:v>06/30(火)</x:v>
+        <x:v>07/01(水)</x:v>
       </x:c>
       <x:c r="DI5" s="2" t="str">
-        <x:v>07/01(水)</x:v>
+        <x:v>07/02(木)</x:v>
       </x:c>
       <x:c r="DJ5" s="2" t="str">
-        <x:v>07/01(水)</x:v>
+        <x:v>07/02(木)</x:v>
       </x:c>
       <x:c r="DK5" s="2" t="str">
-        <x:v>07/01(水)</x:v>
+        <x:v>07/02(木)</x:v>
       </x:c>
       <x:c r="DL5" s="2" t="str">
-        <x:v>07/02(木)</x:v>
+        <x:v>07/03(金)</x:v>
       </x:c>
       <x:c r="DM5" s="2" t="str">
-        <x:v>07/02(木)</x:v>
+        <x:v>07/03(金)</x:v>
       </x:c>
       <x:c r="DN5" s="2" t="str">
-        <x:v>07/02(木)</x:v>
+        <x:v>07/03(金)</x:v>
       </x:c>
       <x:c r="DO5" s="2" t="str">
-        <x:v>07/03(金)</x:v>
+        <x:v>07/04(土)</x:v>
       </x:c>
       <x:c r="DP5" s="2" t="str">
-        <x:v>07/03(金)</x:v>
+        <x:v>07/04(土)</x:v>
       </x:c>
       <x:c r="DQ5" s="2" t="str">
-        <x:v>07/03(金)</x:v>
+        <x:v>07/04(土)</x:v>
       </x:c>
       <x:c r="DR5" s="2" t="str">
-        <x:v>07/04(土)</x:v>
+        <x:v>07/05(日)</x:v>
       </x:c>
       <x:c r="DS5" s="2" t="str">
-        <x:v>07/04(土)</x:v>
+        <x:v>07/05(日)</x:v>
       </x:c>
       <x:c r="DT5" s="2" t="str">
-        <x:v>07/04(土)</x:v>
+        <x:v>07/05(日)</x:v>
       </x:c>
       <x:c r="DU5" s="2" t="str">
-        <x:v>07/05(日)</x:v>
+        <x:v>07/06(月)</x:v>
       </x:c>
       <x:c r="DV5" s="2" t="str">
-        <x:v>07/05(日)</x:v>
+        <x:v>07/06(月)</x:v>
       </x:c>
       <x:c r="DW5" s="2" t="str">
-        <x:v>07/05(日)</x:v>
+        <x:v>07/06(月)</x:v>
       </x:c>
       <x:c r="DX5" s="2" t="str">
-        <x:v>07/06(月)</x:v>
+        <x:v>07/07(火)</x:v>
       </x:c>
       <x:c r="DY5" s="2" t="str">
-        <x:v>07/06(月)</x:v>
+        <x:v>07/07(火)</x:v>
       </x:c>
       <x:c r="DZ5" s="2" t="str">
-        <x:v>07/06(月)</x:v>
+        <x:v>07/07(火)</x:v>
       </x:c>
       <x:c r="EA5" s="2" t="str">
-        <x:v>07/07(火)</x:v>
+        <x:v>07/08(水)</x:v>
       </x:c>
       <x:c r="EB5" s="2" t="str">
-        <x:v>07/07(火)</x:v>
+        <x:v>07/08(水)</x:v>
       </x:c>
       <x:c r="EC5" s="2" t="str">
-        <x:v>07/07(火)</x:v>
+        <x:v>07/08(水)</x:v>
       </x:c>
       <x:c r="ED5" s="2" t="str">
-        <x:v>07/08(水)</x:v>
+        <x:v>07/09(木)</x:v>
       </x:c>
       <x:c r="EE5" s="2" t="str">
-        <x:v>07/08(水)</x:v>
+        <x:v>07/09(木)</x:v>
       </x:c>
       <x:c r="EF5" s="2" t="str">
-        <x:v>07/08(水)</x:v>
+        <x:v>07/09(木)</x:v>
       </x:c>
       <x:c r="EG5" s="2" t="str">
-        <x:v>07/09(木)</x:v>
+        <x:v>07/10(金)</x:v>
       </x:c>
       <x:c r="EH5" s="2" t="str">
-        <x:v>07/09(木)</x:v>
+        <x:v>07/10(金)</x:v>
       </x:c>
       <x:c r="EI5" s="2" t="str">
-        <x:v>07/09(木)</x:v>
+        <x:v>07/10(金)</x:v>
       </x:c>
       <x:c r="EJ5" s="2" t="str">
-        <x:v>07/10(金)</x:v>
+        <x:v>07/11(土)</x:v>
       </x:c>
       <x:c r="EK5" s="2" t="str">
-        <x:v>07/10(金)</x:v>
+        <x:v>07/11(土)</x:v>
       </x:c>
       <x:c r="EL5" s="2" t="str">
-        <x:v>07/10(金)</x:v>
+        <x:v>07/11(土)</x:v>
       </x:c>
       <x:c r="EM5" s="2" t="str">
-        <x:v>07/11(土)</x:v>
+        <x:v>07/12(日)</x:v>
       </x:c>
       <x:c r="EN5" s="2" t="str">
-        <x:v>07/11(土)</x:v>
+        <x:v>07/12(日)</x:v>
       </x:c>
       <x:c r="EO5" s="2" t="str">
-        <x:v>07/11(土)</x:v>
+        <x:v>07/12(日)</x:v>
       </x:c>
       <x:c r="EP5" s="2" t="str">
-        <x:v>07/12(日)</x:v>
+        <x:v>07/13(月)</x:v>
       </x:c>
       <x:c r="EQ5" s="2" t="str">
-        <x:v>07/12(日)</x:v>
+        <x:v>07/13(月)</x:v>
       </x:c>
       <x:c r="ER5" s="2" t="str">
-        <x:v>07/12(日)</x:v>
+        <x:v>07/13(月)</x:v>
       </x:c>
       <x:c r="ES5" s="2" t="str">
-        <x:v>07/13(月)</x:v>
+        <x:v>07/14(火)</x:v>
       </x:c>
       <x:c r="ET5" s="2" t="str">
-        <x:v>07/13(月)</x:v>
+        <x:v>07/14(火)</x:v>
       </x:c>
       <x:c r="EU5" s="2" t="str">
-        <x:v>07/13(月)</x:v>
+        <x:v>07/14(火)</x:v>
       </x:c>
       <x:c r="EV5" s="2" t="str">
-        <x:v>07/14(火)</x:v>
+        <x:v>07/15(水)</x:v>
       </x:c>
       <x:c r="EW5" s="2" t="str">
-        <x:v>07/14(火)</x:v>
+        <x:v>07/15(水)</x:v>
       </x:c>
       <x:c r="EX5" s="2" t="str">
-        <x:v>07/14(火)</x:v>
+        <x:v>07/15(水)</x:v>
       </x:c>
       <x:c r="EY5" s="2" t="str">
-        <x:v>07/15(水)</x:v>
+        <x:v>07/16(木)</x:v>
       </x:c>
       <x:c r="EZ5" s="2" t="str">
-        <x:v>07/15(水)</x:v>
+        <x:v>07/16(木)</x:v>
       </x:c>
       <x:c r="FA5" s="2" t="str">
-        <x:v>07/15(水)</x:v>
+        <x:v>07/16(木)</x:v>
       </x:c>
       <x:c r="FB5" s="2" t="str">
-        <x:v>07/16(木)</x:v>
+        <x:v>07/17(金)</x:v>
       </x:c>
       <x:c r="FC5" s="2" t="str">
-        <x:v>07/16(木)</x:v>
+        <x:v>07/17(金)</x:v>
       </x:c>
       <x:c r="FD5" s="2" t="str">
-        <x:v>07/16(木)</x:v>
+        <x:v>07/17(金)</x:v>
       </x:c>
       <x:c r="FE5" s="2" t="str">
-        <x:v>07/17(金)</x:v>
+        <x:v>07/18(土)</x:v>
       </x:c>
       <x:c r="FF5" s="2" t="str">
-        <x:v>07/17(金)</x:v>
+        <x:v>07/18(土)</x:v>
       </x:c>
       <x:c r="FG5" s="2" t="str">
-        <x:v>07/17(金)</x:v>
+        <x:v>07/18(土)</x:v>
       </x:c>
       <x:c r="FH5" s="2" t="str">
-        <x:v>07/18(土)</x:v>
+        <x:v>07/19(日)</x:v>
       </x:c>
       <x:c r="FI5" s="2" t="str">
-        <x:v>07/18(土)</x:v>
+        <x:v>07/19(日)</x:v>
       </x:c>
       <x:c r="FJ5" s="2" t="str">
-        <x:v>07/18(土)</x:v>
+        <x:v>07/19(日)</x:v>
       </x:c>
       <x:c r="FK5" s="2" t="str">
-        <x:v>07/19(日)</x:v>
+        <x:v>07/20(月)</x:v>
       </x:c>
       <x:c r="FL5" s="2" t="str">
-        <x:v>07/19(日)</x:v>
+        <x:v>07/20(月)</x:v>
       </x:c>
       <x:c r="FM5" s="2" t="str">
-        <x:v>07/19(日)</x:v>
+        <x:v>07/20(月)</x:v>
       </x:c>
       <x:c r="FN5" s="2" t="str">
-        <x:v>07/20(月)</x:v>
+        <x:v>07/21(火)</x:v>
       </x:c>
       <x:c r="FO5" s="2" t="str">
-        <x:v>07/20(月)</x:v>
+        <x:v>07/21(火)</x:v>
       </x:c>
       <x:c r="FP5" s="2" t="str">
-        <x:v>07/20(月)</x:v>
+        <x:v>07/21(火)</x:v>
       </x:c>
       <x:c r="FQ5" s="2" t="str">
-        <x:v>07/21(火)</x:v>
+        <x:v>07/22(水)</x:v>
       </x:c>
       <x:c r="FR5" s="2" t="str">
-        <x:v>07/21(火)</x:v>
+        <x:v>07/22(水)</x:v>
       </x:c>
       <x:c r="FS5" s="2" t="str">
-        <x:v>07/21(火)</x:v>
+        <x:v>07/22(水)</x:v>
       </x:c>
       <x:c r="FT5" s="2" t="str">
-        <x:v>07/22(水)</x:v>
+        <x:v>07/23(木)</x:v>
       </x:c>
       <x:c r="FU5" s="2" t="str">
-        <x:v>07/22(水)</x:v>
+        <x:v>07/23(木)</x:v>
       </x:c>
       <x:c r="FV5" s="2" t="str">
-        <x:v>07/22(水)</x:v>
+        <x:v>07/23(木)</x:v>
       </x:c>
       <x:c r="FW5" s="2" t="str">
-        <x:v>07/23(木)</x:v>
+        <x:v>07/24(金)</x:v>
       </x:c>
       <x:c r="FX5" s="2" t="str">
-        <x:v>07/23(木)</x:v>
+        <x:v>07/24(金)</x:v>
       </x:c>
       <x:c r="FY5" s="2" t="str">
-        <x:v>07/23(木)</x:v>
+        <x:v>07/24(金)</x:v>
       </x:c>
       <x:c r="FZ5" s="2" t="str">
-        <x:v>07/24(金)</x:v>
+        <x:v>07/25(土)</x:v>
       </x:c>
       <x:c r="GA5" s="2" t="str">
-        <x:v>07/24(金)</x:v>
+        <x:v>07/25(土)</x:v>
       </x:c>
       <x:c r="GB5" s="2" t="str">
-        <x:v>07/24(金)</x:v>
+        <x:v>07/25(土)</x:v>
       </x:c>
       <x:c r="GC5" s="2" t="str">
-        <x:v>07/25(土)</x:v>
+        <x:v>07/26(日)</x:v>
       </x:c>
       <x:c r="GD5" s="2" t="str">
-        <x:v>07/25(土)</x:v>
+        <x:v>07/26(日)</x:v>
       </x:c>
       <x:c r="GE5" s="2" t="str">
-        <x:v>07/25(土)</x:v>
+        <x:v>07/26(日)</x:v>
       </x:c>
       <x:c r="GF5" s="2" t="str">
-        <x:v>07/26(日)</x:v>
+        <x:v>07/27(月)</x:v>
       </x:c>
       <x:c r="GG5" s="2" t="str">
-        <x:v>07/26(日)</x:v>
+        <x:v>07/27(月)</x:v>
       </x:c>
       <x:c r="GH5" s="2" t="str">
-        <x:v>07/26(日)</x:v>
+        <x:v>07/27(月)</x:v>
       </x:c>
       <x:c r="GI5" s="2" t="str">
-        <x:v>07/27(月)</x:v>
+        <x:v>07/28(火)</x:v>
       </x:c>
       <x:c r="GJ5" s="2" t="str">
-        <x:v>07/27(月)</x:v>
+        <x:v>07/28(火)</x:v>
       </x:c>
       <x:c r="GK5" s="2" t="str">
-        <x:v>07/27(月)</x:v>
+        <x:v>07/28(火)</x:v>
       </x:c>
       <x:c r="GL5" s="2" t="str">
-        <x:v>07/28(火)</x:v>
+        <x:v>07/29(水)</x:v>
       </x:c>
       <x:c r="GM5" s="2" t="str">
-        <x:v>07/28(火)</x:v>
+        <x:v>07/29(水)</x:v>
       </x:c>
       <x:c r="GN5" s="2" t="str">
-        <x:v>07/28(火)</x:v>
+        <x:v>07/29(水)</x:v>
       </x:c>
       <x:c r="GO5" s="2" t="str">
-        <x:v>07/29(水)</x:v>
+        <x:v>07/30(木)</x:v>
       </x:c>
       <x:c r="GP5" s="2" t="str">
-        <x:v>07/29(水)</x:v>
+        <x:v>07/30(木)</x:v>
       </x:c>
       <x:c r="GQ5" s="2" t="str">
-        <x:v>07/29(水)</x:v>
+        <x:v>07/30(木)</x:v>
       </x:c>
       <x:c r="GR5" s="2" t="str">
-        <x:v>07/30(木)</x:v>
+        <x:v>07/31(金)</x:v>
       </x:c>
       <x:c r="GS5" s="2" t="str">
-        <x:v>07/30(木)</x:v>
+        <x:v>07/31(金)</x:v>
       </x:c>
       <x:c r="GT5" s="2" t="str">
-        <x:v>07/30(木)</x:v>
+        <x:v>07/31(金)</x:v>
       </x:c>
       <x:c r="GU5" s="2" t="str">
-        <x:v>07/31(金)</x:v>
+        <x:v>08/01(土)</x:v>
       </x:c>
       <x:c r="GV5" s="2" t="str">
-        <x:v>07/31(金)</x:v>
+        <x:v>08/01(土)</x:v>
       </x:c>
       <x:c r="GW5" s="2" t="str">
-        <x:v>07/31(金)</x:v>
+        <x:v>08/01(土)</x:v>
       </x:c>
       <x:c r="GX5" s="2" t="str">
-        <x:v>08/01(土)</x:v>
+        <x:v>08/02(日)</x:v>
       </x:c>
       <x:c r="GY5" s="2" t="str">
-        <x:v>08/01(土)</x:v>
+        <x:v>08/02(日)</x:v>
       </x:c>
       <x:c r="GZ5" s="2" t="str">
-        <x:v>08/01(土)</x:v>
+        <x:v>08/02(日)</x:v>
       </x:c>
       <x:c r="HA5" s="2" t="str">
-        <x:v>08/02(日)</x:v>
+        <x:v>08/03(月)</x:v>
       </x:c>
       <x:c r="HB5" s="2" t="str">
-        <x:v>08/02(日)</x:v>
+        <x:v>08/03(月)</x:v>
       </x:c>
       <x:c r="HC5" s="2" t="str">
-        <x:v>08/02(日)</x:v>
+        <x:v>08/03(月)</x:v>
       </x:c>
       <x:c r="HD5" s="2" t="str">
-        <x:v>08/03(月)</x:v>
+        <x:v>08/04(火)</x:v>
       </x:c>
       <x:c r="HE5" s="2" t="str">
-        <x:v>08/03(月)</x:v>
+        <x:v>08/04(火)</x:v>
       </x:c>
       <x:c r="HF5" s="2" t="str">
-        <x:v>08/03(月)</x:v>
+        <x:v>08/04(火)</x:v>
       </x:c>
       <x:c r="HG5" s="2" t="str">
-        <x:v>08/04(火)</x:v>
+        <x:v>08/05(水)</x:v>
       </x:c>
       <x:c r="HH5" s="2" t="str">
-        <x:v>08/04(火)</x:v>
+        <x:v>08/05(水)</x:v>
       </x:c>
       <x:c r="HI5" s="2" t="str">
-        <x:v>08/04(火)</x:v>
+        <x:v>08/05(水)</x:v>
       </x:c>
       <x:c r="HJ5" s="2" t="str">
-        <x:v>08/05(水)</x:v>
+        <x:v>08/06(木)</x:v>
       </x:c>
       <x:c r="HK5" s="2" t="str">
-        <x:v>08/05(水)</x:v>
+        <x:v>08/06(木)</x:v>
       </x:c>
       <x:c r="HL5" s="2" t="str">
-        <x:v>08/05(水)</x:v>
+        <x:v>08/06(木)</x:v>
       </x:c>
       <x:c r="HM5" s="2" t="str">
-        <x:v>08/06(木)</x:v>
+        <x:v>08/07(金)</x:v>
       </x:c>
       <x:c r="HN5" s="2" t="str">
-        <x:v>08/06(木)</x:v>
+        <x:v>08/07(金)</x:v>
       </x:c>
       <x:c r="HO5" s="2" t="str">
-        <x:v>08/06(木)</x:v>
+        <x:v>08/07(金)</x:v>
       </x:c>
       <x:c r="HP5" s="2" t="str">
-        <x:v>08/07(金)</x:v>
+        <x:v>08/08(土)</x:v>
       </x:c>
       <x:c r="HQ5" s="2" t="str">
-        <x:v>08/07(金)</x:v>
+        <x:v>08/08(土)</x:v>
       </x:c>
       <x:c r="HR5" s="2" t="str">
-        <x:v>08/07(金)</x:v>
+        <x:v>08/08(土)</x:v>
       </x:c>
       <x:c r="HS5" s="2" t="str">
-        <x:v>08/08(土)</x:v>
+        <x:v>08/09(日)</x:v>
       </x:c>
       <x:c r="HT5" s="2" t="str">
-        <x:v>08/08(土)</x:v>
+        <x:v>08/09(日)</x:v>
       </x:c>
       <x:c r="HU5" s="2" t="str">
-        <x:v>08/08(土)</x:v>
+        <x:v>08/09(日)</x:v>
       </x:c>
       <x:c r="HV5" s="2" t="str">
-        <x:v>08/09(日)</x:v>
+        <x:v>08/10(月)</x:v>
       </x:c>
       <x:c r="HW5" s="2" t="str">
-        <x:v>08/09(日)</x:v>
+        <x:v>08/10(月)</x:v>
       </x:c>
       <x:c r="HX5" s="2" t="str">
-        <x:v>08/09(日)</x:v>
+        <x:v>08/10(月)</x:v>
       </x:c>
       <x:c r="HY5" s="2" t="str">
-        <x:v>08/10(月)</x:v>
+        <x:v>08/11(火)</x:v>
       </x:c>
       <x:c r="HZ5" s="2" t="str">
-        <x:v>08/10(月)</x:v>
+        <x:v>08/11(火)</x:v>
       </x:c>
       <x:c r="IA5" s="2" t="str">
-        <x:v>08/10(月)</x:v>
+        <x:v>08/11(火)</x:v>
       </x:c>
       <x:c r="IB5" s="2" t="str">
-        <x:v>08/11(火)</x:v>
+        <x:v>08/12(水)</x:v>
       </x:c>
       <x:c r="IC5" s="2" t="str">
-        <x:v>08/11(火)</x:v>
+        <x:v>08/12(水)</x:v>
       </x:c>
       <x:c r="ID5" s="2" t="str">
-        <x:v>08/11(火)</x:v>
+        <x:v>08/12(水)</x:v>
       </x:c>
       <x:c r="IE5" s="2" t="str">
-        <x:v>08/12(水)</x:v>
+        <x:v>08/13(木)</x:v>
       </x:c>
       <x:c r="IF5" s="2" t="str">
-        <x:v>08/12(水)</x:v>
+        <x:v>08/13(木)</x:v>
       </x:c>
       <x:c r="IG5" s="2" t="str">
-        <x:v>08/12(水)</x:v>
+        <x:v>08/13(木)</x:v>
       </x:c>
       <x:c r="IH5" s="2" t="str">
-        <x:v>08/13(木)</x:v>
+        <x:v>08/14(金)</x:v>
       </x:c>
       <x:c r="II5" s="2" t="str">
-        <x:v>08/13(木)</x:v>
+        <x:v>08/14(金)</x:v>
       </x:c>
       <x:c r="IJ5" s="2" t="str">
-        <x:v>08/13(木)</x:v>
+        <x:v>08/14(金)</x:v>
       </x:c>
       <x:c r="IK5" s="2" t="str">
-        <x:v>08/14(金)</x:v>
+        <x:v>08/15(土)</x:v>
       </x:c>
       <x:c r="IL5" s="2" t="str">
-        <x:v>08/14(金)</x:v>
+        <x:v>08/15(土)</x:v>
       </x:c>
       <x:c r="IM5" s="2" t="str">
-        <x:v>08/14(金)</x:v>
+        <x:v>08/15(土)</x:v>
       </x:c>
       <x:c r="IN5" s="2" t="str">
-        <x:v>08/15(土)</x:v>
+        <x:v>08/16(日)</x:v>
       </x:c>
       <x:c r="IO5" s="2" t="str">
-        <x:v>08/15(土)</x:v>
+        <x:v>08/16(日)</x:v>
       </x:c>
       <x:c r="IP5" s="2" t="str">
-        <x:v>08/15(土)</x:v>
+        <x:v>08/16(日)</x:v>
       </x:c>
       <x:c r="IQ5" s="2" t="str">
-        <x:v>08/16(日)</x:v>
+        <x:v>08/17(月)</x:v>
       </x:c>
       <x:c r="IR5" s="2" t="str">
-        <x:v>08/16(日)</x:v>
+        <x:v>08/17(月)</x:v>
       </x:c>
       <x:c r="IS5" s="2" t="str">
-        <x:v>08/16(日)</x:v>
+        <x:v>08/17(月)</x:v>
       </x:c>
       <x:c r="IT5" s="2" t="str">
-        <x:v>08/17(月)</x:v>
+        <x:v>08/18(火)</x:v>
       </x:c>
       <x:c r="IU5" s="2" t="str">
-        <x:v>08/17(月)</x:v>
+        <x:v>08/18(火)</x:v>
       </x:c>
       <x:c r="IV5" s="2" t="str">
-        <x:v>08/17(月)</x:v>
+        <x:v>08/18(火)</x:v>
       </x:c>
       <x:c r="IW5" s="2" t="str">
-        <x:v>08/18(火)</x:v>
+        <x:v>08/19(水)</x:v>
       </x:c>
       <x:c r="IX5" s="2" t="str">
-        <x:v>08/18(火)</x:v>
+        <x:v>08/19(水)</x:v>
       </x:c>
       <x:c r="IY5" s="2" t="str">
-        <x:v>08/18(火)</x:v>
+        <x:v>08/19(水)</x:v>
       </x:c>
       <x:c r="IZ5" s="2" t="str">
-        <x:v>08/19(水)</x:v>
+        <x:v>08/20(木)</x:v>
       </x:c>
       <x:c r="JA5" s="2" t="str">
-        <x:v>08/19(水)</x:v>
+        <x:v>08/20(木)</x:v>
       </x:c>
       <x:c r="JB5" s="2" t="str">
-        <x:v>08/19(水)</x:v>
+        <x:v>08/20(木)</x:v>
       </x:c>
       <x:c r="JC5" s="2" t="str">
-        <x:v>08/20(木)</x:v>
+        <x:v>08/21(金)</x:v>
       </x:c>
       <x:c r="JD5" s="2" t="str">
-        <x:v>08/20(木)</x:v>
+        <x:v>08/21(金)</x:v>
       </x:c>
       <x:c r="JE5" s="2" t="str">
-        <x:v>08/20(木)</x:v>
+        <x:v>08/21(金)</x:v>
       </x:c>
       <x:c r="JF5" s="2" t="str">
-        <x:v>08/21(金)</x:v>
+        <x:v>08/22(土)</x:v>
       </x:c>
       <x:c r="JG5" s="2" t="str">
-        <x:v>08/21(金)</x:v>
+        <x:v>08/22(土)</x:v>
       </x:c>
       <x:c r="JH5" s="2" t="str">
-        <x:v>08/21(金)</x:v>
+        <x:v>08/22(土)</x:v>
       </x:c>
       <x:c r="JI5" s="2" t="str">
-        <x:v>08/22(土)</x:v>
+        <x:v>08/23(日)</x:v>
       </x:c>
       <x:c r="JJ5" s="2" t="str">
-        <x:v>08/22(土)</x:v>
+        <x:v>08/23(日)</x:v>
       </x:c>
       <x:c r="JK5" s="2" t="str">
-        <x:v>08/22(土)</x:v>
+        <x:v>08/23(日)</x:v>
       </x:c>
       <x:c r="JL5" s="2" t="str">
-        <x:v>08/23(日)</x:v>
+        <x:v>08/24(月)</x:v>
       </x:c>
       <x:c r="JM5" s="2" t="str">
-        <x:v>08/23(日)</x:v>
+        <x:v>08/24(月)</x:v>
       </x:c>
       <x:c r="JN5" s="2" t="str">
-        <x:v>08/23(日)</x:v>
+        <x:v>08/24(月)</x:v>
       </x:c>
       <x:c r="JO5" s="2" t="str">
-        <x:v>08/24(月)</x:v>
+        <x:v>08/25(火)</x:v>
       </x:c>
       <x:c r="JP5" s="2" t="str">
-        <x:v>08/24(月)</x:v>
+        <x:v>08/25(火)</x:v>
       </x:c>
       <x:c r="JQ5" s="2" t="str">
-        <x:v>08/24(月)</x:v>
+        <x:v>08/25(火)</x:v>
       </x:c>
       <x:c r="JR5" s="2" t="str">
-        <x:v>08/25(火)</x:v>
+        <x:v>08/26(水)</x:v>
       </x:c>
       <x:c r="JS5" s="2" t="str">
-        <x:v>08/25(火)</x:v>
+        <x:v>08/26(水)</x:v>
       </x:c>
       <x:c r="JT5" s="2" t="str">
-        <x:v>08/25(火)</x:v>
+        <x:v>08/26(水)</x:v>
       </x:c>
       <x:c r="JU5" s="2" t="str">
-        <x:v>08/26(水)</x:v>
+        <x:v>08/27(木)</x:v>
       </x:c>
       <x:c r="JV5" s="2" t="str">
-        <x:v>08/26(水)</x:v>
+        <x:v>08/27(木)</x:v>
       </x:c>
       <x:c r="JW5" s="2" t="str">
-        <x:v>08/26(水)</x:v>
+        <x:v>08/27(木)</x:v>
       </x:c>
       <x:c r="JX5" s="2" t="str">
-        <x:v>08/27(木)</x:v>
+        <x:v>08/28(金)</x:v>
       </x:c>
       <x:c r="JY5" s="2" t="str">
-        <x:v>08/27(木)</x:v>
+        <x:v>08/28(金)</x:v>
       </x:c>
       <x:c r="JZ5" s="2" t="str">
-        <x:v>08/27(木)</x:v>
+        <x:v>08/28(金)</x:v>
       </x:c>
       <x:c r="KA5" s="2" t="str">
-        <x:v>08/28(金)</x:v>
+        <x:v>08/29(土)</x:v>
       </x:c>
       <x:c r="KB5" s="2" t="str">
-        <x:v>08/28(金)</x:v>
+        <x:v>08/29(土)</x:v>
       </x:c>
       <x:c r="KC5" s="2" t="str">
-        <x:v>08/28(金)</x:v>
+        <x:v>08/29(土)</x:v>
       </x:c>
       <x:c r="KD5" s="2" t="str">
-        <x:v>08/29(土)</x:v>
+        <x:v>08/30(日)</x:v>
       </x:c>
       <x:c r="KE5" s="2" t="str">
-        <x:v>08/29(土)</x:v>
+        <x:v>08/30(日)</x:v>
       </x:c>
       <x:c r="KF5" s="2" t="str">
-        <x:v>08/29(土)</x:v>
+        <x:v>08/30(日)</x:v>
       </x:c>
       <x:c r="KG5" s="2" t="str">
-        <x:v>08/30(日)</x:v>
+        <x:v>08/31(月)</x:v>
       </x:c>
       <x:c r="KH5" s="2" t="str">
-        <x:v>08/30(日)</x:v>
+        <x:v>08/31(月)</x:v>
       </x:c>
       <x:c r="KI5" s="2" t="str">
-        <x:v>08/30(日)</x:v>
+        <x:v>08/31(月)</x:v>
       </x:c>
       <x:c r="KJ5" s="2" t="str">
-        <x:v>08/31(月)</x:v>
+        <x:v>09/01(火)</x:v>
       </x:c>
       <x:c r="KK5" s="2" t="str">
-        <x:v>08/31(月)</x:v>
+        <x:v>09/01(火)</x:v>
       </x:c>
       <x:c r="KL5" s="2" t="str">
-        <x:v>08/31(月)</x:v>
+        <x:v>09/01(火)</x:v>
       </x:c>
       <x:c r="KM5" s="2" t="str">
-        <x:v>09/01(火)</x:v>
+        <x:v>09/02(水)</x:v>
       </x:c>
       <x:c r="KN5" s="2" t="str">
-        <x:v>09/01(火)</x:v>
+        <x:v>09/02(水)</x:v>
       </x:c>
       <x:c r="KO5" s="2" t="str">
-        <x:v>09/01(火)</x:v>
+        <x:v>09/02(水)</x:v>
       </x:c>
       <x:c r="KP5" s="2" t="str">
-        <x:v>09/02(水)</x:v>
+        <x:v>09/03(木)</x:v>
       </x:c>
       <x:c r="KQ5" s="2" t="str">
-        <x:v>09/02(水)</x:v>
+        <x:v>09/03(木)</x:v>
       </x:c>
       <x:c r="KR5" s="2" t="str">
-        <x:v>09/02(水)</x:v>
+        <x:v>09/03(木)</x:v>
       </x:c>
       <x:c r="KS5" s="2" t="str">
-        <x:v>09/03(木)</x:v>
+        <x:v>09/04(金)</x:v>
       </x:c>
       <x:c r="KT5" s="2" t="str">
-        <x:v>09/03(木)</x:v>
+        <x:v>09/04(金)</x:v>
       </x:c>
       <x:c r="KU5" s="2" t="str">
-        <x:v>09/03(木)</x:v>
+        <x:v>09/04(金)</x:v>
       </x:c>
       <x:c r="KV5" s="2" t="str">
-        <x:v>09/04(金)</x:v>
+        <x:v>09/05(土)</x:v>
       </x:c>
       <x:c r="KW5" s="2" t="str">
-        <x:v>09/04(金)</x:v>
+        <x:v>09/05(土)</x:v>
       </x:c>
       <x:c r="KX5" s="2" t="str">
-        <x:v>09/04(金)</x:v>
+        <x:v>09/05(土)</x:v>
       </x:c>
       <x:c r="KY5" s="2" t="str">
-        <x:v>09/05(土)</x:v>
+        <x:v>09/06(日)</x:v>
       </x:c>
       <x:c r="KZ5" s="2" t="str">
-        <x:v>09/05(土)</x:v>
+        <x:v>09/06(日)</x:v>
       </x:c>
       <x:c r="LA5" s="2" t="str">
-        <x:v>09/05(土)</x:v>
+        <x:v>09/06(日)</x:v>
       </x:c>
       <x:c r="LB5" s="2" t="str">
-        <x:v>09/06(日)</x:v>
+        <x:v>09/07(月)</x:v>
       </x:c>
       <x:c r="LC5" s="2" t="str">
-        <x:v>09/06(日)</x:v>
+        <x:v>09/07(月)</x:v>
       </x:c>
       <x:c r="LD5" s="2" t="str">
-        <x:v>09/06(日)</x:v>
+        <x:v>09/07(月)</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2451,7 +2451,7 @@
         <x:v/>
       </x:c>
       <x:c r="AH7" s="4" t="n">
-        <x:v>46227</x:v>
+        <x:v>46228</x:v>
       </x:c>
       <x:c r="AI7" s="4" t="n">
         <x:v>46230</x:v>
@@ -2895,13 +2895,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FZ7" s="6" t="n">
-        <x:v>7200.0000</x:v>
+        <x:v>8400.0000</x:v>
       </x:c>
       <x:c r="GA7" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="GB7" s="8" t="n">
-        <x:v>7.4400</x:v>
+        <x:v>8.6800</x:v>
       </x:c>
       <x:c r="GC7" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -2913,22 +2913,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GF7" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1600.0000</x:v>
       </x:c>
       <x:c r="GG7" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="GH7" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.6500</x:v>
       </x:c>
       <x:c r="GI7" s="6" t="n">
-        <x:v>2800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GJ7" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="GK7" s="8" t="n">
-        <x:v>2.8900</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GL7" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -3773,22 +3773,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB8" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>600.0000</x:v>
       </x:c>
       <x:c r="FC8" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FD8" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.6200</x:v>
       </x:c>
       <x:c r="FE8" s="6" t="n">
-        <x:v>600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FF8" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FG8" s="8" t="n">
-        <x:v>0.6200</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FH8" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -4813,22 +4813,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GF9" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2750.0000</x:v>
       </x:c>
       <x:c r="GG9" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="GH9" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.8400</x:v>
       </x:c>
       <x:c r="GI9" s="6" t="n">
-        <x:v>2750.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GJ9" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="GK9" s="8" t="n">
-        <x:v>2.8400</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GL9" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -5220,7 +5220,7 @@
         <x:v>スライス</x:v>
       </x:c>
       <x:c r="G10" s="1" t="str">
-        <x:v>004</x:v>
+        <x:v>005</x:v>
       </x:c>
       <x:c r="H10" s="4" t="n">
         <x:v>46209</x:v>
@@ -5301,10 +5301,10 @@
         <x:v/>
       </x:c>
       <x:c r="AH10" s="4" t="n">
-        <x:v>46212</x:v>
+        <x:v>46213</x:v>
       </x:c>
       <x:c r="AI10" s="4" t="n">
-        <x:v>46212</x:v>
+        <x:v>46213</x:v>
       </x:c>
       <x:c r="AJ10" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -6170,7 +6170,7 @@
         <x:v>スライス</x:v>
       </x:c>
       <x:c r="G11" s="1" t="str">
-        <x:v>019</x:v>
+        <x:v>018</x:v>
       </x:c>
       <x:c r="H11" s="4" t="n">
         <x:v>46190</x:v>
@@ -6251,10 +6251,10 @@
         <x:v/>
       </x:c>
       <x:c r="AH11" s="4" t="n">
-        <x:v>46211</x:v>
+        <x:v>46212</x:v>
       </x:c>
       <x:c r="AI11" s="4" t="n">
-        <x:v>46212</x:v>
+        <x:v>46213</x:v>
       </x:c>
       <x:c r="AJ11" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -6272,7 +6272,7 @@
         <x:v>2000.0000</x:v>
       </x:c>
       <x:c r="AO11" s="6" t="n">
-        <x:v>10000.0000</x:v>
+        <x:v>9000.0000</x:v>
       </x:c>
       <x:c r="AP11" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -6551,22 +6551,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ED11" s="6" t="n">
-        <x:v>1000.0000</x:v>
+        <x:v>8400.0000</x:v>
       </x:c>
       <x:c r="EE11" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EF11" s="8" t="n">
-        <x:v>1.0300</x:v>
+        <x:v>8.6800</x:v>
       </x:c>
       <x:c r="EG11" s="6" t="n">
-        <x:v>9000.0000</x:v>
+        <x:v>600.0000</x:v>
       </x:c>
       <x:c r="EH11" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EI11" s="8" t="n">
-        <x:v>9.3100</x:v>
+        <x:v>0.6200</x:v>
       </x:c>
       <x:c r="EJ11" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -7537,22 +7537,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP12" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1600.0000</x:v>
       </x:c>
       <x:c r="EQ12" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="ER12" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.6500</x:v>
       </x:c>
       <x:c r="ES12" s="6" t="n">
-        <x:v>1600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ET12" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EU12" s="8" t="n">
-        <x:v>1.6500</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV12" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -8496,22 +8496,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES13" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>200.0000</x:v>
       </x:c>
       <x:c r="ET13" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EU13" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.2100</x:v>
       </x:c>
       <x:c r="EV13" s="6" t="n">
-        <x:v>200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EW13" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EX13" s="8" t="n">
-        <x:v>0.2100</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY13" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -9437,22 +9437,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP14" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3400.0000</x:v>
       </x:c>
       <x:c r="EQ14" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="ER14" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3.5200</x:v>
       </x:c>
       <x:c r="ES14" s="6" t="n">
-        <x:v>3400.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ET14" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EU14" s="8" t="n">
-        <x:v>3.5200</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV14" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -10387,22 +10387,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP15" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>800.0000</x:v>
       </x:c>
       <x:c r="EQ15" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="ER15" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.8300</x:v>
       </x:c>
       <x:c r="ES15" s="6" t="n">
-        <x:v>800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ET15" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EU15" s="8" t="n">
-        <x:v>0.8300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV15" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -11337,22 +11337,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP16" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6800.0000</x:v>
       </x:c>
       <x:c r="EQ16" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="ER16" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>7.5600</x:v>
       </x:c>
       <x:c r="ES16" s="6" t="n">
-        <x:v>6800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ET16" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EU16" s="8" t="n">
-        <x:v>7.5600</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV16" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -12296,22 +12296,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES17" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>800.0000</x:v>
       </x:c>
       <x:c r="ET17" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EU17" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.8900</x:v>
       </x:c>
       <x:c r="EV17" s="6" t="n">
-        <x:v>800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EW17" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EX17" s="8" t="n">
-        <x:v>0.8900</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY17" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -13246,22 +13246,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES18" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>800.0000</x:v>
       </x:c>
       <x:c r="ET18" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EU18" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.8300</x:v>
       </x:c>
       <x:c r="EV18" s="6" t="n">
-        <x:v>800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EW18" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EX18" s="8" t="n">
-        <x:v>0.8300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY18" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -14196,22 +14196,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES19" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>200.0000</x:v>
       </x:c>
       <x:c r="ET19" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EU19" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.2100</x:v>
       </x:c>
       <x:c r="EV19" s="6" t="n">
-        <x:v>200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EW19" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EX19" s="8" t="n">
-        <x:v>0.2100</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY19" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -15146,22 +15146,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES20" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>400.0000</x:v>
       </x:c>
       <x:c r="ET20" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EU20" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.4400</x:v>
       </x:c>
       <x:c r="EV20" s="6" t="n">
-        <x:v>400.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EW20" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EX20" s="8" t="n">
-        <x:v>0.4400</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY20" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -16096,22 +16096,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES21" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>800.0000</x:v>
       </x:c>
       <x:c r="ET21" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EU21" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.8900</x:v>
       </x:c>
       <x:c r="EV21" s="6" t="n">
-        <x:v>800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EW21" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EX21" s="8" t="n">
-        <x:v>0.8900</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY21" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -16704,7 +16704,7 @@
         <x:v>46218</x:v>
       </x:c>
       <x:c r="AI22" s="4" t="n">
-        <x:v>46218</x:v>
+        <x:v>46219</x:v>
       </x:c>
       <x:c r="AJ22" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -17055,22 +17055,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV22" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3000.0000</x:v>
       </x:c>
       <x:c r="EW22" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EX22" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3.1000</x:v>
       </x:c>
       <x:c r="EY22" s="6" t="n">
-        <x:v>4000.0000</x:v>
+        <x:v>1000.0000</x:v>
       </x:c>
       <x:c r="EZ22" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FA22" s="8" t="n">
-        <x:v>4.1400</x:v>
+        <x:v>1.0300</x:v>
       </x:c>
       <x:c r="FB22" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -18014,31 +18014,31 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY23" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6400.0000</x:v>
       </x:c>
       <x:c r="EZ23" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FA23" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6.6200</x:v>
       </x:c>
       <x:c r="FB23" s="6" t="n">
-        <x:v>7800.0000</x:v>
+        <x:v>3600.0000</x:v>
       </x:c>
       <x:c r="FC23" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FD23" s="8" t="n">
-        <x:v>8.0600</x:v>
+        <x:v>3.7200</x:v>
       </x:c>
       <x:c r="FE23" s="6" t="n">
-        <x:v>2200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FF23" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FG23" s="8" t="n">
-        <x:v>2.2700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FH23" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -18604,7 +18604,7 @@
         <x:v>46220</x:v>
       </x:c>
       <x:c r="AI24" s="4" t="n">
-        <x:v>46224</x:v>
+        <x:v>46225</x:v>
       </x:c>
       <x:c r="AJ24" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -18973,22 +18973,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB24" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1000.0000</x:v>
       </x:c>
       <x:c r="FC24" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FD24" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.0300</x:v>
       </x:c>
       <x:c r="FE24" s="6" t="n">
-        <x:v>4800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FF24" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FG24" s="8" t="n">
-        <x:v>4.9600</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FH24" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -19009,22 +19009,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FN24" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>8400.0000</x:v>
       </x:c>
       <x:c r="FO24" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FP24" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>8.6800</x:v>
       </x:c>
       <x:c r="FQ24" s="6" t="n">
-        <x:v>5200.0000</x:v>
+        <x:v>600.0000</x:v>
       </x:c>
       <x:c r="FR24" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FS24" s="8" t="n">
-        <x:v>5.3800</x:v>
+        <x:v>0.6200</x:v>
       </x:c>
       <x:c r="FT24" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -19470,7 +19470,7 @@
         <x:v>スライス</x:v>
       </x:c>
       <x:c r="G25" s="1" t="str">
-        <x:v>003</x:v>
+        <x:v>004</x:v>
       </x:c>
       <x:c r="H25" s="4" t="n">
         <x:v>46209</x:v>
@@ -19551,10 +19551,10 @@
         <x:v/>
       </x:c>
       <x:c r="AH25" s="4" t="n">
-        <x:v>46224</x:v>
+        <x:v>46225</x:v>
       </x:c>
       <x:c r="AI25" s="4" t="n">
-        <x:v>46224</x:v>
+        <x:v>46225</x:v>
       </x:c>
       <x:c r="AJ25" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -20420,7 +20420,7 @@
         <x:v>スライス</x:v>
       </x:c>
       <x:c r="G26" s="1" t="str">
-        <x:v>023</x:v>
+        <x:v>022</x:v>
       </x:c>
       <x:c r="H26" s="4" t="n">
         <x:v>46205</x:v>
@@ -20918,31 +20918,31 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FQ26" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2800.0000</x:v>
       </x:c>
       <x:c r="FR26" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FS26" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.8900</x:v>
       </x:c>
       <x:c r="FT26" s="6" t="n">
-        <x:v>7800.0000</x:v>
+        <x:v>7200.0000</x:v>
       </x:c>
       <x:c r="FU26" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FV26" s="8" t="n">
-        <x:v>8.0600</x:v>
+        <x:v>7.4400</x:v>
       </x:c>
       <x:c r="FW26" s="6" t="n">
-        <x:v>2200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FX26" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FY26" s="8" t="n">
-        <x:v>2.2700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FZ26" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -21451,10 +21451,10 @@
         <x:v/>
       </x:c>
       <x:c r="AH27" s="4" t="n">
-        <x:v>46226</x:v>
+        <x:v>46227</x:v>
       </x:c>
       <x:c r="AI27" s="4" t="n">
-        <x:v>46226</x:v>
+        <x:v>46227</x:v>
       </x:c>
       <x:c r="AJ27" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -22836,22 +22836,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FW28" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1260.0000</x:v>
       </x:c>
       <x:c r="FX28" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FY28" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.3000</x:v>
       </x:c>
       <x:c r="FZ28" s="6" t="n">
-        <x:v>1260.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GA28" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="GB28" s="8" t="n">
-        <x:v>1.3000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GC28" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -23597,22 +23597,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DL29" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3600.0000</x:v>
       </x:c>
       <x:c r="DM29" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="DN29" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3.3200</x:v>
       </x:c>
       <x:c r="DO29" s="6" t="n">
-        <x:v>3600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DP29" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="DQ29" s="8" t="n">
-        <x:v>3.3200</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DR29" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -24583,40 +24583,40 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DX30" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4500.0000</x:v>
       </x:c>
       <x:c r="DY30" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="DZ30" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4.1500</x:v>
       </x:c>
       <x:c r="EA30" s="6" t="n">
-        <x:v>4500.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EB30" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EC30" s="8" t="n">
-        <x:v>4.1500</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ED30" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1500.0000</x:v>
       </x:c>
       <x:c r="EE30" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EF30" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.3800</x:v>
       </x:c>
       <x:c r="EG30" s="6" t="n">
-        <x:v>1500.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EH30" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EI30" s="8" t="n">
-        <x:v>1.3800</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ30" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -25524,13 +25524,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DU31" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3000.0000</x:v>
       </x:c>
       <x:c r="DV31" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="DW31" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.7700</x:v>
       </x:c>
       <x:c r="DX31" s="6" t="n">
         <x:v>3000.0000</x:v>
@@ -25542,13 +25542,13 @@
         <x:v>2.7700</x:v>
       </x:c>
       <x:c r="EA31" s="6" t="n">
-        <x:v>3000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EB31" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EC31" s="8" t="n">
-        <x:v>2.7700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ED31" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -26555,22 +26555,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV32" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2700.0000</x:v>
       </x:c>
       <x:c r="EW32" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EX32" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.4900</x:v>
       </x:c>
       <x:c r="EY32" s="6" t="n">
-        <x:v>2700.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EZ32" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="FA32" s="8" t="n">
-        <x:v>2.4900</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB32" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -27514,22 +27514,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY33" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1500.0000</x:v>
       </x:c>
       <x:c r="EZ33" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="FA33" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.3800</x:v>
       </x:c>
       <x:c r="FB33" s="6" t="n">
-        <x:v>1500.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FC33" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="FD33" s="8" t="n">
-        <x:v>1.3800</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FE33" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -28464,22 +28464,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY34" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3900.0000</x:v>
       </x:c>
       <x:c r="EZ34" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="FA34" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3.6000</x:v>
       </x:c>
       <x:c r="FB34" s="6" t="n">
-        <x:v>3900.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FC34" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="FD34" s="8" t="n">
-        <x:v>3.6000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FE34" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -29051,10 +29051,10 @@
         <x:v/>
       </x:c>
       <x:c r="AH35" s="4" t="n">
-        <x:v>46218</x:v>
+        <x:v>46217</x:v>
       </x:c>
       <x:c r="AI35" s="4" t="n">
-        <x:v>46218</x:v>
+        <x:v>46217</x:v>
       </x:c>
       <x:c r="AJ35" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -29396,13 +29396,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES35" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>800.0000</x:v>
       </x:c>
       <x:c r="ET35" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="EU35" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.3200</x:v>
       </x:c>
       <x:c r="EV35" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -29414,13 +29414,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY35" s="6" t="n">
-        <x:v>800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EZ35" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="FA35" s="8" t="n">
-        <x:v>1.3200</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB35" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -30355,22 +30355,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV36" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1200.0000</x:v>
       </x:c>
       <x:c r="EW36" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="EX36" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.9800</x:v>
       </x:c>
       <x:c r="EY36" s="6" t="n">
-        <x:v>1200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EZ36" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="FA36" s="8" t="n">
-        <x:v>1.9800</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB36" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -31170,22 +31170,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DC37" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>194.0000</x:v>
       </x:c>
       <x:c r="DD37" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="DE37" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.2200</x:v>
       </x:c>
       <x:c r="DF37" s="6" t="n">
-        <x:v>194.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DG37" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="DH37" s="8" t="n">
-        <x:v>0.2200</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DI37" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -31904,7 +31904,7 @@
         <x:v>46209</x:v>
       </x:c>
       <x:c r="AI38" s="4" t="n">
-        <x:v>46213</x:v>
+        <x:v>46212</x:v>
       </x:c>
       <x:c r="AJ38" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -32174,22 +32174,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DU38" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>900.0000</x:v>
       </x:c>
       <x:c r="DV38" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="DW38" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.4800</x:v>
       </x:c>
       <x:c r="DX38" s="6" t="n">
-        <x:v>900.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DY38" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="DZ38" s="8" t="n">
-        <x:v>1.4800</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EA38" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -32201,13 +32201,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ED38" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>600.0000</x:v>
       </x:c>
       <x:c r="EE38" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="EF38" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.9900</x:v>
       </x:c>
       <x:c r="EG38" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -32219,13 +32219,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ38" s="6" t="n">
-        <x:v>600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EK38" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="EL38" s="8" t="n">
-        <x:v>0.9900</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM38" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -33124,22 +33124,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DU39" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1800.0000</x:v>
       </x:c>
       <x:c r="DV39" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="DW39" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.0000</x:v>
       </x:c>
       <x:c r="DX39" s="6" t="n">
-        <x:v>1800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DY39" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="DZ39" s="8" t="n">
-        <x:v>2.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EA39" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -33160,22 +33160,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG39" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1200.0000</x:v>
       </x:c>
       <x:c r="EH39" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EI39" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.3300</x:v>
       </x:c>
       <x:c r="EJ39" s="6" t="n">
-        <x:v>1200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EK39" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EL39" s="8" t="n">
-        <x:v>1.3300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM39" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -33720,7 +33720,7 @@
         <x:v>スリット</x:v>
       </x:c>
       <x:c r="G40" s="1" t="str">
-        <x:v>001</x:v>
+        <x:v>004</x:v>
       </x:c>
       <x:c r="H40" s="4" t="n">
         <x:v>46204</x:v>
@@ -33801,10 +33801,10 @@
         <x:v/>
       </x:c>
       <x:c r="AH40" s="4" t="n">
-        <x:v>46213</x:v>
+        <x:v>46216</x:v>
       </x:c>
       <x:c r="AI40" s="4" t="n">
-        <x:v>46213</x:v>
+        <x:v>46216</x:v>
       </x:c>
       <x:c r="AJ40" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -34119,31 +34119,31 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ40" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="EK40" s="8" t="n">
+        <x:v>10.1200</x:v>
+      </x:c>
+      <x:c r="EL40" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="EM40" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="EN40" s="8" t="n">
+        <x:v>10.1200</x:v>
+      </x:c>
+      <x:c r="EO40" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="EP40" s="6" t="n">
         <x:v>400.0000</x:v>
       </x:c>
-      <x:c r="EK40" s="8" t="n">
-        <x:v>10.1200</x:v>
-      </x:c>
-      <x:c r="EL40" s="8" t="n">
+      <x:c r="EQ40" s="8" t="n">
+        <x:v>10.1200</x:v>
+      </x:c>
+      <x:c r="ER40" s="8" t="n">
         <x:v>0.6600</x:v>
-      </x:c>
-      <x:c r="EM40" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="EN40" s="8" t="n">
-        <x:v>10.1200</x:v>
-      </x:c>
-      <x:c r="EO40" s="8" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="EP40" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="EQ40" s="8" t="n">
-        <x:v>10.1200</x:v>
-      </x:c>
-      <x:c r="ER40" s="8" t="n">
-        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES40" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -34979,22 +34979,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DF41" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3600.0000</x:v>
       </x:c>
       <x:c r="DG41" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="DH41" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5.9300</x:v>
       </x:c>
       <x:c r="DI41" s="6" t="n">
-        <x:v>3600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DJ41" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="DK41" s="8" t="n">
-        <x:v>5.9300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DL41" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -36010,22 +36010,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG42" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>100.0000</x:v>
       </x:c>
       <x:c r="EH42" s="8" t="n">
         <x:v>14.9900</x:v>
       </x:c>
       <x:c r="EI42" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.1100</x:v>
       </x:c>
       <x:c r="EJ42" s="6" t="n">
-        <x:v>100.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EK42" s="8" t="n">
         <x:v>14.9900</x:v>
       </x:c>
       <x:c r="EL42" s="8" t="n">
-        <x:v>0.1100</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM42" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -36960,22 +36960,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG43" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>600.0000</x:v>
       </x:c>
       <x:c r="EH43" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EI43" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.6700</x:v>
       </x:c>
       <x:c r="EJ43" s="6" t="n">
-        <x:v>600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EK43" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EL43" s="8" t="n">
-        <x:v>0.6700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM43" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -37910,22 +37910,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG44" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1000.0000</x:v>
       </x:c>
       <x:c r="EH44" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EI44" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.1100</x:v>
       </x:c>
       <x:c r="EJ44" s="6" t="n">
-        <x:v>1000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EK44" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EL44" s="8" t="n">
-        <x:v>1.1100</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM44" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -38860,22 +38860,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG45" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>400.0000</x:v>
       </x:c>
       <x:c r="EH45" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EI45" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.4400</x:v>
       </x:c>
       <x:c r="EJ45" s="6" t="n">
-        <x:v>400.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EK45" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EL45" s="8" t="n">
-        <x:v>0.4400</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM45" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -39501,10 +39501,10 @@
         <x:v/>
       </x:c>
       <x:c r="AH46" s="4" t="n">
-        <x:v>46217</x:v>
+        <x:v>46218</x:v>
       </x:c>
       <x:c r="AI46" s="4" t="n">
-        <x:v>46217</x:v>
+        <x:v>46218</x:v>
       </x:c>
       <x:c r="AJ46" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -40370,7 +40370,7 @@
         <x:v>スリット</x:v>
       </x:c>
       <x:c r="G47" s="1" t="str">
-        <x:v>009</x:v>
+        <x:v>011</x:v>
       </x:c>
       <x:c r="H47" s="4" t="n">
         <x:v>46204</x:v>
@@ -40451,10 +40451,10 @@
         <x:v/>
       </x:c>
       <x:c r="AH47" s="4" t="n">
-        <x:v>46218</x:v>
+        <x:v>46219</x:v>
       </x:c>
       <x:c r="AI47" s="4" t="n">
-        <x:v>46218</x:v>
+        <x:v>46219</x:v>
       </x:c>
       <x:c r="AJ47" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -41320,7 +41320,7 @@
         <x:v>スリット</x:v>
       </x:c>
       <x:c r="G48" s="1" t="str">
-        <x:v>007</x:v>
+        <x:v>009</x:v>
       </x:c>
       <x:c r="H48" s="4" t="n">
         <x:v>46204</x:v>
@@ -41401,10 +41401,10 @@
         <x:v/>
       </x:c>
       <x:c r="AH48" s="4" t="n">
-        <x:v>46224</x:v>
+        <x:v>46220</x:v>
       </x:c>
       <x:c r="AI48" s="4" t="n">
-        <x:v>46224</x:v>
+        <x:v>46220</x:v>
       </x:c>
       <x:c r="AJ48" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -41773,13 +41773,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB48" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>200.0000</x:v>
       </x:c>
       <x:c r="FC48" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="FD48" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.3300</x:v>
       </x:c>
       <x:c r="FE48" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -41818,13 +41818,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FQ48" s="6" t="n">
-        <x:v>200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FR48" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="FS48" s="8" t="n">
-        <x:v>0.3300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FT48" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -42786,22 +42786,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FW49" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>950.0000</x:v>
       </x:c>
       <x:c r="FX49" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="FY49" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.5600</x:v>
       </x:c>
       <x:c r="FZ49" s="6" t="n">
-        <x:v>950.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GA49" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="GB49" s="8" t="n">
-        <x:v>1.5600</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GC49" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -43736,7 +43736,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FW50" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1000.0000</x:v>
       </x:c>
       <x:c r="FX50" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -43745,7 +43745,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FZ50" s="6" t="n">
-        <x:v>1000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GA50" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -44596,22 +44596,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES51" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>400.0000</x:v>
       </x:c>
       <x:c r="ET51" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EU51" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.2700</x:v>
       </x:c>
       <x:c r="EV51" s="6" t="n">
-        <x:v>400.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EW51" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EX51" s="8" t="n">
-        <x:v>0.2700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY51" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -45555,22 +45555,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV52" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>600.0000</x:v>
       </x:c>
       <x:c r="EW52" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EX52" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.4000</x:v>
       </x:c>
       <x:c r="EY52" s="6" t="n">
-        <x:v>600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EZ52" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FA52" s="8" t="n">
-        <x:v>0.4000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB52" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -46595,22 +46595,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FZ53" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3200.0000</x:v>
       </x:c>
       <x:c r="GA53" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="GB53" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.1300</x:v>
       </x:c>
       <x:c r="GC53" s="6" t="n">
-        <x:v>3200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GD53" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="GE53" s="8" t="n">
-        <x:v>2.1300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GF53" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -47536,31 +47536,31 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FW54" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1000.0000</x:v>
       </x:c>
       <x:c r="FX54" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FY54" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.6700</x:v>
       </x:c>
       <x:c r="FZ54" s="6" t="n">
-        <x:v>1000.0000</x:v>
+        <x:v>2000.0000</x:v>
       </x:c>
       <x:c r="GA54" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="GB54" s="8" t="n">
-        <x:v>0.6700</x:v>
+        <x:v>1.3300</x:v>
       </x:c>
       <x:c r="GC54" s="6" t="n">
-        <x:v>2000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GD54" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="GE54" s="8" t="n">
-        <x:v>1.3300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GF54" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -47970,7 +47970,7 @@
         <x:v>SEC</x:v>
       </x:c>
       <x:c r="G55" s="1" t="str">
-        <x:v>007</x:v>
+        <x:v>006</x:v>
       </x:c>
       <x:c r="H55" s="4" t="n">
         <x:v>46199</x:v>
@@ -48360,22 +48360,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG55" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1600.0000</x:v>
       </x:c>
       <x:c r="EH55" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EI55" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.0700</x:v>
       </x:c>
       <x:c r="EJ55" s="6" t="n">
-        <x:v>1600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EK55" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EL55" s="8" t="n">
-        <x:v>1.0700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM55" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -48920,7 +48920,7 @@
         <x:v>SEC</x:v>
       </x:c>
       <x:c r="G56" s="1" t="str">
-        <x:v>011</x:v>
+        <x:v>010</x:v>
       </x:c>
       <x:c r="H56" s="4" t="n">
         <x:v>46204</x:v>
@@ -49001,10 +49001,10 @@
         <x:v/>
       </x:c>
       <x:c r="AH56" s="4" t="n">
-        <x:v>46213</x:v>
+        <x:v>46216</x:v>
       </x:c>
       <x:c r="AI56" s="4" t="n">
-        <x:v>46213</x:v>
+        <x:v>46216</x:v>
       </x:c>
       <x:c r="AJ56" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -49319,31 +49319,31 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ56" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="EK56" s="8" t="n">
+        <x:v>25.0000</x:v>
+      </x:c>
+      <x:c r="EL56" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="EM56" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="EN56" s="8" t="n">
+        <x:v>25.0000</x:v>
+      </x:c>
+      <x:c r="EO56" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="EP56" s="6" t="n">
         <x:v>400.0000</x:v>
       </x:c>
-      <x:c r="EK56" s="8" t="n">
-        <x:v>25.0000</x:v>
-      </x:c>
-      <x:c r="EL56" s="8" t="n">
+      <x:c r="EQ56" s="8" t="n">
+        <x:v>25.0000</x:v>
+      </x:c>
+      <x:c r="ER56" s="8" t="n">
         <x:v>0.2700</x:v>
-      </x:c>
-      <x:c r="EM56" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="EN56" s="8" t="n">
-        <x:v>25.0000</x:v>
-      </x:c>
-      <x:c r="EO56" s="8" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="EP56" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="EQ56" s="8" t="n">
-        <x:v>25.0000</x:v>
-      </x:c>
-      <x:c r="ER56" s="8" t="n">
-        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES56" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -49870,7 +49870,7 @@
         <x:v>SEC</x:v>
       </x:c>
       <x:c r="G57" s="1" t="str">
-        <x:v>013</x:v>
+        <x:v>012</x:v>
       </x:c>
       <x:c r="H57" s="4" t="n">
         <x:v>46199</x:v>
@@ -50251,13 +50251,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ED57" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5000.0000</x:v>
       </x:c>
       <x:c r="EE57" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EF57" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3.3300</x:v>
       </x:c>
       <x:c r="EG57" s="6" t="n">
         <x:v>5000.0000</x:v>
@@ -50269,13 +50269,13 @@
         <x:v>3.3300</x:v>
       </x:c>
       <x:c r="EJ57" s="6" t="n">
-        <x:v>5000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EK57" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EL57" s="8" t="n">
-        <x:v>3.3300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM57" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -50820,7 +50820,7 @@
         <x:v>SEC</x:v>
       </x:c>
       <x:c r="G58" s="1" t="str">
-        <x:v>010</x:v>
+        <x:v>008</x:v>
       </x:c>
       <x:c r="H58" s="4" t="n">
         <x:v>46204</x:v>
@@ -51273,22 +51273,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB58" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2000.0000</x:v>
       </x:c>
       <x:c r="FC58" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FD58" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.3300</x:v>
       </x:c>
       <x:c r="FE58" s="6" t="n">
-        <x:v>2000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FF58" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FG58" s="8" t="n">
-        <x:v>1.3300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FH58" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -52214,22 +52214,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY59" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>200.0000</x:v>
       </x:c>
       <x:c r="EZ59" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FA59" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.1300</x:v>
       </x:c>
       <x:c r="FB59" s="6" t="n">
-        <x:v>200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FC59" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FD59" s="8" t="n">
-        <x:v>0.1300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FE59" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -52720,7 +52720,7 @@
         <x:v>SEC</x:v>
       </x:c>
       <x:c r="G60" s="1" t="str">
-        <x:v>001</x:v>
+        <x:v>003</x:v>
       </x:c>
       <x:c r="H60" s="4" t="n">
         <x:v>46204</x:v>
@@ -52762,7 +52762,7 @@
         <x:v>自動車材料事業部</x:v>
       </x:c>
       <x:c r="U60" s="1" t="str">
-        <x:v>00075319</x:v>
+        <x:v>00075367</x:v>
       </x:c>
       <x:c r="V60" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -52801,16 +52801,16 @@
         <x:v/>
       </x:c>
       <x:c r="AH60" s="4" t="n">
-        <x:v>46220</x:v>
+        <x:v>46224</x:v>
       </x:c>
       <x:c r="AI60" s="4" t="n">
-        <x:v>46220</x:v>
+        <x:v>46224</x:v>
       </x:c>
       <x:c r="AJ60" s="1" t="str">
         <x:v>0:未完</x:v>
       </x:c>
       <x:c r="AK60" s="6" t="n">
-        <x:v>200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AL60" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -53182,40 +53182,40 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FE60" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="FF60" s="8" t="n">
+        <x:v>25.0000</x:v>
+      </x:c>
+      <x:c r="FG60" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="FH60" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="FI60" s="8" t="n">
+        <x:v>25.0000</x:v>
+      </x:c>
+      <x:c r="FJ60" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="FK60" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="FL60" s="8" t="n">
+        <x:v>25.0000</x:v>
+      </x:c>
+      <x:c r="FM60" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="FN60" s="6" t="n">
         <x:v>200.0000</x:v>
       </x:c>
-      <x:c r="FF60" s="8" t="n">
-        <x:v>25.0000</x:v>
-      </x:c>
-      <x:c r="FG60" s="8" t="n">
+      <x:c r="FO60" s="8" t="n">
+        <x:v>25.0000</x:v>
+      </x:c>
+      <x:c r="FP60" s="8" t="n">
         <x:v>0.1300</x:v>
-      </x:c>
-      <x:c r="FH60" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="FI60" s="8" t="n">
-        <x:v>25.0000</x:v>
-      </x:c>
-      <x:c r="FJ60" s="8" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="FK60" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="FL60" s="8" t="n">
-        <x:v>25.0000</x:v>
-      </x:c>
-      <x:c r="FM60" s="8" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="FN60" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="FO60" s="8" t="n">
-        <x:v>25.0000</x:v>
-      </x:c>
-      <x:c r="FP60" s="8" t="n">
-        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FQ60" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -53670,7 +53670,7 @@
         <x:v>SEC</x:v>
       </x:c>
       <x:c r="G61" s="1" t="str">
-        <x:v>010</x:v>
+        <x:v>009</x:v>
       </x:c>
       <x:c r="H61" s="4" t="n">
         <x:v>46209</x:v>
@@ -54114,22 +54114,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY61" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1400.0000</x:v>
       </x:c>
       <x:c r="EZ61" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FA61" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.9300</x:v>
       </x:c>
       <x:c r="FB61" s="6" t="n">
-        <x:v>1400.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FC61" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FD61" s="8" t="n">
-        <x:v>0.9300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FE61" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -54159,22 +54159,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FN61" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>8600.0000</x:v>
       </x:c>
       <x:c r="FO61" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FP61" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5.7300</x:v>
       </x:c>
       <x:c r="FQ61" s="6" t="n">
-        <x:v>8600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FR61" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FS61" s="8" t="n">
-        <x:v>5.7300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FT61" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -54620,7 +54620,7 @@
         <x:v>SEC</x:v>
       </x:c>
       <x:c r="G62" s="1" t="str">
-        <x:v>015</x:v>
+        <x:v>014</x:v>
       </x:c>
       <x:c r="H62" s="4" t="n">
         <x:v>46206</x:v>
@@ -54701,7 +54701,7 @@
         <x:v/>
       </x:c>
       <x:c r="AH62" s="4" t="n">
-        <x:v>46224</x:v>
+        <x:v>46225</x:v>
       </x:c>
       <x:c r="AI62" s="4" t="n">
         <x:v>46225</x:v>
@@ -55118,22 +55118,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FQ62" s="6" t="n">
-        <x:v>1000.0000</x:v>
+        <x:v>10000.0000</x:v>
       </x:c>
       <x:c r="FR62" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FS62" s="8" t="n">
-        <x:v>0.6700</x:v>
+        <x:v>6.6700</x:v>
       </x:c>
       <x:c r="FT62" s="6" t="n">
-        <x:v>9000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FU62" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FV62" s="8" t="n">
-        <x:v>6.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FW62" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -55570,7 +55570,7 @@
         <x:v>SEC</x:v>
       </x:c>
       <x:c r="G63" s="1" t="str">
-        <x:v>008</x:v>
+        <x:v>007</x:v>
       </x:c>
       <x:c r="H63" s="4" t="n">
         <x:v>46209</x:v>
@@ -56077,31 +56077,31 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FT63" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4000.0000</x:v>
       </x:c>
       <x:c r="FU63" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FV63" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.6700</x:v>
       </x:c>
       <x:c r="FW63" s="6" t="n">
-        <x:v>4000.0000</x:v>
+        <x:v>6000.0000</x:v>
       </x:c>
       <x:c r="FX63" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FY63" s="8" t="n">
-        <x:v>2.6700</x:v>
+        <x:v>4.0000</x:v>
       </x:c>
       <x:c r="FZ63" s="6" t="n">
-        <x:v>6000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GA63" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="GB63" s="8" t="n">
-        <x:v>4.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GC63" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -57036,22 +57036,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FW64" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1000.0000</x:v>
       </x:c>
       <x:c r="FX64" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FY64" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.6700</x:v>
       </x:c>
       <x:c r="FZ64" s="6" t="n">
-        <x:v>1000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GA64" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="GB64" s="8" t="n">
-        <x:v>0.6700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GC64" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -57554,7 +57554,7 @@
         <x:v>46210</x:v>
       </x:c>
       <x:c r="AI65" s="4" t="n">
-        <x:v>46216</x:v>
+        <x:v>46212</x:v>
       </x:c>
       <x:c r="AJ65" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -57833,31 +57833,31 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DX65" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1500.0000</x:v>
       </x:c>
       <x:c r="DY65" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="DZ65" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.6300</x:v>
       </x:c>
       <x:c r="EA65" s="6" t="n">
-        <x:v>1500.0000</x:v>
+        <x:v>600.0000</x:v>
       </x:c>
       <x:c r="EB65" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="EC65" s="8" t="n">
-        <x:v>2.6300</x:v>
+        <x:v>1.0500</x:v>
       </x:c>
       <x:c r="ED65" s="6" t="n">
-        <x:v>600.0000</x:v>
+        <x:v>1500.0000</x:v>
       </x:c>
       <x:c r="EE65" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="EF65" s="8" t="n">
-        <x:v>1.0500</x:v>
+        <x:v>2.6300</x:v>
       </x:c>
       <x:c r="EG65" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -57896,13 +57896,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES65" s="6" t="n">
-        <x:v>1500.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ET65" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="EU65" s="8" t="n">
-        <x:v>2.6300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV65" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -58810,22 +58810,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG66" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3600.0000</x:v>
       </x:c>
       <x:c r="EH66" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="EI66" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6.3200</x:v>
       </x:c>
       <x:c r="EJ66" s="6" t="n">
-        <x:v>3000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EK66" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="EL66" s="8" t="n">
-        <x:v>5.2600</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM66" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -58837,22 +58837,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP66" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2400.0000</x:v>
       </x:c>
       <x:c r="EQ66" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="ER66" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4.2100</x:v>
       </x:c>
       <x:c r="ES66" s="6" t="n">
-        <x:v>3000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ET66" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="EU66" s="8" t="n">
-        <x:v>5.2600</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV66" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -59370,7 +59370,7 @@
         <x:v>検査</x:v>
       </x:c>
       <x:c r="G67" s="1" t="str">
-        <x:v>009</x:v>
+        <x:v>010</x:v>
       </x:c>
       <x:c r="H67" s="4" t="n">
         <x:v>46192</x:v>
@@ -59451,10 +59451,10 @@
         <x:v/>
       </x:c>
       <x:c r="AH67" s="4" t="n">
-        <x:v>46212</x:v>
+        <x:v>46216</x:v>
       </x:c>
       <x:c r="AI67" s="4" t="n">
-        <x:v>46213</x:v>
+        <x:v>46218</x:v>
       </x:c>
       <x:c r="AJ67" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -59760,22 +59760,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG67" s="6" t="n">
-        <x:v>4500.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EH67" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="EI67" s="8" t="n">
-        <x:v>7.8900</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ67" s="6" t="n">
-        <x:v>1500.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EK67" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="EL67" s="8" t="n">
-        <x:v>2.6300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM67" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -59787,31 +59787,31 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP67" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1200.0000</x:v>
       </x:c>
       <x:c r="EQ67" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="ER67" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.1100</x:v>
       </x:c>
       <x:c r="ES67" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3600.0000</x:v>
       </x:c>
       <x:c r="ET67" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="EU67" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6.3200</x:v>
       </x:c>
       <x:c r="EV67" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1200.0000</x:v>
       </x:c>
       <x:c r="EW67" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="EX67" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.1100</x:v>
       </x:c>
       <x:c r="EY67" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -60320,7 +60320,7 @@
         <x:v>検査</x:v>
       </x:c>
       <x:c r="G68" s="1" t="str">
-        <x:v>006</x:v>
+        <x:v>007</x:v>
       </x:c>
       <x:c r="H68" s="4" t="n">
         <x:v>46196</x:v>
@@ -60755,31 +60755,31 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV68" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1800.0000</x:v>
       </x:c>
       <x:c r="EW68" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="EX68" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3.1600</x:v>
       </x:c>
       <x:c r="EY68" s="6" t="n">
-        <x:v>2100.0000</x:v>
+        <x:v>900.0000</x:v>
       </x:c>
       <x:c r="EZ68" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="FA68" s="8" t="n">
-        <x:v>3.6800</x:v>
+        <x:v>1.5800</x:v>
       </x:c>
       <x:c r="FB68" s="6" t="n">
-        <x:v>600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FC68" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="FD68" s="8" t="n">
-        <x:v>1.0500</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FE68" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -61270,7 +61270,7 @@
         <x:v>接続</x:v>
       </x:c>
       <x:c r="G69" s="1" t="str">
-        <x:v>004</x:v>
+        <x:v>005</x:v>
       </x:c>
       <x:c r="H69" s="4" t="n">
         <x:v>46204</x:v>
@@ -61351,10 +61351,10 @@
         <x:v/>
       </x:c>
       <x:c r="AH69" s="4" t="n">
-        <x:v>46220</x:v>
+        <x:v>46219</x:v>
       </x:c>
       <x:c r="AI69" s="4" t="n">
-        <x:v>46220</x:v>
+        <x:v>46219</x:v>
       </x:c>
       <x:c r="AJ69" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -61714,13 +61714,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY69" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>200.0000</x:v>
       </x:c>
       <x:c r="EZ69" s="8" t="n">
         <x:v>20.0000</x:v>
       </x:c>
       <x:c r="FA69" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.1700</x:v>
       </x:c>
       <x:c r="FB69" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -61732,13 +61732,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FE69" s="6" t="n">
-        <x:v>200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FF69" s="8" t="n">
         <x:v>20.0000</x:v>
       </x:c>
       <x:c r="FG69" s="8" t="n">
-        <x:v>0.1700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FH69" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -62673,22 +62673,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB70" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2000.0000</x:v>
       </x:c>
       <x:c r="FC70" s="8" t="n">
         <x:v>20.0000</x:v>
       </x:c>
       <x:c r="FD70" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.6700</x:v>
       </x:c>
       <x:c r="FE70" s="6" t="n">
-        <x:v>2000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FF70" s="8" t="n">
         <x:v>20.0000</x:v>
       </x:c>
       <x:c r="FG70" s="8" t="n">
-        <x:v>1.6700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FH70" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -63170,7 +63170,7 @@
         <x:v>検査</x:v>
       </x:c>
       <x:c r="G71" s="1" t="str">
-        <x:v>007</x:v>
+        <x:v>008</x:v>
       </x:c>
       <x:c r="H71" s="4" t="n">
         <x:v>46196</x:v>
@@ -63614,31 +63614,31 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY71" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2100.0000</x:v>
       </x:c>
       <x:c r="EZ71" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="FA71" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3.6800</x:v>
       </x:c>
       <x:c r="FB71" s="6" t="n">
-        <x:v>2700.0000</x:v>
+        <x:v>1800.0000</x:v>
       </x:c>
       <x:c r="FC71" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="FD71" s="8" t="n">
-        <x:v>4.7400</x:v>
+        <x:v>3.1600</x:v>
       </x:c>
       <x:c r="FE71" s="6" t="n">
-        <x:v>1200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FF71" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="FG71" s="8" t="n">
-        <x:v>2.1100</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FH71" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -64573,22 +64573,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB72" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1000.0000</x:v>
       </x:c>
       <x:c r="FC72" s="8" t="n">
         <x:v>20.0000</x:v>
       </x:c>
       <x:c r="FD72" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.8300</x:v>
       </x:c>
       <x:c r="FE72" s="6" t="n">
-        <x:v>1000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FF72" s="8" t="n">
         <x:v>20.0000</x:v>
       </x:c>
       <x:c r="FG72" s="8" t="n">
-        <x:v>0.8300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FH72" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -65523,22 +65523,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB73" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>200.0000</x:v>
       </x:c>
       <x:c r="FC73" s="8" t="n">
         <x:v>20.0000</x:v>
       </x:c>
       <x:c r="FD73" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.1700</x:v>
       </x:c>
       <x:c r="FE73" s="6" t="n">
-        <x:v>200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FF73" s="8" t="n">
         <x:v>20.0000</x:v>
       </x:c>
       <x:c r="FG73" s="8" t="n">
-        <x:v>0.1700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FH73" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -66536,22 +66536,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FW74" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1470.0000</x:v>
       </x:c>
       <x:c r="FX74" s="8" t="n">
         <x:v>20.0000</x:v>
       </x:c>
       <x:c r="FY74" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.2300</x:v>
       </x:c>
       <x:c r="FZ74" s="6" t="n">
-        <x:v>1470.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GA74" s="8" t="n">
         <x:v>20.0000</x:v>
       </x:c>
       <x:c r="GB74" s="8" t="n">
-        <x:v>1.2300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GC74" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -67486,22 +67486,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FW75" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1260.0000</x:v>
       </x:c>
       <x:c r="FX75" s="8" t="n">
         <x:v>20.0000</x:v>
       </x:c>
       <x:c r="FY75" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.0500</x:v>
       </x:c>
       <x:c r="FZ75" s="6" t="n">
-        <x:v>1260.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GA75" s="8" t="n">
         <x:v>20.0000</x:v>
       </x:c>
       <x:c r="GB75" s="8" t="n">
-        <x:v>1.0500</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GC75" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -68220,49 +68220,49 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DC76" s="7" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>194.0000</x:v>
       </x:c>
       <x:c r="DD76" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="DE76" s="9" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.2200</x:v>
       </x:c>
       <x:c r="DF76" s="7" t="n">
-        <x:v>194.0000</x:v>
+        <x:v>3600.0000</x:v>
       </x:c>
       <x:c r="DG76" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="DH76" s="9" t="n">
-        <x:v>0.2200</x:v>
+        <x:v>5.9300</x:v>
       </x:c>
       <x:c r="DI76" s="7" t="n">
-        <x:v>3600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DJ76" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="DK76" s="9" t="n">
-        <x:v>5.9300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DL76" s="7" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3600.0000</x:v>
       </x:c>
       <x:c r="DM76" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="DN76" s="9" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3.3200</x:v>
       </x:c>
       <x:c r="DO76" s="7" t="n">
-        <x:v>3600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DP76" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="DQ76" s="9" t="n">
-        <x:v>3.3200</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DR76" s="7" t="n">
         <x:v>0.0000</x:v>
@@ -68274,58 +68274,58 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DU76" s="7" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5700.0000</x:v>
       </x:c>
       <x:c r="DV76" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="DW76" s="9" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6.2500</x:v>
       </x:c>
       <x:c r="DX76" s="7" t="n">
-        <x:v>5700.0000</x:v>
+        <x:v>9000.0000</x:v>
       </x:c>
       <x:c r="DY76" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="DZ76" s="9" t="n">
-        <x:v>6.2500</x:v>
+        <x:v>9.5500</x:v>
       </x:c>
       <x:c r="EA76" s="7" t="n">
-        <x:v>9000.0000</x:v>
+        <x:v>600.0000</x:v>
       </x:c>
       <x:c r="EB76" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="EC76" s="9" t="n">
-        <x:v>9.5500</x:v>
+        <x:v>1.0500</x:v>
       </x:c>
       <x:c r="ED76" s="7" t="n">
-        <x:v>1600.0000</x:v>
+        <x:v>17000.0000</x:v>
       </x:c>
       <x:c r="EE76" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="EF76" s="9" t="n">
-        <x:v>2.0800</x:v>
+        <x:v>17.0100</x:v>
       </x:c>
       <x:c r="EG76" s="7" t="n">
-        <x:v>20200.0000</x:v>
+        <x:v>14300.0000</x:v>
       </x:c>
       <x:c r="EH76" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="EI76" s="9" t="n">
-        <x:v>22.1200</x:v>
+        <x:v>15.2100</x:v>
       </x:c>
       <x:c r="EJ76" s="7" t="n">
-        <x:v>15800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EK76" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="EL76" s="9" t="n">
-        <x:v>17.8700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM76" s="7" t="n">
         <x:v>0.0000</x:v>
@@ -68337,58 +68337,58 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP76" s="7" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>17000.0000</x:v>
       </x:c>
       <x:c r="EQ76" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="ER76" s="9" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>20.8100</x:v>
       </x:c>
       <x:c r="ES76" s="7" t="n">
-        <x:v>17100.0000</x:v>
+        <x:v>8000.0000</x:v>
       </x:c>
       <x:c r="ET76" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="EU76" s="9" t="n">
-        <x:v>21.4500</x:v>
+        <x:v>11.3800</x:v>
       </x:c>
       <x:c r="EV76" s="7" t="n">
-        <x:v>5100.0000</x:v>
+        <x:v>12000.0000</x:v>
       </x:c>
       <x:c r="EW76" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="EX76" s="9" t="n">
-        <x:v>6.2100</x:v>
+        <x:v>15.7100</x:v>
       </x:c>
       <x:c r="EY76" s="7" t="n">
-        <x:v>11600.0000</x:v>
+        <x:v>17800.0000</x:v>
       </x:c>
       <x:c r="EZ76" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FA76" s="9" t="n">
-        <x:v>14.3400</x:v>
+        <x:v>19.4500</x:v>
       </x:c>
       <x:c r="FB76" s="7" t="n">
-        <x:v>18100.0000</x:v>
+        <x:v>12400.0000</x:v>
       </x:c>
       <x:c r="FC76" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FD76" s="9" t="n">
-        <x:v>19.8900</x:v>
+        <x:v>12.8600</x:v>
       </x:c>
       <x:c r="FE76" s="7" t="n">
-        <x:v>14400.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FF76" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FG76" s="9" t="n">
-        <x:v>14.2600</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FH76" s="7" t="n">
         <x:v>0.0000</x:v>
@@ -68409,76 +68409,76 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FN76" s="7" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>17200.0000</x:v>
       </x:c>
       <x:c r="FO76" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FP76" s="9" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>14.5400</x:v>
       </x:c>
       <x:c r="FQ76" s="7" t="n">
-        <x:v>18000.0000</x:v>
+        <x:v>16400.0000</x:v>
       </x:c>
       <x:c r="FR76" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FS76" s="9" t="n">
-        <x:v>15.2100</x:v>
+        <x:v>13.2800</x:v>
       </x:c>
       <x:c r="FT76" s="7" t="n">
-        <x:v>16800.0000</x:v>
+        <x:v>11200.0000</x:v>
       </x:c>
       <x:c r="FU76" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FV76" s="9" t="n">
-        <x:v>14.0600</x:v>
+        <x:v>10.1100</x:v>
       </x:c>
       <x:c r="FW76" s="7" t="n">
-        <x:v>11950.0000</x:v>
+        <x:v>19690.0000</x:v>
       </x:c>
       <x:c r="FX76" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FY76" s="9" t="n">
-        <x:v>10.8800</x:v>
+        <x:v>16.4200</x:v>
       </x:c>
       <x:c r="FZ76" s="7" t="n">
-        <x:v>21140.0000</x:v>
+        <x:v>13600.0000</x:v>
       </x:c>
       <x:c r="GA76" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="GB76" s="9" t="n">
-        <x:v>17.9200</x:v>
+        <x:v>12.1400</x:v>
       </x:c>
       <x:c r="GC76" s="7" t="n">
-        <x:v>5200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GD76" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="GE76" s="9" t="n">
-        <x:v>3.4600</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GF76" s="7" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4350.0000</x:v>
       </x:c>
       <x:c r="GG76" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="GH76" s="9" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4.4900</x:v>
       </x:c>
       <x:c r="GI76" s="7" t="n">
-        <x:v>5550.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GJ76" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="GK76" s="9" t="n">
-        <x:v>5.7300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GL76" s="7" t="n">
         <x:v>0.0000</x:v>

--- a/.pm-ai-cache/network-source/task-input-newest.xlsx
+++ b/.pm-ai-cache/network-source/task-input-newest.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工程別生産計画問合せ問合せ" sheetId="1" r:id="Rda1820ea73e14e9f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工程別生産計画問合せ問合せ" sheetId="1" r:id="Re83997f787e74396"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -6263,13 +6263,13 @@
         <x:v>10000.0000</x:v>
       </x:c>
       <x:c r="AL11" s="6" t="n">
-        <x:v>1000.0000</x:v>
+        <x:v>3200.0000</x:v>
       </x:c>
       <x:c r="AM11" s="6" t="n">
-        <x:v>9000.0000</x:v>
+        <x:v>6800.0000</x:v>
       </x:c>
       <x:c r="AN11" s="6" t="n">
-        <x:v>2000.0000</x:v>
+        <x:v>3600.0000</x:v>
       </x:c>
       <x:c r="AO11" s="6" t="n">
         <x:v>9000.0000</x:v>
@@ -24313,10 +24313,10 @@
         <x:v>6000.0000</x:v>
       </x:c>
       <x:c r="AL30" s="6" t="n">
-        <x:v>4500.0000</x:v>
+        <x:v>6000.0000</x:v>
       </x:c>
       <x:c r="AM30" s="6" t="n">
-        <x:v>1500.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AN30" s="6" t="n">
         <x:v>4500.0000</x:v>
@@ -31913,13 +31913,13 @@
         <x:v>1500.0000</x:v>
       </x:c>
       <x:c r="AL38" s="6" t="n">
-        <x:v>900.0000</x:v>
+        <x:v>1500.0000</x:v>
       </x:c>
       <x:c r="AM38" s="6" t="n">
-        <x:v>600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AN38" s="6" t="n">
-        <x:v>1800.0000</x:v>
+        <x:v>2400.0000</x:v>
       </x:c>
       <x:c r="AO38" s="6" t="n">
         <x:v>1500.0000</x:v>
@@ -32863,13 +32863,13 @@
         <x:v>3000.0000</x:v>
       </x:c>
       <x:c r="AL39" s="6" t="n">
-        <x:v>1800.0000</x:v>
+        <x:v>3000.0000</x:v>
       </x:c>
       <x:c r="AM39" s="6" t="n">
-        <x:v>1200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AN39" s="6" t="n">
-        <x:v>1800.0000</x:v>
+        <x:v>2400.0000</x:v>
       </x:c>
       <x:c r="AO39" s="6" t="n">
         <x:v>3000.0000</x:v>
@@ -57554,7 +57554,7 @@
         <x:v>46210</x:v>
       </x:c>
       <x:c r="AI65" s="4" t="n">
-        <x:v>46212</x:v>
+        <x:v>46216</x:v>
       </x:c>
       <x:c r="AJ65" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -57851,13 +57851,13 @@
         <x:v>1.0500</x:v>
       </x:c>
       <x:c r="ED65" s="6" t="n">
-        <x:v>1500.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EE65" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="EF65" s="8" t="n">
-        <x:v>2.6300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG65" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -57887,13 +57887,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP65" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1500.0000</x:v>
       </x:c>
       <x:c r="EQ65" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="ER65" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.6300</x:v>
       </x:c>
       <x:c r="ES65" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -58504,7 +58504,7 @@
         <x:v>46213</x:v>
       </x:c>
       <x:c r="AI66" s="4" t="n">
-        <x:v>46216</x:v>
+        <x:v>46217</x:v>
       </x:c>
       <x:c r="AJ66" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -58810,13 +58810,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG66" s="6" t="n">
-        <x:v>3600.0000</x:v>
+        <x:v>2400.0000</x:v>
       </x:c>
       <x:c r="EH66" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="EI66" s="8" t="n">
-        <x:v>6.3200</x:v>
+        <x:v>4.2100</x:v>
       </x:c>
       <x:c r="EJ66" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -58837,22 +58837,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP66" s="6" t="n">
-        <x:v>2400.0000</x:v>
+        <x:v>2100.0000</x:v>
       </x:c>
       <x:c r="EQ66" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="ER66" s="8" t="n">
-        <x:v>4.2100</x:v>
+        <x:v>3.6800</x:v>
       </x:c>
       <x:c r="ES66" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1500.0000</x:v>
       </x:c>
       <x:c r="ET66" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="EU66" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.6300</x:v>
       </x:c>
       <x:c r="EV66" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -59451,10 +59451,10 @@
         <x:v/>
       </x:c>
       <x:c r="AH67" s="4" t="n">
-        <x:v>46216</x:v>
+        <x:v>46212</x:v>
       </x:c>
       <x:c r="AI67" s="4" t="n">
-        <x:v>46218</x:v>
+        <x:v>46213</x:v>
       </x:c>
       <x:c r="AJ67" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -59463,10 +59463,10 @@
         <x:v>6000.0000</x:v>
       </x:c>
       <x:c r="AL67" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3000.0000</x:v>
       </x:c>
       <x:c r="AM67" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3000.0000</x:v>
       </x:c>
       <x:c r="AN67" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -59751,22 +59751,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ED67" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4500.0000</x:v>
       </x:c>
       <x:c r="EE67" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="EF67" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>7.8900</x:v>
       </x:c>
       <x:c r="EG67" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1500.0000</x:v>
       </x:c>
       <x:c r="EH67" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="EI67" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.6300</x:v>
       </x:c>
       <x:c r="EJ67" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -59787,31 +59787,31 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP67" s="6" t="n">
-        <x:v>1200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EQ67" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="ER67" s="8" t="n">
-        <x:v>2.1100</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES67" s="6" t="n">
-        <x:v>3600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ET67" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="EU67" s="8" t="n">
-        <x:v>6.3200</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV67" s="6" t="n">
-        <x:v>1200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EW67" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="EX67" s="8" t="n">
-        <x:v>2.1100</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY67" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -68301,22 +68301,22 @@
         <x:v>1.0500</x:v>
       </x:c>
       <x:c r="ED76" s="7" t="n">
-        <x:v>17000.0000</x:v>
+        <x:v>20000.0000</x:v>
       </x:c>
       <x:c r="EE76" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="EF76" s="9" t="n">
-        <x:v>17.0100</x:v>
+        <x:v>22.2700</x:v>
       </x:c>
       <x:c r="EG76" s="7" t="n">
-        <x:v>14300.0000</x:v>
+        <x:v>14600.0000</x:v>
       </x:c>
       <x:c r="EH76" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="EI76" s="9" t="n">
-        <x:v>15.2100</x:v>
+        <x:v>15.7300</x:v>
       </x:c>
       <x:c r="EJ76" s="7" t="n">
         <x:v>0.0000</x:v>
@@ -68343,25 +68343,25 @@
         <x:v/>
       </x:c>
       <x:c r="ER76" s="9" t="n">
-        <x:v>20.8100</x:v>
+        <x:v>20.8000</x:v>
       </x:c>
       <x:c r="ES76" s="7" t="n">
-        <x:v>8000.0000</x:v>
+        <x:v>5900.0000</x:v>
       </x:c>
       <x:c r="ET76" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="EU76" s="9" t="n">
-        <x:v>11.3800</x:v>
+        <x:v>7.6900</x:v>
       </x:c>
       <x:c r="EV76" s="7" t="n">
-        <x:v>12000.0000</x:v>
+        <x:v>10800.0000</x:v>
       </x:c>
       <x:c r="EW76" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="EX76" s="9" t="n">
-        <x:v>15.7100</x:v>
+        <x:v>13.6000</x:v>
       </x:c>
       <x:c r="EY76" s="7" t="n">
         <x:v>17800.0000</x:v>

--- a/.pm-ai-cache/network-source/task-input-newest.xlsx
+++ b/.pm-ai-cache/network-source/task-input-newest.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工程別生産計画問合せ問合せ" sheetId="1" r:id="Re83997f787e74396"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工程別生産計画問合せ問合せ" sheetId="1" r:id="R51d66d57b5ea4d30"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -6263,13 +6263,13 @@
         <x:v>10000.0000</x:v>
       </x:c>
       <x:c r="AL11" s="6" t="n">
-        <x:v>3200.0000</x:v>
+        <x:v>4400.0000</x:v>
       </x:c>
       <x:c r="AM11" s="6" t="n">
-        <x:v>6800.0000</x:v>
+        <x:v>5600.0000</x:v>
       </x:c>
       <x:c r="AN11" s="6" t="n">
-        <x:v>3600.0000</x:v>
+        <x:v>6400.0000</x:v>
       </x:c>
       <x:c r="AO11" s="6" t="n">
         <x:v>9000.0000</x:v>
@@ -24307,7 +24307,7 @@
         <x:v>46212</x:v>
       </x:c>
       <x:c r="AJ30" s="1" t="str">
-        <x:v>0:未完</x:v>
+        <x:v>1:完了</x:v>
       </x:c>
       <x:c r="AK30" s="6" t="n">
         <x:v>6000.0000</x:v>
@@ -24319,7 +24319,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AN30" s="6" t="n">
-        <x:v>4500.0000</x:v>
+        <x:v>6000.0000</x:v>
       </x:c>
       <x:c r="AO30" s="6" t="n">
         <x:v>6000.0000</x:v>
@@ -46160,7 +46160,7 @@
         <x:v>0:未完</x:v>
       </x:c>
       <x:c r="AK53" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3200.0000</x:v>
       </x:c>
       <x:c r="AL53" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -52720,7 +52720,7 @@
         <x:v>SEC</x:v>
       </x:c>
       <x:c r="G60" s="1" t="str">
-        <x:v>003</x:v>
+        <x:v>004</x:v>
       </x:c>
       <x:c r="H60" s="4" t="n">
         <x:v>46204</x:v>
@@ -52810,7 +52810,7 @@
         <x:v>0:未完</x:v>
       </x:c>
       <x:c r="AK60" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>200.0000</x:v>
       </x:c>
       <x:c r="AL60" s="6" t="n">
         <x:v>0.0000</x:v>

--- a/.pm-ai-cache/network-source/task-input-newest.xlsx
+++ b/.pm-ai-cache/network-source/task-input-newest.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工程別生産計画問合せ問合せ" sheetId="1" r:id="R4f87d275792a46c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工程別生産計画問合せ問合せ" sheetId="1" r:id="Rc3dd8191257040d3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2895,13 +2895,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FZ7" s="6" t="n">
-        <x:v>8400.0000</x:v>
+        <x:v>7400.0000</x:v>
       </x:c>
       <x:c r="GA7" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="GB7" s="8" t="n">
-        <x:v>8.6800</x:v>
+        <x:v>7.6500</x:v>
       </x:c>
       <x:c r="GC7" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -2913,13 +2913,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GF7" s="6" t="n">
-        <x:v>1600.0000</x:v>
+        <x:v>2600.0000</x:v>
       </x:c>
       <x:c r="GG7" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="GH7" s="8" t="n">
-        <x:v>1.6500</x:v>
+        <x:v>2.6900</x:v>
       </x:c>
       <x:c r="GI7" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -5220,7 +5220,7 @@
         <x:v>スライス</x:v>
       </x:c>
       <x:c r="G10" s="1" t="str">
-        <x:v>005</x:v>
+        <x:v>007</x:v>
       </x:c>
       <x:c r="H10" s="4" t="n">
         <x:v>46209</x:v>
@@ -6263,16 +6263,16 @@
         <x:v>10000.0000</x:v>
       </x:c>
       <x:c r="AL11" s="6" t="n">
-        <x:v>5400.0000</x:v>
+        <x:v>9000.0000</x:v>
       </x:c>
       <x:c r="AM11" s="6" t="n">
-        <x:v>4600.0000</x:v>
+        <x:v>1000.0000</x:v>
       </x:c>
       <x:c r="AN11" s="6" t="n">
-        <x:v>8000.0000</x:v>
+        <x:v>15600.0000</x:v>
       </x:c>
       <x:c r="AO11" s="6" t="n">
-        <x:v>9000.0000</x:v>
+        <x:v>10000.0000</x:v>
       </x:c>
       <x:c r="AP11" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -6551,22 +6551,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ED11" s="6" t="n">
-        <x:v>8400.0000</x:v>
+        <x:v>7800.0000</x:v>
       </x:c>
       <x:c r="EE11" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EF11" s="8" t="n">
-        <x:v>8.6800</x:v>
+        <x:v>8.0600</x:v>
       </x:c>
       <x:c r="EG11" s="6" t="n">
-        <x:v>600.0000</x:v>
+        <x:v>2200.0000</x:v>
       </x:c>
       <x:c r="EH11" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EI11" s="8" t="n">
-        <x:v>0.6200</x:v>
+        <x:v>2.2700</x:v>
       </x:c>
       <x:c r="EJ11" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -7120,7 +7120,7 @@
         <x:v>スライス</x:v>
       </x:c>
       <x:c r="G12" s="1" t="str">
-        <x:v>012</x:v>
+        <x:v>011</x:v>
       </x:c>
       <x:c r="H12" s="4" t="n">
         <x:v>46203</x:v>
@@ -11870,7 +11870,7 @@
         <x:v>分割</x:v>
       </x:c>
       <x:c r="G17" s="1" t="str">
-        <x:v>009</x:v>
+        <x:v>010</x:v>
       </x:c>
       <x:c r="H17" s="4" t="n">
         <x:v>46202</x:v>
@@ -11951,10 +11951,10 @@
         <x:v/>
       </x:c>
       <x:c r="AH17" s="4" t="n">
-        <x:v>46217</x:v>
+        <x:v>46216</x:v>
       </x:c>
       <x:c r="AI17" s="4" t="n">
-        <x:v>46217</x:v>
+        <x:v>46216</x:v>
       </x:c>
       <x:c r="AJ17" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -12287,22 +12287,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP17" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>800.0000</x:v>
       </x:c>
       <x:c r="EQ17" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="ER17" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.8900</x:v>
       </x:c>
       <x:c r="ES17" s="6" t="n">
-        <x:v>800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ET17" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EU17" s="8" t="n">
-        <x:v>0.8900</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV17" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -14801,10 +14801,10 @@
         <x:v/>
       </x:c>
       <x:c r="AH20" s="4" t="n">
-        <x:v>46217</x:v>
+        <x:v>46218</x:v>
       </x:c>
       <x:c r="AI20" s="4" t="n">
-        <x:v>46217</x:v>
+        <x:v>46218</x:v>
       </x:c>
       <x:c r="AJ20" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -15146,22 +15146,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES20" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="ET20" s="8" t="n">
+        <x:v>15.0000</x:v>
+      </x:c>
+      <x:c r="EU20" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="EV20" s="6" t="n">
         <x:v>400.0000</x:v>
       </x:c>
-      <x:c r="ET20" s="8" t="n">
-        <x:v>15.0000</x:v>
-      </x:c>
-      <x:c r="EU20" s="8" t="n">
+      <x:c r="EW20" s="8" t="n">
+        <x:v>15.0000</x:v>
+      </x:c>
+      <x:c r="EX20" s="8" t="n">
         <x:v>0.4400</x:v>
-      </x:c>
-      <x:c r="EV20" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="EW20" s="8" t="n">
-        <x:v>15.0000</x:v>
-      </x:c>
-      <x:c r="EX20" s="8" t="n">
-        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY20" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -15670,7 +15670,7 @@
         <x:v>分割</x:v>
       </x:c>
       <x:c r="G21" s="1" t="str">
-        <x:v>005</x:v>
+        <x:v>007</x:v>
       </x:c>
       <x:c r="H21" s="4" t="n">
         <x:v>46203</x:v>
@@ -15751,10 +15751,10 @@
         <x:v/>
       </x:c>
       <x:c r="AH21" s="4" t="n">
-        <x:v>46217</x:v>
+        <x:v>46218</x:v>
       </x:c>
       <x:c r="AI21" s="4" t="n">
-        <x:v>46217</x:v>
+        <x:v>46218</x:v>
       </x:c>
       <x:c r="AJ21" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -16096,22 +16096,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES21" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="ET21" s="8" t="n">
+        <x:v>15.0000</x:v>
+      </x:c>
+      <x:c r="EU21" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="EV21" s="6" t="n">
         <x:v>800.0000</x:v>
       </x:c>
-      <x:c r="ET21" s="8" t="n">
-        <x:v>15.0000</x:v>
-      </x:c>
-      <x:c r="EU21" s="8" t="n">
+      <x:c r="EW21" s="8" t="n">
+        <x:v>15.0000</x:v>
+      </x:c>
+      <x:c r="EX21" s="8" t="n">
         <x:v>0.8900</x:v>
-      </x:c>
-      <x:c r="EV21" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="EW21" s="8" t="n">
-        <x:v>15.0000</x:v>
-      </x:c>
-      <x:c r="EX21" s="8" t="n">
-        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY21" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -16704,7 +16704,7 @@
         <x:v>46218</x:v>
       </x:c>
       <x:c r="AI22" s="4" t="n">
-        <x:v>46219</x:v>
+        <x:v>46218</x:v>
       </x:c>
       <x:c r="AJ22" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -17055,22 +17055,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV22" s="6" t="n">
-        <x:v>3000.0000</x:v>
+        <x:v>4000.0000</x:v>
       </x:c>
       <x:c r="EW22" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EX22" s="8" t="n">
-        <x:v>3.1000</x:v>
+        <x:v>4.1400</x:v>
       </x:c>
       <x:c r="EY22" s="6" t="n">
-        <x:v>1000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EZ22" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FA22" s="8" t="n">
-        <x:v>1.0300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB22" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -18014,22 +18014,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY23" s="6" t="n">
-        <x:v>6400.0000</x:v>
+        <x:v>7400.0000</x:v>
       </x:c>
       <x:c r="EZ23" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FA23" s="8" t="n">
-        <x:v>6.6200</x:v>
+        <x:v>7.6500</x:v>
       </x:c>
       <x:c r="FB23" s="6" t="n">
-        <x:v>3600.0000</x:v>
+        <x:v>2600.0000</x:v>
       </x:c>
       <x:c r="FC23" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FD23" s="8" t="n">
-        <x:v>3.7200</x:v>
+        <x:v>2.6900</x:v>
       </x:c>
       <x:c r="FE23" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -18604,7 +18604,7 @@
         <x:v>46220</x:v>
       </x:c>
       <x:c r="AI24" s="4" t="n">
-        <x:v>46225</x:v>
+        <x:v>46224</x:v>
       </x:c>
       <x:c r="AJ24" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -18973,13 +18973,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB24" s="6" t="n">
-        <x:v>1000.0000</x:v>
+        <x:v>2800.0000</x:v>
       </x:c>
       <x:c r="FC24" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FD24" s="8" t="n">
-        <x:v>1.0300</x:v>
+        <x:v>2.8900</x:v>
       </x:c>
       <x:c r="FE24" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -19009,22 +19009,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FN24" s="6" t="n">
-        <x:v>8400.0000</x:v>
+        <x:v>7200.0000</x:v>
       </x:c>
       <x:c r="FO24" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FP24" s="8" t="n">
-        <x:v>8.6800</x:v>
+        <x:v>7.4400</x:v>
       </x:c>
       <x:c r="FQ24" s="6" t="n">
-        <x:v>600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FR24" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FS24" s="8" t="n">
-        <x:v>0.6200</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FT24" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -20918,22 +20918,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FQ26" s="6" t="n">
-        <x:v>2800.0000</x:v>
+        <x:v>4200.0000</x:v>
       </x:c>
       <x:c r="FR26" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FS26" s="8" t="n">
-        <x:v>2.8900</x:v>
+        <x:v>4.3400</x:v>
       </x:c>
       <x:c r="FT26" s="6" t="n">
-        <x:v>7200.0000</x:v>
+        <x:v>5800.0000</x:v>
       </x:c>
       <x:c r="FU26" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FV26" s="8" t="n">
-        <x:v>7.4400</x:v>
+        <x:v>6.0000</x:v>
       </x:c>
       <x:c r="FW26" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -21451,7 +21451,7 @@
         <x:v/>
       </x:c>
       <x:c r="AH27" s="4" t="n">
-        <x:v>46227</x:v>
+        <x:v>46226</x:v>
       </x:c>
       <x:c r="AI27" s="4" t="n">
         <x:v>46227</x:v>
@@ -21877,22 +21877,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FT27" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1000.0000</x:v>
       </x:c>
       <x:c r="FU27" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FV27" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.0300</x:v>
       </x:c>
       <x:c r="FW27" s="6" t="n">
-        <x:v>5750.0000</x:v>
+        <x:v>4750.0000</x:v>
       </x:c>
       <x:c r="FX27" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FY27" s="8" t="n">
-        <x:v>5.9400</x:v>
+        <x:v>4.9100</x:v>
       </x:c>
       <x:c r="FZ27" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -26120,7 +26120,7 @@
         <x:v>EC</x:v>
       </x:c>
       <x:c r="G32" s="1" t="str">
-        <x:v>002</x:v>
+        <x:v>001</x:v>
       </x:c>
       <x:c r="H32" s="4" t="n">
         <x:v>46196</x:v>
@@ -26201,10 +26201,10 @@
         <x:v/>
       </x:c>
       <x:c r="AH32" s="4" t="n">
-        <x:v>46218</x:v>
+        <x:v>46217</x:v>
       </x:c>
       <x:c r="AI32" s="4" t="n">
-        <x:v>46218</x:v>
+        <x:v>46217</x:v>
       </x:c>
       <x:c r="AJ32" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -26546,22 +26546,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES32" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2700.0000</x:v>
       </x:c>
       <x:c r="ET32" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EU32" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.4900</x:v>
       </x:c>
       <x:c r="EV32" s="6" t="n">
-        <x:v>2700.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EW32" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EX32" s="8" t="n">
-        <x:v>2.4900</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY32" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -27070,7 +27070,7 @@
         <x:v>EC</x:v>
       </x:c>
       <x:c r="G33" s="1" t="str">
-        <x:v>005</x:v>
+        <x:v>003</x:v>
       </x:c>
       <x:c r="H33" s="4" t="n">
         <x:v>46197</x:v>
@@ -27151,10 +27151,10 @@
         <x:v/>
       </x:c>
       <x:c r="AH33" s="4" t="n">
-        <x:v>46219</x:v>
+        <x:v>46218</x:v>
       </x:c>
       <x:c r="AI33" s="4" t="n">
-        <x:v>46219</x:v>
+        <x:v>46218</x:v>
       </x:c>
       <x:c r="AJ33" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -27505,22 +27505,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV33" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1500.0000</x:v>
       </x:c>
       <x:c r="EW33" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EX33" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.3800</x:v>
       </x:c>
       <x:c r="EY33" s="6" t="n">
-        <x:v>1500.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EZ33" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="FA33" s="8" t="n">
-        <x:v>1.3800</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB33" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -28020,7 +28020,7 @@
         <x:v>EC</x:v>
       </x:c>
       <x:c r="G34" s="1" t="str">
-        <x:v>003</x:v>
+        <x:v>002</x:v>
       </x:c>
       <x:c r="H34" s="4" t="n">
         <x:v>46196</x:v>
@@ -28101,7 +28101,7 @@
         <x:v/>
       </x:c>
       <x:c r="AH34" s="4" t="n">
-        <x:v>46219</x:v>
+        <x:v>46218</x:v>
       </x:c>
       <x:c r="AI34" s="4" t="n">
         <x:v>46219</x:v>
@@ -28455,22 +28455,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV34" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2400.0000</x:v>
       </x:c>
       <x:c r="EW34" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EX34" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.2100</x:v>
       </x:c>
       <x:c r="EY34" s="6" t="n">
-        <x:v>3900.0000</x:v>
+        <x:v>1500.0000</x:v>
       </x:c>
       <x:c r="EZ34" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="FA34" s="8" t="n">
-        <x:v>3.6000</x:v>
+        <x:v>1.3800</x:v>
       </x:c>
       <x:c r="FB34" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -29030,7 +29030,7 @@
         <x:v>1.0000</x:v>
       </x:c>
       <x:c r="AA35" s="4" t="n">
-        <x:v>46217</x:v>
+        <x:v>46216</x:v>
       </x:c>
       <x:c r="AB35" s="1" t="str">
         <x:v>SEC機　湖南</x:v>
@@ -29920,7 +29920,7 @@
         <x:v>スリット</x:v>
       </x:c>
       <x:c r="G36" s="1" t="str">
-        <x:v>001</x:v>
+        <x:v>004</x:v>
       </x:c>
       <x:c r="H36" s="4" t="n">
         <x:v>46210</x:v>
@@ -31847,7 +31847,7 @@
         <x:v>0R040-8Y0B- 340X200G-AGA1C</x:v>
       </x:c>
       <x:c r="P38" s="6" t="n">
-        <x:v>400.0000</x:v>
+        <x:v>200.0000</x:v>
       </x:c>
       <x:c r="Q38" s="8" t="n">
         <x:v>800.0000</x:v>
@@ -34751,10 +34751,10 @@
         <x:v/>
       </x:c>
       <x:c r="AH41" s="4" t="n">
-        <x:v>46213</x:v>
+        <x:v>46216</x:v>
       </x:c>
       <x:c r="AI41" s="4" t="n">
-        <x:v>46213</x:v>
+        <x:v>46216</x:v>
       </x:c>
       <x:c r="AJ41" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -35060,40 +35060,40 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG41" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="EH41" s="8" t="n">
+        <x:v>15.0000</x:v>
+      </x:c>
+      <x:c r="EI41" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="EJ41" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="EK41" s="8" t="n">
+        <x:v>15.0000</x:v>
+      </x:c>
+      <x:c r="EL41" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="EM41" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="EN41" s="8" t="n">
+        <x:v>15.0000</x:v>
+      </x:c>
+      <x:c r="EO41" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="EP41" s="6" t="n">
         <x:v>600.0000</x:v>
       </x:c>
-      <x:c r="EH41" s="8" t="n">
-        <x:v>15.0000</x:v>
-      </x:c>
-      <x:c r="EI41" s="8" t="n">
+      <x:c r="EQ41" s="8" t="n">
+        <x:v>15.0000</x:v>
+      </x:c>
+      <x:c r="ER41" s="8" t="n">
         <x:v>0.6700</x:v>
-      </x:c>
-      <x:c r="EJ41" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="EK41" s="8" t="n">
-        <x:v>15.0000</x:v>
-      </x:c>
-      <x:c r="EL41" s="8" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="EM41" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="EN41" s="8" t="n">
-        <x:v>15.0000</x:v>
-      </x:c>
-      <x:c r="EO41" s="8" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="EP41" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="EQ41" s="8" t="n">
-        <x:v>15.0000</x:v>
-      </x:c>
-      <x:c r="ER41" s="8" t="n">
-        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES41" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -35620,7 +35620,7 @@
         <x:v>分割</x:v>
       </x:c>
       <x:c r="G42" s="1" t="str">
-        <x:v>013</x:v>
+        <x:v>012</x:v>
       </x:c>
       <x:c r="H42" s="4" t="n">
         <x:v>46203</x:v>
@@ -35701,10 +35701,10 @@
         <x:v/>
       </x:c>
       <x:c r="AH42" s="4" t="n">
-        <x:v>46213</x:v>
+        <x:v>46216</x:v>
       </x:c>
       <x:c r="AI42" s="4" t="n">
-        <x:v>46213</x:v>
+        <x:v>46216</x:v>
       </x:c>
       <x:c r="AJ42" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -36010,40 +36010,40 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG42" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="EH42" s="8" t="n">
+        <x:v>15.0000</x:v>
+      </x:c>
+      <x:c r="EI42" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="EJ42" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="EK42" s="8" t="n">
+        <x:v>15.0000</x:v>
+      </x:c>
+      <x:c r="EL42" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="EM42" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="EN42" s="8" t="n">
+        <x:v>15.0000</x:v>
+      </x:c>
+      <x:c r="EO42" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="EP42" s="6" t="n">
         <x:v>1000.0000</x:v>
       </x:c>
-      <x:c r="EH42" s="8" t="n">
-        <x:v>15.0000</x:v>
-      </x:c>
-      <x:c r="EI42" s="8" t="n">
+      <x:c r="EQ42" s="8" t="n">
+        <x:v>15.0000</x:v>
+      </x:c>
+      <x:c r="ER42" s="8" t="n">
         <x:v>1.1100</x:v>
-      </x:c>
-      <x:c r="EJ42" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="EK42" s="8" t="n">
-        <x:v>15.0000</x:v>
-      </x:c>
-      <x:c r="EL42" s="8" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="EM42" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="EN42" s="8" t="n">
-        <x:v>15.0000</x:v>
-      </x:c>
-      <x:c r="EO42" s="8" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="EP42" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="EQ42" s="8" t="n">
-        <x:v>15.0000</x:v>
-      </x:c>
-      <x:c r="ER42" s="8" t="n">
-        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES42" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -36570,7 +36570,7 @@
         <x:v>分割</x:v>
       </x:c>
       <x:c r="G43" s="1" t="str">
-        <x:v>001</x:v>
+        <x:v>004</x:v>
       </x:c>
       <x:c r="H43" s="4" t="n">
         <x:v>46209</x:v>
@@ -36651,10 +36651,10 @@
         <x:v/>
       </x:c>
       <x:c r="AH43" s="4" t="n">
-        <x:v>46213</x:v>
+        <x:v>46216</x:v>
       </x:c>
       <x:c r="AI43" s="4" t="n">
-        <x:v>46213</x:v>
+        <x:v>46216</x:v>
       </x:c>
       <x:c r="AJ43" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -36960,40 +36960,40 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG43" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="EH43" s="8" t="n">
+        <x:v>15.0000</x:v>
+      </x:c>
+      <x:c r="EI43" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="EJ43" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="EK43" s="8" t="n">
+        <x:v>15.0000</x:v>
+      </x:c>
+      <x:c r="EL43" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="EM43" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="EN43" s="8" t="n">
+        <x:v>15.0000</x:v>
+      </x:c>
+      <x:c r="EO43" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="EP43" s="6" t="n">
         <x:v>400.0000</x:v>
       </x:c>
-      <x:c r="EH43" s="8" t="n">
-        <x:v>15.0000</x:v>
-      </x:c>
-      <x:c r="EI43" s="8" t="n">
+      <x:c r="EQ43" s="8" t="n">
+        <x:v>15.0000</x:v>
+      </x:c>
+      <x:c r="ER43" s="8" t="n">
         <x:v>0.4400</x:v>
-      </x:c>
-      <x:c r="EJ43" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="EK43" s="8" t="n">
-        <x:v>15.0000</x:v>
-      </x:c>
-      <x:c r="EL43" s="8" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="EM43" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="EN43" s="8" t="n">
-        <x:v>15.0000</x:v>
-      </x:c>
-      <x:c r="EO43" s="8" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="EP43" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="EQ43" s="8" t="n">
-        <x:v>15.0000</x:v>
-      </x:c>
-      <x:c r="ER43" s="8" t="n">
-        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES43" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -40370,7 +40370,7 @@
         <x:v>スリット</x:v>
       </x:c>
       <x:c r="G47" s="1" t="str">
-        <x:v>003</x:v>
+        <x:v>007</x:v>
       </x:c>
       <x:c r="H47" s="4" t="n">
         <x:v>46209</x:v>
@@ -40451,10 +40451,10 @@
         <x:v/>
       </x:c>
       <x:c r="AH47" s="4" t="n">
-        <x:v>46227</x:v>
+        <x:v>46228</x:v>
       </x:c>
       <x:c r="AI47" s="4" t="n">
-        <x:v>46227</x:v>
+        <x:v>46228</x:v>
       </x:c>
       <x:c r="AJ47" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -40886,22 +40886,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FW47" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="FX47" s="8" t="n">
+        <x:v>10.1200</x:v>
+      </x:c>
+      <x:c r="FY47" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="FZ47" s="6" t="n">
         <x:v>950.0000</x:v>
       </x:c>
-      <x:c r="FX47" s="8" t="n">
-        <x:v>10.1200</x:v>
-      </x:c>
-      <x:c r="FY47" s="8" t="n">
+      <x:c r="GA47" s="8" t="n">
+        <x:v>10.1200</x:v>
+      </x:c>
+      <x:c r="GB47" s="8" t="n">
         <x:v>1.5600</x:v>
-      </x:c>
-      <x:c r="FZ47" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="GA47" s="8" t="n">
-        <x:v>10.1200</x:v>
-      </x:c>
-      <x:c r="GB47" s="8" t="n">
-        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GC47" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -41320,7 +41320,7 @@
         <x:v>梱包</x:v>
       </x:c>
       <x:c r="G48" s="1" t="str">
-        <x:v>002</x:v>
+        <x:v>006</x:v>
       </x:c>
       <x:c r="H48" s="4" t="n">
         <x:v>46209</x:v>
@@ -41401,10 +41401,10 @@
         <x:v/>
       </x:c>
       <x:c r="AH48" s="4" t="n">
-        <x:v>46227</x:v>
+        <x:v>46228</x:v>
       </x:c>
       <x:c r="AI48" s="4" t="n">
-        <x:v>46227</x:v>
+        <x:v>46228</x:v>
       </x:c>
       <x:c r="AJ48" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -41836,16 +41836,16 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FW48" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="FX48" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="FY48" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="FZ48" s="6" t="n">
         <x:v>1000.0000</x:v>
-      </x:c>
-      <x:c r="FX48" s="8" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="FY48" s="8" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="FZ48" s="6" t="n">
-        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GA48" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -42330,7 +42330,7 @@
         <x:v>1.0000</x:v>
       </x:c>
       <x:c r="AA49" s="4" t="n">
-        <x:v>46217</x:v>
+        <x:v>46216</x:v>
       </x:c>
       <x:c r="AB49" s="1" t="str">
         <x:v>SEC機　湖南</x:v>
@@ -43220,7 +43220,7 @@
         <x:v>SEC</x:v>
       </x:c>
       <x:c r="G50" s="1" t="str">
-        <x:v>001</x:v>
+        <x:v>002</x:v>
       </x:c>
       <x:c r="H50" s="4" t="n">
         <x:v>46210</x:v>
@@ -43301,10 +43301,10 @@
         <x:v/>
       </x:c>
       <x:c r="AH50" s="4" t="n">
-        <x:v>46218</x:v>
+        <x:v>46217</x:v>
       </x:c>
       <x:c r="AI50" s="4" t="n">
-        <x:v>46218</x:v>
+        <x:v>46217</x:v>
       </x:c>
       <x:c r="AJ50" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -43646,22 +43646,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES50" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>600.0000</x:v>
       </x:c>
       <x:c r="ET50" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EU50" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.4000</x:v>
       </x:c>
       <x:c r="EV50" s="6" t="n">
-        <x:v>600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EW50" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EX50" s="8" t="n">
-        <x:v>0.4000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY50" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -44170,16 +44170,16 @@
         <x:v>SEC</x:v>
       </x:c>
       <x:c r="G51" s="1" t="str">
-        <x:v>003</x:v>
+        <x:v>006</x:v>
       </x:c>
       <x:c r="H51" s="4" t="n">
-        <x:v>46210</x:v>
+        <x:v>46199</x:v>
       </x:c>
       <x:c r="I51" s="1" t="str">
-        <x:v>C7-22</x:v>
+        <x:v>C7-6</x:v>
       </x:c>
       <x:c r="J51" s="1" t="str">
-        <x:v>00081379</x:v>
+        <x:v>00081039</x:v>
       </x:c>
       <x:c r="K51" s="1" t="str">
         <x:v>6710</x:v>
@@ -44188,19 +44188,19 @@
         <x:v>6713</x:v>
       </x:c>
       <x:c r="M51" s="1" t="str">
-        <x:v>50080-AY0B- 680X200F-AGA1C</x:v>
+        <x:v>30040-AG00- 935X200F-AGA1C</x:v>
       </x:c>
       <x:c r="N51" s="1" t="str">
         <x:v/>
       </x:c>
       <x:c r="O51" s="1" t="str">
-        <x:v>0R040-8Y0B- 680X200F-AGA1C</x:v>
+        <x:v>30020-KG00- 935X200F-AGA1C</x:v>
       </x:c>
       <x:c r="P51" s="6" t="n">
+        <x:v>1600.0000</x:v>
+      </x:c>
+      <x:c r="Q51" s="8" t="n">
         <x:v>3200.0000</x:v>
-      </x:c>
-      <x:c r="Q51" s="8" t="n">
-        <x:v>6400.0000</x:v>
       </x:c>
       <x:c r="R51" s="1" t="str">
         <x:v>SEC</x:v>
@@ -44212,7 +44212,7 @@
         <x:v>自動車材料事業部</x:v>
       </x:c>
       <x:c r="U51" s="1" t="str">
-        <x:v>00075366</x:v>
+        <x:v>00075114</x:v>
       </x:c>
       <x:c r="V51" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -44230,37 +44230,37 @@
         <x:v>1.0000</x:v>
       </x:c>
       <x:c r="AA51" s="4" t="n">
-        <x:v>46218</x:v>
+        <x:v>46212</x:v>
       </x:c>
       <x:c r="AB51" s="1" t="str">
         <x:v>SEC機　湖南</x:v>
       </x:c>
       <x:c r="AC51" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AD51" s="4" t="n">
-        <x:v>46233</x:v>
+        <x:v>46216</x:v>
       </x:c>
       <x:c r="AE51" s="4" t="n">
-        <x:v>46233</x:v>
-      </x:c>
-      <x:c r="AF51" s="4" t="str">
-        <x:v/>
+        <x:v>46216</x:v>
+      </x:c>
+      <x:c r="AF51" s="4" t="n">
+        <x:v>46216</x:v>
       </x:c>
       <x:c r="AG51" s="4" t="str">
         <x:v/>
       </x:c>
       <x:c r="AH51" s="4" t="n">
-        <x:v>46228</x:v>
+        <x:v>46216</x:v>
       </x:c>
       <x:c r="AI51" s="4" t="n">
-        <x:v>46228</x:v>
+        <x:v>46216</x:v>
       </x:c>
       <x:c r="AJ51" s="1" t="str">
         <x:v>0:未完</x:v>
       </x:c>
       <x:c r="AK51" s="6" t="n">
-        <x:v>3200.0000</x:v>
+        <x:v>1600.0000</x:v>
       </x:c>
       <x:c r="AL51" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -44272,7 +44272,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AO51" s="6" t="n">
-        <x:v>3200.0000</x:v>
+        <x:v>1600.0000</x:v>
       </x:c>
       <x:c r="AP51" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -44587,13 +44587,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP51" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1600.0000</x:v>
       </x:c>
       <x:c r="EQ51" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="ER51" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.0700</x:v>
       </x:c>
       <x:c r="ES51" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -44695,13 +44695,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FZ51" s="6" t="n">
-        <x:v>3200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GA51" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="GB51" s="8" t="n">
-        <x:v>2.1300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GC51" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -45120,16 +45120,16 @@
         <x:v>SEC</x:v>
       </x:c>
       <x:c r="G52" s="1" t="str">
-        <x:v>005</x:v>
+        <x:v>010</x:v>
       </x:c>
       <x:c r="H52" s="4" t="n">
-        <x:v>46210</x:v>
+        <x:v>46204</x:v>
       </x:c>
       <x:c r="I52" s="1" t="str">
-        <x:v>C7-21</x:v>
+        <x:v>C7-12</x:v>
       </x:c>
       <x:c r="J52" s="1" t="str">
-        <x:v>00081378</x:v>
+        <x:v>00081159</x:v>
       </x:c>
       <x:c r="K52" s="1" t="str">
         <x:v>6710</x:v>
@@ -45138,22 +45138,22 @@
         <x:v>6713</x:v>
       </x:c>
       <x:c r="M52" s="1" t="str">
-        <x:v>50080-AY0B- 870X200F-AGA1C</x:v>
+        <x:v>50080-AY0B- 680X200F-AGA1C</x:v>
       </x:c>
       <x:c r="N52" s="1" t="str">
         <x:v/>
       </x:c>
       <x:c r="O52" s="1" t="str">
-        <x:v>0R040-8Y0B- 870X200F-AGA1H</x:v>
+        <x:v>0R040-8Y0B- 340X200G-AGA1C</x:v>
       </x:c>
       <x:c r="P52" s="6" t="n">
-        <x:v>3000.0000</x:v>
+        <x:v>200.0000</x:v>
       </x:c>
       <x:c r="Q52" s="8" t="n">
-        <x:v>6000.0000</x:v>
+        <x:v>800.0000</x:v>
       </x:c>
       <x:c r="R52" s="1" t="str">
-        <x:v>SEC</x:v>
+        <x:v>SEC,スリット</x:v>
       </x:c>
       <x:c r="S52" s="1" t="str">
         <x:v>東レ株式会社</x:v>
@@ -45162,7 +45162,7 @@
         <x:v>自動車材料事業部</x:v>
       </x:c>
       <x:c r="U52" s="1" t="str">
-        <x:v>00075340</x:v>
+        <x:v>00075153</x:v>
       </x:c>
       <x:c r="V52" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -45174,43 +45174,43 @@
         <x:v>01</x:v>
       </x:c>
       <x:c r="Y52" s="6" t="n">
-        <x:v>2.0000</x:v>
+        <x:v>1.0000</x:v>
       </x:c>
       <x:c r="Z52" s="6" t="n">
         <x:v>1.0000</x:v>
       </x:c>
       <x:c r="AA52" s="4" t="n">
-        <x:v>46217</x:v>
+        <x:v>46212</x:v>
       </x:c>
       <x:c r="AB52" s="1" t="str">
         <x:v>SEC機　湖南</x:v>
       </x:c>
       <x:c r="AC52" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AD52" s="4" t="n">
-        <x:v>46233</x:v>
+        <x:v>46216</x:v>
       </x:c>
       <x:c r="AE52" s="4" t="n">
-        <x:v>46233</x:v>
-      </x:c>
-      <x:c r="AF52" s="4" t="str">
-        <x:v/>
+        <x:v>46216</x:v>
+      </x:c>
+      <x:c r="AF52" s="4" t="n">
+        <x:v>46216</x:v>
       </x:c>
       <x:c r="AG52" s="4" t="str">
         <x:v/>
       </x:c>
       <x:c r="AH52" s="4" t="n">
-        <x:v>46227</x:v>
+        <x:v>46216</x:v>
       </x:c>
       <x:c r="AI52" s="4" t="n">
-        <x:v>46228</x:v>
+        <x:v>46216</x:v>
       </x:c>
       <x:c r="AJ52" s="1" t="str">
         <x:v>0:未完</x:v>
       </x:c>
       <x:c r="AK52" s="6" t="n">
-        <x:v>3000.0000</x:v>
+        <x:v>200.0000</x:v>
       </x:c>
       <x:c r="AL52" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -45222,7 +45222,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AO52" s="6" t="n">
-        <x:v>3000.0000</x:v>
+        <x:v>200.0000</x:v>
       </x:c>
       <x:c r="AP52" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -45537,13 +45537,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP52" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>200.0000</x:v>
       </x:c>
       <x:c r="EQ52" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="ER52" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.1300</x:v>
       </x:c>
       <x:c r="ES52" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -45636,22 +45636,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FW52" s="6" t="n">
-        <x:v>1000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FX52" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FY52" s="8" t="n">
-        <x:v>0.6700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FZ52" s="6" t="n">
-        <x:v>2000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GA52" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="GB52" s="8" t="n">
-        <x:v>1.3300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GC52" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -46070,16 +46070,16 @@
         <x:v>SEC</x:v>
       </x:c>
       <x:c r="G53" s="1" t="str">
-        <x:v>006</x:v>
+        <x:v>013</x:v>
       </x:c>
       <x:c r="H53" s="4" t="n">
         <x:v>46199</x:v>
       </x:c>
       <x:c r="I53" s="1" t="str">
-        <x:v>C7-6</x:v>
+        <x:v>C7-4</x:v>
       </x:c>
       <x:c r="J53" s="1" t="str">
-        <x:v>00081039</x:v>
+        <x:v>00081029</x:v>
       </x:c>
       <x:c r="K53" s="1" t="str">
         <x:v>6710</x:v>
@@ -46088,19 +46088,19 @@
         <x:v>6713</x:v>
       </x:c>
       <x:c r="M53" s="1" t="str">
-        <x:v>30040-AG00- 935X200F-AGA1C</x:v>
+        <x:v>50080-AY0B- 870X200F-AGA1C</x:v>
       </x:c>
       <x:c r="N53" s="1" t="str">
         <x:v/>
       </x:c>
       <x:c r="O53" s="1" t="str">
-        <x:v>30020-KG00- 935X200F-AGA1C</x:v>
+        <x:v>0R040-8Y0B- 870X200F-AGA1H</x:v>
       </x:c>
       <x:c r="P53" s="6" t="n">
-        <x:v>1600.0000</x:v>
+        <x:v>10000.0000</x:v>
       </x:c>
       <x:c r="Q53" s="8" t="n">
-        <x:v>3200.0000</x:v>
+        <x:v>20000.0000</x:v>
       </x:c>
       <x:c r="R53" s="1" t="str">
         <x:v>SEC</x:v>
@@ -46112,7 +46112,7 @@
         <x:v>自動車材料事業部</x:v>
       </x:c>
       <x:c r="U53" s="1" t="str">
-        <x:v>00075114</x:v>
+        <x:v>00075010</x:v>
       </x:c>
       <x:c r="V53" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -46124,19 +46124,19 @@
         <x:v>01</x:v>
       </x:c>
       <x:c r="Y53" s="6" t="n">
-        <x:v>1.0000</x:v>
+        <x:v>2.0000</x:v>
       </x:c>
       <x:c r="Z53" s="6" t="n">
         <x:v>1.0000</x:v>
       </x:c>
       <x:c r="AA53" s="4" t="n">
-        <x:v>46212</x:v>
+        <x:v>46211</x:v>
       </x:c>
       <x:c r="AB53" s="1" t="str">
         <x:v>SEC機　湖南</x:v>
       </x:c>
       <x:c r="AC53" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AD53" s="4" t="n">
         <x:v>46216</x:v>
@@ -46154,346 +46154,346 @@
         <x:v>46213</x:v>
       </x:c>
       <x:c r="AI53" s="4" t="n">
-        <x:v>46213</x:v>
+        <x:v>46216</x:v>
       </x:c>
       <x:c r="AJ53" s="1" t="str">
         <x:v>0:未完</x:v>
       </x:c>
       <x:c r="AK53" s="6" t="n">
+        <x:v>10000.0000</x:v>
+      </x:c>
+      <x:c r="AL53" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="AM53" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="AN53" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="AO53" s="6" t="n">
+        <x:v>10000.0000</x:v>
+      </x:c>
+      <x:c r="AP53" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="AQ53" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="AR53" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="AS53" s="8" t="n">
+        <x:v>25.0000</x:v>
+      </x:c>
+      <x:c r="AT53" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="AU53" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="AV53" s="8" t="n">
+        <x:v>25.0000</x:v>
+      </x:c>
+      <x:c r="AW53" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="AX53" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="AY53" s="8" t="n">
+        <x:v>25.0000</x:v>
+      </x:c>
+      <x:c r="AZ53" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="BA53" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="BB53" s="8" t="n">
+        <x:v>25.0000</x:v>
+      </x:c>
+      <x:c r="BC53" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="BD53" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="BE53" s="8" t="n">
+        <x:v>25.0000</x:v>
+      </x:c>
+      <x:c r="BF53" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="BG53" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="BH53" s="8" t="n">
+        <x:v>25.0000</x:v>
+      </x:c>
+      <x:c r="BI53" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="BJ53" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="BK53" s="8" t="n">
+        <x:v>25.0000</x:v>
+      </x:c>
+      <x:c r="BL53" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="BM53" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="BN53" s="8" t="n">
+        <x:v>25.0000</x:v>
+      </x:c>
+      <x:c r="BO53" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="BP53" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="BQ53" s="8" t="n">
+        <x:v>25.0000</x:v>
+      </x:c>
+      <x:c r="BR53" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="BS53" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="BT53" s="8" t="n">
+        <x:v>25.0000</x:v>
+      </x:c>
+      <x:c r="BU53" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="BV53" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="BW53" s="8" t="n">
+        <x:v>25.0000</x:v>
+      </x:c>
+      <x:c r="BX53" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="BY53" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="BZ53" s="8" t="n">
+        <x:v>25.0000</x:v>
+      </x:c>
+      <x:c r="CA53" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="CB53" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="CC53" s="8" t="n">
+        <x:v>25.0000</x:v>
+      </x:c>
+      <x:c r="CD53" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="CE53" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="CF53" s="8" t="n">
+        <x:v>25.0000</x:v>
+      </x:c>
+      <x:c r="CG53" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="CH53" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="CI53" s="8" t="n">
+        <x:v>25.0000</x:v>
+      </x:c>
+      <x:c r="CJ53" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="CK53" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="CL53" s="8" t="n">
+        <x:v>25.0000</x:v>
+      </x:c>
+      <x:c r="CM53" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="CN53" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="CO53" s="8" t="n">
+        <x:v>25.0000</x:v>
+      </x:c>
+      <x:c r="CP53" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="CQ53" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="CR53" s="8" t="n">
+        <x:v>25.0000</x:v>
+      </x:c>
+      <x:c r="CS53" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="CT53" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="CU53" s="8" t="n">
+        <x:v>25.0000</x:v>
+      </x:c>
+      <x:c r="CV53" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="CW53" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="CX53" s="8" t="n">
+        <x:v>25.0000</x:v>
+      </x:c>
+      <x:c r="CY53" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="CZ53" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="DA53" s="8" t="n">
+        <x:v>25.0000</x:v>
+      </x:c>
+      <x:c r="DB53" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="DC53" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="DD53" s="8" t="n">
+        <x:v>25.0000</x:v>
+      </x:c>
+      <x:c r="DE53" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="DF53" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="DG53" s="8" t="n">
+        <x:v>25.0000</x:v>
+      </x:c>
+      <x:c r="DH53" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="DI53" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="DJ53" s="8" t="n">
+        <x:v>25.0000</x:v>
+      </x:c>
+      <x:c r="DK53" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="DL53" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="DM53" s="8" t="n">
+        <x:v>25.0000</x:v>
+      </x:c>
+      <x:c r="DN53" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="DO53" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="DP53" s="8" t="n">
+        <x:v>25.0000</x:v>
+      </x:c>
+      <x:c r="DQ53" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="DR53" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="DS53" s="8" t="n">
+        <x:v>25.0000</x:v>
+      </x:c>
+      <x:c r="DT53" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="DU53" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="DV53" s="8" t="n">
+        <x:v>25.0000</x:v>
+      </x:c>
+      <x:c r="DW53" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="DX53" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="DY53" s="8" t="n">
+        <x:v>25.0000</x:v>
+      </x:c>
+      <x:c r="DZ53" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="EA53" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="EB53" s="8" t="n">
+        <x:v>25.0000</x:v>
+      </x:c>
+      <x:c r="EC53" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="ED53" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="EE53" s="8" t="n">
+        <x:v>25.0000</x:v>
+      </x:c>
+      <x:c r="EF53" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="EG53" s="6" t="n">
+        <x:v>8400.0000</x:v>
+      </x:c>
+      <x:c r="EH53" s="8" t="n">
+        <x:v>25.0000</x:v>
+      </x:c>
+      <x:c r="EI53" s="8" t="n">
+        <x:v>5.6000</x:v>
+      </x:c>
+      <x:c r="EJ53" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="EK53" s="8" t="n">
+        <x:v>25.0000</x:v>
+      </x:c>
+      <x:c r="EL53" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="EM53" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="EN53" s="8" t="n">
+        <x:v>25.0000</x:v>
+      </x:c>
+      <x:c r="EO53" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="EP53" s="6" t="n">
         <x:v>1600.0000</x:v>
       </x:c>
-      <x:c r="AL53" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="AM53" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="AN53" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="AO53" s="6" t="n">
-        <x:v>1600.0000</x:v>
-      </x:c>
-      <x:c r="AP53" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="AQ53" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="AR53" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="AS53" s="8" t="n">
-        <x:v>25.0000</x:v>
-      </x:c>
-      <x:c r="AT53" s="8" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="AU53" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="AV53" s="8" t="n">
-        <x:v>25.0000</x:v>
-      </x:c>
-      <x:c r="AW53" s="8" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="AX53" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="AY53" s="8" t="n">
-        <x:v>25.0000</x:v>
-      </x:c>
-      <x:c r="AZ53" s="8" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="BA53" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="BB53" s="8" t="n">
-        <x:v>25.0000</x:v>
-      </x:c>
-      <x:c r="BC53" s="8" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="BD53" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="BE53" s="8" t="n">
-        <x:v>25.0000</x:v>
-      </x:c>
-      <x:c r="BF53" s="8" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="BG53" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="BH53" s="8" t="n">
-        <x:v>25.0000</x:v>
-      </x:c>
-      <x:c r="BI53" s="8" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="BJ53" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="BK53" s="8" t="n">
-        <x:v>25.0000</x:v>
-      </x:c>
-      <x:c r="BL53" s="8" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="BM53" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="BN53" s="8" t="n">
-        <x:v>25.0000</x:v>
-      </x:c>
-      <x:c r="BO53" s="8" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="BP53" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="BQ53" s="8" t="n">
-        <x:v>25.0000</x:v>
-      </x:c>
-      <x:c r="BR53" s="8" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="BS53" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="BT53" s="8" t="n">
-        <x:v>25.0000</x:v>
-      </x:c>
-      <x:c r="BU53" s="8" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="BV53" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="BW53" s="8" t="n">
-        <x:v>25.0000</x:v>
-      </x:c>
-      <x:c r="BX53" s="8" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="BY53" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="BZ53" s="8" t="n">
-        <x:v>25.0000</x:v>
-      </x:c>
-      <x:c r="CA53" s="8" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="CB53" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="CC53" s="8" t="n">
-        <x:v>25.0000</x:v>
-      </x:c>
-      <x:c r="CD53" s="8" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="CE53" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="CF53" s="8" t="n">
-        <x:v>25.0000</x:v>
-      </x:c>
-      <x:c r="CG53" s="8" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="CH53" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="CI53" s="8" t="n">
-        <x:v>25.0000</x:v>
-      </x:c>
-      <x:c r="CJ53" s="8" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="CK53" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="CL53" s="8" t="n">
-        <x:v>25.0000</x:v>
-      </x:c>
-      <x:c r="CM53" s="8" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="CN53" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="CO53" s="8" t="n">
-        <x:v>25.0000</x:v>
-      </x:c>
-      <x:c r="CP53" s="8" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="CQ53" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="CR53" s="8" t="n">
-        <x:v>25.0000</x:v>
-      </x:c>
-      <x:c r="CS53" s="8" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="CT53" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="CU53" s="8" t="n">
-        <x:v>25.0000</x:v>
-      </x:c>
-      <x:c r="CV53" s="8" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="CW53" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="CX53" s="8" t="n">
-        <x:v>25.0000</x:v>
-      </x:c>
-      <x:c r="CY53" s="8" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="CZ53" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="DA53" s="8" t="n">
-        <x:v>25.0000</x:v>
-      </x:c>
-      <x:c r="DB53" s="8" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="DC53" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="DD53" s="8" t="n">
-        <x:v>25.0000</x:v>
-      </x:c>
-      <x:c r="DE53" s="8" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="DF53" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="DG53" s="8" t="n">
-        <x:v>25.0000</x:v>
-      </x:c>
-      <x:c r="DH53" s="8" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="DI53" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="DJ53" s="8" t="n">
-        <x:v>25.0000</x:v>
-      </x:c>
-      <x:c r="DK53" s="8" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="DL53" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="DM53" s="8" t="n">
-        <x:v>25.0000</x:v>
-      </x:c>
-      <x:c r="DN53" s="8" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="DO53" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="DP53" s="8" t="n">
-        <x:v>25.0000</x:v>
-      </x:c>
-      <x:c r="DQ53" s="8" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="DR53" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="DS53" s="8" t="n">
-        <x:v>25.0000</x:v>
-      </x:c>
-      <x:c r="DT53" s="8" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="DU53" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="DV53" s="8" t="n">
-        <x:v>25.0000</x:v>
-      </x:c>
-      <x:c r="DW53" s="8" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="DX53" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="DY53" s="8" t="n">
-        <x:v>25.0000</x:v>
-      </x:c>
-      <x:c r="DZ53" s="8" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="EA53" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="EB53" s="8" t="n">
-        <x:v>25.0000</x:v>
-      </x:c>
-      <x:c r="EC53" s="8" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="ED53" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="EE53" s="8" t="n">
-        <x:v>25.0000</x:v>
-      </x:c>
-      <x:c r="EF53" s="8" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="EG53" s="6" t="n">
-        <x:v>1600.0000</x:v>
-      </x:c>
-      <x:c r="EH53" s="8" t="n">
-        <x:v>25.0000</x:v>
-      </x:c>
-      <x:c r="EI53" s="8" t="n">
+      <x:c r="EQ53" s="8" t="n">
+        <x:v>25.0000</x:v>
+      </x:c>
+      <x:c r="ER53" s="8" t="n">
         <x:v>1.0700</x:v>
-      </x:c>
-      <x:c r="EJ53" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="EK53" s="8" t="n">
-        <x:v>25.0000</x:v>
-      </x:c>
-      <x:c r="EL53" s="8" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="EM53" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="EN53" s="8" t="n">
-        <x:v>25.0000</x:v>
-      </x:c>
-      <x:c r="EO53" s="8" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="EP53" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="EQ53" s="8" t="n">
-        <x:v>25.0000</x:v>
-      </x:c>
-      <x:c r="ER53" s="8" t="n">
-        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES53" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -47020,16 +47020,16 @@
         <x:v>SEC</x:v>
       </x:c>
       <x:c r="G54" s="1" t="str">
-        <x:v>010</x:v>
+        <x:v>008</x:v>
       </x:c>
       <x:c r="H54" s="4" t="n">
         <x:v>46204</x:v>
       </x:c>
       <x:c r="I54" s="1" t="str">
-        <x:v>C7-12</x:v>
+        <x:v>C7-10</x:v>
       </x:c>
       <x:c r="J54" s="1" t="str">
-        <x:v>00081159</x:v>
+        <x:v>00081157</x:v>
       </x:c>
       <x:c r="K54" s="1" t="str">
         <x:v>6710</x:v>
@@ -47038,22 +47038,22 @@
         <x:v>6713</x:v>
       </x:c>
       <x:c r="M54" s="1" t="str">
-        <x:v>50080-AY0B- 680X200F-AGA1C</x:v>
+        <x:v>50080-AY0B- 870X200F-ABG1F</x:v>
       </x:c>
       <x:c r="N54" s="1" t="str">
         <x:v/>
       </x:c>
       <x:c r="O54" s="1" t="str">
-        <x:v>0R040-8Y0B- 340X200G-AGA1C</x:v>
+        <x:v>0R040-8Y0B- 870X200F-ABG1C</x:v>
       </x:c>
       <x:c r="P54" s="6" t="n">
-        <x:v>400.0000</x:v>
+        <x:v>2000.0000</x:v>
       </x:c>
       <x:c r="Q54" s="8" t="n">
-        <x:v>800.0000</x:v>
+        <x:v>4000.0000</x:v>
       </x:c>
       <x:c r="R54" s="1" t="str">
-        <x:v>SEC,スリット</x:v>
+        <x:v>接続,SEC</x:v>
       </x:c>
       <x:c r="S54" s="1" t="str">
         <x:v>東レ株式会社</x:v>
@@ -47062,7 +47062,7 @@
         <x:v>自動車材料事業部</x:v>
       </x:c>
       <x:c r="U54" s="1" t="str">
-        <x:v>00075153</x:v>
+        <x:v>00075155</x:v>
       </x:c>
       <x:c r="V54" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -47080,37 +47080,37 @@
         <x:v>1.0000</x:v>
       </x:c>
       <x:c r="AA54" s="4" t="n">
-        <x:v>46212</x:v>
+        <x:v>46216</x:v>
       </x:c>
       <x:c r="AB54" s="1" t="str">
-        <x:v>SEC機　湖南</x:v>
+        <x:v>熱融着機　湖南</x:v>
       </x:c>
       <x:c r="AC54" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AD54" s="4" t="n">
-        <x:v>46216</x:v>
+        <x:v>46221</x:v>
       </x:c>
       <x:c r="AE54" s="4" t="n">
-        <x:v>46216</x:v>
+        <x:v>46221</x:v>
       </x:c>
       <x:c r="AF54" s="4" t="n">
-        <x:v>46216</x:v>
+        <x:v>46221</x:v>
       </x:c>
       <x:c r="AG54" s="4" t="str">
         <x:v/>
       </x:c>
       <x:c r="AH54" s="4" t="n">
-        <x:v>46216</x:v>
+        <x:v>46220</x:v>
       </x:c>
       <x:c r="AI54" s="4" t="n">
-        <x:v>46216</x:v>
+        <x:v>46220</x:v>
       </x:c>
       <x:c r="AJ54" s="1" t="str">
         <x:v>0:未完</x:v>
       </x:c>
       <x:c r="AK54" s="6" t="n">
-        <x:v>400.0000</x:v>
+        <x:v>2000.0000</x:v>
       </x:c>
       <x:c r="AL54" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -47122,7 +47122,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AO54" s="6" t="n">
-        <x:v>400.0000</x:v>
+        <x:v>2000.0000</x:v>
       </x:c>
       <x:c r="AP54" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -47437,13 +47437,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP54" s="6" t="n">
-        <x:v>400.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EQ54" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="ER54" s="8" t="n">
-        <x:v>0.2700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES54" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -47473,13 +47473,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB54" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2000.0000</x:v>
       </x:c>
       <x:c r="FC54" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FD54" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.3300</x:v>
       </x:c>
       <x:c r="FE54" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -47970,16 +47970,16 @@
         <x:v>SEC</x:v>
       </x:c>
       <x:c r="G55" s="1" t="str">
-        <x:v>012</x:v>
+        <x:v>011</x:v>
       </x:c>
       <x:c r="H55" s="4" t="n">
-        <x:v>46199</x:v>
+        <x:v>46204</x:v>
       </x:c>
       <x:c r="I55" s="1" t="str">
-        <x:v>C7-4</x:v>
+        <x:v>C7-9</x:v>
       </x:c>
       <x:c r="J55" s="1" t="str">
-        <x:v>00081029</x:v>
+        <x:v>00081156</x:v>
       </x:c>
       <x:c r="K55" s="1" t="str">
         <x:v>6710</x:v>
@@ -47988,22 +47988,22 @@
         <x:v>6713</x:v>
       </x:c>
       <x:c r="M55" s="1" t="str">
-        <x:v>50080-AY0B- 870X200F-AGA1C</x:v>
+        <x:v>50080-AY0B- 870X200F-ABG1F</x:v>
       </x:c>
       <x:c r="N55" s="1" t="str">
         <x:v/>
       </x:c>
       <x:c r="O55" s="1" t="str">
-        <x:v>0R040-8Y0B- 870X200F-AGA1H</x:v>
+        <x:v>0R040-8Y0B- 825X200F-ABG1C</x:v>
       </x:c>
       <x:c r="P55" s="6" t="n">
-        <x:v>10000.0000</x:v>
+        <x:v>200.0000</x:v>
       </x:c>
       <x:c r="Q55" s="8" t="n">
-        <x:v>20000.0000</x:v>
+        <x:v>400.0000</x:v>
       </x:c>
       <x:c r="R55" s="1" t="str">
-        <x:v>SEC</x:v>
+        <x:v>接続,スリット,SEC</x:v>
       </x:c>
       <x:c r="S55" s="1" t="str">
         <x:v>東レ株式会社</x:v>
@@ -48012,7 +48012,7 @@
         <x:v>自動車材料事業部</x:v>
       </x:c>
       <x:c r="U55" s="1" t="str">
-        <x:v>00075010</x:v>
+        <x:v>00075154</x:v>
       </x:c>
       <x:c r="V55" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -48024,43 +48024,43 @@
         <x:v>01</x:v>
       </x:c>
       <x:c r="Y55" s="6" t="n">
-        <x:v>2.0000</x:v>
+        <x:v>1.0000</x:v>
       </x:c>
       <x:c r="Z55" s="6" t="n">
         <x:v>1.0000</x:v>
       </x:c>
       <x:c r="AA55" s="4" t="n">
-        <x:v>46211</x:v>
+        <x:v>46216</x:v>
       </x:c>
       <x:c r="AB55" s="1" t="str">
-        <x:v>SEC機　湖南</x:v>
+        <x:v>熱融着機　湖南</x:v>
       </x:c>
       <x:c r="AC55" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AD55" s="4" t="n">
-        <x:v>46216</x:v>
+        <x:v>46221</x:v>
       </x:c>
       <x:c r="AE55" s="4" t="n">
-        <x:v>46216</x:v>
+        <x:v>46221</x:v>
       </x:c>
       <x:c r="AF55" s="4" t="n">
-        <x:v>46216</x:v>
+        <x:v>46221</x:v>
       </x:c>
       <x:c r="AG55" s="4" t="str">
         <x:v/>
       </x:c>
       <x:c r="AH55" s="4" t="n">
-        <x:v>46212</x:v>
+        <x:v>46219</x:v>
       </x:c>
       <x:c r="AI55" s="4" t="n">
-        <x:v>46213</x:v>
+        <x:v>46219</x:v>
       </x:c>
       <x:c r="AJ55" s="1" t="str">
         <x:v>0:未完</x:v>
       </x:c>
       <x:c r="AK55" s="6" t="n">
-        <x:v>10000.0000</x:v>
+        <x:v>200.0000</x:v>
       </x:c>
       <x:c r="AL55" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -48072,7 +48072,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AO55" s="6" t="n">
-        <x:v>10000.0000</x:v>
+        <x:v>200.0000</x:v>
       </x:c>
       <x:c r="AP55" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -48351,22 +48351,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ED55" s="6" t="n">
-        <x:v>5000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EE55" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EF55" s="8" t="n">
-        <x:v>3.3300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG55" s="6" t="n">
-        <x:v>5000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EH55" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EI55" s="8" t="n">
-        <x:v>3.3300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ55" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -48414,13 +48414,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY55" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>200.0000</x:v>
       </x:c>
       <x:c r="EZ55" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FA55" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.1300</x:v>
       </x:c>
       <x:c r="FB55" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -48920,16 +48920,16 @@
         <x:v>SEC</x:v>
       </x:c>
       <x:c r="G56" s="1" t="str">
-        <x:v>008</x:v>
+        <x:v>004</x:v>
       </x:c>
       <x:c r="H56" s="4" t="n">
         <x:v>46204</x:v>
       </x:c>
       <x:c r="I56" s="1" t="str">
-        <x:v>C7-10</x:v>
+        <x:v>C7-11</x:v>
       </x:c>
       <x:c r="J56" s="1" t="str">
-        <x:v>00081157</x:v>
+        <x:v>00081158</x:v>
       </x:c>
       <x:c r="K56" s="1" t="str">
         <x:v>6710</x:v>
@@ -48938,22 +48938,22 @@
         <x:v>6713</x:v>
       </x:c>
       <x:c r="M56" s="1" t="str">
-        <x:v>50080-AY0B- 870X200F-ABG1F</x:v>
+        <x:v>50060-AY0B- 870X200F-ABG1F</x:v>
       </x:c>
       <x:c r="N56" s="1" t="str">
         <x:v/>
       </x:c>
       <x:c r="O56" s="1" t="str">
-        <x:v>0R040-8Y0B- 870X200F-ABG1C</x:v>
+        <x:v>0R040-8Y0B- 680X200F-ABG1C</x:v>
       </x:c>
       <x:c r="P56" s="6" t="n">
-        <x:v>2000.0000</x:v>
+        <x:v>200.0000</x:v>
       </x:c>
       <x:c r="Q56" s="8" t="n">
-        <x:v>4000.0000</x:v>
+        <x:v>400.0000</x:v>
       </x:c>
       <x:c r="R56" s="1" t="str">
-        <x:v>接続,SEC</x:v>
+        <x:v>接続,スリット,SEC</x:v>
       </x:c>
       <x:c r="S56" s="1" t="str">
         <x:v>東レ株式会社</x:v>
@@ -48962,7 +48962,7 @@
         <x:v>自動車材料事業部</x:v>
       </x:c>
       <x:c r="U56" s="1" t="str">
-        <x:v>00075155</x:v>
+        <x:v>00075367</x:v>
       </x:c>
       <x:c r="V56" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -48989,13 +48989,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AD56" s="4" t="n">
-        <x:v>46221</x:v>
+        <x:v>46225</x:v>
       </x:c>
       <x:c r="AE56" s="4" t="n">
-        <x:v>46221</x:v>
+        <x:v>46225</x:v>
       </x:c>
       <x:c r="AF56" s="4" t="n">
-        <x:v>46221</x:v>
+        <x:v>46225</x:v>
       </x:c>
       <x:c r="AG56" s="4" t="str">
         <x:v/>
@@ -49010,7 +49010,7 @@
         <x:v>0:未完</x:v>
       </x:c>
       <x:c r="AK56" s="6" t="n">
-        <x:v>2000.0000</x:v>
+        <x:v>200.0000</x:v>
       </x:c>
       <x:c r="AL56" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -49022,7 +49022,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AO56" s="6" t="n">
-        <x:v>2000.0000</x:v>
+        <x:v>200.0000</x:v>
       </x:c>
       <x:c r="AP56" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -49373,13 +49373,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB56" s="6" t="n">
-        <x:v>2000.0000</x:v>
+        <x:v>200.0000</x:v>
       </x:c>
       <x:c r="FC56" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FD56" s="8" t="n">
-        <x:v>1.3300</x:v>
+        <x:v>0.1300</x:v>
       </x:c>
       <x:c r="FE56" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -49870,16 +49870,16 @@
         <x:v>SEC</x:v>
       </x:c>
       <x:c r="G57" s="1" t="str">
-        <x:v>011</x:v>
+        <x:v>010</x:v>
       </x:c>
       <x:c r="H57" s="4" t="n">
-        <x:v>46204</x:v>
+        <x:v>46209</x:v>
       </x:c>
       <x:c r="I57" s="1" t="str">
-        <x:v>C7-9</x:v>
+        <x:v>C7-16</x:v>
       </x:c>
       <x:c r="J57" s="1" t="str">
-        <x:v>00081156</x:v>
+        <x:v>00081306</x:v>
       </x:c>
       <x:c r="K57" s="1" t="str">
         <x:v>6710</x:v>
@@ -49888,22 +49888,22 @@
         <x:v>6713</x:v>
       </x:c>
       <x:c r="M57" s="1" t="str">
-        <x:v>50080-AY0B- 870X200F-ABG1F</x:v>
+        <x:v>50080-AY0B- 870X200F-AGA1C</x:v>
       </x:c>
       <x:c r="N57" s="1" t="str">
         <x:v/>
       </x:c>
       <x:c r="O57" s="1" t="str">
-        <x:v>0R040-8Y0B- 825X200F-ABG1C</x:v>
+        <x:v>0R040-8Y0B- 870X200F-AGA1H</x:v>
       </x:c>
       <x:c r="P57" s="6" t="n">
-        <x:v>200.0000</x:v>
+        <x:v>10000.0000</x:v>
       </x:c>
       <x:c r="Q57" s="8" t="n">
-        <x:v>400.0000</x:v>
+        <x:v>20000.0000</x:v>
       </x:c>
       <x:c r="R57" s="1" t="str">
-        <x:v>接続,スリット,SEC</x:v>
+        <x:v>SEC</x:v>
       </x:c>
       <x:c r="S57" s="1" t="str">
         <x:v>東レ株式会社</x:v>
@@ -49912,7 +49912,7 @@
         <x:v>自動車材料事業部</x:v>
       </x:c>
       <x:c r="U57" s="1" t="str">
-        <x:v>00075154</x:v>
+        <x:v>00075320</x:v>
       </x:c>
       <x:c r="V57" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -49924,28 +49924,28 @@
         <x:v>01</x:v>
       </x:c>
       <x:c r="Y57" s="6" t="n">
-        <x:v>1.0000</x:v>
+        <x:v>2.0000</x:v>
       </x:c>
       <x:c r="Z57" s="6" t="n">
         <x:v>1.0000</x:v>
       </x:c>
       <x:c r="AA57" s="4" t="n">
-        <x:v>46216</x:v>
+        <x:v>46219</x:v>
       </x:c>
       <x:c r="AB57" s="1" t="str">
-        <x:v>熱融着機　湖南</x:v>
+        <x:v>SEC機　湖南</x:v>
       </x:c>
       <x:c r="AC57" s="1" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="AD57" s="4" t="n">
-        <x:v>46221</x:v>
+        <x:v>46225</x:v>
       </x:c>
       <x:c r="AE57" s="4" t="n">
-        <x:v>46221</x:v>
+        <x:v>46225</x:v>
       </x:c>
       <x:c r="AF57" s="4" t="n">
-        <x:v>46221</x:v>
+        <x:v>46225</x:v>
       </x:c>
       <x:c r="AG57" s="4" t="str">
         <x:v/>
@@ -49954,13 +49954,13 @@
         <x:v>46219</x:v>
       </x:c>
       <x:c r="AI57" s="4" t="n">
-        <x:v>46219</x:v>
+        <x:v>46224</x:v>
       </x:c>
       <x:c r="AJ57" s="1" t="str">
         <x:v>0:未完</x:v>
       </x:c>
       <x:c r="AK57" s="6" t="n">
-        <x:v>200.0000</x:v>
+        <x:v>10000.0000</x:v>
       </x:c>
       <x:c r="AL57" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -49972,7 +49972,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AO57" s="6" t="n">
-        <x:v>200.0000</x:v>
+        <x:v>10000.0000</x:v>
       </x:c>
       <x:c r="AP57" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -50314,22 +50314,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY57" s="6" t="n">
-        <x:v>200.0000</x:v>
+        <x:v>1000.0000</x:v>
       </x:c>
       <x:c r="EZ57" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FA57" s="8" t="n">
-        <x:v>0.1300</x:v>
+        <x:v>0.6700</x:v>
       </x:c>
       <x:c r="FB57" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5800.0000</x:v>
       </x:c>
       <x:c r="FC57" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FD57" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3.8700</x:v>
       </x:c>
       <x:c r="FE57" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -50359,13 +50359,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FN57" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3200.0000</x:v>
       </x:c>
       <x:c r="FO57" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FP57" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.1300</x:v>
       </x:c>
       <x:c r="FQ57" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -50820,16 +50820,16 @@
         <x:v>SEC</x:v>
       </x:c>
       <x:c r="G58" s="1" t="str">
-        <x:v>004</x:v>
+        <x:v>014</x:v>
       </x:c>
       <x:c r="H58" s="4" t="n">
-        <x:v>46204</x:v>
+        <x:v>46206</x:v>
       </x:c>
       <x:c r="I58" s="1" t="str">
-        <x:v>C7-11</x:v>
+        <x:v>C7-15</x:v>
       </x:c>
       <x:c r="J58" s="1" t="str">
-        <x:v>00081158</x:v>
+        <x:v>00081267</x:v>
       </x:c>
       <x:c r="K58" s="1" t="str">
         <x:v>6710</x:v>
@@ -50838,22 +50838,22 @@
         <x:v>6713</x:v>
       </x:c>
       <x:c r="M58" s="1" t="str">
-        <x:v>50060-AY0B- 870X200F-ABG1F</x:v>
+        <x:v>50080-AY0B- 870X200F-ABG1C</x:v>
       </x:c>
       <x:c r="N58" s="1" t="str">
         <x:v/>
       </x:c>
       <x:c r="O58" s="1" t="str">
-        <x:v>0R040-8Y0B- 680X200F-ABG1C</x:v>
+        <x:v>0R040-8Y0B- 870X200F-ABG1C</x:v>
       </x:c>
       <x:c r="P58" s="6" t="n">
-        <x:v>200.0000</x:v>
+        <x:v>10000.0000</x:v>
       </x:c>
       <x:c r="Q58" s="8" t="n">
-        <x:v>400.0000</x:v>
+        <x:v>20000.0000</x:v>
       </x:c>
       <x:c r="R58" s="1" t="str">
-        <x:v>接続,スリット,SEC</x:v>
+        <x:v>SEC</x:v>
       </x:c>
       <x:c r="S58" s="1" t="str">
         <x:v>東レ株式会社</x:v>
@@ -50862,7 +50862,7 @@
         <x:v>自動車材料事業部</x:v>
       </x:c>
       <x:c r="U58" s="1" t="str">
-        <x:v>00075367</x:v>
+        <x:v>00075237</x:v>
       </x:c>
       <x:c r="V58" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -50880,37 +50880,37 @@
         <x:v>1.0000</x:v>
       </x:c>
       <x:c r="AA58" s="4" t="n">
-        <x:v>46216</x:v>
+        <x:v>46220</x:v>
       </x:c>
       <x:c r="AB58" s="1" t="str">
-        <x:v>熱融着機　湖南</x:v>
+        <x:v>SEC機　湖南</x:v>
       </x:c>
       <x:c r="AC58" s="1" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="AD58" s="4" t="n">
-        <x:v>46225</x:v>
+        <x:v>46226</x:v>
       </x:c>
       <x:c r="AE58" s="4" t="n">
-        <x:v>46225</x:v>
+        <x:v>46226</x:v>
       </x:c>
       <x:c r="AF58" s="4" t="n">
-        <x:v>46225</x:v>
+        <x:v>46226</x:v>
       </x:c>
       <x:c r="AG58" s="4" t="str">
         <x:v/>
       </x:c>
       <x:c r="AH58" s="4" t="n">
-        <x:v>46224</x:v>
+        <x:v>46225</x:v>
       </x:c>
       <x:c r="AI58" s="4" t="n">
-        <x:v>46224</x:v>
+        <x:v>46225</x:v>
       </x:c>
       <x:c r="AJ58" s="1" t="str">
         <x:v>0:未完</x:v>
       </x:c>
       <x:c r="AK58" s="6" t="n">
-        <x:v>200.0000</x:v>
+        <x:v>10000.0000</x:v>
       </x:c>
       <x:c r="AL58" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -50922,7 +50922,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AO58" s="6" t="n">
-        <x:v>200.0000</x:v>
+        <x:v>10000.0000</x:v>
       </x:c>
       <x:c r="AP58" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -51309,22 +51309,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FN58" s="6" t="n">
-        <x:v>200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FO58" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FP58" s="8" t="n">
-        <x:v>0.1300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FQ58" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>10000.0000</x:v>
       </x:c>
       <x:c r="FR58" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FS58" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6.6700</x:v>
       </x:c>
       <x:c r="FT58" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -51770,16 +51770,16 @@
         <x:v>SEC</x:v>
       </x:c>
       <x:c r="G59" s="1" t="str">
-        <x:v>009</x:v>
+        <x:v>003</x:v>
       </x:c>
       <x:c r="H59" s="4" t="n">
-        <x:v>46209</x:v>
+        <x:v>46210</x:v>
       </x:c>
       <x:c r="I59" s="1" t="str">
-        <x:v>C7-16</x:v>
+        <x:v>C7-22</x:v>
       </x:c>
       <x:c r="J59" s="1" t="str">
-        <x:v>00081306</x:v>
+        <x:v>00081379</x:v>
       </x:c>
       <x:c r="K59" s="1" t="str">
         <x:v>6710</x:v>
@@ -51788,19 +51788,19 @@
         <x:v>6713</x:v>
       </x:c>
       <x:c r="M59" s="1" t="str">
-        <x:v>50080-AY0B- 870X200F-AGA1C</x:v>
+        <x:v>50080-AY0B- 680X200F-AGA1C</x:v>
       </x:c>
       <x:c r="N59" s="1" t="str">
         <x:v/>
       </x:c>
       <x:c r="O59" s="1" t="str">
-        <x:v>0R040-8Y0B- 870X200F-AGA1H</x:v>
+        <x:v>0R040-8Y0B- 680X200F-AGA1C</x:v>
       </x:c>
       <x:c r="P59" s="6" t="n">
-        <x:v>10000.0000</x:v>
+        <x:v>3200.0000</x:v>
       </x:c>
       <x:c r="Q59" s="8" t="n">
-        <x:v>20000.0000</x:v>
+        <x:v>6400.0000</x:v>
       </x:c>
       <x:c r="R59" s="1" t="str">
         <x:v>SEC</x:v>
@@ -51812,7 +51812,7 @@
         <x:v>自動車材料事業部</x:v>
       </x:c>
       <x:c r="U59" s="1" t="str">
-        <x:v>00075320</x:v>
+        <x:v>00075366</x:v>
       </x:c>
       <x:c r="V59" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -51824,43 +51824,43 @@
         <x:v>01</x:v>
       </x:c>
       <x:c r="Y59" s="6" t="n">
-        <x:v>2.0000</x:v>
+        <x:v>1.0000</x:v>
       </x:c>
       <x:c r="Z59" s="6" t="n">
         <x:v>1.0000</x:v>
       </x:c>
       <x:c r="AA59" s="4" t="n">
-        <x:v>46219</x:v>
+        <x:v>46227</x:v>
       </x:c>
       <x:c r="AB59" s="1" t="str">
         <x:v>SEC機　湖南</x:v>
       </x:c>
       <x:c r="AC59" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AD59" s="4" t="n">
-        <x:v>46225</x:v>
+        <x:v>46230</x:v>
       </x:c>
       <x:c r="AE59" s="4" t="n">
-        <x:v>46225</x:v>
+        <x:v>46230</x:v>
       </x:c>
       <x:c r="AF59" s="4" t="n">
-        <x:v>46225</x:v>
+        <x:v>46230</x:v>
       </x:c>
       <x:c r="AG59" s="4" t="str">
         <x:v/>
       </x:c>
       <x:c r="AH59" s="4" t="n">
-        <x:v>46219</x:v>
+        <x:v>46227</x:v>
       </x:c>
       <x:c r="AI59" s="4" t="n">
-        <x:v>46224</x:v>
+        <x:v>46228</x:v>
       </x:c>
       <x:c r="AJ59" s="1" t="str">
         <x:v>0:未完</x:v>
       </x:c>
       <x:c r="AK59" s="6" t="n">
-        <x:v>10000.0000</x:v>
+        <x:v>3200.0000</x:v>
       </x:c>
       <x:c r="AL59" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -51872,7 +51872,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AO59" s="6" t="n">
-        <x:v>10000.0000</x:v>
+        <x:v>3200.0000</x:v>
       </x:c>
       <x:c r="AP59" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -52214,13 +52214,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY59" s="6" t="n">
-        <x:v>1400.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EZ59" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FA59" s="8" t="n">
-        <x:v>0.9300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB59" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -52259,13 +52259,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FN59" s="6" t="n">
-        <x:v>8600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FO59" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FP59" s="8" t="n">
-        <x:v>5.7300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FQ59" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -52286,22 +52286,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FW59" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1200.0000</x:v>
       </x:c>
       <x:c r="FX59" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FY59" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.8000</x:v>
       </x:c>
       <x:c r="FZ59" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2000.0000</x:v>
       </x:c>
       <x:c r="GA59" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="GB59" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.3300</x:v>
       </x:c>
       <x:c r="GC59" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -52720,16 +52720,16 @@
         <x:v>SEC</x:v>
       </x:c>
       <x:c r="G60" s="1" t="str">
-        <x:v>014</x:v>
+        <x:v>007</x:v>
       </x:c>
       <x:c r="H60" s="4" t="n">
-        <x:v>46206</x:v>
+        <x:v>46210</x:v>
       </x:c>
       <x:c r="I60" s="1" t="str">
-        <x:v>C7-15</x:v>
+        <x:v>C7-21</x:v>
       </x:c>
       <x:c r="J60" s="1" t="str">
-        <x:v>00081267</x:v>
+        <x:v>00081378</x:v>
       </x:c>
       <x:c r="K60" s="1" t="str">
         <x:v>6710</x:v>
@@ -52738,19 +52738,19 @@
         <x:v>6713</x:v>
       </x:c>
       <x:c r="M60" s="1" t="str">
-        <x:v>50080-AY0B- 870X200F-ABG1C</x:v>
+        <x:v>50080-AY0B- 870X200F-AGA1C</x:v>
       </x:c>
       <x:c r="N60" s="1" t="str">
         <x:v/>
       </x:c>
       <x:c r="O60" s="1" t="str">
-        <x:v>0R040-8Y0B- 870X200F-ABG1C</x:v>
+        <x:v>0R040-8Y0B- 870X200F-AGA1H</x:v>
       </x:c>
       <x:c r="P60" s="6" t="n">
-        <x:v>10000.0000</x:v>
+        <x:v>3000.0000</x:v>
       </x:c>
       <x:c r="Q60" s="8" t="n">
-        <x:v>20000.0000</x:v>
+        <x:v>6000.0000</x:v>
       </x:c>
       <x:c r="R60" s="1" t="str">
         <x:v>SEC</x:v>
@@ -52762,7 +52762,7 @@
         <x:v>自動車材料事業部</x:v>
       </x:c>
       <x:c r="U60" s="1" t="str">
-        <x:v>00075237</x:v>
+        <x:v>00075340</x:v>
       </x:c>
       <x:c r="V60" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -52774,13 +52774,13 @@
         <x:v>01</x:v>
       </x:c>
       <x:c r="Y60" s="6" t="n">
-        <x:v>1.0000</x:v>
+        <x:v>2.0000</x:v>
       </x:c>
       <x:c r="Z60" s="6" t="n">
         <x:v>1.0000</x:v>
       </x:c>
       <x:c r="AA60" s="4" t="n">
-        <x:v>46220</x:v>
+        <x:v>46227</x:v>
       </x:c>
       <x:c r="AB60" s="1" t="str">
         <x:v>SEC機　湖南</x:v>
@@ -52789,28 +52789,28 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AD60" s="4" t="n">
-        <x:v>46226</x:v>
+        <x:v>46230</x:v>
       </x:c>
       <x:c r="AE60" s="4" t="n">
-        <x:v>46226</x:v>
+        <x:v>46230</x:v>
       </x:c>
       <x:c r="AF60" s="4" t="n">
-        <x:v>46226</x:v>
+        <x:v>46230</x:v>
       </x:c>
       <x:c r="AG60" s="4" t="str">
         <x:v/>
       </x:c>
       <x:c r="AH60" s="4" t="n">
-        <x:v>46225</x:v>
+        <x:v>46227</x:v>
       </x:c>
       <x:c r="AI60" s="4" t="n">
-        <x:v>46225</x:v>
+        <x:v>46227</x:v>
       </x:c>
       <x:c r="AJ60" s="1" t="str">
         <x:v>0:未完</x:v>
       </x:c>
       <x:c r="AK60" s="6" t="n">
-        <x:v>10000.0000</x:v>
+        <x:v>3000.0000</x:v>
       </x:c>
       <x:c r="AL60" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -52822,7 +52822,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AO60" s="6" t="n">
-        <x:v>10000.0000</x:v>
+        <x:v>3000.0000</x:v>
       </x:c>
       <x:c r="AP60" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -53218,13 +53218,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FQ60" s="6" t="n">
-        <x:v>10000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FR60" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FS60" s="8" t="n">
-        <x:v>6.6700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FT60" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -53236,13 +53236,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FW60" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3000.0000</x:v>
       </x:c>
       <x:c r="FX60" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FY60" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.0000</x:v>
       </x:c>
       <x:c r="FZ60" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -53670,7 +53670,7 @@
         <x:v>SEC</x:v>
       </x:c>
       <x:c r="G61" s="1" t="str">
-        <x:v>007</x:v>
+        <x:v>008</x:v>
       </x:c>
       <x:c r="H61" s="4" t="n">
         <x:v>46209</x:v>
@@ -53751,7 +53751,7 @@
         <x:v/>
       </x:c>
       <x:c r="AH61" s="4" t="n">
-        <x:v>46226</x:v>
+        <x:v>46224</x:v>
       </x:c>
       <x:c r="AI61" s="4" t="n">
         <x:v>46227</x:v>
@@ -54159,13 +54159,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FN61" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5800.0000</x:v>
       </x:c>
       <x:c r="FO61" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FP61" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3.8700</x:v>
       </x:c>
       <x:c r="FQ61" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -54186,13 +54186,13 @@
         <x:v>2.6700</x:v>
       </x:c>
       <x:c r="FW61" s="6" t="n">
-        <x:v>6000.0000</x:v>
+        <x:v>200.0000</x:v>
       </x:c>
       <x:c r="FX61" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FY61" s="8" t="n">
-        <x:v>4.0000</x:v>
+        <x:v>0.1300</x:v>
       </x:c>
       <x:c r="FZ61" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -54620,7 +54620,7 @@
         <x:v>SEC</x:v>
       </x:c>
       <x:c r="G62" s="1" t="str">
-        <x:v>004</x:v>
+        <x:v>005</x:v>
       </x:c>
       <x:c r="H62" s="4" t="n">
         <x:v>46209</x:v>
@@ -54701,10 +54701,10 @@
         <x:v/>
       </x:c>
       <x:c r="AH62" s="4" t="n">
-        <x:v>46227</x:v>
+        <x:v>46228</x:v>
       </x:c>
       <x:c r="AI62" s="4" t="n">
-        <x:v>46227</x:v>
+        <x:v>46228</x:v>
       </x:c>
       <x:c r="AJ62" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -55136,22 +55136,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FW62" s="6" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="FX62" s="8" t="n">
+        <x:v>25.0000</x:v>
+      </x:c>
+      <x:c r="FY62" s="8" t="n">
+        <x:v>0.0000</x:v>
+      </x:c>
+      <x:c r="FZ62" s="6" t="n">
         <x:v>1000.0000</x:v>
       </x:c>
-      <x:c r="FX62" s="8" t="n">
-        <x:v>25.0000</x:v>
-      </x:c>
-      <x:c r="FY62" s="8" t="n">
+      <x:c r="GA62" s="8" t="n">
+        <x:v>25.0000</x:v>
+      </x:c>
+      <x:c r="GB62" s="8" t="n">
         <x:v>0.6700</x:v>
-      </x:c>
-      <x:c r="FZ62" s="6" t="n">
-        <x:v>0.0000</x:v>
-      </x:c>
-      <x:c r="GA62" s="8" t="n">
-        <x:v>25.0000</x:v>
-      </x:c>
-      <x:c r="GB62" s="8" t="n">
-        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GC62" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -55663,13 +55663,13 @@
         <x:v>6000.0000</x:v>
       </x:c>
       <x:c r="AL63" s="6" t="n">
-        <x:v>3000.0000</x:v>
+        <x:v>4500.0000</x:v>
       </x:c>
       <x:c r="AM63" s="6" t="n">
-        <x:v>3000.0000</x:v>
+        <x:v>1500.0000</x:v>
       </x:c>
       <x:c r="AN63" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3300.0000</x:v>
       </x:c>
       <x:c r="AO63" s="6" t="n">
         <x:v>6000.0000</x:v>
@@ -58504,7 +58504,7 @@
         <x:v>46218</x:v>
       </x:c>
       <x:c r="AI66" s="4" t="n">
-        <x:v>46219</x:v>
+        <x:v>46218</x:v>
       </x:c>
       <x:c r="AJ66" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -58855,22 +58855,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV66" s="6" t="n">
-        <x:v>1800.0000</x:v>
+        <x:v>2700.0000</x:v>
       </x:c>
       <x:c r="EW66" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="EX66" s="8" t="n">
-        <x:v>3.1600</x:v>
+        <x:v>4.7400</x:v>
       </x:c>
       <x:c r="EY66" s="6" t="n">
-        <x:v>900.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EZ66" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="FA66" s="8" t="n">
-        <x:v>1.5800</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB66" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -60320,7 +60320,7 @@
         <x:v>接続</x:v>
       </x:c>
       <x:c r="G68" s="1" t="str">
-        <x:v>008</x:v>
+        <x:v>009</x:v>
       </x:c>
       <x:c r="H68" s="4" t="n">
         <x:v>46204</x:v>
@@ -60401,7 +60401,7 @@
         <x:v/>
       </x:c>
       <x:c r="AH68" s="4" t="n">
-        <x:v>46220</x:v>
+        <x:v>46219</x:v>
       </x:c>
       <x:c r="AI68" s="4" t="n">
         <x:v>46220</x:v>
@@ -60764,22 +60764,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY68" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1000.0000</x:v>
       </x:c>
       <x:c r="EZ68" s="8" t="n">
         <x:v>20.0000</x:v>
       </x:c>
       <x:c r="FA68" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.8300</x:v>
       </x:c>
       <x:c r="FB68" s="6" t="n">
-        <x:v>2000.0000</x:v>
+        <x:v>1000.0000</x:v>
       </x:c>
       <x:c r="FC68" s="8" t="n">
         <x:v>20.0000</x:v>
       </x:c>
       <x:c r="FD68" s="8" t="n">
-        <x:v>1.6700</x:v>
+        <x:v>0.8300</x:v>
       </x:c>
       <x:c r="FE68" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -61351,10 +61351,10 @@
         <x:v/>
       </x:c>
       <x:c r="AH69" s="4" t="n">
+        <x:v>46218</x:v>
+      </x:c>
+      <x:c r="AI69" s="4" t="n">
         <x:v>46219</x:v>
-      </x:c>
-      <x:c r="AI69" s="4" t="n">
-        <x:v>46220</x:v>
       </x:c>
       <x:c r="AJ69" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -61705,31 +61705,31 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV69" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>900.0000</x:v>
       </x:c>
       <x:c r="EW69" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="EX69" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.5800</x:v>
       </x:c>
       <x:c r="EY69" s="6" t="n">
-        <x:v>2100.0000</x:v>
+        <x:v>3000.0000</x:v>
       </x:c>
       <x:c r="EZ69" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="FA69" s="8" t="n">
-        <x:v>3.6800</x:v>
+        <x:v>5.2600</x:v>
       </x:c>
       <x:c r="FB69" s="6" t="n">
-        <x:v>1800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FC69" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="FD69" s="8" t="n">
-        <x:v>3.1600</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FE69" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -64201,10 +64201,10 @@
         <x:v/>
       </x:c>
       <x:c r="AH72" s="4" t="n">
-        <x:v>46227</x:v>
+        <x:v>46226</x:v>
       </x:c>
       <x:c r="AI72" s="4" t="n">
-        <x:v>46227</x:v>
+        <x:v>46226</x:v>
       </x:c>
       <x:c r="AJ72" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -64627,22 +64627,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FT72" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1470.0000</x:v>
       </x:c>
       <x:c r="FU72" s="8" t="n">
         <x:v>20.0000</x:v>
       </x:c>
       <x:c r="FV72" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.2300</x:v>
       </x:c>
       <x:c r="FW72" s="6" t="n">
-        <x:v>1470.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FX72" s="8" t="n">
         <x:v>20.0000</x:v>
       </x:c>
       <x:c r="FY72" s="8" t="n">
-        <x:v>1.2300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FZ72" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -66401,22 +66401,22 @@
         <x:v>1.0500</x:v>
       </x:c>
       <x:c r="ED74" s="7" t="n">
-        <x:v>19400.0000</x:v>
+        <x:v>13800.0000</x:v>
       </x:c>
       <x:c r="EE74" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="EF74" s="9" t="n">
-        <x:v>21.2800</x:v>
+        <x:v>17.3300</x:v>
       </x:c>
       <x:c r="EG74" s="7" t="n">
-        <x:v>14000.0000</x:v>
+        <x:v>15400.0000</x:v>
       </x:c>
       <x:c r="EH74" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="EI74" s="9" t="n">
-        <x:v>15.4500</x:v>
+        <x:v>16.0800</x:v>
       </x:c>
       <x:c r="EJ74" s="7" t="n">
         <x:v>0.0000</x:v>
@@ -66437,49 +66437,49 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP74" s="7" t="n">
-        <x:v>17900.0000</x:v>
+        <x:v>23700.0000</x:v>
       </x:c>
       <x:c r="EQ74" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="ER74" s="9" t="n">
-        <x:v>22.3800</x:v>
+        <x:v>27.4900</x:v>
       </x:c>
       <x:c r="ES74" s="7" t="n">
-        <x:v>4400.0000</x:v>
+        <x:v>5700.0000</x:v>
       </x:c>
       <x:c r="ET74" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="EU74" s="9" t="n">
-        <x:v>5.0600</x:v>
+        <x:v>5.7300</x:v>
       </x:c>
       <x:c r="EV74" s="7" t="n">
-        <x:v>10800.0000</x:v>
+        <x:v>15400.0000</x:v>
       </x:c>
       <x:c r="EW74" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="EX74" s="9" t="n">
-        <x:v>13.6000</x:v>
+        <x:v>19.8300</x:v>
       </x:c>
       <x:c r="EY74" s="7" t="n">
-        <x:v>17800.0000</x:v>
+        <x:v>14500.0000</x:v>
       </x:c>
       <x:c r="EZ74" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FA74" s="9" t="n">
-        <x:v>19.4500</x:v>
+        <x:v>16.4200</x:v>
       </x:c>
       <x:c r="FB74" s="7" t="n">
-        <x:v>12400.0000</x:v>
+        <x:v>16400.0000</x:v>
       </x:c>
       <x:c r="FC74" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FD74" s="9" t="n">
-        <x:v>12.8600</x:v>
+        <x:v>13.6900</x:v>
       </x:c>
       <x:c r="FE74" s="7" t="n">
         <x:v>0.0000</x:v>
@@ -66509,49 +66509,49 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FN74" s="7" t="n">
-        <x:v>17200.0000</x:v>
+        <x:v>16200.0000</x:v>
       </x:c>
       <x:c r="FO74" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FP74" s="9" t="n">
-        <x:v>14.5400</x:v>
+        <x:v>13.4400</x:v>
       </x:c>
       <x:c r="FQ74" s="7" t="n">
-        <x:v>16400.0000</x:v>
+        <x:v>17200.0000</x:v>
       </x:c>
       <x:c r="FR74" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FS74" s="9" t="n">
-        <x:v>13.2800</x:v>
+        <x:v>14.1100</x:v>
       </x:c>
       <x:c r="FT74" s="7" t="n">
-        <x:v>11200.0000</x:v>
+        <x:v>12270.0000</x:v>
       </x:c>
       <x:c r="FU74" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FV74" s="9" t="n">
-        <x:v>10.1100</x:v>
+        <x:v>10.9300</x:v>
       </x:c>
       <x:c r="FW74" s="7" t="n">
-        <x:v>19690.0000</x:v>
+        <x:v>11670.0000</x:v>
       </x:c>
       <x:c r="FX74" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FY74" s="9" t="n">
-        <x:v>16.4200</x:v>
+        <x:v>10.1900</x:v>
       </x:c>
       <x:c r="FZ74" s="7" t="n">
-        <x:v>13600.0000</x:v>
+        <x:v>12350.0000</x:v>
       </x:c>
       <x:c r="GA74" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="GB74" s="9" t="n">
-        <x:v>12.1400</x:v>
+        <x:v>11.2100</x:v>
       </x:c>
       <x:c r="GC74" s="7" t="n">
         <x:v>0.0000</x:v>
@@ -66563,13 +66563,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GF74" s="7" t="n">
-        <x:v>4350.0000</x:v>
+        <x:v>5350.0000</x:v>
       </x:c>
       <x:c r="GG74" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="GH74" s="9" t="n">
-        <x:v>4.4900</x:v>
+        <x:v>5.5300</x:v>
       </x:c>
       <x:c r="GI74" s="7" t="n">
         <x:v>0.0000</x:v>

--- a/.pm-ai-cache/network-source/task-input-newest.xlsx
+++ b/.pm-ai-cache/network-source/task-input-newest.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工程別生産計画問合せ問合せ" sheetId="1" r:id="Rc3dd8191257040d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工程別生産計画問合せ問合せ" sheetId="1" r:id="Rab6fe4967c004621"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3320,37 +3320,37 @@
         <x:v>スライス</x:v>
       </x:c>
       <x:c r="G8" s="1" t="str">
-        <x:v>001</x:v>
+        <x:v>011</x:v>
       </x:c>
       <x:c r="H8" s="4" t="n">
-        <x:v>46210</x:v>
+        <x:v>46209</x:v>
       </x:c>
       <x:c r="I8" s="1" t="str">
-        <x:v>T7-10</x:v>
+        <x:v>V7-9</x:v>
       </x:c>
       <x:c r="J8" s="1" t="str">
-        <x:v>00081375</x:v>
+        <x:v>00081331</x:v>
       </x:c>
       <x:c r="K8" s="1" t="str">
-        <x:v>6710</x:v>
+        <x:v>6780</x:v>
       </x:c>
       <x:c r="L8" s="1" t="str">
-        <x:v>6713</x:v>
+        <x:v>6783</x:v>
       </x:c>
       <x:c r="M8" s="1" t="str">
-        <x:v>30040-AG00-1030X200F-ABK0C</x:v>
+        <x:v>30030-AT60-1000X200F-A   C</x:v>
       </x:c>
       <x:c r="N8" s="1" t="str">
         <x:v/>
       </x:c>
       <x:c r="O8" s="1" t="str">
-        <x:v>30020-BG00-1030X200F-ABK0C</x:v>
+        <x:v>30015-BT60-1000X200F-A   C</x:v>
       </x:c>
       <x:c r="P8" s="6" t="n">
-        <x:v>600.0000</x:v>
+        <x:v>200.0000</x:v>
       </x:c>
       <x:c r="Q8" s="8" t="n">
-        <x:v>1200.0000</x:v>
+        <x:v>400.0000</x:v>
       </x:c>
       <x:c r="R8" s="1" t="str">
         <x:v>スライス</x:v>
@@ -3362,7 +3362,7 @@
         <x:v>自動車材料事業部</x:v>
       </x:c>
       <x:c r="U8" s="1" t="str">
-        <x:v>00075335</x:v>
+        <x:v>00075267</x:v>
       </x:c>
       <x:c r="V8" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -3380,7 +3380,7 @@
         <x:v>1.0000</x:v>
       </x:c>
       <x:c r="AA8" s="4" t="n">
-        <x:v>46219</x:v>
+        <x:v>46211</x:v>
       </x:c>
       <x:c r="AB8" s="1" t="str">
         <x:v>スライス機1　湖南</x:v>
@@ -3389,28 +3389,28 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AD8" s="4" t="n">
-        <x:v>46224</x:v>
+        <x:v>46217</x:v>
       </x:c>
       <x:c r="AE8" s="4" t="n">
-        <x:v>46224</x:v>
-      </x:c>
-      <x:c r="AF8" s="4" t="str">
-        <x:v/>
+        <x:v>46217</x:v>
+      </x:c>
+      <x:c r="AF8" s="4" t="n">
+        <x:v>46217</x:v>
       </x:c>
       <x:c r="AG8" s="4" t="str">
         <x:v/>
       </x:c>
       <x:c r="AH8" s="4" t="n">
-        <x:v>46220</x:v>
+        <x:v>46213</x:v>
       </x:c>
       <x:c r="AI8" s="4" t="n">
-        <x:v>46220</x:v>
+        <x:v>46213</x:v>
       </x:c>
       <x:c r="AJ8" s="1" t="str">
         <x:v>0:未完</x:v>
       </x:c>
       <x:c r="AK8" s="6" t="n">
-        <x:v>600.0000</x:v>
+        <x:v>200.0000</x:v>
       </x:c>
       <x:c r="AL8" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -3422,7 +3422,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AO8" s="6" t="n">
-        <x:v>600.0000</x:v>
+        <x:v>200.0000</x:v>
       </x:c>
       <x:c r="AP8" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -3710,13 +3710,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG8" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>200.0000</x:v>
       </x:c>
       <x:c r="EH8" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EI8" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.2100</x:v>
       </x:c>
       <x:c r="EJ8" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -3773,13 +3773,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB8" s="6" t="n">
-        <x:v>600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FC8" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FD8" s="8" t="n">
-        <x:v>0.6200</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FE8" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -4270,16 +4270,16 @@
         <x:v>スライス</x:v>
       </x:c>
       <x:c r="G9" s="1" t="str">
-        <x:v>001</x:v>
+        <x:v>021</x:v>
       </x:c>
       <x:c r="H9" s="4" t="n">
-        <x:v>46210</x:v>
+        <x:v>46190</x:v>
       </x:c>
       <x:c r="I9" s="1" t="str">
-        <x:v>T7-9</x:v>
+        <x:v>Y6-25</x:v>
       </x:c>
       <x:c r="J9" s="1" t="str">
-        <x:v>00081374</x:v>
+        <x:v>00080752</x:v>
       </x:c>
       <x:c r="K9" s="1" t="str">
         <x:v>6710</x:v>
@@ -4288,19 +4288,19 @@
         <x:v>6713</x:v>
       </x:c>
       <x:c r="M9" s="1" t="str">
-        <x:v>30040-AY00- 640X250F-A   C</x:v>
+        <x:v>30066-AY00- 640X200F-AGA0C</x:v>
       </x:c>
       <x:c r="N9" s="1" t="str">
         <x:v/>
       </x:c>
       <x:c r="O9" s="1" t="str">
-        <x:v>30020-BY00- 640X250F-A   C</x:v>
+        <x:v>30033-BY00- 640X200F-AGA0C</x:v>
       </x:c>
       <x:c r="P9" s="6" t="n">
-        <x:v>2750.0000</x:v>
+        <x:v>10000.0000</x:v>
       </x:c>
       <x:c r="Q9" s="8" t="n">
-        <x:v>5500.0000</x:v>
+        <x:v>20000.0000</x:v>
       </x:c>
       <x:c r="R9" s="1" t="str">
         <x:v>スライス</x:v>
@@ -4312,10 +4312,10 @@
         <x:v>自動車材料事業部</x:v>
       </x:c>
       <x:c r="U9" s="1" t="str">
-        <x:v>00075334</x:v>
+        <x:v>00075280</x:v>
       </x:c>
       <x:c r="V9" s="1" t="str">
-        <x:v>0:未完</x:v>
+        <x:v>1:完了</x:v>
       </x:c>
       <x:c r="W9" s="1" t="str">
         <x:v>0001</x:v>
@@ -4330,49 +4330,49 @@
         <x:v>1.0000</x:v>
       </x:c>
       <x:c r="AA9" s="4" t="n">
-        <x:v>46227</x:v>
+        <x:v>46210</x:v>
       </x:c>
       <x:c r="AB9" s="1" t="str">
         <x:v>スライス機1　湖南</x:v>
       </x:c>
       <x:c r="AC9" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AD9" s="4" t="n">
-        <x:v>46232</x:v>
+        <x:v>46217</x:v>
       </x:c>
       <x:c r="AE9" s="4" t="n">
-        <x:v>46232</x:v>
-      </x:c>
-      <x:c r="AF9" s="4" t="str">
-        <x:v/>
+        <x:v>46217</x:v>
+      </x:c>
+      <x:c r="AF9" s="4" t="n">
+        <x:v>46217</x:v>
       </x:c>
       <x:c r="AG9" s="4" t="str">
         <x:v/>
       </x:c>
       <x:c r="AH9" s="4" t="n">
-        <x:v>46230</x:v>
+        <x:v>46212</x:v>
       </x:c>
       <x:c r="AI9" s="4" t="n">
-        <x:v>46230</x:v>
+        <x:v>46213</x:v>
       </x:c>
       <x:c r="AJ9" s="1" t="str">
         <x:v>0:未完</x:v>
       </x:c>
       <x:c r="AK9" s="6" t="n">
-        <x:v>2750.0000</x:v>
+        <x:v>10000.0000</x:v>
       </x:c>
       <x:c r="AL9" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>9000.0000</x:v>
       </x:c>
       <x:c r="AM9" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1000.0000</x:v>
       </x:c>
       <x:c r="AN9" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>18000.0000</x:v>
       </x:c>
       <x:c r="AO9" s="6" t="n">
-        <x:v>2750.0000</x:v>
+        <x:v>10000.0000</x:v>
       </x:c>
       <x:c r="AP9" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -4651,22 +4651,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ED9" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>8000.0000</x:v>
       </x:c>
       <x:c r="EE9" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EF9" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>8.2700</x:v>
       </x:c>
       <x:c r="EG9" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2000.0000</x:v>
       </x:c>
       <x:c r="EH9" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EI9" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.0700</x:v>
       </x:c>
       <x:c r="EJ9" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -4813,13 +4813,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GF9" s="6" t="n">
-        <x:v>2750.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GG9" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="GH9" s="8" t="n">
-        <x:v>2.8400</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GI9" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -5220,37 +5220,37 @@
         <x:v>スライス</x:v>
       </x:c>
       <x:c r="G10" s="1" t="str">
-        <x:v>007</x:v>
+        <x:v>011</x:v>
       </x:c>
       <x:c r="H10" s="4" t="n">
-        <x:v>46209</x:v>
+        <x:v>46203</x:v>
       </x:c>
       <x:c r="I10" s="1" t="str">
-        <x:v>V7-9</x:v>
+        <x:v>V7-5</x:v>
       </x:c>
       <x:c r="J10" s="1" t="str">
-        <x:v>00081331</x:v>
+        <x:v>00081131</x:v>
       </x:c>
       <x:c r="K10" s="1" t="str">
-        <x:v>6780</x:v>
+        <x:v>6710</x:v>
       </x:c>
       <x:c r="L10" s="1" t="str">
-        <x:v>6783</x:v>
+        <x:v>6713</x:v>
       </x:c>
       <x:c r="M10" s="1" t="str">
-        <x:v>30030-AT60-1000X200F-A   C</x:v>
+        <x:v>30040-AG00-1030X200F-ABK0C</x:v>
       </x:c>
       <x:c r="N10" s="1" t="str">
         <x:v/>
       </x:c>
       <x:c r="O10" s="1" t="str">
-        <x:v>30015-BT60-1000X200F-A   C</x:v>
+        <x:v>30020-BG00-1030X200F-ABK0C</x:v>
       </x:c>
       <x:c r="P10" s="6" t="n">
-        <x:v>200.0000</x:v>
+        <x:v>1600.0000</x:v>
       </x:c>
       <x:c r="Q10" s="8" t="n">
-        <x:v>400.0000</x:v>
+        <x:v>3200.0000</x:v>
       </x:c>
       <x:c r="R10" s="1" t="str">
         <x:v>スライス</x:v>
@@ -5262,7 +5262,7 @@
         <x:v>自動車材料事業部</x:v>
       </x:c>
       <x:c r="U10" s="1" t="str">
-        <x:v>00075267</x:v>
+        <x:v>00075115</x:v>
       </x:c>
       <x:c r="V10" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -5280,7 +5280,7 @@
         <x:v>1.0000</x:v>
       </x:c>
       <x:c r="AA10" s="4" t="n">
-        <x:v>46211</x:v>
+        <x:v>46212</x:v>
       </x:c>
       <x:c r="AB10" s="1" t="str">
         <x:v>スライス機1　湖南</x:v>
@@ -5289,28 +5289,28 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AD10" s="4" t="n">
-        <x:v>46217</x:v>
+        <x:v>46218</x:v>
       </x:c>
       <x:c r="AE10" s="4" t="n">
-        <x:v>46217</x:v>
+        <x:v>46218</x:v>
       </x:c>
       <x:c r="AF10" s="4" t="n">
-        <x:v>46217</x:v>
+        <x:v>46218</x:v>
       </x:c>
       <x:c r="AG10" s="4" t="str">
         <x:v/>
       </x:c>
       <x:c r="AH10" s="4" t="n">
-        <x:v>46213</x:v>
+        <x:v>46216</x:v>
       </x:c>
       <x:c r="AI10" s="4" t="n">
-        <x:v>46213</x:v>
+        <x:v>46216</x:v>
       </x:c>
       <x:c r="AJ10" s="1" t="str">
         <x:v>0:未完</x:v>
       </x:c>
       <x:c r="AK10" s="6" t="n">
-        <x:v>200.0000</x:v>
+        <x:v>1600.0000</x:v>
       </x:c>
       <x:c r="AL10" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -5322,7 +5322,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AO10" s="6" t="n">
-        <x:v>200.0000</x:v>
+        <x:v>1600.0000</x:v>
       </x:c>
       <x:c r="AP10" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -5610,13 +5610,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG10" s="6" t="n">
-        <x:v>200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EH10" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EI10" s="8" t="n">
-        <x:v>0.2100</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ10" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -5637,13 +5637,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP10" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1600.0000</x:v>
       </x:c>
       <x:c r="EQ10" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="ER10" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.6500</x:v>
       </x:c>
       <x:c r="ES10" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -6170,16 +6170,16 @@
         <x:v>スライス</x:v>
       </x:c>
       <x:c r="G11" s="1" t="str">
-        <x:v>018</x:v>
+        <x:v>012</x:v>
       </x:c>
       <x:c r="H11" s="4" t="n">
-        <x:v>46190</x:v>
+        <x:v>46203</x:v>
       </x:c>
       <x:c r="I11" s="1" t="str">
-        <x:v>Y6-25</x:v>
+        <x:v>V7-6</x:v>
       </x:c>
       <x:c r="J11" s="1" t="str">
-        <x:v>00080752</x:v>
+        <x:v>00081132</x:v>
       </x:c>
       <x:c r="K11" s="1" t="str">
         <x:v>6710</x:v>
@@ -6188,19 +6188,19 @@
         <x:v>6713</x:v>
       </x:c>
       <x:c r="M11" s="1" t="str">
-        <x:v>30066-AY00- 640X200F-AGA0C</x:v>
+        <x:v>30040-AG00-1000X200F-A   C</x:v>
       </x:c>
       <x:c r="N11" s="1" t="str">
         <x:v/>
       </x:c>
       <x:c r="O11" s="1" t="str">
-        <x:v>30033-BY00- 640X200F-AGA0C</x:v>
+        <x:v>30020-BG00-1000X200F-A   C</x:v>
       </x:c>
       <x:c r="P11" s="6" t="n">
-        <x:v>10000.0000</x:v>
+        <x:v>200.0000</x:v>
       </x:c>
       <x:c r="Q11" s="8" t="n">
-        <x:v>20000.0000</x:v>
+        <x:v>400.0000</x:v>
       </x:c>
       <x:c r="R11" s="1" t="str">
         <x:v>スライス</x:v>
@@ -6212,10 +6212,10 @@
         <x:v>自動車材料事業部</x:v>
       </x:c>
       <x:c r="U11" s="1" t="str">
-        <x:v>00075280</x:v>
+        <x:v>00075116</x:v>
       </x:c>
       <x:c r="V11" s="1" t="str">
-        <x:v>1:完了</x:v>
+        <x:v>0:未完</x:v>
       </x:c>
       <x:c r="W11" s="1" t="str">
         <x:v>0001</x:v>
@@ -6230,7 +6230,7 @@
         <x:v>1.0000</x:v>
       </x:c>
       <x:c r="AA11" s="4" t="n">
-        <x:v>46210</x:v>
+        <x:v>46212</x:v>
       </x:c>
       <x:c r="AB11" s="1" t="str">
         <x:v>スライス機1　湖南</x:v>
@@ -6239,40 +6239,40 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AD11" s="4" t="n">
-        <x:v>46217</x:v>
+        <x:v>46218</x:v>
       </x:c>
       <x:c r="AE11" s="4" t="n">
-        <x:v>46217</x:v>
+        <x:v>46218</x:v>
       </x:c>
       <x:c r="AF11" s="4" t="n">
-        <x:v>46217</x:v>
+        <x:v>46218</x:v>
       </x:c>
       <x:c r="AG11" s="4" t="str">
         <x:v/>
       </x:c>
       <x:c r="AH11" s="4" t="n">
-        <x:v>46212</x:v>
+        <x:v>46217</x:v>
       </x:c>
       <x:c r="AI11" s="4" t="n">
-        <x:v>46213</x:v>
+        <x:v>46217</x:v>
       </x:c>
       <x:c r="AJ11" s="1" t="str">
         <x:v>0:未完</x:v>
       </x:c>
       <x:c r="AK11" s="6" t="n">
-        <x:v>10000.0000</x:v>
+        <x:v>200.0000</x:v>
       </x:c>
       <x:c r="AL11" s="6" t="n">
-        <x:v>9000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AM11" s="6" t="n">
-        <x:v>1000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AN11" s="6" t="n">
-        <x:v>15600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AO11" s="6" t="n">
-        <x:v>10000.0000</x:v>
+        <x:v>200.0000</x:v>
       </x:c>
       <x:c r="AP11" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -6551,22 +6551,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ED11" s="6" t="n">
-        <x:v>7800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EE11" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EF11" s="8" t="n">
-        <x:v>8.0600</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG11" s="6" t="n">
-        <x:v>2200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EH11" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EI11" s="8" t="n">
-        <x:v>2.2700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ11" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -6596,13 +6596,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES11" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>200.0000</x:v>
       </x:c>
       <x:c r="ET11" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EU11" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.2100</x:v>
       </x:c>
       <x:c r="EV11" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -7120,16 +7120,16 @@
         <x:v>スライス</x:v>
       </x:c>
       <x:c r="G12" s="1" t="str">
-        <x:v>011</x:v>
+        <x:v>013</x:v>
       </x:c>
       <x:c r="H12" s="4" t="n">
-        <x:v>46203</x:v>
+        <x:v>46202</x:v>
       </x:c>
       <x:c r="I12" s="1" t="str">
-        <x:v>V7-5</x:v>
+        <x:v>V7-1</x:v>
       </x:c>
       <x:c r="J12" s="1" t="str">
-        <x:v>00081131</x:v>
+        <x:v>00081084</x:v>
       </x:c>
       <x:c r="K12" s="1" t="str">
         <x:v>6710</x:v>
@@ -7138,22 +7138,22 @@
         <x:v>6713</x:v>
       </x:c>
       <x:c r="M12" s="1" t="str">
-        <x:v>30040-AG00-1030X200F-ABK0C</x:v>
+        <x:v>30060-AG00-1000X200F-A   C</x:v>
       </x:c>
       <x:c r="N12" s="1" t="str">
         <x:v/>
       </x:c>
       <x:c r="O12" s="1" t="str">
-        <x:v>30020-BG00-1030X200F-ABK0C</x:v>
+        <x:v>30030-BG00-1000X100F-A   C</x:v>
       </x:c>
       <x:c r="P12" s="6" t="n">
-        <x:v>1600.0000</x:v>
+        <x:v>3400.0000</x:v>
       </x:c>
       <x:c r="Q12" s="8" t="n">
-        <x:v>3200.0000</x:v>
+        <x:v>6800.0000</x:v>
       </x:c>
       <x:c r="R12" s="1" t="str">
-        <x:v>スライス</x:v>
+        <x:v>分割,スライス</x:v>
       </x:c>
       <x:c r="S12" s="1" t="str">
         <x:v>東レ株式会社</x:v>
@@ -7162,7 +7162,7 @@
         <x:v>自動車材料事業部</x:v>
       </x:c>
       <x:c r="U12" s="1" t="str">
-        <x:v>00075115</x:v>
+        <x:v>00075246</x:v>
       </x:c>
       <x:c r="V12" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -7210,7 +7210,7 @@
         <x:v>0:未完</x:v>
       </x:c>
       <x:c r="AK12" s="6" t="n">
-        <x:v>1600.0000</x:v>
+        <x:v>3400.0000</x:v>
       </x:c>
       <x:c r="AL12" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -7222,7 +7222,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AO12" s="6" t="n">
-        <x:v>1600.0000</x:v>
+        <x:v>3400.0000</x:v>
       </x:c>
       <x:c r="AP12" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -7537,13 +7537,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP12" s="6" t="n">
-        <x:v>1600.0000</x:v>
+        <x:v>3400.0000</x:v>
       </x:c>
       <x:c r="EQ12" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="ER12" s="8" t="n">
-        <x:v>1.6500</x:v>
+        <x:v>3.5200</x:v>
       </x:c>
       <x:c r="ES12" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -8070,16 +8070,16 @@
         <x:v>スライス</x:v>
       </x:c>
       <x:c r="G13" s="1" t="str">
-        <x:v>012</x:v>
+        <x:v>017</x:v>
       </x:c>
       <x:c r="H13" s="4" t="n">
-        <x:v>46203</x:v>
+        <x:v>46202</x:v>
       </x:c>
       <x:c r="I13" s="1" t="str">
-        <x:v>V7-6</x:v>
+        <x:v>V7-4</x:v>
       </x:c>
       <x:c r="J13" s="1" t="str">
-        <x:v>00081132</x:v>
+        <x:v>00081087</x:v>
       </x:c>
       <x:c r="K13" s="1" t="str">
         <x:v>6710</x:v>
@@ -8088,22 +8088,22 @@
         <x:v>6713</x:v>
       </x:c>
       <x:c r="M13" s="1" t="str">
-        <x:v>30040-AG00-1000X200F-A   C</x:v>
+        <x:v>50060-AM0C-1030X200F-ABK0C</x:v>
       </x:c>
       <x:c r="N13" s="1" t="str">
         <x:v/>
       </x:c>
       <x:c r="O13" s="1" t="str">
-        <x:v>30020-BG00-1000X200F-A   C</x:v>
+        <x:v>50030-BM0C-1030X100F-ABK0C</x:v>
       </x:c>
       <x:c r="P13" s="6" t="n">
-        <x:v>200.0000</x:v>
+        <x:v>800.0000</x:v>
       </x:c>
       <x:c r="Q13" s="8" t="n">
-        <x:v>400.0000</x:v>
+        <x:v>1600.0000</x:v>
       </x:c>
       <x:c r="R13" s="1" t="str">
-        <x:v>スライス</x:v>
+        <x:v>分割,スライス</x:v>
       </x:c>
       <x:c r="S13" s="1" t="str">
         <x:v>東レ株式会社</x:v>
@@ -8112,7 +8112,7 @@
         <x:v>自動車材料事業部</x:v>
       </x:c>
       <x:c r="U13" s="1" t="str">
-        <x:v>00075116</x:v>
+        <x:v>00075087</x:v>
       </x:c>
       <x:c r="V13" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -8151,16 +8151,16 @@
         <x:v/>
       </x:c>
       <x:c r="AH13" s="4" t="n">
-        <x:v>46217</x:v>
+        <x:v>46216</x:v>
       </x:c>
       <x:c r="AI13" s="4" t="n">
-        <x:v>46217</x:v>
+        <x:v>46216</x:v>
       </x:c>
       <x:c r="AJ13" s="1" t="str">
         <x:v>0:未完</x:v>
       </x:c>
       <x:c r="AK13" s="6" t="n">
-        <x:v>200.0000</x:v>
+        <x:v>800.0000</x:v>
       </x:c>
       <x:c r="AL13" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -8172,7 +8172,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AO13" s="6" t="n">
-        <x:v>200.0000</x:v>
+        <x:v>800.0000</x:v>
       </x:c>
       <x:c r="AP13" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -8487,22 +8487,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP13" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>800.0000</x:v>
       </x:c>
       <x:c r="EQ13" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="ER13" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.8300</x:v>
       </x:c>
       <x:c r="ES13" s="6" t="n">
-        <x:v>200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ET13" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EU13" s="8" t="n">
-        <x:v>0.2100</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV13" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -9014,13 +9014,13 @@
         <x:v>スライス機1　湖南</x:v>
       </x:c>
       <x:c r="E14" s="1" t="str">
-        <x:v>0001</x:v>
+        <x:v>0011</x:v>
       </x:c>
       <x:c r="F14" s="1" t="str">
-        <x:v>スライス</x:v>
+        <x:v>分割</x:v>
       </x:c>
       <x:c r="G14" s="1" t="str">
-        <x:v>013</x:v>
+        <x:v>009</x:v>
       </x:c>
       <x:c r="H14" s="4" t="n">
         <x:v>46202</x:v>
@@ -9062,13 +9062,13 @@
         <x:v>自動車材料事業部</x:v>
       </x:c>
       <x:c r="U14" s="1" t="str">
-        <x:v>00075246</x:v>
+        <x:v>00075245</x:v>
       </x:c>
       <x:c r="V14" s="1" t="str">
         <x:v>0:未完</x:v>
       </x:c>
       <x:c r="W14" s="1" t="str">
-        <x:v>0001</x:v>
+        <x:v>0011</x:v>
       </x:c>
       <x:c r="X14" s="1" t="str">
         <x:v>01</x:v>
@@ -9110,7 +9110,7 @@
         <x:v>0:未完</x:v>
       </x:c>
       <x:c r="AK14" s="6" t="n">
-        <x:v>3400.0000</x:v>
+        <x:v>6800.0000</x:v>
       </x:c>
       <x:c r="AL14" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -9122,7 +9122,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AO14" s="6" t="n">
-        <x:v>3400.0000</x:v>
+        <x:v>6800.0000</x:v>
       </x:c>
       <x:c r="AP14" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -9134,7 +9134,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AS14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="AT14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9143,7 +9143,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AV14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="AW14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9152,7 +9152,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AY14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="AZ14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9161,7 +9161,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BB14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="BC14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9170,7 +9170,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BE14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="BF14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9179,7 +9179,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BH14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="BI14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9188,7 +9188,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BK14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="BL14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9197,7 +9197,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BN14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="BO14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9206,7 +9206,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BQ14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="BR14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9215,7 +9215,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BT14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="BU14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9224,7 +9224,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BW14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="BX14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9233,7 +9233,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BZ14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="CA14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9242,7 +9242,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CC14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="CD14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9251,7 +9251,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CF14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="CG14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9260,7 +9260,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CI14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="CJ14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9269,7 +9269,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CL14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="CM14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9278,7 +9278,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CO14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="CP14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9287,7 +9287,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CR14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="CS14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9296,7 +9296,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CU14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="CV14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9305,7 +9305,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CX14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="CY14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9314,7 +9314,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DA14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="DB14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9323,7 +9323,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DD14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="DE14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9332,7 +9332,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DG14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="DH14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9341,7 +9341,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DJ14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="DK14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9350,7 +9350,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DM14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="DN14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9359,7 +9359,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DP14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="DQ14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9368,7 +9368,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DS14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="DT14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9377,7 +9377,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DV14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="DW14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9386,7 +9386,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DY14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="DZ14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9395,7 +9395,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EB14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EC14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9404,7 +9404,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EE14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EF14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9413,7 +9413,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EH14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EI14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9422,7 +9422,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EK14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EL14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9431,25 +9431,25 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EO14" s="8" t="n">
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP14" s="6" t="n">
-        <x:v>3400.0000</x:v>
+        <x:v>6800.0000</x:v>
       </x:c>
       <x:c r="EQ14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="ER14" s="8" t="n">
-        <x:v>3.5200</x:v>
+        <x:v>7.5600</x:v>
       </x:c>
       <x:c r="ES14" s="6" t="n">
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ET14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EU14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9458,7 +9458,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EW14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EX14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9467,7 +9467,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EZ14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FA14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9476,7 +9476,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FC14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FD14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9485,7 +9485,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FF14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FG14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9494,7 +9494,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FI14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FJ14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9503,7 +9503,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FL14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FM14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9512,7 +9512,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FO14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FP14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9521,7 +9521,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FR14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FS14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9530,7 +9530,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FU14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FV14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9539,7 +9539,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FX14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FY14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9548,7 +9548,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GA14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="GB14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9557,7 +9557,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GD14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="GE14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9566,7 +9566,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GG14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="GH14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9575,7 +9575,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GJ14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="GK14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9584,7 +9584,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GM14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="GN14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9593,7 +9593,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GP14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="GQ14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9602,7 +9602,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GS14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="GT14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9611,7 +9611,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GV14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="GW14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9620,7 +9620,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GY14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="GZ14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9629,7 +9629,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HB14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="HC14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9638,7 +9638,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HE14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="HF14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9647,7 +9647,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HH14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="HI14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9656,7 +9656,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HK14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="HL14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9665,7 +9665,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HN14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="HO14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9674,7 +9674,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HQ14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="HR14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9683,7 +9683,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HT14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="HU14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9692,7 +9692,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HW14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="HX14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9701,7 +9701,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HZ14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="IA14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9710,7 +9710,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="IC14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="ID14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9719,7 +9719,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="IF14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="IG14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9728,7 +9728,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="II14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="IJ14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9737,7 +9737,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="IL14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="IM14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9746,7 +9746,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="IO14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="IP14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9755,7 +9755,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="IR14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="IS14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9764,7 +9764,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="IU14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="IV14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9773,7 +9773,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="IX14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="IY14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9782,7 +9782,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JA14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="JB14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9791,7 +9791,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JD14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="JE14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9800,7 +9800,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JG14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="JH14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9809,7 +9809,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JJ14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="JK14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9818,7 +9818,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JM14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="JN14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9827,7 +9827,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JP14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="JQ14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9836,7 +9836,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JS14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="JT14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9845,7 +9845,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JV14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="JW14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9854,7 +9854,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JY14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="JZ14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9863,7 +9863,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KB14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="KC14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9872,7 +9872,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KE14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="KF14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9881,7 +9881,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KH14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="KI14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9890,7 +9890,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KK14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="KL14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9899,7 +9899,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KN14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="KO14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9908,7 +9908,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KQ14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="KR14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9917,7 +9917,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KT14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="KU14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9926,7 +9926,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KW14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="KX14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9935,7 +9935,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KZ14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="LA14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9944,7 +9944,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="LC14" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="LD14" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -9964,13 +9964,13 @@
         <x:v>スライス機1　湖南</x:v>
       </x:c>
       <x:c r="E15" s="1" t="str">
-        <x:v>0001</x:v>
+        <x:v>0011</x:v>
       </x:c>
       <x:c r="F15" s="1" t="str">
-        <x:v>スライス</x:v>
+        <x:v>分割</x:v>
       </x:c>
       <x:c r="G15" s="1" t="str">
-        <x:v>017</x:v>
+        <x:v>010</x:v>
       </x:c>
       <x:c r="H15" s="4" t="n">
         <x:v>46202</x:v>
@@ -10012,13 +10012,13 @@
         <x:v>自動車材料事業部</x:v>
       </x:c>
       <x:c r="U15" s="1" t="str">
-        <x:v>00075087</x:v>
+        <x:v>00075086</x:v>
       </x:c>
       <x:c r="V15" s="1" t="str">
         <x:v>0:未完</x:v>
       </x:c>
       <x:c r="W15" s="1" t="str">
-        <x:v>0001</x:v>
+        <x:v>0011</x:v>
       </x:c>
       <x:c r="X15" s="1" t="str">
         <x:v>01</x:v>
@@ -10084,7 +10084,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AS15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="AT15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10093,7 +10093,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AV15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="AW15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10102,7 +10102,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AY15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="AZ15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10111,7 +10111,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BB15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="BC15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10120,7 +10120,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BE15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="BF15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10129,7 +10129,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BH15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="BI15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10138,7 +10138,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BK15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="BL15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10147,7 +10147,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BN15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="BO15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10156,7 +10156,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BQ15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="BR15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10165,7 +10165,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BT15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="BU15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10174,7 +10174,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BW15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="BX15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10183,7 +10183,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BZ15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="CA15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10192,7 +10192,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CC15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="CD15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10201,7 +10201,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CF15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="CG15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10210,7 +10210,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CI15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="CJ15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10219,7 +10219,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CL15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="CM15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10228,7 +10228,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CO15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="CP15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10237,7 +10237,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CR15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="CS15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10246,7 +10246,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CU15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="CV15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10255,7 +10255,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CX15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="CY15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10264,7 +10264,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DA15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="DB15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10273,7 +10273,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DD15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="DE15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10282,7 +10282,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DG15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="DH15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10291,7 +10291,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DJ15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="DK15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10300,7 +10300,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DM15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="DN15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10309,7 +10309,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DP15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="DQ15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10318,7 +10318,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DS15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="DT15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10327,7 +10327,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DV15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="DW15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10336,7 +10336,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DY15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="DZ15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10345,7 +10345,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EB15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EC15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10354,7 +10354,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EE15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EF15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10363,7 +10363,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EH15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EI15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10372,7 +10372,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EK15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EL15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10381,7 +10381,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EO15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10390,16 +10390,16 @@
         <x:v>800.0000</x:v>
       </x:c>
       <x:c r="EQ15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="ER15" s="8" t="n">
-        <x:v>0.8300</x:v>
+        <x:v>0.8900</x:v>
       </x:c>
       <x:c r="ES15" s="6" t="n">
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ET15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EU15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10408,7 +10408,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EW15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EX15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10417,7 +10417,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EZ15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FA15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10426,7 +10426,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FC15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FD15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10435,7 +10435,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FF15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FG15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10444,7 +10444,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FI15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FJ15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10453,7 +10453,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FL15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FM15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10462,7 +10462,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FO15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FP15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10471,7 +10471,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FR15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FS15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10480,7 +10480,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FU15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FV15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10489,7 +10489,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FX15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FY15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10498,7 +10498,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GA15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="GB15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10507,7 +10507,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GD15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="GE15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10516,7 +10516,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GG15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="GH15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10525,7 +10525,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GJ15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="GK15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10534,7 +10534,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GM15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="GN15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10543,7 +10543,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GP15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="GQ15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10552,7 +10552,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GS15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="GT15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10561,7 +10561,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GV15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="GW15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10570,7 +10570,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GY15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="GZ15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10579,7 +10579,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HB15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="HC15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10588,7 +10588,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HE15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="HF15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10597,7 +10597,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HH15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="HI15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10606,7 +10606,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HK15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="HL15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10615,7 +10615,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HN15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="HO15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10624,7 +10624,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HQ15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="HR15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10633,7 +10633,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HT15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="HU15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10642,7 +10642,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HW15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="HX15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10651,7 +10651,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HZ15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="IA15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10660,7 +10660,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="IC15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="ID15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10669,7 +10669,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="IF15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="IG15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10678,7 +10678,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="II15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="IJ15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10687,7 +10687,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="IL15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="IM15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10696,7 +10696,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="IO15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="IP15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10705,7 +10705,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="IR15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="IS15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10714,7 +10714,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="IU15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="IV15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10723,7 +10723,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="IX15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="IY15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10732,7 +10732,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JA15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="JB15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10741,7 +10741,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JD15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="JE15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10750,7 +10750,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JG15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="JH15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10759,7 +10759,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JJ15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="JK15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10768,7 +10768,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JM15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="JN15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10777,7 +10777,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JP15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="JQ15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10786,7 +10786,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JS15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="JT15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10795,7 +10795,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JV15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="JW15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10804,7 +10804,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JY15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="JZ15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10813,7 +10813,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KB15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="KC15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10822,7 +10822,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KE15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="KF15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10831,7 +10831,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KH15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="KI15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10840,7 +10840,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KK15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="KL15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10849,7 +10849,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KN15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="KO15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10858,7 +10858,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KQ15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="KR15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10867,7 +10867,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KT15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="KU15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10876,7 +10876,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KW15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="KX15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10885,7 +10885,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KZ15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="LA15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10894,7 +10894,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="LC15" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="LD15" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -10914,22 +10914,22 @@
         <x:v>スライス機1　湖南</x:v>
       </x:c>
       <x:c r="E16" s="1" t="str">
-        <x:v>0011</x:v>
+        <x:v>0001</x:v>
       </x:c>
       <x:c r="F16" s="1" t="str">
-        <x:v>分割</x:v>
+        <x:v>スライス</x:v>
       </x:c>
       <x:c r="G16" s="1" t="str">
-        <x:v>009</x:v>
+        <x:v>015</x:v>
       </x:c>
       <x:c r="H16" s="4" t="n">
-        <x:v>46202</x:v>
+        <x:v>46203</x:v>
       </x:c>
       <x:c r="I16" s="1" t="str">
-        <x:v>V7-1</x:v>
+        <x:v>V7-8</x:v>
       </x:c>
       <x:c r="J16" s="1" t="str">
-        <x:v>00081084</x:v>
+        <x:v>00081134</x:v>
       </x:c>
       <x:c r="K16" s="1" t="str">
         <x:v>6710</x:v>
@@ -10938,19 +10938,19 @@
         <x:v>6713</x:v>
       </x:c>
       <x:c r="M16" s="1" t="str">
-        <x:v>30060-AG00-1000X200F-A   C</x:v>
+        <x:v>30060-AG00-1000X200F-ABK0C</x:v>
       </x:c>
       <x:c r="N16" s="1" t="str">
         <x:v/>
       </x:c>
       <x:c r="O16" s="1" t="str">
-        <x:v>30030-BG00-1000X100F-A   C</x:v>
+        <x:v>30030-BG00-1000X100F-ABK0C</x:v>
       </x:c>
       <x:c r="P16" s="6" t="n">
-        <x:v>3400.0000</x:v>
+        <x:v>800.0000</x:v>
       </x:c>
       <x:c r="Q16" s="8" t="n">
-        <x:v>6800.0000</x:v>
+        <x:v>1600.0000</x:v>
       </x:c>
       <x:c r="R16" s="1" t="str">
         <x:v>分割,スライス</x:v>
@@ -10962,13 +10962,13 @@
         <x:v>自動車材料事業部</x:v>
       </x:c>
       <x:c r="U16" s="1" t="str">
-        <x:v>00075245</x:v>
+        <x:v>00075118</x:v>
       </x:c>
       <x:c r="V16" s="1" t="str">
         <x:v>0:未完</x:v>
       </x:c>
       <x:c r="W16" s="1" t="str">
-        <x:v>0011</x:v>
+        <x:v>0001</x:v>
       </x:c>
       <x:c r="X16" s="1" t="str">
         <x:v>01</x:v>
@@ -10989,28 +10989,28 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AD16" s="4" t="n">
-        <x:v>46218</x:v>
+        <x:v>46219</x:v>
       </x:c>
       <x:c r="AE16" s="4" t="n">
-        <x:v>46218</x:v>
+        <x:v>46219</x:v>
       </x:c>
       <x:c r="AF16" s="4" t="n">
-        <x:v>46218</x:v>
+        <x:v>46219</x:v>
       </x:c>
       <x:c r="AG16" s="4" t="str">
         <x:v/>
       </x:c>
       <x:c r="AH16" s="4" t="n">
-        <x:v>46216</x:v>
+        <x:v>46217</x:v>
       </x:c>
       <x:c r="AI16" s="4" t="n">
-        <x:v>46216</x:v>
+        <x:v>46217</x:v>
       </x:c>
       <x:c r="AJ16" s="1" t="str">
         <x:v>0:未完</x:v>
       </x:c>
       <x:c r="AK16" s="6" t="n">
-        <x:v>6800.0000</x:v>
+        <x:v>800.0000</x:v>
       </x:c>
       <x:c r="AL16" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -11022,7 +11022,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AO16" s="6" t="n">
-        <x:v>6800.0000</x:v>
+        <x:v>800.0000</x:v>
       </x:c>
       <x:c r="AP16" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -11034,7 +11034,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AS16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="AT16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11043,7 +11043,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AV16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="AW16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11052,7 +11052,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AY16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="AZ16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11061,7 +11061,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BB16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="BC16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11070,7 +11070,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BE16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="BF16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11079,7 +11079,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BH16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="BI16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11088,7 +11088,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BK16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="BL16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11097,7 +11097,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BN16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="BO16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11106,7 +11106,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BQ16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="BR16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11115,7 +11115,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BT16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="BU16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11124,7 +11124,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BW16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="BX16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11133,7 +11133,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BZ16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="CA16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11142,7 +11142,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CC16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="CD16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11151,7 +11151,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CF16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="CG16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11160,7 +11160,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CI16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="CJ16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11169,7 +11169,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CL16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="CM16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11178,7 +11178,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CO16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="CP16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11187,7 +11187,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CR16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="CS16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11196,7 +11196,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CU16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="CV16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11205,7 +11205,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CX16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="CY16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11214,7 +11214,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DA16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="DB16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11223,7 +11223,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DD16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="DE16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11232,7 +11232,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DG16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="DH16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11241,7 +11241,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DJ16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="DK16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11250,7 +11250,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DM16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="DN16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11259,7 +11259,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DP16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="DQ16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11268,7 +11268,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DS16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="DT16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11277,7 +11277,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DV16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="DW16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11286,7 +11286,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DY16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="DZ16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11295,7 +11295,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EB16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EC16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11304,7 +11304,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EE16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EF16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11313,7 +11313,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EH16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EI16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11322,7 +11322,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EK16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EL16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11331,34 +11331,34 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EO16" s="8" t="n">
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP16" s="6" t="n">
-        <x:v>6800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EQ16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="ER16" s="8" t="n">
-        <x:v>7.5600</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES16" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>800.0000</x:v>
       </x:c>
       <x:c r="ET16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EU16" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.8300</x:v>
       </x:c>
       <x:c r="EV16" s="6" t="n">
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EW16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EX16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11367,7 +11367,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EZ16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FA16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11376,7 +11376,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FC16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FD16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11385,7 +11385,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FF16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FG16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11394,7 +11394,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FI16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FJ16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11403,7 +11403,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FL16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FM16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11412,7 +11412,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FO16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FP16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11421,7 +11421,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FR16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FS16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11430,7 +11430,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FU16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FV16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11439,7 +11439,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FX16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FY16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11448,7 +11448,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GA16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="GB16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11457,7 +11457,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GD16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="GE16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11466,7 +11466,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GG16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="GH16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11475,7 +11475,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GJ16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="GK16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11484,7 +11484,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GM16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="GN16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11493,7 +11493,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GP16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="GQ16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11502,7 +11502,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GS16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="GT16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11511,7 +11511,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GV16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="GW16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11520,7 +11520,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GY16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="GZ16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11529,7 +11529,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HB16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="HC16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11538,7 +11538,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HE16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="HF16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11547,7 +11547,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HH16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="HI16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11556,7 +11556,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HK16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="HL16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11565,7 +11565,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HN16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="HO16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11574,7 +11574,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HQ16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="HR16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11583,7 +11583,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HT16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="HU16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11592,7 +11592,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HW16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="HX16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11601,7 +11601,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HZ16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="IA16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11610,7 +11610,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="IC16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="ID16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11619,7 +11619,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="IF16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="IG16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11628,7 +11628,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="II16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="IJ16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11637,7 +11637,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="IL16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="IM16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11646,7 +11646,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="IO16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="IP16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11655,7 +11655,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="IR16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="IS16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11664,7 +11664,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="IU16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="IV16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11673,7 +11673,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="IX16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="IY16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11682,7 +11682,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JA16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="JB16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11691,7 +11691,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JD16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="JE16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11700,7 +11700,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JG16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="JH16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11709,7 +11709,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JJ16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="JK16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11718,7 +11718,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JM16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="JN16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11727,7 +11727,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JP16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="JQ16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11736,7 +11736,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JS16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="JT16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11745,7 +11745,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JV16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="JW16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11754,7 +11754,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JY16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="JZ16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11763,7 +11763,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KB16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="KC16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11772,7 +11772,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KE16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="KF16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11781,7 +11781,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KH16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="KI16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11790,7 +11790,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KK16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="KL16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11799,7 +11799,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KN16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="KO16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11808,7 +11808,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KQ16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="KR16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11817,7 +11817,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KT16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="KU16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11826,7 +11826,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KW16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="KX16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11835,7 +11835,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KZ16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="LA16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11844,7 +11844,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="LC16" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="LD16" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11864,43 +11864,43 @@
         <x:v>スライス機1　湖南</x:v>
       </x:c>
       <x:c r="E17" s="1" t="str">
-        <x:v>0011</x:v>
+        <x:v>0001</x:v>
       </x:c>
       <x:c r="F17" s="1" t="str">
-        <x:v>分割</x:v>
+        <x:v>スライス</x:v>
       </x:c>
       <x:c r="G17" s="1" t="str">
-        <x:v>010</x:v>
+        <x:v>017</x:v>
       </x:c>
       <x:c r="H17" s="4" t="n">
-        <x:v>46202</x:v>
+        <x:v>46209</x:v>
       </x:c>
       <x:c r="I17" s="1" t="str">
-        <x:v>V7-4</x:v>
+        <x:v>V7-11</x:v>
       </x:c>
       <x:c r="J17" s="1" t="str">
-        <x:v>00081087</x:v>
+        <x:v>00081333</x:v>
       </x:c>
       <x:c r="K17" s="1" t="str">
-        <x:v>6710</x:v>
+        <x:v>6780</x:v>
       </x:c>
       <x:c r="L17" s="1" t="str">
-        <x:v>6713</x:v>
+        <x:v>6783</x:v>
       </x:c>
       <x:c r="M17" s="1" t="str">
-        <x:v>50060-AM0C-1030X200F-ABK0C</x:v>
+        <x:v>30050-AS60-1000X200F-A   C</x:v>
       </x:c>
       <x:c r="N17" s="1" t="str">
         <x:v/>
       </x:c>
       <x:c r="O17" s="1" t="str">
-        <x:v>50030-BM0C-1030X100F-ABK0C</x:v>
+        <x:v>30025-BS60-1000X200F-A   C</x:v>
       </x:c>
       <x:c r="P17" s="6" t="n">
-        <x:v>800.0000</x:v>
+        <x:v>200.0000</x:v>
       </x:c>
       <x:c r="Q17" s="8" t="n">
-        <x:v>1600.0000</x:v>
+        <x:v>400.0000</x:v>
       </x:c>
       <x:c r="R17" s="1" t="str">
         <x:v>分割,スライス</x:v>
@@ -11912,13 +11912,13 @@
         <x:v>自動車材料事業部</x:v>
       </x:c>
       <x:c r="U17" s="1" t="str">
-        <x:v>00075086</x:v>
+        <x:v>00075275</x:v>
       </x:c>
       <x:c r="V17" s="1" t="str">
         <x:v>0:未完</x:v>
       </x:c>
       <x:c r="W17" s="1" t="str">
-        <x:v>0011</x:v>
+        <x:v>0001</x:v>
       </x:c>
       <x:c r="X17" s="1" t="str">
         <x:v>01</x:v>
@@ -11930,7 +11930,7 @@
         <x:v>1.0000</x:v>
       </x:c>
       <x:c r="AA17" s="4" t="n">
-        <x:v>46212</x:v>
+        <x:v>46213</x:v>
       </x:c>
       <x:c r="AB17" s="1" t="str">
         <x:v>スライス機1　湖南</x:v>
@@ -11939,28 +11939,28 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AD17" s="4" t="n">
-        <x:v>46218</x:v>
+        <x:v>46219</x:v>
       </x:c>
       <x:c r="AE17" s="4" t="n">
-        <x:v>46218</x:v>
+        <x:v>46219</x:v>
       </x:c>
       <x:c r="AF17" s="4" t="n">
-        <x:v>46218</x:v>
+        <x:v>46219</x:v>
       </x:c>
       <x:c r="AG17" s="4" t="str">
         <x:v/>
       </x:c>
       <x:c r="AH17" s="4" t="n">
-        <x:v>46216</x:v>
+        <x:v>46217</x:v>
       </x:c>
       <x:c r="AI17" s="4" t="n">
-        <x:v>46216</x:v>
+        <x:v>46217</x:v>
       </x:c>
       <x:c r="AJ17" s="1" t="str">
         <x:v>0:未完</x:v>
       </x:c>
       <x:c r="AK17" s="6" t="n">
-        <x:v>800.0000</x:v>
+        <x:v>200.0000</x:v>
       </x:c>
       <x:c r="AL17" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -11972,7 +11972,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AO17" s="6" t="n">
-        <x:v>800.0000</x:v>
+        <x:v>200.0000</x:v>
       </x:c>
       <x:c r="AP17" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -11984,7 +11984,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AS17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="AT17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -11993,7 +11993,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AV17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="AW17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12002,7 +12002,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AY17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="AZ17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12011,7 +12011,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BB17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="BC17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12020,7 +12020,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BE17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="BF17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12029,7 +12029,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BH17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="BI17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12038,7 +12038,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BK17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="BL17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12047,7 +12047,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BN17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="BO17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12056,7 +12056,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BQ17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="BR17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12065,7 +12065,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BT17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="BU17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12074,7 +12074,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BW17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="BX17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12083,7 +12083,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BZ17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="CA17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12092,7 +12092,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CC17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="CD17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12101,7 +12101,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CF17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="CG17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12110,7 +12110,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CI17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="CJ17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12119,7 +12119,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CL17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="CM17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12128,7 +12128,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CO17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="CP17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12137,7 +12137,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CR17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="CS17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12146,7 +12146,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CU17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="CV17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12155,7 +12155,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CX17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="CY17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12164,7 +12164,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DA17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="DB17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12173,7 +12173,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DD17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="DE17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12182,7 +12182,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DG17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="DH17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12191,7 +12191,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DJ17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="DK17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12200,7 +12200,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DM17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="DN17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12209,7 +12209,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DP17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="DQ17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12218,7 +12218,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DS17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="DT17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12227,7 +12227,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DV17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="DW17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12236,7 +12236,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DY17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="DZ17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12245,7 +12245,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EB17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EC17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12254,7 +12254,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EE17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EF17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12263,7 +12263,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EH17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EI17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12272,7 +12272,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EK17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EL17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12281,34 +12281,34 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EO17" s="8" t="n">
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP17" s="6" t="n">
-        <x:v>800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EQ17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="ER17" s="8" t="n">
-        <x:v>0.8900</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES17" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>200.0000</x:v>
       </x:c>
       <x:c r="ET17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EU17" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.2100</x:v>
       </x:c>
       <x:c r="EV17" s="6" t="n">
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EW17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EX17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12317,7 +12317,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EZ17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FA17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12326,7 +12326,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FC17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FD17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12335,7 +12335,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FF17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FG17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12344,7 +12344,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FI17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FJ17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12353,7 +12353,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FL17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FM17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12362,7 +12362,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FO17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FP17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12371,7 +12371,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FR17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FS17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12380,7 +12380,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FU17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FV17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12389,7 +12389,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FX17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FY17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12398,7 +12398,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GA17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="GB17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12407,7 +12407,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GD17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="GE17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12416,7 +12416,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GG17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="GH17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12425,7 +12425,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GJ17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="GK17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12434,7 +12434,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GM17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="GN17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12443,7 +12443,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GP17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="GQ17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12452,7 +12452,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GS17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="GT17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12461,7 +12461,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GV17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="GW17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12470,7 +12470,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GY17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="GZ17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12479,7 +12479,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HB17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="HC17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12488,7 +12488,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HE17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="HF17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12497,7 +12497,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HH17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="HI17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12506,7 +12506,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HK17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="HL17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12515,7 +12515,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HN17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="HO17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12524,7 +12524,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HQ17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="HR17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12533,7 +12533,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HT17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="HU17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12542,7 +12542,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HW17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="HX17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12551,7 +12551,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HZ17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="IA17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12560,7 +12560,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="IC17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="ID17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12569,7 +12569,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="IF17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="IG17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12578,7 +12578,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="II17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="IJ17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12587,7 +12587,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="IL17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="IM17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12596,7 +12596,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="IO17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="IP17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12605,7 +12605,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="IR17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="IS17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12614,7 +12614,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="IU17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="IV17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12623,7 +12623,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="IX17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="IY17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12632,7 +12632,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JA17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="JB17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12641,7 +12641,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JD17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="JE17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12650,7 +12650,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JG17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="JH17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12659,7 +12659,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JJ17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="JK17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12668,7 +12668,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JM17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="JN17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12677,7 +12677,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JP17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="JQ17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12686,7 +12686,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JS17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="JT17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12695,7 +12695,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JV17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="JW17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12704,7 +12704,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JY17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="JZ17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12713,7 +12713,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KB17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="KC17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12722,7 +12722,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KE17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="KF17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12731,7 +12731,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KH17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="KI17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12740,7 +12740,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KK17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="KL17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12749,7 +12749,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KN17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="KO17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12758,7 +12758,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KQ17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="KR17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12767,7 +12767,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KT17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="KU17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12776,7 +12776,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KW17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="KX17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12785,7 +12785,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KZ17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="LA17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12794,7 +12794,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="LC17" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="LD17" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12814,43 +12814,43 @@
         <x:v>スライス機1　湖南</x:v>
       </x:c>
       <x:c r="E18" s="1" t="str">
-        <x:v>0001</x:v>
+        <x:v>0011</x:v>
       </x:c>
       <x:c r="F18" s="1" t="str">
-        <x:v>スライス</x:v>
+        <x:v>分割</x:v>
       </x:c>
       <x:c r="G18" s="1" t="str">
-        <x:v>015</x:v>
+        <x:v>004</x:v>
       </x:c>
       <x:c r="H18" s="4" t="n">
-        <x:v>46203</x:v>
+        <x:v>46209</x:v>
       </x:c>
       <x:c r="I18" s="1" t="str">
-        <x:v>V7-8</x:v>
+        <x:v>V7-11</x:v>
       </x:c>
       <x:c r="J18" s="1" t="str">
-        <x:v>00081134</x:v>
+        <x:v>00081333</x:v>
       </x:c>
       <x:c r="K18" s="1" t="str">
-        <x:v>6710</x:v>
+        <x:v>6780</x:v>
       </x:c>
       <x:c r="L18" s="1" t="str">
-        <x:v>6713</x:v>
+        <x:v>6783</x:v>
       </x:c>
       <x:c r="M18" s="1" t="str">
-        <x:v>30060-AG00-1000X200F-ABK0C</x:v>
+        <x:v>30050-AS60-1000X200F-A   C</x:v>
       </x:c>
       <x:c r="N18" s="1" t="str">
         <x:v/>
       </x:c>
       <x:c r="O18" s="1" t="str">
-        <x:v>30030-BG00-1000X100F-ABK0C</x:v>
+        <x:v>30025-BS60-1000X200F-A   C</x:v>
       </x:c>
       <x:c r="P18" s="6" t="n">
-        <x:v>800.0000</x:v>
+        <x:v>200.0000</x:v>
       </x:c>
       <x:c r="Q18" s="8" t="n">
-        <x:v>1600.0000</x:v>
+        <x:v>400.0000</x:v>
       </x:c>
       <x:c r="R18" s="1" t="str">
         <x:v>分割,スライス</x:v>
@@ -12862,13 +12862,13 @@
         <x:v>自動車材料事業部</x:v>
       </x:c>
       <x:c r="U18" s="1" t="str">
-        <x:v>00075118</x:v>
+        <x:v>00075274</x:v>
       </x:c>
       <x:c r="V18" s="1" t="str">
         <x:v>0:未完</x:v>
       </x:c>
       <x:c r="W18" s="1" t="str">
-        <x:v>0001</x:v>
+        <x:v>0011</x:v>
       </x:c>
       <x:c r="X18" s="1" t="str">
         <x:v>01</x:v>
@@ -12880,7 +12880,7 @@
         <x:v>1.0000</x:v>
       </x:c>
       <x:c r="AA18" s="4" t="n">
-        <x:v>46212</x:v>
+        <x:v>46213</x:v>
       </x:c>
       <x:c r="AB18" s="1" t="str">
         <x:v>スライス機1　湖南</x:v>
@@ -12901,16 +12901,16 @@
         <x:v/>
       </x:c>
       <x:c r="AH18" s="4" t="n">
-        <x:v>46217</x:v>
+        <x:v>46218</x:v>
       </x:c>
       <x:c r="AI18" s="4" t="n">
-        <x:v>46217</x:v>
+        <x:v>46218</x:v>
       </x:c>
       <x:c r="AJ18" s="1" t="str">
         <x:v>0:未完</x:v>
       </x:c>
       <x:c r="AK18" s="6" t="n">
-        <x:v>800.0000</x:v>
+        <x:v>400.0000</x:v>
       </x:c>
       <x:c r="AL18" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -12922,7 +12922,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AO18" s="6" t="n">
-        <x:v>800.0000</x:v>
+        <x:v>400.0000</x:v>
       </x:c>
       <x:c r="AP18" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -12934,7 +12934,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AS18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="AT18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12943,7 +12943,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AV18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="AW18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12952,7 +12952,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AY18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="AZ18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12961,7 +12961,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BB18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="BC18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12970,7 +12970,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BE18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="BF18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12979,7 +12979,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BH18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="BI18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12988,7 +12988,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BK18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="BL18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -12997,7 +12997,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BN18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="BO18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13006,7 +13006,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BQ18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="BR18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13015,7 +13015,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BT18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="BU18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13024,7 +13024,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BW18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="BX18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13033,7 +13033,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BZ18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="CA18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13042,7 +13042,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CC18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="CD18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13051,7 +13051,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CF18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="CG18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13060,7 +13060,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CI18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="CJ18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13069,7 +13069,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CL18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="CM18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13078,7 +13078,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CO18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="CP18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13087,7 +13087,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CR18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="CS18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13096,7 +13096,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CU18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="CV18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13105,7 +13105,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CX18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="CY18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13114,7 +13114,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DA18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="DB18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13123,7 +13123,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DD18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="DE18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13132,7 +13132,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DG18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="DH18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13141,7 +13141,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DJ18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="DK18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13150,7 +13150,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DM18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="DN18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13159,7 +13159,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DP18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="DQ18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13168,7 +13168,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DS18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="DT18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13177,7 +13177,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DV18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="DW18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13186,7 +13186,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DY18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="DZ18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13195,7 +13195,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EB18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EC18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13204,7 +13204,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EE18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EF18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13213,7 +13213,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EH18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EI18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13222,7 +13222,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EK18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EL18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13231,7 +13231,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EO18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13240,34 +13240,34 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EQ18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="ER18" s="8" t="n">
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES18" s="6" t="n">
-        <x:v>800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ET18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EU18" s="8" t="n">
-        <x:v>0.8300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV18" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>400.0000</x:v>
       </x:c>
       <x:c r="EW18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EX18" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.4400</x:v>
       </x:c>
       <x:c r="EY18" s="6" t="n">
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EZ18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FA18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13276,7 +13276,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FC18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FD18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13285,7 +13285,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FF18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FG18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13294,7 +13294,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FI18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FJ18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13303,7 +13303,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FL18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FM18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13312,7 +13312,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FO18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FP18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13321,7 +13321,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FR18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FS18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13330,7 +13330,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FU18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FV18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13339,7 +13339,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FX18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FY18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13348,7 +13348,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GA18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="GB18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13357,7 +13357,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GD18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="GE18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13366,7 +13366,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GG18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="GH18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13375,7 +13375,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GJ18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="GK18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13384,7 +13384,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GM18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="GN18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13393,7 +13393,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GP18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="GQ18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13402,7 +13402,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GS18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="GT18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13411,7 +13411,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GV18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="GW18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13420,7 +13420,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GY18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="GZ18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13429,7 +13429,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HB18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="HC18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13438,7 +13438,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HE18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="HF18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13447,7 +13447,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HH18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="HI18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13456,7 +13456,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HK18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="HL18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13465,7 +13465,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HN18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="HO18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13474,7 +13474,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HQ18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="HR18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13483,7 +13483,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HT18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="HU18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13492,7 +13492,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HW18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="HX18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13501,7 +13501,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HZ18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="IA18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13510,7 +13510,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="IC18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="ID18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13519,7 +13519,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="IF18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="IG18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13528,7 +13528,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="II18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="IJ18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13537,7 +13537,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="IL18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="IM18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13546,7 +13546,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="IO18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="IP18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13555,7 +13555,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="IR18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="IS18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13564,7 +13564,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="IU18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="IV18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13573,7 +13573,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="IX18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="IY18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13582,7 +13582,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JA18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="JB18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13591,7 +13591,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JD18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="JE18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13600,7 +13600,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JG18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="JH18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13609,7 +13609,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JJ18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="JK18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13618,7 +13618,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JM18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="JN18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13627,7 +13627,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JP18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="JQ18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13636,7 +13636,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JS18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="JT18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13645,7 +13645,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JV18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="JW18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13654,7 +13654,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JY18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="JZ18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13663,7 +13663,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KB18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="KC18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13672,7 +13672,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KE18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="KF18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13681,7 +13681,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KH18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="KI18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13690,7 +13690,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KK18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="KL18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13699,7 +13699,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KN18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="KO18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13708,7 +13708,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KQ18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="KR18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13717,7 +13717,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KT18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="KU18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13726,7 +13726,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KW18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="KX18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13735,7 +13735,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KZ18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="LA18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13744,7 +13744,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="LC18" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="LD18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13764,43 +13764,43 @@
         <x:v>スライス機1　湖南</x:v>
       </x:c>
       <x:c r="E19" s="1" t="str">
-        <x:v>0001</x:v>
+        <x:v>0011</x:v>
       </x:c>
       <x:c r="F19" s="1" t="str">
-        <x:v>スライス</x:v>
+        <x:v>分割</x:v>
       </x:c>
       <x:c r="G19" s="1" t="str">
-        <x:v>017</x:v>
+        <x:v>007</x:v>
       </x:c>
       <x:c r="H19" s="4" t="n">
-        <x:v>46209</x:v>
+        <x:v>46203</x:v>
       </x:c>
       <x:c r="I19" s="1" t="str">
-        <x:v>V7-11</x:v>
+        <x:v>V7-8</x:v>
       </x:c>
       <x:c r="J19" s="1" t="str">
-        <x:v>00081333</x:v>
+        <x:v>00081134</x:v>
       </x:c>
       <x:c r="K19" s="1" t="str">
-        <x:v>6780</x:v>
+        <x:v>6710</x:v>
       </x:c>
       <x:c r="L19" s="1" t="str">
-        <x:v>6783</x:v>
+        <x:v>6713</x:v>
       </x:c>
       <x:c r="M19" s="1" t="str">
-        <x:v>30050-AS60-1000X200F-A   C</x:v>
+        <x:v>30060-AG00-1000X200F-ABK0C</x:v>
       </x:c>
       <x:c r="N19" s="1" t="str">
         <x:v/>
       </x:c>
       <x:c r="O19" s="1" t="str">
-        <x:v>30025-BS60-1000X200F-A   C</x:v>
+        <x:v>30030-BG00-1000X100F-ABK0C</x:v>
       </x:c>
       <x:c r="P19" s="6" t="n">
-        <x:v>200.0000</x:v>
+        <x:v>800.0000</x:v>
       </x:c>
       <x:c r="Q19" s="8" t="n">
-        <x:v>400.0000</x:v>
+        <x:v>1600.0000</x:v>
       </x:c>
       <x:c r="R19" s="1" t="str">
         <x:v>分割,スライス</x:v>
@@ -13812,13 +13812,13 @@
         <x:v>自動車材料事業部</x:v>
       </x:c>
       <x:c r="U19" s="1" t="str">
-        <x:v>00075275</x:v>
+        <x:v>00075117</x:v>
       </x:c>
       <x:c r="V19" s="1" t="str">
         <x:v>0:未完</x:v>
       </x:c>
       <x:c r="W19" s="1" t="str">
-        <x:v>0001</x:v>
+        <x:v>0011</x:v>
       </x:c>
       <x:c r="X19" s="1" t="str">
         <x:v>01</x:v>
@@ -13830,7 +13830,7 @@
         <x:v>1.0000</x:v>
       </x:c>
       <x:c r="AA19" s="4" t="n">
-        <x:v>46213</x:v>
+        <x:v>46212</x:v>
       </x:c>
       <x:c r="AB19" s="1" t="str">
         <x:v>スライス機1　湖南</x:v>
@@ -13851,16 +13851,16 @@
         <x:v/>
       </x:c>
       <x:c r="AH19" s="4" t="n">
-        <x:v>46217</x:v>
+        <x:v>46218</x:v>
       </x:c>
       <x:c r="AI19" s="4" t="n">
-        <x:v>46217</x:v>
+        <x:v>46218</x:v>
       </x:c>
       <x:c r="AJ19" s="1" t="str">
         <x:v>0:未完</x:v>
       </x:c>
       <x:c r="AK19" s="6" t="n">
-        <x:v>200.0000</x:v>
+        <x:v>800.0000</x:v>
       </x:c>
       <x:c r="AL19" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -13872,7 +13872,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AO19" s="6" t="n">
-        <x:v>200.0000</x:v>
+        <x:v>800.0000</x:v>
       </x:c>
       <x:c r="AP19" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -13884,7 +13884,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AS19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="AT19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13893,7 +13893,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AV19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="AW19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13902,7 +13902,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AY19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="AZ19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13911,7 +13911,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BB19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="BC19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13920,7 +13920,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BE19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="BF19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13929,7 +13929,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BH19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="BI19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13938,7 +13938,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BK19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="BL19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13947,7 +13947,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BN19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="BO19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13956,7 +13956,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BQ19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="BR19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13965,7 +13965,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BT19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="BU19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13974,7 +13974,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BW19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="BX19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13983,7 +13983,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BZ19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="CA19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13992,7 +13992,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CC19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="CD19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14001,7 +14001,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CF19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="CG19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14010,7 +14010,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CI19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="CJ19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14019,7 +14019,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CL19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="CM19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14028,7 +14028,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CO19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="CP19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14037,7 +14037,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CR19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="CS19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14046,7 +14046,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CU19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="CV19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14055,7 +14055,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CX19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="CY19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14064,7 +14064,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DA19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="DB19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14073,7 +14073,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DD19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="DE19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14082,7 +14082,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DG19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="DH19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14091,7 +14091,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DJ19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="DK19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14100,7 +14100,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DM19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="DN19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14109,7 +14109,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DP19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="DQ19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14118,7 +14118,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DS19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="DT19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14127,7 +14127,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DV19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="DW19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14136,7 +14136,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DY19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="DZ19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14145,7 +14145,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EB19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EC19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14154,7 +14154,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EE19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EF19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14163,7 +14163,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EH19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EI19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14172,7 +14172,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EK19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EL19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14181,7 +14181,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EO19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14190,34 +14190,34 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EQ19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="ER19" s="8" t="n">
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES19" s="6" t="n">
-        <x:v>200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ET19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EU19" s="8" t="n">
-        <x:v>0.2100</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV19" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>800.0000</x:v>
       </x:c>
       <x:c r="EW19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EX19" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.8900</x:v>
       </x:c>
       <x:c r="EY19" s="6" t="n">
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EZ19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FA19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14226,7 +14226,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FC19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FD19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14235,7 +14235,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FF19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FG19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14244,7 +14244,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FI19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FJ19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14253,7 +14253,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FL19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FM19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14262,7 +14262,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FO19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FP19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14271,7 +14271,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FR19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FS19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14280,7 +14280,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FU19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FV19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14289,7 +14289,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FX19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FY19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14298,7 +14298,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GA19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="GB19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14307,7 +14307,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GD19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="GE19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14316,7 +14316,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GG19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="GH19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14325,7 +14325,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GJ19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="GK19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14334,7 +14334,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GM19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="GN19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14343,7 +14343,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GP19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="GQ19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14352,7 +14352,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GS19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="GT19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14361,7 +14361,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GV19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="GW19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14370,7 +14370,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GY19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="GZ19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14379,7 +14379,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HB19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="HC19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14388,7 +14388,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HE19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="HF19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14397,7 +14397,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HH19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="HI19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14406,7 +14406,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HK19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="HL19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14415,7 +14415,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HN19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="HO19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14424,7 +14424,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HQ19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="HR19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14433,7 +14433,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HT19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="HU19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14442,7 +14442,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HW19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="HX19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14451,7 +14451,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HZ19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="IA19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14460,7 +14460,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="IC19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="ID19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14469,7 +14469,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="IF19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="IG19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14478,7 +14478,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="II19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="IJ19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14487,7 +14487,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="IL19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="IM19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14496,7 +14496,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="IO19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="IP19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14505,7 +14505,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="IR19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="IS19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14514,7 +14514,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="IU19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="IV19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14523,7 +14523,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="IX19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="IY19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14532,7 +14532,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JA19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="JB19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14541,7 +14541,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JD19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="JE19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14550,7 +14550,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JG19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="JH19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14559,7 +14559,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JJ19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="JK19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14568,7 +14568,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JM19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="JN19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14577,7 +14577,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JP19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="JQ19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14586,7 +14586,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JS19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="JT19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14595,7 +14595,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JV19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="JW19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14604,7 +14604,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JY19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="JZ19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14613,7 +14613,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KB19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="KC19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14622,7 +14622,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KE19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="KF19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14631,7 +14631,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KH19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="KI19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14640,7 +14640,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KK19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="KL19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14649,7 +14649,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KN19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="KO19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14658,7 +14658,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KQ19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="KR19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14667,7 +14667,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KT19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="KU19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14676,7 +14676,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KW19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="KX19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14685,7 +14685,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KZ19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="LA19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14694,7 +14694,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="LC19" s="8" t="n">
-        <x:v>16.1200</x:v>
+        <x:v>15.0000</x:v>
       </x:c>
       <x:c r="LD19" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14714,46 +14714,46 @@
         <x:v>スライス機1　湖南</x:v>
       </x:c>
       <x:c r="E20" s="1" t="str">
-        <x:v>0011</x:v>
+        <x:v>0001</x:v>
       </x:c>
       <x:c r="F20" s="1" t="str">
-        <x:v>分割</x:v>
+        <x:v>スライス</x:v>
       </x:c>
       <x:c r="G20" s="1" t="str">
-        <x:v>004</x:v>
+        <x:v>015</x:v>
       </x:c>
       <x:c r="H20" s="4" t="n">
-        <x:v>46209</x:v>
+        <x:v>46204</x:v>
       </x:c>
       <x:c r="I20" s="1" t="str">
-        <x:v>V7-11</x:v>
+        <x:v>T7-4</x:v>
       </x:c>
       <x:c r="J20" s="1" t="str">
-        <x:v>00081333</x:v>
+        <x:v>00081171</x:v>
       </x:c>
       <x:c r="K20" s="1" t="str">
-        <x:v>6780</x:v>
+        <x:v>6710</x:v>
       </x:c>
       <x:c r="L20" s="1" t="str">
-        <x:v>6783</x:v>
+        <x:v>6713</x:v>
       </x:c>
       <x:c r="M20" s="1" t="str">
-        <x:v>30050-AS60-1000X200F-A   C</x:v>
+        <x:v>30044-AG00-1000X200F-AWH1C</x:v>
       </x:c>
       <x:c r="N20" s="1" t="str">
         <x:v/>
       </x:c>
       <x:c r="O20" s="1" t="str">
-        <x:v>30025-BS60-1000X200F-A   C</x:v>
+        <x:v>30022-BG00-1000X200F-AWH1C</x:v>
       </x:c>
       <x:c r="P20" s="6" t="n">
-        <x:v>200.0000</x:v>
+        <x:v>4000.0000</x:v>
       </x:c>
       <x:c r="Q20" s="8" t="n">
-        <x:v>400.0000</x:v>
+        <x:v>8000.0000</x:v>
       </x:c>
       <x:c r="R20" s="1" t="str">
-        <x:v>分割,スライス</x:v>
+        <x:v>スライス</x:v>
       </x:c>
       <x:c r="S20" s="1" t="str">
         <x:v>東レ株式会社</x:v>
@@ -14762,13 +14762,13 @@
         <x:v>自動車材料事業部</x:v>
       </x:c>
       <x:c r="U20" s="1" t="str">
-        <x:v>00075274</x:v>
+        <x:v>00075164</x:v>
       </x:c>
       <x:c r="V20" s="1" t="str">
         <x:v>0:未完</x:v>
       </x:c>
       <x:c r="W20" s="1" t="str">
-        <x:v>0011</x:v>
+        <x:v>0001</x:v>
       </x:c>
       <x:c r="X20" s="1" t="str">
         <x:v>01</x:v>
@@ -14780,22 +14780,22 @@
         <x:v>1.0000</x:v>
       </x:c>
       <x:c r="AA20" s="4" t="n">
-        <x:v>46213</x:v>
+        <x:v>46218</x:v>
       </x:c>
       <x:c r="AB20" s="1" t="str">
         <x:v>スライス機1　湖南</x:v>
       </x:c>
       <x:c r="AC20" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AD20" s="4" t="n">
-        <x:v>46219</x:v>
+        <x:v>46220</x:v>
       </x:c>
       <x:c r="AE20" s="4" t="n">
-        <x:v>46219</x:v>
+        <x:v>46220</x:v>
       </x:c>
       <x:c r="AF20" s="4" t="n">
-        <x:v>46219</x:v>
+        <x:v>46220</x:v>
       </x:c>
       <x:c r="AG20" s="4" t="str">
         <x:v/>
@@ -14810,7 +14810,7 @@
         <x:v>0:未完</x:v>
       </x:c>
       <x:c r="AK20" s="6" t="n">
-        <x:v>400.0000</x:v>
+        <x:v>4000.0000</x:v>
       </x:c>
       <x:c r="AL20" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -14822,7 +14822,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AO20" s="6" t="n">
-        <x:v>400.0000</x:v>
+        <x:v>4000.0000</x:v>
       </x:c>
       <x:c r="AP20" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -14834,7 +14834,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AS20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="AT20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14843,7 +14843,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AV20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="AW20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14852,7 +14852,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AY20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="AZ20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14861,7 +14861,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BB20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="BC20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14870,7 +14870,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BE20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="BF20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14879,7 +14879,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BH20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="BI20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14888,7 +14888,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BK20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="BL20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14897,7 +14897,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BN20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="BO20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14906,7 +14906,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BQ20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="BR20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14915,7 +14915,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BT20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="BU20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14924,7 +14924,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BW20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="BX20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14933,7 +14933,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BZ20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="CA20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14942,7 +14942,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CC20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="CD20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14951,7 +14951,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CF20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="CG20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14960,7 +14960,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CI20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="CJ20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14969,7 +14969,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CL20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="CM20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14978,7 +14978,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CO20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="CP20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14987,7 +14987,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CR20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="CS20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14996,7 +14996,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CU20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="CV20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15005,7 +15005,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CX20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="CY20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15014,7 +15014,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DA20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="DB20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15023,7 +15023,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DD20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="DE20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15032,7 +15032,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DG20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="DH20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15041,7 +15041,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DJ20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="DK20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15050,7 +15050,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DM20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="DN20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15059,7 +15059,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DP20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="DQ20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15068,7 +15068,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DS20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="DT20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15077,7 +15077,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DV20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="DW20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15086,7 +15086,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DY20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="DZ20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15095,7 +15095,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EB20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EC20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15104,7 +15104,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EE20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EF20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15113,7 +15113,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EH20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EI20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15122,7 +15122,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EK20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EL20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15131,7 +15131,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EO20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15140,7 +15140,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EQ20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="ER20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15149,25 +15149,25 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ET20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EU20" s="8" t="n">
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV20" s="6" t="n">
-        <x:v>400.0000</x:v>
+        <x:v>4000.0000</x:v>
       </x:c>
       <x:c r="EW20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EX20" s="8" t="n">
-        <x:v>0.4400</x:v>
+        <x:v>4.1400</x:v>
       </x:c>
       <x:c r="EY20" s="6" t="n">
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EZ20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FA20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15176,7 +15176,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FC20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FD20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15185,7 +15185,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FF20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FG20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15194,7 +15194,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FI20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FJ20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15203,7 +15203,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FL20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FM20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15212,7 +15212,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FO20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FP20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15221,7 +15221,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FR20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FS20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15230,7 +15230,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FU20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FV20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15239,7 +15239,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FX20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FY20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15248,7 +15248,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GA20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="GB20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15257,7 +15257,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GD20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="GE20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15266,7 +15266,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GG20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="GH20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15275,7 +15275,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GJ20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="GK20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15284,7 +15284,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GM20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="GN20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15293,7 +15293,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GP20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="GQ20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15302,7 +15302,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GS20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="GT20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15311,7 +15311,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GV20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="GW20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15320,7 +15320,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GY20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="GZ20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15329,7 +15329,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HB20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="HC20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15338,7 +15338,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HE20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="HF20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15347,7 +15347,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HH20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="HI20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15356,7 +15356,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HK20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="HL20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15365,7 +15365,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HN20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="HO20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15374,7 +15374,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HQ20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="HR20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15383,7 +15383,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HT20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="HU20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15392,7 +15392,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HW20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="HX20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15401,7 +15401,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HZ20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="IA20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15410,7 +15410,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="IC20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="ID20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15419,7 +15419,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="IF20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="IG20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15428,7 +15428,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="II20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="IJ20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15437,7 +15437,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="IL20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="IM20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15446,7 +15446,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="IO20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="IP20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15455,7 +15455,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="IR20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="IS20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15464,7 +15464,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="IU20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="IV20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15473,7 +15473,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="IX20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="IY20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15482,7 +15482,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JA20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="JB20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15491,7 +15491,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JD20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="JE20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15500,7 +15500,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JG20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="JH20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15509,7 +15509,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JJ20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="JK20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15518,7 +15518,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JM20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="JN20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15527,7 +15527,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JP20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="JQ20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15536,7 +15536,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JS20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="JT20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15545,7 +15545,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JV20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="JW20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15554,7 +15554,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JY20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="JZ20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15563,7 +15563,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KB20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="KC20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15572,7 +15572,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KE20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="KF20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15581,7 +15581,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KH20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="KI20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15590,7 +15590,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KK20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="KL20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15599,7 +15599,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KN20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="KO20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15608,7 +15608,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KQ20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="KR20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15617,7 +15617,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KT20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="KU20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15626,7 +15626,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KW20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="KX20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15635,7 +15635,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KZ20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="LA20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15644,7 +15644,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="LC20" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="LD20" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15664,22 +15664,22 @@
         <x:v>スライス機1　湖南</x:v>
       </x:c>
       <x:c r="E21" s="1" t="str">
-        <x:v>0011</x:v>
+        <x:v>0001</x:v>
       </x:c>
       <x:c r="F21" s="1" t="str">
-        <x:v>分割</x:v>
+        <x:v>スライス</x:v>
       </x:c>
       <x:c r="G21" s="1" t="str">
-        <x:v>007</x:v>
+        <x:v>021</x:v>
       </x:c>
       <x:c r="H21" s="4" t="n">
-        <x:v>46203</x:v>
+        <x:v>46190</x:v>
       </x:c>
       <x:c r="I21" s="1" t="str">
-        <x:v>V7-8</x:v>
+        <x:v>Y6-26</x:v>
       </x:c>
       <x:c r="J21" s="1" t="str">
-        <x:v>00081134</x:v>
+        <x:v>00080753</x:v>
       </x:c>
       <x:c r="K21" s="1" t="str">
         <x:v>6710</x:v>
@@ -15688,22 +15688,22 @@
         <x:v>6713</x:v>
       </x:c>
       <x:c r="M21" s="1" t="str">
-        <x:v>30060-AG00-1000X200F-ABK0C</x:v>
+        <x:v>30066-AY00- 640X200F-AGA0C</x:v>
       </x:c>
       <x:c r="N21" s="1" t="str">
         <x:v/>
       </x:c>
       <x:c r="O21" s="1" t="str">
-        <x:v>30030-BG00-1000X100F-ABK0C</x:v>
+        <x:v>30033-BY00- 640X200F-AGA0C</x:v>
       </x:c>
       <x:c r="P21" s="6" t="n">
-        <x:v>800.0000</x:v>
+        <x:v>10000.0000</x:v>
       </x:c>
       <x:c r="Q21" s="8" t="n">
-        <x:v>1600.0000</x:v>
+        <x:v>20000.0000</x:v>
       </x:c>
       <x:c r="R21" s="1" t="str">
-        <x:v>分割,スライス</x:v>
+        <x:v>スライス</x:v>
       </x:c>
       <x:c r="S21" s="1" t="str">
         <x:v>東レ株式会社</x:v>
@@ -15712,13 +15712,13 @@
         <x:v>自動車材料事業部</x:v>
       </x:c>
       <x:c r="U21" s="1" t="str">
-        <x:v>00075117</x:v>
+        <x:v>00075281</x:v>
       </x:c>
       <x:c r="V21" s="1" t="str">
         <x:v>0:未完</x:v>
       </x:c>
       <x:c r="W21" s="1" t="str">
-        <x:v>0011</x:v>
+        <x:v>0001</x:v>
       </x:c>
       <x:c r="X21" s="1" t="str">
         <x:v>01</x:v>
@@ -15730,7 +15730,7 @@
         <x:v>1.0000</x:v>
       </x:c>
       <x:c r="AA21" s="4" t="n">
-        <x:v>46212</x:v>
+        <x:v>46211</x:v>
       </x:c>
       <x:c r="AB21" s="1" t="str">
         <x:v>スライス機1　湖南</x:v>
@@ -15739,28 +15739,28 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AD21" s="4" t="n">
-        <x:v>46219</x:v>
+        <x:v>46220</x:v>
       </x:c>
       <x:c r="AE21" s="4" t="n">
-        <x:v>46219</x:v>
+        <x:v>46220</x:v>
       </x:c>
       <x:c r="AF21" s="4" t="n">
-        <x:v>46219</x:v>
+        <x:v>46220</x:v>
       </x:c>
       <x:c r="AG21" s="4" t="str">
         <x:v/>
       </x:c>
       <x:c r="AH21" s="4" t="n">
-        <x:v>46218</x:v>
+        <x:v>46219</x:v>
       </x:c>
       <x:c r="AI21" s="4" t="n">
-        <x:v>46218</x:v>
+        <x:v>46220</x:v>
       </x:c>
       <x:c r="AJ21" s="1" t="str">
         <x:v>0:未完</x:v>
       </x:c>
       <x:c r="AK21" s="6" t="n">
-        <x:v>800.0000</x:v>
+        <x:v>10000.0000</x:v>
       </x:c>
       <x:c r="AL21" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -15772,7 +15772,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AO21" s="6" t="n">
-        <x:v>800.0000</x:v>
+        <x:v>10000.0000</x:v>
       </x:c>
       <x:c r="AP21" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -15784,7 +15784,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AS21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="AT21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15793,7 +15793,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AV21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="AW21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15802,7 +15802,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AY21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="AZ21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15811,7 +15811,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BB21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="BC21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15820,7 +15820,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BE21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="BF21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15829,7 +15829,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BH21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="BI21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15838,7 +15838,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BK21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="BL21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15847,7 +15847,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BN21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="BO21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15856,7 +15856,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BQ21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="BR21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15865,7 +15865,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BT21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="BU21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15874,7 +15874,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BW21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="BX21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15883,7 +15883,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="BZ21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="CA21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15892,7 +15892,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CC21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="CD21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15901,7 +15901,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CF21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="CG21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15910,7 +15910,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CI21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="CJ21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15919,7 +15919,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CL21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="CM21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15928,7 +15928,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CO21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="CP21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15937,7 +15937,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CR21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="CS21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15946,7 +15946,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CU21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="CV21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15955,7 +15955,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CX21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="CY21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15964,7 +15964,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DA21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="DB21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15973,7 +15973,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DD21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="DE21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15982,7 +15982,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DG21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="DH21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -15991,7 +15991,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DJ21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="DK21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16000,7 +16000,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DM21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="DN21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16009,7 +16009,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DP21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="DQ21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16018,7 +16018,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DS21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="DT21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16027,7 +16027,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DV21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="DW21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16036,7 +16036,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DY21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="DZ21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16045,7 +16045,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EB21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EC21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16054,7 +16054,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EE21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EF21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16063,7 +16063,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EH21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EI21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16072,7 +16072,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EK21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EL21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16081,7 +16081,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EO21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16090,7 +16090,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EQ21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="ER21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16099,43 +16099,43 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ET21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EU21" s="8" t="n">
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV21" s="6" t="n">
-        <x:v>800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EW21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EX21" s="8" t="n">
-        <x:v>0.8900</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY21" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>7400.0000</x:v>
       </x:c>
       <x:c r="EZ21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FA21" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>7.6500</x:v>
       </x:c>
       <x:c r="FB21" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2600.0000</x:v>
       </x:c>
       <x:c r="FC21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FD21" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.6900</x:v>
       </x:c>
       <x:c r="FE21" s="6" t="n">
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FF21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FG21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16144,7 +16144,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FI21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FJ21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16153,7 +16153,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FL21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FM21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16162,7 +16162,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FO21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FP21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16171,7 +16171,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FR21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FS21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16180,7 +16180,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FU21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FV21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16189,7 +16189,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FX21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FY21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16198,7 +16198,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GA21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="GB21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16207,7 +16207,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GD21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="GE21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16216,7 +16216,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GG21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="GH21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16225,7 +16225,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GJ21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="GK21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16234,7 +16234,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GM21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="GN21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16243,7 +16243,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GP21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="GQ21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16252,7 +16252,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GS21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="GT21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16261,7 +16261,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GV21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="GW21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16270,7 +16270,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GY21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="GZ21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16279,7 +16279,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HB21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="HC21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16288,7 +16288,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HE21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="HF21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16297,7 +16297,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HH21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="HI21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16306,7 +16306,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HK21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="HL21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16315,7 +16315,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HN21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="HO21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16324,7 +16324,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HQ21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="HR21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16333,7 +16333,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HT21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="HU21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16342,7 +16342,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HW21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="HX21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16351,7 +16351,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="HZ21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="IA21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16360,7 +16360,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="IC21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="ID21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16369,7 +16369,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="IF21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="IG21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16378,7 +16378,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="II21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="IJ21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16387,7 +16387,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="IL21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="IM21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16396,7 +16396,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="IO21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="IP21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16405,7 +16405,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="IR21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="IS21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16414,7 +16414,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="IU21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="IV21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16423,7 +16423,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="IX21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="IY21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16432,7 +16432,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JA21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="JB21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16441,7 +16441,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JD21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="JE21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16450,7 +16450,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JG21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="JH21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16459,7 +16459,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JJ21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="JK21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16468,7 +16468,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JM21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="JN21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16477,7 +16477,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JP21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="JQ21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16486,7 +16486,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JS21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="JT21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16495,7 +16495,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JV21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="JW21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16504,7 +16504,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="JY21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="JZ21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16513,7 +16513,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KB21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="KC21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16522,7 +16522,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KE21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="KF21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16531,7 +16531,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KH21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="KI21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16540,7 +16540,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KK21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="KL21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16549,7 +16549,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KN21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="KO21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16558,7 +16558,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KQ21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="KR21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16567,7 +16567,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KT21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="KU21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16576,7 +16576,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KW21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="KX21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16585,7 +16585,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="KZ21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="LA21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16594,7 +16594,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="LC21" s="8" t="n">
-        <x:v>15.0000</x:v>
+        <x:v>16.1200</x:v>
       </x:c>
       <x:c r="LD21" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -16620,16 +16620,16 @@
         <x:v>スライス</x:v>
       </x:c>
       <x:c r="G22" s="1" t="str">
-        <x:v>015</x:v>
+        <x:v>001</x:v>
       </x:c>
       <x:c r="H22" s="4" t="n">
-        <x:v>46204</x:v>
+        <x:v>46210</x:v>
       </x:c>
       <x:c r="I22" s="1" t="str">
-        <x:v>T7-4</x:v>
+        <x:v>T7-10</x:v>
       </x:c>
       <x:c r="J22" s="1" t="str">
-        <x:v>00081171</x:v>
+        <x:v>00081375</x:v>
       </x:c>
       <x:c r="K22" s="1" t="str">
         <x:v>6710</x:v>
@@ -16638,19 +16638,19 @@
         <x:v>6713</x:v>
       </x:c>
       <x:c r="M22" s="1" t="str">
-        <x:v>30044-AG00-1000X200F-AWH1C</x:v>
+        <x:v>30040-AG00-1030X200F-ABK0C</x:v>
       </x:c>
       <x:c r="N22" s="1" t="str">
         <x:v/>
       </x:c>
       <x:c r="O22" s="1" t="str">
-        <x:v>30022-BG00-1000X200F-AWH1C</x:v>
+        <x:v>30020-BG00-1030X200F-ABK0C</x:v>
       </x:c>
       <x:c r="P22" s="6" t="n">
-        <x:v>4000.0000</x:v>
+        <x:v>600.0000</x:v>
       </x:c>
       <x:c r="Q22" s="8" t="n">
-        <x:v>8000.0000</x:v>
+        <x:v>1200.0000</x:v>
       </x:c>
       <x:c r="R22" s="1" t="str">
         <x:v>スライス</x:v>
@@ -16662,7 +16662,7 @@
         <x:v>自動車材料事業部</x:v>
       </x:c>
       <x:c r="U22" s="1" t="str">
-        <x:v>00075164</x:v>
+        <x:v>00075335</x:v>
       </x:c>
       <x:c r="V22" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -16680,37 +16680,37 @@
         <x:v>1.0000</x:v>
       </x:c>
       <x:c r="AA22" s="4" t="n">
-        <x:v>46218</x:v>
+        <x:v>46219</x:v>
       </x:c>
       <x:c r="AB22" s="1" t="str">
         <x:v>スライス機1　湖南</x:v>
       </x:c>
       <x:c r="AC22" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AD22" s="4" t="n">
-        <x:v>46220</x:v>
+        <x:v>46224</x:v>
       </x:c>
       <x:c r="AE22" s="4" t="n">
-        <x:v>46220</x:v>
+        <x:v>46224</x:v>
       </x:c>
       <x:c r="AF22" s="4" t="n">
-        <x:v>46220</x:v>
+        <x:v>46224</x:v>
       </x:c>
       <x:c r="AG22" s="4" t="str">
         <x:v/>
       </x:c>
       <x:c r="AH22" s="4" t="n">
-        <x:v>46218</x:v>
+        <x:v>46220</x:v>
       </x:c>
       <x:c r="AI22" s="4" t="n">
-        <x:v>46218</x:v>
+        <x:v>46220</x:v>
       </x:c>
       <x:c r="AJ22" s="1" t="str">
         <x:v>0:未完</x:v>
       </x:c>
       <x:c r="AK22" s="6" t="n">
-        <x:v>4000.0000</x:v>
+        <x:v>600.0000</x:v>
       </x:c>
       <x:c r="AL22" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -16722,7 +16722,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AO22" s="6" t="n">
-        <x:v>4000.0000</x:v>
+        <x:v>600.0000</x:v>
       </x:c>
       <x:c r="AP22" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -17055,13 +17055,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV22" s="6" t="n">
-        <x:v>4000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EW22" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EX22" s="8" t="n">
-        <x:v>4.1400</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY22" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -17073,13 +17073,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB22" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>600.0000</x:v>
       </x:c>
       <x:c r="FC22" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FD22" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.6200</x:v>
       </x:c>
       <x:c r="FE22" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -17570,16 +17570,16 @@
         <x:v>スライス</x:v>
       </x:c>
       <x:c r="G23" s="1" t="str">
-        <x:v>021</x:v>
+        <x:v>019</x:v>
       </x:c>
       <x:c r="H23" s="4" t="n">
-        <x:v>46190</x:v>
+        <x:v>46205</x:v>
       </x:c>
       <x:c r="I23" s="1" t="str">
-        <x:v>Y6-26</x:v>
+        <x:v>C7-13</x:v>
       </x:c>
       <x:c r="J23" s="1" t="str">
-        <x:v>00080753</x:v>
+        <x:v>00081213</x:v>
       </x:c>
       <x:c r="K23" s="1" t="str">
         <x:v>6710</x:v>
@@ -17612,7 +17612,7 @@
         <x:v>自動車材料事業部</x:v>
       </x:c>
       <x:c r="U23" s="1" t="str">
-        <x:v>00075281</x:v>
+        <x:v>00075208</x:v>
       </x:c>
       <x:c r="V23" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -17630,7 +17630,7 @@
         <x:v>1.0000</x:v>
       </x:c>
       <x:c r="AA23" s="4" t="n">
-        <x:v>46211</x:v>
+        <x:v>46218</x:v>
       </x:c>
       <x:c r="AB23" s="1" t="str">
         <x:v>スライス機1　湖南</x:v>
@@ -17639,22 +17639,22 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AD23" s="4" t="n">
-        <x:v>46220</x:v>
+        <x:v>46224</x:v>
       </x:c>
       <x:c r="AE23" s="4" t="n">
-        <x:v>46220</x:v>
+        <x:v>46224</x:v>
       </x:c>
       <x:c r="AF23" s="4" t="n">
-        <x:v>46220</x:v>
+        <x:v>46224</x:v>
       </x:c>
       <x:c r="AG23" s="4" t="str">
         <x:v/>
       </x:c>
       <x:c r="AH23" s="4" t="n">
-        <x:v>46219</x:v>
+        <x:v>46220</x:v>
       </x:c>
       <x:c r="AI23" s="4" t="n">
-        <x:v>46220</x:v>
+        <x:v>46224</x:v>
       </x:c>
       <x:c r="AJ23" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -18014,22 +18014,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY23" s="6" t="n">
-        <x:v>7400.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EZ23" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FA23" s="8" t="n">
-        <x:v>7.6500</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB23" s="6" t="n">
-        <x:v>2600.0000</x:v>
+        <x:v>2800.0000</x:v>
       </x:c>
       <x:c r="FC23" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FD23" s="8" t="n">
-        <x:v>2.6900</x:v>
+        <x:v>2.8900</x:v>
       </x:c>
       <x:c r="FE23" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -18059,13 +18059,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FN23" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>7200.0000</x:v>
       </x:c>
       <x:c r="FO23" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FP23" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>7.4400</x:v>
       </x:c>
       <x:c r="FQ23" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -18520,16 +18520,16 @@
         <x:v>スライス</x:v>
       </x:c>
       <x:c r="G24" s="1" t="str">
-        <x:v>019</x:v>
+        <x:v>004</x:v>
       </x:c>
       <x:c r="H24" s="4" t="n">
-        <x:v>46205</x:v>
+        <x:v>46209</x:v>
       </x:c>
       <x:c r="I24" s="1" t="str">
-        <x:v>C7-13</x:v>
+        <x:v>T7-6</x:v>
       </x:c>
       <x:c r="J24" s="1" t="str">
-        <x:v>00081213</x:v>
+        <x:v>00081318</x:v>
       </x:c>
       <x:c r="K24" s="1" t="str">
         <x:v>6710</x:v>
@@ -18538,19 +18538,19 @@
         <x:v>6713</x:v>
       </x:c>
       <x:c r="M24" s="1" t="str">
-        <x:v>30066-AY00- 640X200F-AGA0C</x:v>
+        <x:v>30040-AY00- 640X250F-A   C</x:v>
       </x:c>
       <x:c r="N24" s="1" t="str">
         <x:v/>
       </x:c>
       <x:c r="O24" s="1" t="str">
-        <x:v>30033-BY00- 640X200F-AGA0C</x:v>
+        <x:v>30020-BY00- 640X250F-A   C</x:v>
       </x:c>
       <x:c r="P24" s="6" t="n">
-        <x:v>10000.0000</x:v>
+        <x:v>3000.0000</x:v>
       </x:c>
       <x:c r="Q24" s="8" t="n">
-        <x:v>20000.0000</x:v>
+        <x:v>6000.0000</x:v>
       </x:c>
       <x:c r="R24" s="1" t="str">
         <x:v>スライス</x:v>
@@ -18562,7 +18562,7 @@
         <x:v>自動車材料事業部</x:v>
       </x:c>
       <x:c r="U24" s="1" t="str">
-        <x:v>00075208</x:v>
+        <x:v>00075250</x:v>
       </x:c>
       <x:c r="V24" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -18580,37 +18580,37 @@
         <x:v>1.0000</x:v>
       </x:c>
       <x:c r="AA24" s="4" t="n">
-        <x:v>46218</x:v>
+        <x:v>46220</x:v>
       </x:c>
       <x:c r="AB24" s="1" t="str">
         <x:v>スライス機1　湖南</x:v>
       </x:c>
       <x:c r="AC24" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AD24" s="4" t="n">
-        <x:v>46224</x:v>
+        <x:v>46225</x:v>
       </x:c>
       <x:c r="AE24" s="4" t="n">
-        <x:v>46224</x:v>
+        <x:v>46225</x:v>
       </x:c>
       <x:c r="AF24" s="4" t="n">
-        <x:v>46224</x:v>
+        <x:v>46225</x:v>
       </x:c>
       <x:c r="AG24" s="4" t="str">
         <x:v/>
       </x:c>
       <x:c r="AH24" s="4" t="n">
-        <x:v>46220</x:v>
+        <x:v>46225</x:v>
       </x:c>
       <x:c r="AI24" s="4" t="n">
-        <x:v>46224</x:v>
+        <x:v>46225</x:v>
       </x:c>
       <x:c r="AJ24" s="1" t="str">
         <x:v>0:未完</x:v>
       </x:c>
       <x:c r="AK24" s="6" t="n">
-        <x:v>10000.0000</x:v>
+        <x:v>3000.0000</x:v>
       </x:c>
       <x:c r="AL24" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -18622,7 +18622,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AO24" s="6" t="n">
-        <x:v>10000.0000</x:v>
+        <x:v>3000.0000</x:v>
       </x:c>
       <x:c r="AP24" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -18973,13 +18973,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB24" s="6" t="n">
-        <x:v>2800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FC24" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FD24" s="8" t="n">
-        <x:v>2.8900</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FE24" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -19009,22 +19009,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FN24" s="6" t="n">
-        <x:v>7200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FO24" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FP24" s="8" t="n">
-        <x:v>7.4400</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FQ24" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3000.0000</x:v>
       </x:c>
       <x:c r="FR24" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FS24" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3.1000</x:v>
       </x:c>
       <x:c r="FT24" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -19470,16 +19470,16 @@
         <x:v>スライス</x:v>
       </x:c>
       <x:c r="G25" s="1" t="str">
-        <x:v>004</x:v>
+        <x:v>022</x:v>
       </x:c>
       <x:c r="H25" s="4" t="n">
-        <x:v>46209</x:v>
+        <x:v>46205</x:v>
       </x:c>
       <x:c r="I25" s="1" t="str">
-        <x:v>T7-6</x:v>
+        <x:v>C7-14</x:v>
       </x:c>
       <x:c r="J25" s="1" t="str">
-        <x:v>00081318</x:v>
+        <x:v>00081214</x:v>
       </x:c>
       <x:c r="K25" s="1" t="str">
         <x:v>6710</x:v>
@@ -19488,19 +19488,19 @@
         <x:v>6713</x:v>
       </x:c>
       <x:c r="M25" s="1" t="str">
-        <x:v>30040-AY00- 640X250F-A   C</x:v>
+        <x:v>30066-AY00- 640X200F-AGA0C</x:v>
       </x:c>
       <x:c r="N25" s="1" t="str">
         <x:v/>
       </x:c>
       <x:c r="O25" s="1" t="str">
-        <x:v>30020-BY00- 640X250F-A   C</x:v>
+        <x:v>30033-BY00- 640X200F-AGA0C</x:v>
       </x:c>
       <x:c r="P25" s="6" t="n">
-        <x:v>3000.0000</x:v>
+        <x:v>10000.0000</x:v>
       </x:c>
       <x:c r="Q25" s="8" t="n">
-        <x:v>6000.0000</x:v>
+        <x:v>20000.0000</x:v>
       </x:c>
       <x:c r="R25" s="1" t="str">
         <x:v>スライス</x:v>
@@ -19512,7 +19512,7 @@
         <x:v>自動車材料事業部</x:v>
       </x:c>
       <x:c r="U25" s="1" t="str">
-        <x:v>00075250</x:v>
+        <x:v>00075209</x:v>
       </x:c>
       <x:c r="V25" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -19530,22 +19530,22 @@
         <x:v>1.0000</x:v>
       </x:c>
       <x:c r="AA25" s="4" t="n">
-        <x:v>46220</x:v>
+        <x:v>46219</x:v>
       </x:c>
       <x:c r="AB25" s="1" t="str">
         <x:v>スライス機1　湖南</x:v>
       </x:c>
       <x:c r="AC25" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AD25" s="4" t="n">
-        <x:v>46225</x:v>
+        <x:v>46226</x:v>
       </x:c>
       <x:c r="AE25" s="4" t="n">
-        <x:v>46225</x:v>
+        <x:v>46226</x:v>
       </x:c>
       <x:c r="AF25" s="4" t="n">
-        <x:v>46225</x:v>
+        <x:v>46226</x:v>
       </x:c>
       <x:c r="AG25" s="4" t="str">
         <x:v/>
@@ -19554,13 +19554,13 @@
         <x:v>46225</x:v>
       </x:c>
       <x:c r="AI25" s="4" t="n">
-        <x:v>46225</x:v>
+        <x:v>46226</x:v>
       </x:c>
       <x:c r="AJ25" s="1" t="str">
         <x:v>0:未完</x:v>
       </x:c>
       <x:c r="AK25" s="6" t="n">
-        <x:v>3000.0000</x:v>
+        <x:v>10000.0000</x:v>
       </x:c>
       <x:c r="AL25" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -19572,7 +19572,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AO25" s="6" t="n">
-        <x:v>3000.0000</x:v>
+        <x:v>10000.0000</x:v>
       </x:c>
       <x:c r="AP25" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -19968,22 +19968,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FQ25" s="6" t="n">
-        <x:v>3000.0000</x:v>
+        <x:v>4200.0000</x:v>
       </x:c>
       <x:c r="FR25" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FS25" s="8" t="n">
-        <x:v>3.1000</x:v>
+        <x:v>4.3400</x:v>
       </x:c>
       <x:c r="FT25" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5800.0000</x:v>
       </x:c>
       <x:c r="FU25" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FV25" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6.0000</x:v>
       </x:c>
       <x:c r="FW25" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -20420,16 +20420,16 @@
         <x:v>スライス</x:v>
       </x:c>
       <x:c r="G26" s="1" t="str">
-        <x:v>022</x:v>
+        <x:v>020</x:v>
       </x:c>
       <x:c r="H26" s="4" t="n">
         <x:v>46205</x:v>
       </x:c>
       <x:c r="I26" s="1" t="str">
-        <x:v>C7-14</x:v>
+        <x:v>T7-5</x:v>
       </x:c>
       <x:c r="J26" s="1" t="str">
-        <x:v>00081214</x:v>
+        <x:v>00081226</x:v>
       </x:c>
       <x:c r="K26" s="1" t="str">
         <x:v>6710</x:v>
@@ -20438,19 +20438,19 @@
         <x:v>6713</x:v>
       </x:c>
       <x:c r="M26" s="1" t="str">
-        <x:v>30066-AY00- 640X200F-AGA0C</x:v>
+        <x:v>20040-AY00- 640X250F-AWH1C</x:v>
       </x:c>
       <x:c r="N26" s="1" t="str">
         <x:v/>
       </x:c>
       <x:c r="O26" s="1" t="str">
-        <x:v>30033-BY00- 640X200F-AGA0C</x:v>
+        <x:v>20020-BY00- 640X250F-AWH1C</x:v>
       </x:c>
       <x:c r="P26" s="6" t="n">
-        <x:v>10000.0000</x:v>
+        <x:v>5750.0000</x:v>
       </x:c>
       <x:c r="Q26" s="8" t="n">
-        <x:v>20000.0000</x:v>
+        <x:v>11500.0000</x:v>
       </x:c>
       <x:c r="R26" s="1" t="str">
         <x:v>スライス</x:v>
@@ -20462,7 +20462,7 @@
         <x:v>自動車材料事業部</x:v>
       </x:c>
       <x:c r="U26" s="1" t="str">
-        <x:v>00075209</x:v>
+        <x:v>00075211</x:v>
       </x:c>
       <x:c r="V26" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -20480,37 +20480,37 @@
         <x:v>1.0000</x:v>
       </x:c>
       <x:c r="AA26" s="4" t="n">
-        <x:v>46219</x:v>
+        <x:v>46224</x:v>
       </x:c>
       <x:c r="AB26" s="1" t="str">
         <x:v>スライス機1　湖南</x:v>
       </x:c>
       <x:c r="AC26" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AD26" s="4" t="n">
-        <x:v>46226</x:v>
+        <x:v>46227</x:v>
       </x:c>
       <x:c r="AE26" s="4" t="n">
-        <x:v>46226</x:v>
+        <x:v>46227</x:v>
       </x:c>
       <x:c r="AF26" s="4" t="n">
-        <x:v>46226</x:v>
+        <x:v>46227</x:v>
       </x:c>
       <x:c r="AG26" s="4" t="str">
         <x:v/>
       </x:c>
       <x:c r="AH26" s="4" t="n">
-        <x:v>46225</x:v>
+        <x:v>46226</x:v>
       </x:c>
       <x:c r="AI26" s="4" t="n">
-        <x:v>46226</x:v>
+        <x:v>46227</x:v>
       </x:c>
       <x:c r="AJ26" s="1" t="str">
         <x:v>0:未完</x:v>
       </x:c>
       <x:c r="AK26" s="6" t="n">
-        <x:v>10000.0000</x:v>
+        <x:v>5750.0000</x:v>
       </x:c>
       <x:c r="AL26" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -20522,7 +20522,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AO26" s="6" t="n">
-        <x:v>10000.0000</x:v>
+        <x:v>5750.0000</x:v>
       </x:c>
       <x:c r="AP26" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -20918,31 +20918,31 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FQ26" s="6" t="n">
-        <x:v>4200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FR26" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FS26" s="8" t="n">
-        <x:v>4.3400</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FT26" s="6" t="n">
-        <x:v>5800.0000</x:v>
+        <x:v>1000.0000</x:v>
       </x:c>
       <x:c r="FU26" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FV26" s="8" t="n">
-        <x:v>6.0000</x:v>
+        <x:v>1.0300</x:v>
       </x:c>
       <x:c r="FW26" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4750.0000</x:v>
       </x:c>
       <x:c r="FX26" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FY26" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4.9100</x:v>
       </x:c>
       <x:c r="FZ26" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -21370,16 +21370,16 @@
         <x:v>スライス</x:v>
       </x:c>
       <x:c r="G27" s="1" t="str">
-        <x:v>020</x:v>
+        <x:v>004</x:v>
       </x:c>
       <x:c r="H27" s="4" t="n">
-        <x:v>46205</x:v>
+        <x:v>46210</x:v>
       </x:c>
       <x:c r="I27" s="1" t="str">
-        <x:v>T7-5</x:v>
+        <x:v>A7-2</x:v>
       </x:c>
       <x:c r="J27" s="1" t="str">
-        <x:v>00081226</x:v>
+        <x:v>00081372</x:v>
       </x:c>
       <x:c r="K27" s="1" t="str">
         <x:v>6710</x:v>
@@ -21388,31 +21388,31 @@
         <x:v>6713</x:v>
       </x:c>
       <x:c r="M27" s="1" t="str">
-        <x:v>20040-AY00- 640X250F-AWH1C</x:v>
+        <x:v>40100-AG00-1080X105F-A   C</x:v>
       </x:c>
       <x:c r="N27" s="1" t="str">
         <x:v/>
       </x:c>
       <x:c r="O27" s="1" t="str">
-        <x:v>20020-BY00- 640X250F-AWH1C</x:v>
+        <x:v>40050-BG00-1080X210F-A   X</x:v>
       </x:c>
       <x:c r="P27" s="6" t="n">
-        <x:v>5750.0000</x:v>
+        <x:v>1260.0000</x:v>
       </x:c>
       <x:c r="Q27" s="8" t="n">
-        <x:v>11500.0000</x:v>
+        <x:v>2520.0000</x:v>
       </x:c>
       <x:c r="R27" s="1" t="str">
-        <x:v>スライス</x:v>
+        <x:v>スライス,接続</x:v>
       </x:c>
       <x:c r="S27" s="1" t="str">
-        <x:v>東レ株式会社</x:v>
+        <x:v>東レペフ加工品株式会社</x:v>
       </x:c>
       <x:c r="T27" s="1" t="str">
-        <x:v>自動車材料事業部</x:v>
+        <x:v>(国分・湖南用)</x:v>
       </x:c>
       <x:c r="U27" s="1" t="str">
-        <x:v>00075211</x:v>
+        <x:v>00075330</x:v>
       </x:c>
       <x:c r="V27" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -21421,7 +21421,7 @@
         <x:v>0001</x:v>
       </x:c>
       <x:c r="X27" s="1" t="str">
-        <x:v>01</x:v>
+        <x:v>02</x:v>
       </x:c>
       <x:c r="Y27" s="6" t="n">
         <x:v>1.0000</x:v>
@@ -21430,7 +21430,7 @@
         <x:v>1.0000</x:v>
       </x:c>
       <x:c r="AA27" s="4" t="n">
-        <x:v>46224</x:v>
+        <x:v>46225</x:v>
       </x:c>
       <x:c r="AB27" s="1" t="str">
         <x:v>スライス機1　湖南</x:v>
@@ -21439,19 +21439,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AD27" s="4" t="n">
-        <x:v>46227</x:v>
+        <x:v>46231</x:v>
       </x:c>
       <x:c r="AE27" s="4" t="n">
-        <x:v>46227</x:v>
+        <x:v>46231</x:v>
       </x:c>
       <x:c r="AF27" s="4" t="n">
-        <x:v>46227</x:v>
+        <x:v>46231</x:v>
       </x:c>
       <x:c r="AG27" s="4" t="str">
         <x:v/>
       </x:c>
       <x:c r="AH27" s="4" t="n">
-        <x:v>46226</x:v>
+        <x:v>46227</x:v>
       </x:c>
       <x:c r="AI27" s="4" t="n">
         <x:v>46227</x:v>
@@ -21460,7 +21460,7 @@
         <x:v>0:未完</x:v>
       </x:c>
       <x:c r="AK27" s="6" t="n">
-        <x:v>5750.0000</x:v>
+        <x:v>1260.0000</x:v>
       </x:c>
       <x:c r="AL27" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -21472,7 +21472,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AO27" s="6" t="n">
-        <x:v>5750.0000</x:v>
+        <x:v>1260.0000</x:v>
       </x:c>
       <x:c r="AP27" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -21877,22 +21877,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FT27" s="6" t="n">
-        <x:v>1000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FU27" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FV27" s="8" t="n">
-        <x:v>1.0300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FW27" s="6" t="n">
-        <x:v>4750.0000</x:v>
+        <x:v>1260.0000</x:v>
       </x:c>
       <x:c r="FX27" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FY27" s="8" t="n">
-        <x:v>4.9100</x:v>
+        <x:v>1.3000</x:v>
       </x:c>
       <x:c r="FZ27" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -22320,16 +22320,16 @@
         <x:v>スライス</x:v>
       </x:c>
       <x:c r="G28" s="1" t="str">
-        <x:v>004</x:v>
+        <x:v>001</x:v>
       </x:c>
       <x:c r="H28" s="4" t="n">
         <x:v>46210</x:v>
       </x:c>
       <x:c r="I28" s="1" t="str">
-        <x:v>A7-2</x:v>
+        <x:v>T7-9</x:v>
       </x:c>
       <x:c r="J28" s="1" t="str">
-        <x:v>00081372</x:v>
+        <x:v>00081374</x:v>
       </x:c>
       <x:c r="K28" s="1" t="str">
         <x:v>6710</x:v>
@@ -22338,31 +22338,31 @@
         <x:v>6713</x:v>
       </x:c>
       <x:c r="M28" s="1" t="str">
-        <x:v>40100-AG00-1080X105F-A   C</x:v>
+        <x:v>30040-AY00- 640X250F-A   C</x:v>
       </x:c>
       <x:c r="N28" s="1" t="str">
         <x:v/>
       </x:c>
       <x:c r="O28" s="1" t="str">
-        <x:v>40050-BG00-1080X210F-A   X</x:v>
+        <x:v>30020-BY00- 640X250F-A   C</x:v>
       </x:c>
       <x:c r="P28" s="6" t="n">
-        <x:v>1260.0000</x:v>
+        <x:v>2750.0000</x:v>
       </x:c>
       <x:c r="Q28" s="8" t="n">
-        <x:v>2520.0000</x:v>
+        <x:v>5500.0000</x:v>
       </x:c>
       <x:c r="R28" s="1" t="str">
-        <x:v>スライス,接続</x:v>
+        <x:v>スライス</x:v>
       </x:c>
       <x:c r="S28" s="1" t="str">
-        <x:v>東レペフ加工品株式会社</x:v>
+        <x:v>東レ株式会社</x:v>
       </x:c>
       <x:c r="T28" s="1" t="str">
-        <x:v>(国分・湖南用)</x:v>
+        <x:v>自動車材料事業部</x:v>
       </x:c>
       <x:c r="U28" s="1" t="str">
-        <x:v>00075330</x:v>
+        <x:v>00075334</x:v>
       </x:c>
       <x:c r="V28" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -22371,7 +22371,7 @@
         <x:v>0001</x:v>
       </x:c>
       <x:c r="X28" s="1" t="str">
-        <x:v>02</x:v>
+        <x:v>01</x:v>
       </x:c>
       <x:c r="Y28" s="6" t="n">
         <x:v>1.0000</x:v>
@@ -22380,7 +22380,7 @@
         <x:v>1.0000</x:v>
       </x:c>
       <x:c r="AA28" s="4" t="n">
-        <x:v>46225</x:v>
+        <x:v>46227</x:v>
       </x:c>
       <x:c r="AB28" s="1" t="str">
         <x:v>スライス機1　湖南</x:v>
@@ -22389,28 +22389,28 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AD28" s="4" t="n">
-        <x:v>46231</x:v>
+        <x:v>46232</x:v>
       </x:c>
       <x:c r="AE28" s="4" t="n">
-        <x:v>46231</x:v>
+        <x:v>46232</x:v>
       </x:c>
       <x:c r="AF28" s="4" t="n">
-        <x:v>46231</x:v>
+        <x:v>46232</x:v>
       </x:c>
       <x:c r="AG28" s="4" t="str">
         <x:v/>
       </x:c>
       <x:c r="AH28" s="4" t="n">
-        <x:v>46227</x:v>
+        <x:v>46230</x:v>
       </x:c>
       <x:c r="AI28" s="4" t="n">
-        <x:v>46227</x:v>
+        <x:v>46230</x:v>
       </x:c>
       <x:c r="AJ28" s="1" t="str">
         <x:v>0:未完</x:v>
       </x:c>
       <x:c r="AK28" s="6" t="n">
-        <x:v>1260.0000</x:v>
+        <x:v>2750.0000</x:v>
       </x:c>
       <x:c r="AL28" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -22422,7 +22422,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AO28" s="6" t="n">
-        <x:v>1260.0000</x:v>
+        <x:v>2750.0000</x:v>
       </x:c>
       <x:c r="AP28" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -22836,13 +22836,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FW28" s="6" t="n">
-        <x:v>1260.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FX28" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FY28" s="8" t="n">
-        <x:v>1.3000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FZ28" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -22863,13 +22863,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GF28" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2750.0000</x:v>
       </x:c>
       <x:c r="GG28" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="GH28" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.8400</x:v>
       </x:c>
       <x:c r="GI28" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -24304,7 +24304,7 @@
         <x:v>46210</x:v>
       </x:c>
       <x:c r="AI30" s="4" t="n">
-        <x:v>46212</x:v>
+        <x:v>46211</x:v>
       </x:c>
       <x:c r="AJ30" s="1" t="str">
         <x:v>1:完了</x:v>
@@ -24592,22 +24592,22 @@
         <x:v>4.1500</x:v>
       </x:c>
       <x:c r="EA30" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1500.0000</x:v>
       </x:c>
       <x:c r="EB30" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EC30" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.3800</x:v>
       </x:c>
       <x:c r="ED30" s="6" t="n">
-        <x:v>1500.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EE30" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EF30" s="8" t="n">
-        <x:v>1.3800</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG30" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -26204,7 +26204,7 @@
         <x:v>46217</x:v>
       </x:c>
       <x:c r="AI32" s="4" t="n">
-        <x:v>46217</x:v>
+        <x:v>46218</x:v>
       </x:c>
       <x:c r="AJ32" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -26546,22 +26546,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES32" s="6" t="n">
-        <x:v>2700.0000</x:v>
+        <x:v>2100.0000</x:v>
       </x:c>
       <x:c r="ET32" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EU32" s="8" t="n">
-        <x:v>2.4900</x:v>
+        <x:v>1.9400</x:v>
       </x:c>
       <x:c r="EV32" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>600.0000</x:v>
       </x:c>
       <x:c r="EW32" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EX32" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.5500</x:v>
       </x:c>
       <x:c r="EY32" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -28101,7 +28101,7 @@
         <x:v/>
       </x:c>
       <x:c r="AH34" s="4" t="n">
-        <x:v>46218</x:v>
+        <x:v>46219</x:v>
       </x:c>
       <x:c r="AI34" s="4" t="n">
         <x:v>46219</x:v>
@@ -28455,22 +28455,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV34" s="6" t="n">
-        <x:v>2400.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EW34" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EX34" s="8" t="n">
-        <x:v>2.2100</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY34" s="6" t="n">
-        <x:v>1500.0000</x:v>
+        <x:v>3900.0000</x:v>
       </x:c>
       <x:c r="EZ34" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="FA34" s="8" t="n">
-        <x:v>1.3800</x:v>
+        <x:v>3.6000</x:v>
       </x:c>
       <x:c r="FB34" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -29920,7 +29920,7 @@
         <x:v>スリット</x:v>
       </x:c>
       <x:c r="G36" s="1" t="str">
-        <x:v>004</x:v>
+        <x:v>003</x:v>
       </x:c>
       <x:c r="H36" s="4" t="n">
         <x:v>46210</x:v>
@@ -33738,7 +33738,7 @@
         <x:v>6713</x:v>
       </x:c>
       <x:c r="M40" s="1" t="str">
-        <x:v>30060-AG00-1000X100F-ABK0C</x:v>
+        <x:v>30100-AG00-1000X100F-ABK0C</x:v>
       </x:c>
       <x:c r="N40" s="1" t="str">
         <x:v/>
@@ -33762,7 +33762,7 @@
         <x:v>自動車材料事業部</x:v>
       </x:c>
       <x:c r="U40" s="1" t="str">
-        <x:v>00075253</x:v>
+        <x:v>00075410</x:v>
       </x:c>
       <x:c r="V40" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -33801,10 +33801,10 @@
         <x:v/>
       </x:c>
       <x:c r="AH40" s="4" t="n">
-        <x:v>46213</x:v>
+        <x:v>46216</x:v>
       </x:c>
       <x:c r="AI40" s="4" t="n">
-        <x:v>46213</x:v>
+        <x:v>46216</x:v>
       </x:c>
       <x:c r="AJ40" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -34110,13 +34110,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG40" s="6" t="n">
-        <x:v>100.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EH40" s="8" t="n">
         <x:v>14.9900</x:v>
       </x:c>
       <x:c r="EI40" s="8" t="n">
-        <x:v>0.1100</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ40" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -34137,13 +34137,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP40" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>100.0000</x:v>
       </x:c>
       <x:c r="EQ40" s="8" t="n">
         <x:v>14.9900</x:v>
       </x:c>
       <x:c r="ER40" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.1100</x:v>
       </x:c>
       <x:c r="ES40" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -34670,7 +34670,7 @@
         <x:v>分割</x:v>
       </x:c>
       <x:c r="G41" s="1" t="str">
-        <x:v>009</x:v>
+        <x:v>008</x:v>
       </x:c>
       <x:c r="H41" s="4" t="n">
         <x:v>46202</x:v>
@@ -35620,7 +35620,7 @@
         <x:v>分割</x:v>
       </x:c>
       <x:c r="G42" s="1" t="str">
-        <x:v>012</x:v>
+        <x:v>011</x:v>
       </x:c>
       <x:c r="H42" s="4" t="n">
         <x:v>46203</x:v>
@@ -36570,7 +36570,7 @@
         <x:v>分割</x:v>
       </x:c>
       <x:c r="G43" s="1" t="str">
-        <x:v>004</x:v>
+        <x:v>005</x:v>
       </x:c>
       <x:c r="H43" s="4" t="n">
         <x:v>46209</x:v>
@@ -37520,7 +37520,7 @@
         <x:v>スリット</x:v>
       </x:c>
       <x:c r="G44" s="1" t="str">
-        <x:v>013</x:v>
+        <x:v>012</x:v>
       </x:c>
       <x:c r="H44" s="4" t="n">
         <x:v>46197</x:v>
@@ -38470,7 +38470,7 @@
         <x:v>スリット</x:v>
       </x:c>
       <x:c r="G45" s="1" t="str">
-        <x:v>011</x:v>
+        <x:v>010</x:v>
       </x:c>
       <x:c r="H45" s="4" t="n">
         <x:v>46204</x:v>
@@ -42351,10 +42351,10 @@
         <x:v/>
       </x:c>
       <x:c r="AH49" s="4" t="n">
-        <x:v>46217</x:v>
+        <x:v>46216</x:v>
       </x:c>
       <x:c r="AI49" s="4" t="n">
-        <x:v>46217</x:v>
+        <x:v>46216</x:v>
       </x:c>
       <x:c r="AJ49" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -42687,22 +42687,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP49" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>400.0000</x:v>
       </x:c>
       <x:c r="EQ49" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="ER49" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.2700</x:v>
       </x:c>
       <x:c r="ES49" s="6" t="n">
-        <x:v>400.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ET49" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EU49" s="8" t="n">
-        <x:v>0.2700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV49" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -46460,13 +46460,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG53" s="6" t="n">
-        <x:v>8400.0000</x:v>
+        <x:v>9200.0000</x:v>
       </x:c>
       <x:c r="EH53" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EI53" s="8" t="n">
-        <x:v>5.6000</x:v>
+        <x:v>6.1300</x:v>
       </x:c>
       <x:c r="EJ53" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -46487,13 +46487,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP53" s="6" t="n">
-        <x:v>1600.0000</x:v>
+        <x:v>800.0000</x:v>
       </x:c>
       <x:c r="EQ53" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="ER53" s="8" t="n">
-        <x:v>1.0700</x:v>
+        <x:v>0.5300</x:v>
       </x:c>
       <x:c r="ES53" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -47101,10 +47101,10 @@
         <x:v/>
       </x:c>
       <x:c r="AH54" s="4" t="n">
-        <x:v>46220</x:v>
+        <x:v>46219</x:v>
       </x:c>
       <x:c r="AI54" s="4" t="n">
-        <x:v>46220</x:v>
+        <x:v>46219</x:v>
       </x:c>
       <x:c r="AJ54" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -47464,22 +47464,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY54" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2000.0000</x:v>
       </x:c>
       <x:c r="EZ54" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FA54" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.3300</x:v>
       </x:c>
       <x:c r="FB54" s="6" t="n">
-        <x:v>2000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FC54" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FD54" s="8" t="n">
-        <x:v>1.3300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FE54" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -47970,7 +47970,7 @@
         <x:v>SEC</x:v>
       </x:c>
       <x:c r="G55" s="1" t="str">
-        <x:v>011</x:v>
+        <x:v>012</x:v>
       </x:c>
       <x:c r="H55" s="4" t="n">
         <x:v>46204</x:v>
@@ -48051,10 +48051,10 @@
         <x:v/>
       </x:c>
       <x:c r="AH55" s="4" t="n">
-        <x:v>46219</x:v>
+        <x:v>46218</x:v>
       </x:c>
       <x:c r="AI55" s="4" t="n">
-        <x:v>46219</x:v>
+        <x:v>46218</x:v>
       </x:c>
       <x:c r="AJ55" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -48405,22 +48405,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV55" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>200.0000</x:v>
       </x:c>
       <x:c r="EW55" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EX55" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.1300</x:v>
       </x:c>
       <x:c r="EY55" s="6" t="n">
-        <x:v>200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EZ55" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FA55" s="8" t="n">
-        <x:v>0.1300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB55" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -49870,7 +49870,7 @@
         <x:v>SEC</x:v>
       </x:c>
       <x:c r="G57" s="1" t="str">
-        <x:v>010</x:v>
+        <x:v>011</x:v>
       </x:c>
       <x:c r="H57" s="4" t="n">
         <x:v>46209</x:v>
@@ -49972,7 +49972,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="AO57" s="6" t="n">
-        <x:v>10000.0000</x:v>
+        <x:v>13200.0000</x:v>
       </x:c>
       <x:c r="AP57" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -50314,22 +50314,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY57" s="6" t="n">
-        <x:v>1000.0000</x:v>
+        <x:v>2800.0000</x:v>
       </x:c>
       <x:c r="EZ57" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FA57" s="8" t="n">
-        <x:v>0.6700</x:v>
+        <x:v>1.8700</x:v>
       </x:c>
       <x:c r="FB57" s="6" t="n">
-        <x:v>5800.0000</x:v>
+        <x:v>7200.0000</x:v>
       </x:c>
       <x:c r="FC57" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FD57" s="8" t="n">
-        <x:v>3.8700</x:v>
+        <x:v>4.8000</x:v>
       </x:c>
       <x:c r="FE57" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -50901,10 +50901,10 @@
         <x:v/>
       </x:c>
       <x:c r="AH58" s="4" t="n">
-        <x:v>46225</x:v>
+        <x:v>46224</x:v>
       </x:c>
       <x:c r="AI58" s="4" t="n">
-        <x:v>46225</x:v>
+        <x:v>46224</x:v>
       </x:c>
       <x:c r="AJ58" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -51309,22 +51309,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FN58" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>10000.0000</x:v>
       </x:c>
       <x:c r="FO58" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FP58" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6.6700</x:v>
       </x:c>
       <x:c r="FQ58" s="6" t="n">
-        <x:v>10000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FR58" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FS58" s="8" t="n">
-        <x:v>6.6700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FT58" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -51797,10 +51797,10 @@
         <x:v>0R040-8Y0B- 680X200F-AGA1C</x:v>
       </x:c>
       <x:c r="P59" s="6" t="n">
-        <x:v>3200.0000</x:v>
+        <x:v>3400.0000</x:v>
       </x:c>
       <x:c r="Q59" s="8" t="n">
-        <x:v>6400.0000</x:v>
+        <x:v>6800.0000</x:v>
       </x:c>
       <x:c r="R59" s="1" t="str">
         <x:v>SEC</x:v>
@@ -51860,7 +51860,7 @@
         <x:v>0:未完</x:v>
       </x:c>
       <x:c r="AK59" s="6" t="n">
-        <x:v>3200.0000</x:v>
+        <x:v>3400.0000</x:v>
       </x:c>
       <x:c r="AL59" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -52286,22 +52286,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FW59" s="6" t="n">
+        <x:v>2000.0000</x:v>
+      </x:c>
+      <x:c r="FX59" s="8" t="n">
+        <x:v>25.0000</x:v>
+      </x:c>
+      <x:c r="FY59" s="8" t="n">
+        <x:v>1.3300</x:v>
+      </x:c>
+      <x:c r="FZ59" s="6" t="n">
         <x:v>1200.0000</x:v>
       </x:c>
-      <x:c r="FX59" s="8" t="n">
-        <x:v>25.0000</x:v>
-      </x:c>
-      <x:c r="FY59" s="8" t="n">
+      <x:c r="GA59" s="8" t="n">
+        <x:v>25.0000</x:v>
+      </x:c>
+      <x:c r="GB59" s="8" t="n">
         <x:v>0.8000</x:v>
-      </x:c>
-      <x:c r="FZ59" s="6" t="n">
-        <x:v>2000.0000</x:v>
-      </x:c>
-      <x:c r="GA59" s="8" t="n">
-        <x:v>25.0000</x:v>
-      </x:c>
-      <x:c r="GB59" s="8" t="n">
-        <x:v>1.3300</x:v>
       </x:c>
       <x:c r="GC59" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -53670,7 +53670,7 @@
         <x:v>SEC</x:v>
       </x:c>
       <x:c r="G61" s="1" t="str">
-        <x:v>008</x:v>
+        <x:v>009</x:v>
       </x:c>
       <x:c r="H61" s="4" t="n">
         <x:v>46209</x:v>
@@ -53751,10 +53751,10 @@
         <x:v/>
       </x:c>
       <x:c r="AH61" s="4" t="n">
-        <x:v>46224</x:v>
+        <x:v>46225</x:v>
       </x:c>
       <x:c r="AI61" s="4" t="n">
-        <x:v>46227</x:v>
+        <x:v>46225</x:v>
       </x:c>
       <x:c r="AJ61" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -54159,40 +54159,40 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FN61" s="6" t="n">
-        <x:v>5800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FO61" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FP61" s="8" t="n">
-        <x:v>3.8700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FQ61" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>10000.0000</x:v>
       </x:c>
       <x:c r="FR61" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FS61" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6.6700</x:v>
       </x:c>
       <x:c r="FT61" s="6" t="n">
-        <x:v>4000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FU61" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FV61" s="8" t="n">
-        <x:v>2.6700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FW61" s="6" t="n">
-        <x:v>200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FX61" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FY61" s="8" t="n">
-        <x:v>0.1300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FZ61" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -55615,7 +55615,7 @@
         <x:v>00074866</x:v>
       </x:c>
       <x:c r="V63" s="1" t="str">
-        <x:v>0:未完</x:v>
+        <x:v>1:完了</x:v>
       </x:c>
       <x:c r="W63" s="1" t="str">
         <x:v>0019</x:v>
@@ -55669,7 +55669,7 @@
         <x:v>1500.0000</x:v>
       </x:c>
       <x:c r="AN63" s="6" t="n">
-        <x:v>3300.0000</x:v>
+        <x:v>4500.0000</x:v>
       </x:c>
       <x:c r="AO63" s="6" t="n">
         <x:v>6000.0000</x:v>
@@ -66392,31 +66392,31 @@
         <x:v>9.5500</x:v>
       </x:c>
       <x:c r="EA74" s="7" t="n">
-        <x:v>600.0000</x:v>
+        <x:v>2100.0000</x:v>
       </x:c>
       <x:c r="EB74" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="EC74" s="9" t="n">
-        <x:v>1.0500</x:v>
+        <x:v>2.4300</x:v>
       </x:c>
       <x:c r="ED74" s="7" t="n">
-        <x:v>13800.0000</x:v>
+        <x:v>12500.0000</x:v>
       </x:c>
       <x:c r="EE74" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="EF74" s="9" t="n">
-        <x:v>17.3300</x:v>
+        <x:v>16.1600</x:v>
       </x:c>
       <x:c r="EG74" s="7" t="n">
-        <x:v>15400.0000</x:v>
+        <x:v>15900.0000</x:v>
       </x:c>
       <x:c r="EH74" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="EI74" s="9" t="n">
-        <x:v>16.0800</x:v>
+        <x:v>16.3000</x:v>
       </x:c>
       <x:c r="EJ74" s="7" t="n">
         <x:v>0.0000</x:v>
@@ -66437,49 +66437,49 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP74" s="7" t="n">
-        <x:v>23700.0000</x:v>
+        <x:v>23400.0000</x:v>
       </x:c>
       <x:c r="EQ74" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="ER74" s="9" t="n">
-        <x:v>27.4900</x:v>
+        <x:v>27.3300</x:v>
       </x:c>
       <x:c r="ES74" s="7" t="n">
-        <x:v>5700.0000</x:v>
+        <x:v>4700.0000</x:v>
       </x:c>
       <x:c r="ET74" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="EU74" s="9" t="n">
-        <x:v>5.7300</x:v>
+        <x:v>4.9100</x:v>
       </x:c>
       <x:c r="EV74" s="7" t="n">
-        <x:v>15400.0000</x:v>
+        <x:v>13800.0000</x:v>
       </x:c>
       <x:c r="EW74" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="EX74" s="9" t="n">
-        <x:v>19.8300</x:v>
+        <x:v>18.3000</x:v>
       </x:c>
       <x:c r="EY74" s="7" t="n">
-        <x:v>14500.0000</x:v>
+        <x:v>20500.0000</x:v>
       </x:c>
       <x:c r="EZ74" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FA74" s="9" t="n">
-        <x:v>16.4200</x:v>
+        <x:v>21.0400</x:v>
       </x:c>
       <x:c r="FB74" s="7" t="n">
-        <x:v>16400.0000</x:v>
+        <x:v>15800.0000</x:v>
       </x:c>
       <x:c r="FC74" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FD74" s="9" t="n">
-        <x:v>13.6900</x:v>
+        <x:v>13.2900</x:v>
       </x:c>
       <x:c r="FE74" s="7" t="n">
         <x:v>0.0000</x:v>
@@ -66509,13 +66509,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FN74" s="7" t="n">
-        <x:v>16200.0000</x:v>
+        <x:v>20400.0000</x:v>
       </x:c>
       <x:c r="FO74" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FP74" s="9" t="n">
-        <x:v>13.4400</x:v>
+        <x:v>16.2400</x:v>
       </x:c>
       <x:c r="FQ74" s="7" t="n">
         <x:v>17200.0000</x:v>
@@ -66527,31 +66527,31 @@
         <x:v>14.1100</x:v>
       </x:c>
       <x:c r="FT74" s="7" t="n">
-        <x:v>12270.0000</x:v>
+        <x:v>8270.0000</x:v>
       </x:c>
       <x:c r="FU74" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FV74" s="9" t="n">
-        <x:v>10.9300</x:v>
+        <x:v>8.2600</x:v>
       </x:c>
       <x:c r="FW74" s="7" t="n">
-        <x:v>11670.0000</x:v>
+        <x:v>12270.0000</x:v>
       </x:c>
       <x:c r="FX74" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FY74" s="9" t="n">
-        <x:v>10.1900</x:v>
+        <x:v>10.5900</x:v>
       </x:c>
       <x:c r="FZ74" s="7" t="n">
-        <x:v>12350.0000</x:v>
+        <x:v>11550.0000</x:v>
       </x:c>
       <x:c r="GA74" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="GB74" s="9" t="n">
-        <x:v>11.2100</x:v>
+        <x:v>10.6800</x:v>
       </x:c>
       <x:c r="GC74" s="7" t="n">
         <x:v>0.0000</x:v>

--- a/.pm-ai-cache/network-source/task-input-newest.xlsx
+++ b/.pm-ai-cache/network-source/task-input-newest.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工程別生産計画問合せ問合せ" sheetId="1" r:id="Ra71838a6c6d349c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工程別生産計画問合せ問合せ" sheetId="1" r:id="R7e23442506d04a1f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -10,7 +10,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6">
   <x:si>
-    <x:t xml:space="preserve">表示基準日 : 2026年07月10日 </x:t>
+    <x:t xml:space="preserve">表示基準日 : 2026年07月12日 </x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">S </x:t>
@@ -581,823 +581,823 @@
         <x:v/>
       </x:c>
       <x:c r="AR5" s="2" t="str">
-        <x:v>06/10(水)</x:v>
+        <x:v>06/12(金)</x:v>
       </x:c>
       <x:c r="AS5" s="2" t="str">
-        <x:v>06/10(水)</x:v>
+        <x:v>06/12(金)</x:v>
       </x:c>
       <x:c r="AT5" s="2" t="str">
-        <x:v>06/10(水)</x:v>
+        <x:v>06/12(金)</x:v>
       </x:c>
       <x:c r="AU5" s="2" t="str">
-        <x:v>06/11(木)</x:v>
+        <x:v>06/13(土)</x:v>
       </x:c>
       <x:c r="AV5" s="2" t="str">
-        <x:v>06/11(木)</x:v>
+        <x:v>06/13(土)</x:v>
       </x:c>
       <x:c r="AW5" s="2" t="str">
-        <x:v>06/11(木)</x:v>
+        <x:v>06/13(土)</x:v>
       </x:c>
       <x:c r="AX5" s="2" t="str">
-        <x:v>06/12(金)</x:v>
+        <x:v>06/14(日)</x:v>
       </x:c>
       <x:c r="AY5" s="2" t="str">
-        <x:v>06/12(金)</x:v>
+        <x:v>06/14(日)</x:v>
       </x:c>
       <x:c r="AZ5" s="2" t="str">
-        <x:v>06/12(金)</x:v>
+        <x:v>06/14(日)</x:v>
       </x:c>
       <x:c r="BA5" s="2" t="str">
-        <x:v>06/13(土)</x:v>
+        <x:v>06/15(月)</x:v>
       </x:c>
       <x:c r="BB5" s="2" t="str">
-        <x:v>06/13(土)</x:v>
+        <x:v>06/15(月)</x:v>
       </x:c>
       <x:c r="BC5" s="2" t="str">
-        <x:v>06/13(土)</x:v>
+        <x:v>06/15(月)</x:v>
       </x:c>
       <x:c r="BD5" s="2" t="str">
-        <x:v>06/14(日)</x:v>
+        <x:v>06/16(火)</x:v>
       </x:c>
       <x:c r="BE5" s="2" t="str">
-        <x:v>06/14(日)</x:v>
+        <x:v>06/16(火)</x:v>
       </x:c>
       <x:c r="BF5" s="2" t="str">
-        <x:v>06/14(日)</x:v>
+        <x:v>06/16(火)</x:v>
       </x:c>
       <x:c r="BG5" s="2" t="str">
-        <x:v>06/15(月)</x:v>
+        <x:v>06/17(水)</x:v>
       </x:c>
       <x:c r="BH5" s="2" t="str">
-        <x:v>06/15(月)</x:v>
+        <x:v>06/17(水)</x:v>
       </x:c>
       <x:c r="BI5" s="2" t="str">
-        <x:v>06/15(月)</x:v>
+        <x:v>06/17(水)</x:v>
       </x:c>
       <x:c r="BJ5" s="2" t="str">
-        <x:v>06/16(火)</x:v>
+        <x:v>06/18(木)</x:v>
       </x:c>
       <x:c r="BK5" s="2" t="str">
-        <x:v>06/16(火)</x:v>
+        <x:v>06/18(木)</x:v>
       </x:c>
       <x:c r="BL5" s="2" t="str">
-        <x:v>06/16(火)</x:v>
+        <x:v>06/18(木)</x:v>
       </x:c>
       <x:c r="BM5" s="2" t="str">
-        <x:v>06/17(水)</x:v>
+        <x:v>06/19(金)</x:v>
       </x:c>
       <x:c r="BN5" s="2" t="str">
-        <x:v>06/17(水)</x:v>
+        <x:v>06/19(金)</x:v>
       </x:c>
       <x:c r="BO5" s="2" t="str">
-        <x:v>06/17(水)</x:v>
+        <x:v>06/19(金)</x:v>
       </x:c>
       <x:c r="BP5" s="2" t="str">
-        <x:v>06/18(木)</x:v>
+        <x:v>06/20(土)</x:v>
       </x:c>
       <x:c r="BQ5" s="2" t="str">
-        <x:v>06/18(木)</x:v>
+        <x:v>06/20(土)</x:v>
       </x:c>
       <x:c r="BR5" s="2" t="str">
-        <x:v>06/18(木)</x:v>
+        <x:v>06/20(土)</x:v>
       </x:c>
       <x:c r="BS5" s="2" t="str">
-        <x:v>06/19(金)</x:v>
+        <x:v>06/21(日)</x:v>
       </x:c>
       <x:c r="BT5" s="2" t="str">
-        <x:v>06/19(金)</x:v>
+        <x:v>06/21(日)</x:v>
       </x:c>
       <x:c r="BU5" s="2" t="str">
-        <x:v>06/19(金)</x:v>
+        <x:v>06/21(日)</x:v>
       </x:c>
       <x:c r="BV5" s="2" t="str">
-        <x:v>06/20(土)</x:v>
+        <x:v>06/22(月)</x:v>
       </x:c>
       <x:c r="BW5" s="2" t="str">
-        <x:v>06/20(土)</x:v>
+        <x:v>06/22(月)</x:v>
       </x:c>
       <x:c r="BX5" s="2" t="str">
-        <x:v>06/20(土)</x:v>
+        <x:v>06/22(月)</x:v>
       </x:c>
       <x:c r="BY5" s="2" t="str">
-        <x:v>06/21(日)</x:v>
+        <x:v>06/23(火)</x:v>
       </x:c>
       <x:c r="BZ5" s="2" t="str">
-        <x:v>06/21(日)</x:v>
+        <x:v>06/23(火)</x:v>
       </x:c>
       <x:c r="CA5" s="2" t="str">
-        <x:v>06/21(日)</x:v>
+        <x:v>06/23(火)</x:v>
       </x:c>
       <x:c r="CB5" s="2" t="str">
-        <x:v>06/22(月)</x:v>
+        <x:v>06/24(水)</x:v>
       </x:c>
       <x:c r="CC5" s="2" t="str">
-        <x:v>06/22(月)</x:v>
+        <x:v>06/24(水)</x:v>
       </x:c>
       <x:c r="CD5" s="2" t="str">
-        <x:v>06/22(月)</x:v>
+        <x:v>06/24(水)</x:v>
       </x:c>
       <x:c r="CE5" s="2" t="str">
-        <x:v>06/23(火)</x:v>
+        <x:v>06/25(木)</x:v>
       </x:c>
       <x:c r="CF5" s="2" t="str">
-        <x:v>06/23(火)</x:v>
+        <x:v>06/25(木)</x:v>
       </x:c>
       <x:c r="CG5" s="2" t="str">
-        <x:v>06/23(火)</x:v>
+        <x:v>06/25(木)</x:v>
       </x:c>
       <x:c r="CH5" s="2" t="str">
-        <x:v>06/24(水)</x:v>
+        <x:v>06/26(金)</x:v>
       </x:c>
       <x:c r="CI5" s="2" t="str">
-        <x:v>06/24(水)</x:v>
+        <x:v>06/26(金)</x:v>
       </x:c>
       <x:c r="CJ5" s="2" t="str">
-        <x:v>06/24(水)</x:v>
+        <x:v>06/26(金)</x:v>
       </x:c>
       <x:c r="CK5" s="2" t="str">
-        <x:v>06/25(木)</x:v>
+        <x:v>06/27(土)</x:v>
       </x:c>
       <x:c r="CL5" s="2" t="str">
-        <x:v>06/25(木)</x:v>
+        <x:v>06/27(土)</x:v>
       </x:c>
       <x:c r="CM5" s="2" t="str">
-        <x:v>06/25(木)</x:v>
+        <x:v>06/27(土)</x:v>
       </x:c>
       <x:c r="CN5" s="2" t="str">
-        <x:v>06/26(金)</x:v>
+        <x:v>06/28(日)</x:v>
       </x:c>
       <x:c r="CO5" s="2" t="str">
-        <x:v>06/26(金)</x:v>
+        <x:v>06/28(日)</x:v>
       </x:c>
       <x:c r="CP5" s="2" t="str">
-        <x:v>06/26(金)</x:v>
+        <x:v>06/28(日)</x:v>
       </x:c>
       <x:c r="CQ5" s="2" t="str">
-        <x:v>06/27(土)</x:v>
+        <x:v>06/29(月)</x:v>
       </x:c>
       <x:c r="CR5" s="2" t="str">
-        <x:v>06/27(土)</x:v>
+        <x:v>06/29(月)</x:v>
       </x:c>
       <x:c r="CS5" s="2" t="str">
-        <x:v>06/27(土)</x:v>
+        <x:v>06/29(月)</x:v>
       </x:c>
       <x:c r="CT5" s="2" t="str">
-        <x:v>06/28(日)</x:v>
+        <x:v>06/30(火)</x:v>
       </x:c>
       <x:c r="CU5" s="2" t="str">
-        <x:v>06/28(日)</x:v>
+        <x:v>06/30(火)</x:v>
       </x:c>
       <x:c r="CV5" s="2" t="str">
-        <x:v>06/28(日)</x:v>
+        <x:v>06/30(火)</x:v>
       </x:c>
       <x:c r="CW5" s="2" t="str">
-        <x:v>06/29(月)</x:v>
+        <x:v>07/01(水)</x:v>
       </x:c>
       <x:c r="CX5" s="2" t="str">
-        <x:v>06/29(月)</x:v>
+        <x:v>07/01(水)</x:v>
       </x:c>
       <x:c r="CY5" s="2" t="str">
-        <x:v>06/29(月)</x:v>
+        <x:v>07/01(水)</x:v>
       </x:c>
       <x:c r="CZ5" s="2" t="str">
-        <x:v>06/30(火)</x:v>
+        <x:v>07/02(木)</x:v>
       </x:c>
       <x:c r="DA5" s="2" t="str">
-        <x:v>06/30(火)</x:v>
+        <x:v>07/02(木)</x:v>
       </x:c>
       <x:c r="DB5" s="2" t="str">
-        <x:v>06/30(火)</x:v>
+        <x:v>07/02(木)</x:v>
       </x:c>
       <x:c r="DC5" s="2" t="str">
-        <x:v>07/01(水)</x:v>
+        <x:v>07/03(金)</x:v>
       </x:c>
       <x:c r="DD5" s="2" t="str">
-        <x:v>07/01(水)</x:v>
+        <x:v>07/03(金)</x:v>
       </x:c>
       <x:c r="DE5" s="2" t="str">
-        <x:v>07/01(水)</x:v>
+        <x:v>07/03(金)</x:v>
       </x:c>
       <x:c r="DF5" s="2" t="str">
-        <x:v>07/02(木)</x:v>
+        <x:v>07/04(土)</x:v>
       </x:c>
       <x:c r="DG5" s="2" t="str">
-        <x:v>07/02(木)</x:v>
+        <x:v>07/04(土)</x:v>
       </x:c>
       <x:c r="DH5" s="2" t="str">
-        <x:v>07/02(木)</x:v>
+        <x:v>07/04(土)</x:v>
       </x:c>
       <x:c r="DI5" s="2" t="str">
-        <x:v>07/03(金)</x:v>
+        <x:v>07/05(日)</x:v>
       </x:c>
       <x:c r="DJ5" s="2" t="str">
-        <x:v>07/03(金)</x:v>
+        <x:v>07/05(日)</x:v>
       </x:c>
       <x:c r="DK5" s="2" t="str">
-        <x:v>07/03(金)</x:v>
+        <x:v>07/05(日)</x:v>
       </x:c>
       <x:c r="DL5" s="2" t="str">
-        <x:v>07/04(土)</x:v>
+        <x:v>07/06(月)</x:v>
       </x:c>
       <x:c r="DM5" s="2" t="str">
-        <x:v>07/04(土)</x:v>
+        <x:v>07/06(月)</x:v>
       </x:c>
       <x:c r="DN5" s="2" t="str">
-        <x:v>07/04(土)</x:v>
+        <x:v>07/06(月)</x:v>
       </x:c>
       <x:c r="DO5" s="2" t="str">
-        <x:v>07/05(日)</x:v>
+        <x:v>07/07(火)</x:v>
       </x:c>
       <x:c r="DP5" s="2" t="str">
-        <x:v>07/05(日)</x:v>
+        <x:v>07/07(火)</x:v>
       </x:c>
       <x:c r="DQ5" s="2" t="str">
-        <x:v>07/05(日)</x:v>
+        <x:v>07/07(火)</x:v>
       </x:c>
       <x:c r="DR5" s="2" t="str">
-        <x:v>07/06(月)</x:v>
+        <x:v>07/08(水)</x:v>
       </x:c>
       <x:c r="DS5" s="2" t="str">
-        <x:v>07/06(月)</x:v>
+        <x:v>07/08(水)</x:v>
       </x:c>
       <x:c r="DT5" s="2" t="str">
-        <x:v>07/06(月)</x:v>
+        <x:v>07/08(水)</x:v>
       </x:c>
       <x:c r="DU5" s="2" t="str">
-        <x:v>07/07(火)</x:v>
+        <x:v>07/09(木)</x:v>
       </x:c>
       <x:c r="DV5" s="2" t="str">
-        <x:v>07/07(火)</x:v>
+        <x:v>07/09(木)</x:v>
       </x:c>
       <x:c r="DW5" s="2" t="str">
-        <x:v>07/07(火)</x:v>
+        <x:v>07/09(木)</x:v>
       </x:c>
       <x:c r="DX5" s="2" t="str">
-        <x:v>07/08(水)</x:v>
+        <x:v>07/10(金)</x:v>
       </x:c>
       <x:c r="DY5" s="2" t="str">
-        <x:v>07/08(水)</x:v>
+        <x:v>07/10(金)</x:v>
       </x:c>
       <x:c r="DZ5" s="2" t="str">
-        <x:v>07/08(水)</x:v>
+        <x:v>07/10(金)</x:v>
       </x:c>
       <x:c r="EA5" s="2" t="str">
-        <x:v>07/09(木)</x:v>
+        <x:v>07/11(土)</x:v>
       </x:c>
       <x:c r="EB5" s="2" t="str">
-        <x:v>07/09(木)</x:v>
+        <x:v>07/11(土)</x:v>
       </x:c>
       <x:c r="EC5" s="2" t="str">
-        <x:v>07/09(木)</x:v>
+        <x:v>07/11(土)</x:v>
       </x:c>
       <x:c r="ED5" s="2" t="str">
-        <x:v>07/10(金)</x:v>
+        <x:v>07/12(日)</x:v>
       </x:c>
       <x:c r="EE5" s="2" t="str">
-        <x:v>07/10(金)</x:v>
+        <x:v>07/12(日)</x:v>
       </x:c>
       <x:c r="EF5" s="2" t="str">
-        <x:v>07/10(金)</x:v>
+        <x:v>07/12(日)</x:v>
       </x:c>
       <x:c r="EG5" s="2" t="str">
-        <x:v>07/11(土)</x:v>
+        <x:v>07/13(月)</x:v>
       </x:c>
       <x:c r="EH5" s="2" t="str">
-        <x:v>07/11(土)</x:v>
+        <x:v>07/13(月)</x:v>
       </x:c>
       <x:c r="EI5" s="2" t="str">
-        <x:v>07/11(土)</x:v>
+        <x:v>07/13(月)</x:v>
       </x:c>
       <x:c r="EJ5" s="2" t="str">
-        <x:v>07/12(日)</x:v>
+        <x:v>07/14(火)</x:v>
       </x:c>
       <x:c r="EK5" s="2" t="str">
-        <x:v>07/12(日)</x:v>
+        <x:v>07/14(火)</x:v>
       </x:c>
       <x:c r="EL5" s="2" t="str">
-        <x:v>07/12(日)</x:v>
+        <x:v>07/14(火)</x:v>
       </x:c>
       <x:c r="EM5" s="2" t="str">
-        <x:v>07/13(月)</x:v>
+        <x:v>07/15(水)</x:v>
       </x:c>
       <x:c r="EN5" s="2" t="str">
-        <x:v>07/13(月)</x:v>
+        <x:v>07/15(水)</x:v>
       </x:c>
       <x:c r="EO5" s="2" t="str">
-        <x:v>07/13(月)</x:v>
+        <x:v>07/15(水)</x:v>
       </x:c>
       <x:c r="EP5" s="2" t="str">
-        <x:v>07/14(火)</x:v>
+        <x:v>07/16(木)</x:v>
       </x:c>
       <x:c r="EQ5" s="2" t="str">
-        <x:v>07/14(火)</x:v>
+        <x:v>07/16(木)</x:v>
       </x:c>
       <x:c r="ER5" s="2" t="str">
-        <x:v>07/14(火)</x:v>
+        <x:v>07/16(木)</x:v>
       </x:c>
       <x:c r="ES5" s="2" t="str">
-        <x:v>07/15(水)</x:v>
+        <x:v>07/17(金)</x:v>
       </x:c>
       <x:c r="ET5" s="2" t="str">
-        <x:v>07/15(水)</x:v>
+        <x:v>07/17(金)</x:v>
       </x:c>
       <x:c r="EU5" s="2" t="str">
-        <x:v>07/15(水)</x:v>
+        <x:v>07/17(金)</x:v>
       </x:c>
       <x:c r="EV5" s="2" t="str">
-        <x:v>07/16(木)</x:v>
+        <x:v>07/18(土)</x:v>
       </x:c>
       <x:c r="EW5" s="2" t="str">
-        <x:v>07/16(木)</x:v>
+        <x:v>07/18(土)</x:v>
       </x:c>
       <x:c r="EX5" s="2" t="str">
-        <x:v>07/16(木)</x:v>
+        <x:v>07/18(土)</x:v>
       </x:c>
       <x:c r="EY5" s="2" t="str">
-        <x:v>07/17(金)</x:v>
+        <x:v>07/19(日)</x:v>
       </x:c>
       <x:c r="EZ5" s="2" t="str">
-        <x:v>07/17(金)</x:v>
+        <x:v>07/19(日)</x:v>
       </x:c>
       <x:c r="FA5" s="2" t="str">
-        <x:v>07/17(金)</x:v>
+        <x:v>07/19(日)</x:v>
       </x:c>
       <x:c r="FB5" s="2" t="str">
-        <x:v>07/18(土)</x:v>
+        <x:v>07/20(月)</x:v>
       </x:c>
       <x:c r="FC5" s="2" t="str">
-        <x:v>07/18(土)</x:v>
+        <x:v>07/20(月)</x:v>
       </x:c>
       <x:c r="FD5" s="2" t="str">
-        <x:v>07/18(土)</x:v>
+        <x:v>07/20(月)</x:v>
       </x:c>
       <x:c r="FE5" s="2" t="str">
-        <x:v>07/19(日)</x:v>
+        <x:v>07/21(火)</x:v>
       </x:c>
       <x:c r="FF5" s="2" t="str">
-        <x:v>07/19(日)</x:v>
+        <x:v>07/21(火)</x:v>
       </x:c>
       <x:c r="FG5" s="2" t="str">
-        <x:v>07/19(日)</x:v>
+        <x:v>07/21(火)</x:v>
       </x:c>
       <x:c r="FH5" s="2" t="str">
-        <x:v>07/20(月)</x:v>
+        <x:v>07/22(水)</x:v>
       </x:c>
       <x:c r="FI5" s="2" t="str">
-        <x:v>07/20(月)</x:v>
+        <x:v>07/22(水)</x:v>
       </x:c>
       <x:c r="FJ5" s="2" t="str">
-        <x:v>07/20(月)</x:v>
+        <x:v>07/22(水)</x:v>
       </x:c>
       <x:c r="FK5" s="2" t="str">
-        <x:v>07/21(火)</x:v>
+        <x:v>07/23(木)</x:v>
       </x:c>
       <x:c r="FL5" s="2" t="str">
-        <x:v>07/21(火)</x:v>
+        <x:v>07/23(木)</x:v>
       </x:c>
       <x:c r="FM5" s="2" t="str">
-        <x:v>07/21(火)</x:v>
+        <x:v>07/23(木)</x:v>
       </x:c>
       <x:c r="FN5" s="2" t="str">
-        <x:v>07/22(水)</x:v>
+        <x:v>07/24(金)</x:v>
       </x:c>
       <x:c r="FO5" s="2" t="str">
-        <x:v>07/22(水)</x:v>
+        <x:v>07/24(金)</x:v>
       </x:c>
       <x:c r="FP5" s="2" t="str">
-        <x:v>07/22(水)</x:v>
+        <x:v>07/24(金)</x:v>
       </x:c>
       <x:c r="FQ5" s="2" t="str">
-        <x:v>07/23(木)</x:v>
+        <x:v>07/25(土)</x:v>
       </x:c>
       <x:c r="FR5" s="2" t="str">
-        <x:v>07/23(木)</x:v>
+        <x:v>07/25(土)</x:v>
       </x:c>
       <x:c r="FS5" s="2" t="str">
-        <x:v>07/23(木)</x:v>
+        <x:v>07/25(土)</x:v>
       </x:c>
       <x:c r="FT5" s="2" t="str">
-        <x:v>07/24(金)</x:v>
+        <x:v>07/26(日)</x:v>
       </x:c>
       <x:c r="FU5" s="2" t="str">
-        <x:v>07/24(金)</x:v>
+        <x:v>07/26(日)</x:v>
       </x:c>
       <x:c r="FV5" s="2" t="str">
-        <x:v>07/24(金)</x:v>
+        <x:v>07/26(日)</x:v>
       </x:c>
       <x:c r="FW5" s="2" t="str">
-        <x:v>07/25(土)</x:v>
+        <x:v>07/27(月)</x:v>
       </x:c>
       <x:c r="FX5" s="2" t="str">
-        <x:v>07/25(土)</x:v>
+        <x:v>07/27(月)</x:v>
       </x:c>
       <x:c r="FY5" s="2" t="str">
-        <x:v>07/25(土)</x:v>
+        <x:v>07/27(月)</x:v>
       </x:c>
       <x:c r="FZ5" s="2" t="str">
-        <x:v>07/26(日)</x:v>
+        <x:v>07/28(火)</x:v>
       </x:c>
       <x:c r="GA5" s="2" t="str">
-        <x:v>07/26(日)</x:v>
+        <x:v>07/28(火)</x:v>
       </x:c>
       <x:c r="GB5" s="2" t="str">
-        <x:v>07/26(日)</x:v>
+        <x:v>07/28(火)</x:v>
       </x:c>
       <x:c r="GC5" s="2" t="str">
-        <x:v>07/27(月)</x:v>
+        <x:v>07/29(水)</x:v>
       </x:c>
       <x:c r="GD5" s="2" t="str">
-        <x:v>07/27(月)</x:v>
+        <x:v>07/29(水)</x:v>
       </x:c>
       <x:c r="GE5" s="2" t="str">
-        <x:v>07/27(月)</x:v>
+        <x:v>07/29(水)</x:v>
       </x:c>
       <x:c r="GF5" s="2" t="str">
-        <x:v>07/28(火)</x:v>
+        <x:v>07/30(木)</x:v>
       </x:c>
       <x:c r="GG5" s="2" t="str">
-        <x:v>07/28(火)</x:v>
+        <x:v>07/30(木)</x:v>
       </x:c>
       <x:c r="GH5" s="2" t="str">
-        <x:v>07/28(火)</x:v>
+        <x:v>07/30(木)</x:v>
       </x:c>
       <x:c r="GI5" s="2" t="str">
-        <x:v>07/29(水)</x:v>
+        <x:v>07/31(金)</x:v>
       </x:c>
       <x:c r="GJ5" s="2" t="str">
-        <x:v>07/29(水)</x:v>
+        <x:v>07/31(金)</x:v>
       </x:c>
       <x:c r="GK5" s="2" t="str">
-        <x:v>07/29(水)</x:v>
+        <x:v>07/31(金)</x:v>
       </x:c>
       <x:c r="GL5" s="2" t="str">
-        <x:v>07/30(木)</x:v>
+        <x:v>08/01(土)</x:v>
       </x:c>
       <x:c r="GM5" s="2" t="str">
-        <x:v>07/30(木)</x:v>
+        <x:v>08/01(土)</x:v>
       </x:c>
       <x:c r="GN5" s="2" t="str">
-        <x:v>07/30(木)</x:v>
+        <x:v>08/01(土)</x:v>
       </x:c>
       <x:c r="GO5" s="2" t="str">
-        <x:v>07/31(金)</x:v>
+        <x:v>08/02(日)</x:v>
       </x:c>
       <x:c r="GP5" s="2" t="str">
-        <x:v>07/31(金)</x:v>
+        <x:v>08/02(日)</x:v>
       </x:c>
       <x:c r="GQ5" s="2" t="str">
-        <x:v>07/31(金)</x:v>
+        <x:v>08/02(日)</x:v>
       </x:c>
       <x:c r="GR5" s="2" t="str">
-        <x:v>08/01(土)</x:v>
+        <x:v>08/03(月)</x:v>
       </x:c>
       <x:c r="GS5" s="2" t="str">
-        <x:v>08/01(土)</x:v>
+        <x:v>08/03(月)</x:v>
       </x:c>
       <x:c r="GT5" s="2" t="str">
-        <x:v>08/01(土)</x:v>
+        <x:v>08/03(月)</x:v>
       </x:c>
       <x:c r="GU5" s="2" t="str">
-        <x:v>08/02(日)</x:v>
+        <x:v>08/04(火)</x:v>
       </x:c>
       <x:c r="GV5" s="2" t="str">
-        <x:v>08/02(日)</x:v>
+        <x:v>08/04(火)</x:v>
       </x:c>
       <x:c r="GW5" s="2" t="str">
-        <x:v>08/02(日)</x:v>
+        <x:v>08/04(火)</x:v>
       </x:c>
       <x:c r="GX5" s="2" t="str">
-        <x:v>08/03(月)</x:v>
+        <x:v>08/05(水)</x:v>
       </x:c>
       <x:c r="GY5" s="2" t="str">
-        <x:v>08/03(月)</x:v>
+        <x:v>08/05(水)</x:v>
       </x:c>
       <x:c r="GZ5" s="2" t="str">
-        <x:v>08/03(月)</x:v>
+        <x:v>08/05(水)</x:v>
       </x:c>
       <x:c r="HA5" s="2" t="str">
-        <x:v>08/04(火)</x:v>
+        <x:v>08/06(木)</x:v>
       </x:c>
       <x:c r="HB5" s="2" t="str">
-        <x:v>08/04(火)</x:v>
+        <x:v>08/06(木)</x:v>
       </x:c>
       <x:c r="HC5" s="2" t="str">
-        <x:v>08/04(火)</x:v>
+        <x:v>08/06(木)</x:v>
       </x:c>
       <x:c r="HD5" s="2" t="str">
-        <x:v>08/05(水)</x:v>
+        <x:v>08/07(金)</x:v>
       </x:c>
       <x:c r="HE5" s="2" t="str">
-        <x:v>08/05(水)</x:v>
+        <x:v>08/07(金)</x:v>
       </x:c>
       <x:c r="HF5" s="2" t="str">
-        <x:v>08/05(水)</x:v>
+        <x:v>08/07(金)</x:v>
       </x:c>
       <x:c r="HG5" s="2" t="str">
-        <x:v>08/06(木)</x:v>
+        <x:v>08/08(土)</x:v>
       </x:c>
       <x:c r="HH5" s="2" t="str">
-        <x:v>08/06(木)</x:v>
+        <x:v>08/08(土)</x:v>
       </x:c>
       <x:c r="HI5" s="2" t="str">
-        <x:v>08/06(木)</x:v>
+        <x:v>08/08(土)</x:v>
       </x:c>
       <x:c r="HJ5" s="2" t="str">
-        <x:v>08/07(金)</x:v>
+        <x:v>08/09(日)</x:v>
       </x:c>
       <x:c r="HK5" s="2" t="str">
-        <x:v>08/07(金)</x:v>
+        <x:v>08/09(日)</x:v>
       </x:c>
       <x:c r="HL5" s="2" t="str">
-        <x:v>08/07(金)</x:v>
+        <x:v>08/09(日)</x:v>
       </x:c>
       <x:c r="HM5" s="2" t="str">
-        <x:v>08/08(土)</x:v>
+        <x:v>08/10(月)</x:v>
       </x:c>
       <x:c r="HN5" s="2" t="str">
-        <x:v>08/08(土)</x:v>
+        <x:v>08/10(月)</x:v>
       </x:c>
       <x:c r="HO5" s="2" t="str">
-        <x:v>08/08(土)</x:v>
+        <x:v>08/10(月)</x:v>
       </x:c>
       <x:c r="HP5" s="2" t="str">
-        <x:v>08/09(日)</x:v>
+        <x:v>08/11(火)</x:v>
       </x:c>
       <x:c r="HQ5" s="2" t="str">
-        <x:v>08/09(日)</x:v>
+        <x:v>08/11(火)</x:v>
       </x:c>
       <x:c r="HR5" s="2" t="str">
-        <x:v>08/09(日)</x:v>
+        <x:v>08/11(火)</x:v>
       </x:c>
       <x:c r="HS5" s="2" t="str">
-        <x:v>08/10(月)</x:v>
+        <x:v>08/12(水)</x:v>
       </x:c>
       <x:c r="HT5" s="2" t="str">
-        <x:v>08/10(月)</x:v>
+        <x:v>08/12(水)</x:v>
       </x:c>
       <x:c r="HU5" s="2" t="str">
-        <x:v>08/10(月)</x:v>
+        <x:v>08/12(水)</x:v>
       </x:c>
       <x:c r="HV5" s="2" t="str">
-        <x:v>08/11(火)</x:v>
+        <x:v>08/13(木)</x:v>
       </x:c>
       <x:c r="HW5" s="2" t="str">
-        <x:v>08/11(火)</x:v>
+        <x:v>08/13(木)</x:v>
       </x:c>
       <x:c r="HX5" s="2" t="str">
-        <x:v>08/11(火)</x:v>
+        <x:v>08/13(木)</x:v>
       </x:c>
       <x:c r="HY5" s="2" t="str">
-        <x:v>08/12(水)</x:v>
+        <x:v>08/14(金)</x:v>
       </x:c>
       <x:c r="HZ5" s="2" t="str">
-        <x:v>08/12(水)</x:v>
+        <x:v>08/14(金)</x:v>
       </x:c>
       <x:c r="IA5" s="2" t="str">
-        <x:v>08/12(水)</x:v>
+        <x:v>08/14(金)</x:v>
       </x:c>
       <x:c r="IB5" s="2" t="str">
-        <x:v>08/13(木)</x:v>
+        <x:v>08/15(土)</x:v>
       </x:c>
       <x:c r="IC5" s="2" t="str">
-        <x:v>08/13(木)</x:v>
+        <x:v>08/15(土)</x:v>
       </x:c>
       <x:c r="ID5" s="2" t="str">
-        <x:v>08/13(木)</x:v>
+        <x:v>08/15(土)</x:v>
       </x:c>
       <x:c r="IE5" s="2" t="str">
-        <x:v>08/14(金)</x:v>
+        <x:v>08/16(日)</x:v>
       </x:c>
       <x:c r="IF5" s="2" t="str">
-        <x:v>08/14(金)</x:v>
+        <x:v>08/16(日)</x:v>
       </x:c>
       <x:c r="IG5" s="2" t="str">
-        <x:v>08/14(金)</x:v>
+        <x:v>08/16(日)</x:v>
       </x:c>
       <x:c r="IH5" s="2" t="str">
-        <x:v>08/15(土)</x:v>
+        <x:v>08/17(月)</x:v>
       </x:c>
       <x:c r="II5" s="2" t="str">
-        <x:v>08/15(土)</x:v>
+        <x:v>08/17(月)</x:v>
       </x:c>
       <x:c r="IJ5" s="2" t="str">
-        <x:v>08/15(土)</x:v>
+        <x:v>08/17(月)</x:v>
       </x:c>
       <x:c r="IK5" s="2" t="str">
-        <x:v>08/16(日)</x:v>
+        <x:v>08/18(火)</x:v>
       </x:c>
       <x:c r="IL5" s="2" t="str">
-        <x:v>08/16(日)</x:v>
+        <x:v>08/18(火)</x:v>
       </x:c>
       <x:c r="IM5" s="2" t="str">
-        <x:v>08/16(日)</x:v>
+        <x:v>08/18(火)</x:v>
       </x:c>
       <x:c r="IN5" s="2" t="str">
-        <x:v>08/17(月)</x:v>
+        <x:v>08/19(水)</x:v>
       </x:c>
       <x:c r="IO5" s="2" t="str">
-        <x:v>08/17(月)</x:v>
+        <x:v>08/19(水)</x:v>
       </x:c>
       <x:c r="IP5" s="2" t="str">
-        <x:v>08/17(月)</x:v>
+        <x:v>08/19(水)</x:v>
       </x:c>
       <x:c r="IQ5" s="2" t="str">
-        <x:v>08/18(火)</x:v>
+        <x:v>08/20(木)</x:v>
       </x:c>
       <x:c r="IR5" s="2" t="str">
-        <x:v>08/18(火)</x:v>
+        <x:v>08/20(木)</x:v>
       </x:c>
       <x:c r="IS5" s="2" t="str">
-        <x:v>08/18(火)</x:v>
+        <x:v>08/20(木)</x:v>
       </x:c>
       <x:c r="IT5" s="2" t="str">
-        <x:v>08/19(水)</x:v>
+        <x:v>08/21(金)</x:v>
       </x:c>
       <x:c r="IU5" s="2" t="str">
-        <x:v>08/19(水)</x:v>
+        <x:v>08/21(金)</x:v>
       </x:c>
       <x:c r="IV5" s="2" t="str">
-        <x:v>08/19(水)</x:v>
+        <x:v>08/21(金)</x:v>
       </x:c>
       <x:c r="IW5" s="2" t="str">
-        <x:v>08/20(木)</x:v>
+        <x:v>08/22(土)</x:v>
       </x:c>
       <x:c r="IX5" s="2" t="str">
-        <x:v>08/20(木)</x:v>
+        <x:v>08/22(土)</x:v>
       </x:c>
       <x:c r="IY5" s="2" t="str">
-        <x:v>08/20(木)</x:v>
+        <x:v>08/22(土)</x:v>
       </x:c>
       <x:c r="IZ5" s="2" t="str">
-        <x:v>08/21(金)</x:v>
+        <x:v>08/23(日)</x:v>
       </x:c>
       <x:c r="JA5" s="2" t="str">
-        <x:v>08/21(金)</x:v>
+        <x:v>08/23(日)</x:v>
       </x:c>
       <x:c r="JB5" s="2" t="str">
-        <x:v>08/21(金)</x:v>
+        <x:v>08/23(日)</x:v>
       </x:c>
       <x:c r="JC5" s="2" t="str">
-        <x:v>08/22(土)</x:v>
+        <x:v>08/24(月)</x:v>
       </x:c>
       <x:c r="JD5" s="2" t="str">
-        <x:v>08/22(土)</x:v>
+        <x:v>08/24(月)</x:v>
       </x:c>
       <x:c r="JE5" s="2" t="str">
-        <x:v>08/22(土)</x:v>
+        <x:v>08/24(月)</x:v>
       </x:c>
       <x:c r="JF5" s="2" t="str">
-        <x:v>08/23(日)</x:v>
+        <x:v>08/25(火)</x:v>
       </x:c>
       <x:c r="JG5" s="2" t="str">
-        <x:v>08/23(日)</x:v>
+        <x:v>08/25(火)</x:v>
       </x:c>
       <x:c r="JH5" s="2" t="str">
-        <x:v>08/23(日)</x:v>
+        <x:v>08/25(火)</x:v>
       </x:c>
       <x:c r="JI5" s="2" t="str">
-        <x:v>08/24(月)</x:v>
+        <x:v>08/26(水)</x:v>
       </x:c>
       <x:c r="JJ5" s="2" t="str">
-        <x:v>08/24(月)</x:v>
+        <x:v>08/26(水)</x:v>
       </x:c>
       <x:c r="JK5" s="2" t="str">
-        <x:v>08/24(月)</x:v>
+        <x:v>08/26(水)</x:v>
       </x:c>
       <x:c r="JL5" s="2" t="str">
-        <x:v>08/25(火)</x:v>
+        <x:v>08/27(木)</x:v>
       </x:c>
       <x:c r="JM5" s="2" t="str">
-        <x:v>08/25(火)</x:v>
+        <x:v>08/27(木)</x:v>
       </x:c>
       <x:c r="JN5" s="2" t="str">
-        <x:v>08/25(火)</x:v>
+        <x:v>08/27(木)</x:v>
       </x:c>
       <x:c r="JO5" s="2" t="str">
-        <x:v>08/26(水)</x:v>
+        <x:v>08/28(金)</x:v>
       </x:c>
       <x:c r="JP5" s="2" t="str">
-        <x:v>08/26(水)</x:v>
+        <x:v>08/28(金)</x:v>
       </x:c>
       <x:c r="JQ5" s="2" t="str">
-        <x:v>08/26(水)</x:v>
+        <x:v>08/28(金)</x:v>
       </x:c>
       <x:c r="JR5" s="2" t="str">
-        <x:v>08/27(木)</x:v>
+        <x:v>08/29(土)</x:v>
       </x:c>
       <x:c r="JS5" s="2" t="str">
-        <x:v>08/27(木)</x:v>
+        <x:v>08/29(土)</x:v>
       </x:c>
       <x:c r="JT5" s="2" t="str">
-        <x:v>08/27(木)</x:v>
+        <x:v>08/29(土)</x:v>
       </x:c>
       <x:c r="JU5" s="2" t="str">
-        <x:v>08/28(金)</x:v>
+        <x:v>08/30(日)</x:v>
       </x:c>
       <x:c r="JV5" s="2" t="str">
-        <x:v>08/28(金)</x:v>
+        <x:v>08/30(日)</x:v>
       </x:c>
       <x:c r="JW5" s="2" t="str">
-        <x:v>08/28(金)</x:v>
+        <x:v>08/30(日)</x:v>
       </x:c>
       <x:c r="JX5" s="2" t="str">
-        <x:v>08/29(土)</x:v>
+        <x:v>08/31(月)</x:v>
       </x:c>
       <x:c r="JY5" s="2" t="str">
-        <x:v>08/29(土)</x:v>
+        <x:v>08/31(月)</x:v>
       </x:c>
       <x:c r="JZ5" s="2" t="str">
-        <x:v>08/29(土)</x:v>
+        <x:v>08/31(月)</x:v>
       </x:c>
       <x:c r="KA5" s="2" t="str">
-        <x:v>08/30(日)</x:v>
+        <x:v>09/01(火)</x:v>
       </x:c>
       <x:c r="KB5" s="2" t="str">
-        <x:v>08/30(日)</x:v>
+        <x:v>09/01(火)</x:v>
       </x:c>
       <x:c r="KC5" s="2" t="str">
-        <x:v>08/30(日)</x:v>
+        <x:v>09/01(火)</x:v>
       </x:c>
       <x:c r="KD5" s="2" t="str">
-        <x:v>08/31(月)</x:v>
+        <x:v>09/02(水)</x:v>
       </x:c>
       <x:c r="KE5" s="2" t="str">
-        <x:v>08/31(月)</x:v>
+        <x:v>09/02(水)</x:v>
       </x:c>
       <x:c r="KF5" s="2" t="str">
-        <x:v>08/31(月)</x:v>
+        <x:v>09/02(水)</x:v>
       </x:c>
       <x:c r="KG5" s="2" t="str">
-        <x:v>09/01(火)</x:v>
+        <x:v>09/03(木)</x:v>
       </x:c>
       <x:c r="KH5" s="2" t="str">
-        <x:v>09/01(火)</x:v>
+        <x:v>09/03(木)</x:v>
       </x:c>
       <x:c r="KI5" s="2" t="str">
-        <x:v>09/01(火)</x:v>
+        <x:v>09/03(木)</x:v>
       </x:c>
       <x:c r="KJ5" s="2" t="str">
-        <x:v>09/02(水)</x:v>
+        <x:v>09/04(金)</x:v>
       </x:c>
       <x:c r="KK5" s="2" t="str">
-        <x:v>09/02(水)</x:v>
+        <x:v>09/04(金)</x:v>
       </x:c>
       <x:c r="KL5" s="2" t="str">
-        <x:v>09/02(水)</x:v>
+        <x:v>09/04(金)</x:v>
       </x:c>
       <x:c r="KM5" s="2" t="str">
-        <x:v>09/03(木)</x:v>
+        <x:v>09/05(土)</x:v>
       </x:c>
       <x:c r="KN5" s="2" t="str">
-        <x:v>09/03(木)</x:v>
+        <x:v>09/05(土)</x:v>
       </x:c>
       <x:c r="KO5" s="2" t="str">
-        <x:v>09/03(木)</x:v>
+        <x:v>09/05(土)</x:v>
       </x:c>
       <x:c r="KP5" s="2" t="str">
-        <x:v>09/04(金)</x:v>
+        <x:v>09/06(日)</x:v>
       </x:c>
       <x:c r="KQ5" s="2" t="str">
-        <x:v>09/04(金)</x:v>
+        <x:v>09/06(日)</x:v>
       </x:c>
       <x:c r="KR5" s="2" t="str">
-        <x:v>09/04(金)</x:v>
+        <x:v>09/06(日)</x:v>
       </x:c>
       <x:c r="KS5" s="2" t="str">
-        <x:v>09/05(土)</x:v>
+        <x:v>09/07(月)</x:v>
       </x:c>
       <x:c r="KT5" s="2" t="str">
-        <x:v>09/05(土)</x:v>
+        <x:v>09/07(月)</x:v>
       </x:c>
       <x:c r="KU5" s="2" t="str">
-        <x:v>09/05(土)</x:v>
+        <x:v>09/07(月)</x:v>
       </x:c>
       <x:c r="KV5" s="2" t="str">
-        <x:v>09/06(日)</x:v>
+        <x:v>09/08(火)</x:v>
       </x:c>
       <x:c r="KW5" s="2" t="str">
-        <x:v>09/06(日)</x:v>
+        <x:v>09/08(火)</x:v>
       </x:c>
       <x:c r="KX5" s="2" t="str">
-        <x:v>09/06(日)</x:v>
+        <x:v>09/08(火)</x:v>
       </x:c>
       <x:c r="KY5" s="2" t="str">
-        <x:v>09/07(月)</x:v>
+        <x:v>09/09(水)</x:v>
       </x:c>
       <x:c r="KZ5" s="2" t="str">
-        <x:v>09/07(月)</x:v>
+        <x:v>09/09(水)</x:v>
       </x:c>
       <x:c r="LA5" s="2" t="str">
-        <x:v>09/07(月)</x:v>
+        <x:v>09/09(水)</x:v>
       </x:c>
       <x:c r="LB5" s="2" t="str">
-        <x:v>09/08(火)</x:v>
+        <x:v>09/10(木)</x:v>
       </x:c>
       <x:c r="LC5" s="2" t="str">
-        <x:v>09/08(火)</x:v>
+        <x:v>09/10(木)</x:v>
       </x:c>
       <x:c r="LD5" s="2" t="str">
-        <x:v>09/08(火)</x:v>
+        <x:v>09/10(木)</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2868,13 +2868,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FQ7" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>7400.0000</x:v>
       </x:c>
       <x:c r="FR7" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FS7" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>7.6500</x:v>
       </x:c>
       <x:c r="FT7" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -2886,13 +2886,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FW7" s="6" t="n">
-        <x:v>7400.0000</x:v>
+        <x:v>2600.0000</x:v>
       </x:c>
       <x:c r="FX7" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FY7" s="8" t="n">
-        <x:v>7.6500</x:v>
+        <x:v>2.6900</x:v>
       </x:c>
       <x:c r="FZ7" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -2904,13 +2904,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GC7" s="6" t="n">
-        <x:v>2600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GD7" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="GE7" s="8" t="n">
-        <x:v>2.6900</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GF7" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -3710,13 +3710,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG8" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1600.0000</x:v>
       </x:c>
       <x:c r="EH8" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EI8" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.6500</x:v>
       </x:c>
       <x:c r="EJ8" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -3728,13 +3728,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM8" s="6" t="n">
-        <x:v>1600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN8" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EO8" s="8" t="n">
-        <x:v>1.6500</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP8" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -4669,13 +4669,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ9" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>200.0000</x:v>
       </x:c>
       <x:c r="EK9" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EL9" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.2100</x:v>
       </x:c>
       <x:c r="EM9" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -4687,13 +4687,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP9" s="6" t="n">
-        <x:v>200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EQ9" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="ER9" s="8" t="n">
-        <x:v>0.2100</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES9" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -5610,13 +5610,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG10" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3400.0000</x:v>
       </x:c>
       <x:c r="EH10" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EI10" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3.5200</x:v>
       </x:c>
       <x:c r="EJ10" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -5628,13 +5628,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM10" s="6" t="n">
-        <x:v>3400.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN10" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EO10" s="8" t="n">
-        <x:v>3.5200</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP10" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -6560,13 +6560,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG11" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>800.0000</x:v>
       </x:c>
       <x:c r="EH11" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EI11" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.8300</x:v>
       </x:c>
       <x:c r="EJ11" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -6578,13 +6578,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM11" s="6" t="n">
-        <x:v>800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN11" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EO11" s="8" t="n">
-        <x:v>0.8300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP11" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -7510,13 +7510,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG12" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6800.0000</x:v>
       </x:c>
       <x:c r="EH12" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EI12" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>7.5600</x:v>
       </x:c>
       <x:c r="EJ12" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -7528,13 +7528,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM12" s="6" t="n">
-        <x:v>6800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN12" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EO12" s="8" t="n">
-        <x:v>7.5600</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP12" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -8460,13 +8460,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG13" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>800.0000</x:v>
       </x:c>
       <x:c r="EH13" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EI13" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.8900</x:v>
       </x:c>
       <x:c r="EJ13" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -8478,13 +8478,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM13" s="6" t="n">
-        <x:v>800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN13" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EO13" s="8" t="n">
-        <x:v>0.8900</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP13" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -9419,13 +9419,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ14" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>800.0000</x:v>
       </x:c>
       <x:c r="EK14" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EL14" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.8300</x:v>
       </x:c>
       <x:c r="EM14" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -9437,13 +9437,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP14" s="6" t="n">
-        <x:v>800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EQ14" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="ER14" s="8" t="n">
-        <x:v>0.8300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES14" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -10369,13 +10369,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ15" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>200.0000</x:v>
       </x:c>
       <x:c r="EK15" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EL15" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.2100</x:v>
       </x:c>
       <x:c r="EM15" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -10387,13 +10387,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP15" s="6" t="n">
-        <x:v>200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EQ15" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="ER15" s="8" t="n">
-        <x:v>0.2100</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES15" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -11328,13 +11328,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM16" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>800.0000</x:v>
       </x:c>
       <x:c r="EN16" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EO16" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.8900</x:v>
       </x:c>
       <x:c r="EP16" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -11346,13 +11346,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES16" s="6" t="n">
-        <x:v>800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ET16" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EU16" s="8" t="n">
-        <x:v>0.8900</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV16" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -12278,13 +12278,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM17" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4000.0000</x:v>
       </x:c>
       <x:c r="EN17" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EO17" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4.1400</x:v>
       </x:c>
       <x:c r="EP17" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -12296,13 +12296,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES17" s="6" t="n">
-        <x:v>4000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ET17" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EU17" s="8" t="n">
-        <x:v>4.1400</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV17" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -13237,40 +13237,40 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP18" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>7400.0000</x:v>
       </x:c>
       <x:c r="EQ18" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="ER18" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>7.6500</x:v>
       </x:c>
       <x:c r="ES18" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2600.0000</x:v>
       </x:c>
       <x:c r="ET18" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EU18" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.6900</x:v>
       </x:c>
       <x:c r="EV18" s="6" t="n">
-        <x:v>7400.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EW18" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EX18" s="8" t="n">
-        <x:v>7.6500</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY18" s="6" t="n">
-        <x:v>2600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EZ18" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FA18" s="8" t="n">
-        <x:v>2.6900</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB18" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -14196,13 +14196,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES19" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>600.0000</x:v>
       </x:c>
       <x:c r="ET19" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EU19" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.6200</x:v>
       </x:c>
       <x:c r="EV19" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -14214,13 +14214,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY19" s="6" t="n">
-        <x:v>600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EZ19" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FA19" s="8" t="n">
-        <x:v>0.6200</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB19" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -15146,13 +15146,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES20" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2800.0000</x:v>
       </x:c>
       <x:c r="ET20" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="EU20" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.8900</x:v>
       </x:c>
       <x:c r="EV20" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -15164,13 +15164,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY20" s="6" t="n">
-        <x:v>2800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EZ20" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FA20" s="8" t="n">
-        <x:v>2.8900</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB20" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -15182,13 +15182,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FE20" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>7200.0000</x:v>
       </x:c>
       <x:c r="FF20" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FG20" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>7.4400</x:v>
       </x:c>
       <x:c r="FH20" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -15200,13 +15200,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FK20" s="6" t="n">
-        <x:v>7200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FL20" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FM20" s="8" t="n">
-        <x:v>7.4400</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FN20" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -16141,13 +16141,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FH21" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3000.0000</x:v>
       </x:c>
       <x:c r="FI21" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FJ21" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3.1000</x:v>
       </x:c>
       <x:c r="FK21" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -16159,13 +16159,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FN21" s="6" t="n">
-        <x:v>3000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FO21" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FP21" s="8" t="n">
-        <x:v>3.1000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FQ21" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -17091,40 +17091,40 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FH22" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4200.0000</x:v>
       </x:c>
       <x:c r="FI22" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FJ22" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4.3400</x:v>
       </x:c>
       <x:c r="FK22" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5800.0000</x:v>
       </x:c>
       <x:c r="FL22" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FM22" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6.0000</x:v>
       </x:c>
       <x:c r="FN22" s="6" t="n">
-        <x:v>4200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FO22" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FP22" s="8" t="n">
-        <x:v>4.3400</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FQ22" s="6" t="n">
-        <x:v>5800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FR22" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FS22" s="8" t="n">
-        <x:v>6.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FT22" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -18050,40 +18050,40 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FK23" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1000.0000</x:v>
       </x:c>
       <x:c r="FL23" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FM23" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.0300</x:v>
       </x:c>
       <x:c r="FN23" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4750.0000</x:v>
       </x:c>
       <x:c r="FO23" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FP23" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4.9100</x:v>
       </x:c>
       <x:c r="FQ23" s="6" t="n">
-        <x:v>1000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FR23" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FS23" s="8" t="n">
-        <x:v>1.0300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FT23" s="6" t="n">
-        <x:v>4750.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FU23" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FV23" s="8" t="n">
-        <x:v>4.9100</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FW23" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -19009,13 +19009,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FN24" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1260.0000</x:v>
       </x:c>
       <x:c r="FO24" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FP24" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.3000</x:v>
       </x:c>
       <x:c r="FQ24" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -19027,13 +19027,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FT24" s="6" t="n">
-        <x:v>1260.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FU24" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FV24" s="8" t="n">
-        <x:v>1.3000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FW24" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -19986,13 +19986,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FW25" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2750.0000</x:v>
       </x:c>
       <x:c r="FX25" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="FY25" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.8400</x:v>
       </x:c>
       <x:c r="FZ25" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -20004,13 +20004,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GC25" s="6" t="n">
-        <x:v>2750.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GD25" s="8" t="n">
         <x:v>16.1200</x:v>
       </x:c>
       <x:c r="GE25" s="8" t="n">
-        <x:v>2.8400</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GF25" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -20756,40 +20756,40 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DO26" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4500.0000</x:v>
       </x:c>
       <x:c r="DP26" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="DQ26" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4.1500</x:v>
       </x:c>
       <x:c r="DR26" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1500.0000</x:v>
       </x:c>
       <x:c r="DS26" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="DT26" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.3800</x:v>
       </x:c>
       <x:c r="DU26" s="6" t="n">
-        <x:v>4500.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DV26" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="DW26" s="8" t="n">
-        <x:v>4.1500</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DX26" s="6" t="n">
-        <x:v>1500.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DY26" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="DZ26" s="8" t="n">
-        <x:v>1.3800</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EA26" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -21670,13 +21670,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DC27" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3600.0000</x:v>
       </x:c>
       <x:c r="DD27" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="DE27" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3.3200</x:v>
       </x:c>
       <x:c r="DF27" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -21688,13 +21688,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DI27" s="6" t="n">
-        <x:v>3600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DJ27" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="DK27" s="8" t="n">
-        <x:v>3.3200</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DL27" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -22719,40 +22719,40 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ28" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2100.0000</x:v>
       </x:c>
       <x:c r="EK28" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EL28" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.9400</x:v>
       </x:c>
       <x:c r="EM28" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>600.0000</x:v>
       </x:c>
       <x:c r="EN28" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EO28" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.5500</x:v>
       </x:c>
       <x:c r="EP28" s="6" t="n">
-        <x:v>2100.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EQ28" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="ER28" s="8" t="n">
-        <x:v>1.9400</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES28" s="6" t="n">
-        <x:v>600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ET28" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EU28" s="8" t="n">
-        <x:v>0.5500</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV28" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -23678,13 +23678,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM29" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1500.0000</x:v>
       </x:c>
       <x:c r="EN29" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EO29" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.3800</x:v>
       </x:c>
       <x:c r="EP29" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -23696,13 +23696,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES29" s="6" t="n">
-        <x:v>1500.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ET29" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EU29" s="8" t="n">
-        <x:v>1.3800</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV29" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -24637,13 +24637,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP30" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3900.0000</x:v>
       </x:c>
       <x:c r="EQ30" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="ER30" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3.6000</x:v>
       </x:c>
       <x:c r="ES30" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -24655,13 +24655,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV30" s="6" t="n">
-        <x:v>3900.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EW30" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EX30" s="8" t="n">
-        <x:v>3.6000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY30" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -25569,13 +25569,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ31" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>800.0000</x:v>
       </x:c>
       <x:c r="EK31" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="EL31" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.3200</x:v>
       </x:c>
       <x:c r="EM31" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -25587,13 +25587,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP31" s="6" t="n">
-        <x:v>800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EQ31" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="ER31" s="8" t="n">
-        <x:v>1.3200</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES31" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -26519,13 +26519,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ32" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1200.0000</x:v>
       </x:c>
       <x:c r="EK32" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="EL32" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.9800</x:v>
       </x:c>
       <x:c r="EM32" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -26537,13 +26537,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP32" s="6" t="n">
-        <x:v>1200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EQ32" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="ER32" s="8" t="n">
-        <x:v>1.9800</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES32" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -27343,13 +27343,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CT33" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>194.0000</x:v>
       </x:c>
       <x:c r="CU33" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="CV33" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.2200</x:v>
       </x:c>
       <x:c r="CW33" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -27361,13 +27361,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CZ33" s="6" t="n">
-        <x:v>194.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DA33" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="DB33" s="8" t="n">
-        <x:v>0.2200</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DC33" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -28410,13 +28410,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG34" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>400.0000</x:v>
       </x:c>
       <x:c r="EH34" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="EI34" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.6600</x:v>
       </x:c>
       <x:c r="EJ34" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -28428,13 +28428,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM34" s="6" t="n">
-        <x:v>400.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN34" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="EO34" s="8" t="n">
-        <x:v>0.6600</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP34" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -29252,13 +29252,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CW35" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3600.0000</x:v>
       </x:c>
       <x:c r="CX35" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="CY35" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5.9300</x:v>
       </x:c>
       <x:c r="CZ35" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -29270,13 +29270,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DC35" s="6" t="n">
-        <x:v>3600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DD35" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="DE35" s="8" t="n">
-        <x:v>5.9300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DF35" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -29920,7 +29920,7 @@
         <x:v>分割</x:v>
       </x:c>
       <x:c r="G36" s="1" t="str">
-        <x:v>003</x:v>
+        <x:v>009</x:v>
       </x:c>
       <x:c r="H36" s="4" t="n">
         <x:v>46209</x:v>
@@ -30001,10 +30001,10 @@
         <x:v/>
       </x:c>
       <x:c r="AH36" s="4" t="n">
-        <x:v>46211</x:v>
+        <x:v>46216</x:v>
       </x:c>
       <x:c r="AI36" s="4" t="n">
-        <x:v>46211</x:v>
+        <x:v>46216</x:v>
       </x:c>
       <x:c r="AJ36" s="1" t="str">
         <x:v>0:未完</x:v>
@@ -30283,13 +30283,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DX36" s="6" t="n">
-        <x:v>100.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DY36" s="8" t="n">
         <x:v>14.9900</x:v>
       </x:c>
       <x:c r="DZ36" s="8" t="n">
-        <x:v>0.1100</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EA36" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -30310,13 +30310,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG36" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>100.0000</x:v>
       </x:c>
       <x:c r="EH36" s="8" t="n">
         <x:v>14.9900</x:v>
       </x:c>
       <x:c r="EI36" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.1100</x:v>
       </x:c>
       <x:c r="EJ36" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -31260,13 +31260,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG37" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>600.0000</x:v>
       </x:c>
       <x:c r="EH37" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EI37" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.6700</x:v>
       </x:c>
       <x:c r="EJ37" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -31278,13 +31278,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM37" s="6" t="n">
-        <x:v>600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN37" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="EO37" s="8" t="n">
-        <x:v>0.6700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP37" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -32228,13 +32228,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM38" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1500.0000</x:v>
       </x:c>
       <x:c r="EN38" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="EO38" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.4700</x:v>
       </x:c>
       <x:c r="EP38" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -32246,13 +32246,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES38" s="6" t="n">
-        <x:v>1500.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ET38" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="EU38" s="8" t="n">
-        <x:v>2.4700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV38" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -33178,13 +33178,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM39" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>200.0000</x:v>
       </x:c>
       <x:c r="EN39" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="EO39" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.3300</x:v>
       </x:c>
       <x:c r="EP39" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -33196,13 +33196,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES39" s="6" t="n">
-        <x:v>200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ET39" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="EU39" s="8" t="n">
-        <x:v>0.3300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV39" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -34146,13 +34146,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES40" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>200.0000</x:v>
       </x:c>
       <x:c r="ET40" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="EU40" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.3300</x:v>
       </x:c>
       <x:c r="EV40" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -34164,13 +34164,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY40" s="6" t="n">
-        <x:v>200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EZ40" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="FA40" s="8" t="n">
-        <x:v>0.3300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB40" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -35168,13 +35168,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FQ41" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>950.0000</x:v>
       </x:c>
       <x:c r="FR41" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="FS41" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.5600</x:v>
       </x:c>
       <x:c r="FT41" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -35186,13 +35186,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FW41" s="6" t="n">
-        <x:v>950.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FX41" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="FY41" s="8" t="n">
-        <x:v>1.5600</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FZ41" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -36118,7 +36118,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FQ42" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1000.0000</x:v>
       </x:c>
       <x:c r="FR42" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -36136,7 +36136,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FW42" s="6" t="n">
-        <x:v>1000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FX42" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -36960,13 +36960,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG43" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>400.0000</x:v>
       </x:c>
       <x:c r="EH43" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EI43" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.2700</x:v>
       </x:c>
       <x:c r="EJ43" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -36978,13 +36978,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM43" s="6" t="n">
-        <x:v>400.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN43" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EO43" s="8" t="n">
-        <x:v>0.2700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP43" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -37919,13 +37919,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ44" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>600.0000</x:v>
       </x:c>
       <x:c r="EK44" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EL44" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.4000</x:v>
       </x:c>
       <x:c r="EM44" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -37937,13 +37937,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP44" s="6" t="n">
-        <x:v>600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EQ44" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="ER44" s="8" t="n">
-        <x:v>0.4000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES44" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -38833,13 +38833,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DX45" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1600.0000</x:v>
       </x:c>
       <x:c r="DY45" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="DZ45" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.0700</x:v>
       </x:c>
       <x:c r="EA45" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -38851,13 +38851,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ED45" s="6" t="n">
-        <x:v>1600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EE45" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EF45" s="8" t="n">
-        <x:v>1.0700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG45" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -39810,13 +39810,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG46" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>200.0000</x:v>
       </x:c>
       <x:c r="EH46" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EI46" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.1300</x:v>
       </x:c>
       <x:c r="EJ46" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -39828,13 +39828,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM46" s="6" t="n">
-        <x:v>200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN46" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EO46" s="8" t="n">
-        <x:v>0.1300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP46" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -40415,7 +40415,7 @@
         <x:v>00075010</x:v>
       </x:c>
       <x:c r="V47" s="1" t="str">
-        <x:v>0:未完</x:v>
+        <x:v>1:完了</x:v>
       </x:c>
       <x:c r="W47" s="1" t="str">
         <x:v>0004</x:v>
@@ -40463,13 +40463,13 @@
         <x:v>10000.0000</x:v>
       </x:c>
       <x:c r="AL47" s="6" t="n">
-        <x:v>7600.0000</x:v>
+        <x:v>8000.0000</x:v>
       </x:c>
       <x:c r="AM47" s="6" t="n">
-        <x:v>2400.0000</x:v>
+        <x:v>2000.0000</x:v>
       </x:c>
       <x:c r="AN47" s="6" t="n">
-        <x:v>14400.0000</x:v>
+        <x:v>16000.0000</x:v>
       </x:c>
       <x:c r="AO47" s="6" t="n">
         <x:v>10000.0000</x:v>
@@ -40733,13 +40733,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DX47" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>8000.0000</x:v>
       </x:c>
       <x:c r="DY47" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="DZ47" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5.3300</x:v>
       </x:c>
       <x:c r="EA47" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -40751,22 +40751,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ED47" s="6" t="n">
-        <x:v>8000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EE47" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EF47" s="8" t="n">
-        <x:v>5.3300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG47" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2000.0000</x:v>
       </x:c>
       <x:c r="EH47" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EI47" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.3300</x:v>
       </x:c>
       <x:c r="EJ47" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -40778,13 +40778,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM47" s="6" t="n">
-        <x:v>2000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN47" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EO47" s="8" t="n">
-        <x:v>1.3300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP47" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -41737,13 +41737,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP48" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2000.0000</x:v>
       </x:c>
       <x:c r="EQ48" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="ER48" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.3300</x:v>
       </x:c>
       <x:c r="ES48" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -41755,13 +41755,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV48" s="6" t="n">
-        <x:v>2000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EW48" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EX48" s="8" t="n">
-        <x:v>1.3300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY48" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -42678,13 +42678,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM49" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>200.0000</x:v>
       </x:c>
       <x:c r="EN49" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EO49" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.1300</x:v>
       </x:c>
       <x:c r="EP49" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -42696,13 +42696,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES49" s="6" t="n">
-        <x:v>200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ET49" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EU49" s="8" t="n">
-        <x:v>0.1300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV49" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -43646,13 +43646,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES50" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>200.0000</x:v>
       </x:c>
       <x:c r="ET50" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EU50" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.1300</x:v>
       </x:c>
       <x:c r="EV50" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -43664,13 +43664,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY50" s="6" t="n">
-        <x:v>200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EZ50" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FA50" s="8" t="n">
-        <x:v>0.1300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB50" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -44587,40 +44587,40 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP51" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2800.0000</x:v>
       </x:c>
       <x:c r="EQ51" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="ER51" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.8700</x:v>
       </x:c>
       <x:c r="ES51" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>7200.0000</x:v>
       </x:c>
       <x:c r="ET51" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EU51" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4.8000</x:v>
       </x:c>
       <x:c r="EV51" s="6" t="n">
-        <x:v>2800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EW51" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EX51" s="8" t="n">
-        <x:v>1.8700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY51" s="6" t="n">
-        <x:v>7200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EZ51" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FA51" s="8" t="n">
-        <x:v>4.8000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB51" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -44632,13 +44632,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FE51" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3200.0000</x:v>
       </x:c>
       <x:c r="FF51" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FG51" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.1300</x:v>
       </x:c>
       <x:c r="FH51" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -44650,13 +44650,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FK51" s="6" t="n">
-        <x:v>3200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FL51" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FM51" s="8" t="n">
-        <x:v>2.1300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FN51" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -45582,13 +45582,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FE52" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>10000.0000</x:v>
       </x:c>
       <x:c r="FF52" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FG52" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6.6700</x:v>
       </x:c>
       <x:c r="FH52" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -45600,13 +45600,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FK52" s="6" t="n">
-        <x:v>10000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FL52" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FM52" s="8" t="n">
-        <x:v>6.6700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FN52" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -46559,40 +46559,40 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FN53" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2000.0000</x:v>
       </x:c>
       <x:c r="FO53" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FP53" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.3300</x:v>
       </x:c>
       <x:c r="FQ53" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1400.0000</x:v>
       </x:c>
       <x:c r="FR53" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FS53" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.9300</x:v>
       </x:c>
       <x:c r="FT53" s="6" t="n">
-        <x:v>2000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FU53" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FV53" s="8" t="n">
-        <x:v>1.3300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FW53" s="6" t="n">
-        <x:v>1400.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FX53" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FY53" s="8" t="n">
-        <x:v>0.9300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FZ53" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -47509,13 +47509,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FN54" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3000.0000</x:v>
       </x:c>
       <x:c r="FO54" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FP54" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.0000</x:v>
       </x:c>
       <x:c r="FQ54" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -47527,13 +47527,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FT54" s="6" t="n">
-        <x:v>3000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FU54" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FV54" s="8" t="n">
-        <x:v>2.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FW54" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -48441,13 +48441,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FH55" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>10000.0000</x:v>
       </x:c>
       <x:c r="FI55" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FJ55" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6.6700</x:v>
       </x:c>
       <x:c r="FK55" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -48459,13 +48459,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FN55" s="6" t="n">
-        <x:v>10000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FO55" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FP55" s="8" t="n">
-        <x:v>6.6700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FQ55" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -49418,13 +49418,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FQ56" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1000.0000</x:v>
       </x:c>
       <x:c r="FR56" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FS56" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.6700</x:v>
       </x:c>
       <x:c r="FT56" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -49436,13 +49436,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FW56" s="6" t="n">
-        <x:v>1000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FX56" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FY56" s="8" t="n">
-        <x:v>0.6700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FZ56" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -50233,13 +50233,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DX57" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3000.0000</x:v>
       </x:c>
       <x:c r="DY57" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="DZ57" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5.2600</x:v>
       </x:c>
       <x:c r="EA57" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -50251,22 +50251,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ED57" s="6" t="n">
-        <x:v>3000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EE57" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="EF57" s="8" t="n">
-        <x:v>5.2600</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG57" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3000.0000</x:v>
       </x:c>
       <x:c r="EH57" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="EI57" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5.2600</x:v>
       </x:c>
       <x:c r="EJ57" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -50278,13 +50278,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM57" s="6" t="n">
-        <x:v>3000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN57" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="EO57" s="8" t="n">
-        <x:v>5.2600</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP57" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -51156,40 +51156,40 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DO58" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1500.0000</x:v>
       </x:c>
       <x:c r="DP58" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="DQ58" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.6300</x:v>
       </x:c>
       <x:c r="DR58" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>600.0000</x:v>
       </x:c>
       <x:c r="DS58" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="DT58" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.0500</x:v>
       </x:c>
       <x:c r="DU58" s="6" t="n">
-        <x:v>1500.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DV58" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="DW58" s="8" t="n">
-        <x:v>2.6300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DX58" s="6" t="n">
-        <x:v>600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DY58" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="DZ58" s="8" t="n">
-        <x:v>1.0500</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EA58" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -51210,13 +51210,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG58" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1500.0000</x:v>
       </x:c>
       <x:c r="EH58" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="EI58" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.6300</x:v>
       </x:c>
       <x:c r="EJ58" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -51228,13 +51228,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM58" s="6" t="n">
-        <x:v>1500.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN58" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="EO58" s="8" t="n">
-        <x:v>2.6300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP58" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -52178,13 +52178,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM59" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2700.0000</x:v>
       </x:c>
       <x:c r="EN59" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="EO59" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4.7400</x:v>
       </x:c>
       <x:c r="EP59" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -52196,13 +52196,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES59" s="6" t="n">
-        <x:v>2700.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ET59" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="EU59" s="8" t="n">
-        <x:v>4.7400</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV59" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -53128,13 +53128,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM60" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>200.0000</x:v>
       </x:c>
       <x:c r="EN60" s="8" t="n">
         <x:v>20.0000</x:v>
       </x:c>
       <x:c r="EO60" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.1700</x:v>
       </x:c>
       <x:c r="EP60" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -53146,13 +53146,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES60" s="6" t="n">
-        <x:v>200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ET60" s="8" t="n">
         <x:v>20.0000</x:v>
       </x:c>
       <x:c r="EU60" s="8" t="n">
-        <x:v>0.1700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV60" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -54078,13 +54078,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM61" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2000.0000</x:v>
       </x:c>
       <x:c r="EN61" s="8" t="n">
         <x:v>20.0000</x:v>
       </x:c>
       <x:c r="EO61" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.6700</x:v>
       </x:c>
       <x:c r="EP61" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -54096,13 +54096,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES61" s="6" t="n">
-        <x:v>2000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ET61" s="8" t="n">
         <x:v>20.0000</x:v>
       </x:c>
       <x:c r="EU61" s="8" t="n">
-        <x:v>1.6700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EV61" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -55037,40 +55037,40 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP62" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3000.0000</x:v>
       </x:c>
       <x:c r="EQ62" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="ER62" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5.2600</x:v>
       </x:c>
       <x:c r="ES62" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>900.0000</x:v>
       </x:c>
       <x:c r="ET62" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="EU62" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.5800</x:v>
       </x:c>
       <x:c r="EV62" s="6" t="n">
-        <x:v>3000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EW62" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="EX62" s="8" t="n">
-        <x:v>5.2600</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY62" s="6" t="n">
-        <x:v>900.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EZ62" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="FA62" s="8" t="n">
-        <x:v>1.5800</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB62" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -55996,13 +55996,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES63" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1000.0000</x:v>
       </x:c>
       <x:c r="ET63" s="8" t="n">
         <x:v>20.0000</x:v>
       </x:c>
       <x:c r="EU63" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.8300</x:v>
       </x:c>
       <x:c r="EV63" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -56014,13 +56014,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY63" s="6" t="n">
-        <x:v>1000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EZ63" s="8" t="n">
         <x:v>20.0000</x:v>
       </x:c>
       <x:c r="FA63" s="8" t="n">
-        <x:v>0.8300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB63" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -56946,13 +56946,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ES64" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>200.0000</x:v>
       </x:c>
       <x:c r="ET64" s="8" t="n">
         <x:v>20.0000</x:v>
       </x:c>
       <x:c r="EU64" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.1700</x:v>
       </x:c>
       <x:c r="EV64" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -56964,13 +56964,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY64" s="6" t="n">
-        <x:v>200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EZ64" s="8" t="n">
         <x:v>20.0000</x:v>
       </x:c>
       <x:c r="FA64" s="8" t="n">
-        <x:v>0.1700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB64" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -57950,13 +57950,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FK65" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1470.0000</x:v>
       </x:c>
       <x:c r="FL65" s="8" t="n">
         <x:v>20.0000</x:v>
       </x:c>
       <x:c r="FM65" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.2300</x:v>
       </x:c>
       <x:c r="FN65" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -57968,13 +57968,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FQ65" s="6" t="n">
-        <x:v>1470.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FR65" s="8" t="n">
         <x:v>20.0000</x:v>
       </x:c>
       <x:c r="FS65" s="8" t="n">
-        <x:v>1.2300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FT65" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -58909,13 +58909,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FN66" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1260.0000</x:v>
       </x:c>
       <x:c r="FO66" s="8" t="n">
         <x:v>20.0000</x:v>
       </x:c>
       <x:c r="FP66" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.0500</x:v>
       </x:c>
       <x:c r="FQ66" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -58927,13 +58927,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FT66" s="6" t="n">
-        <x:v>1260.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FU66" s="8" t="n">
         <x:v>20.0000</x:v>
       </x:c>
       <x:c r="FV66" s="8" t="n">
-        <x:v>1.0500</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FW66" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -59643,31 +59643,31 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="CT67" s="7" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>194.0000</x:v>
       </x:c>
       <x:c r="CU67" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="CV67" s="9" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.2200</x:v>
       </x:c>
       <x:c r="CW67" s="7" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3600.0000</x:v>
       </x:c>
       <x:c r="CX67" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="CY67" s="9" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5.9300</x:v>
       </x:c>
       <x:c r="CZ67" s="7" t="n">
-        <x:v>194.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DA67" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="DB67" s="9" t="n">
-        <x:v>0.2200</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DC67" s="7" t="n">
         <x:v>3600.0000</x:v>
@@ -59676,7 +59676,7 @@
         <x:v/>
       </x:c>
       <x:c r="DE67" s="9" t="n">
-        <x:v>5.9300</x:v>
+        <x:v>3.3200</x:v>
       </x:c>
       <x:c r="DF67" s="7" t="n">
         <x:v>0.0000</x:v>
@@ -59688,13 +59688,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DI67" s="7" t="n">
-        <x:v>3600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DJ67" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="DK67" s="9" t="n">
-        <x:v>3.3200</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DL67" s="7" t="n">
         <x:v>0.0000</x:v>
@@ -59706,40 +59706,40 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DO67" s="7" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6000.0000</x:v>
       </x:c>
       <x:c r="DP67" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="DQ67" s="9" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6.7800</x:v>
       </x:c>
       <x:c r="DR67" s="7" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2100.0000</x:v>
       </x:c>
       <x:c r="DS67" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="DT67" s="9" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.4300</x:v>
       </x:c>
       <x:c r="DU67" s="7" t="n">
-        <x:v>6000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DV67" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="DW67" s="9" t="n">
-        <x:v>6.7800</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DX67" s="7" t="n">
-        <x:v>2200.0000</x:v>
+        <x:v>12600.0000</x:v>
       </x:c>
       <x:c r="DY67" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="DZ67" s="9" t="n">
-        <x:v>2.5400</x:v>
+        <x:v>11.6600</x:v>
       </x:c>
       <x:c r="EA67" s="7" t="n">
         <x:v>0.0000</x:v>
@@ -59751,76 +59751,76 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ED67" s="7" t="n">
-        <x:v>12600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EE67" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="EF67" s="9" t="n">
-        <x:v>11.6600</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG67" s="7" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>21600.0000</x:v>
       </x:c>
       <x:c r="EH67" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="EI67" s="9" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>25.5100</x:v>
       </x:c>
       <x:c r="EJ67" s="7" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5900.0000</x:v>
       </x:c>
       <x:c r="EK67" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="EL67" s="9" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6.8900</x:v>
       </x:c>
       <x:c r="EM67" s="7" t="n">
-        <x:v>21500.0000</x:v>
+        <x:v>13700.0000</x:v>
       </x:c>
       <x:c r="EN67" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="EO67" s="9" t="n">
-        <x:v>25.4000</x:v>
+        <x:v>16.4700</x:v>
       </x:c>
       <x:c r="EP67" s="7" t="n">
-        <x:v>5900.0000</x:v>
+        <x:v>19100.0000</x:v>
       </x:c>
       <x:c r="EQ67" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="ER67" s="9" t="n">
-        <x:v>6.8900</x:v>
+        <x:v>19.7100</x:v>
       </x:c>
       <x:c r="ES67" s="7" t="n">
-        <x:v>13700.0000</x:v>
+        <x:v>15700.0000</x:v>
       </x:c>
       <x:c r="ET67" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="EU67" s="9" t="n">
-        <x:v>16.4700</x:v>
+        <x:v>14.0400</x:v>
       </x:c>
       <x:c r="EV67" s="7" t="n">
-        <x:v>19100.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EW67" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="EX67" s="9" t="n">
-        <x:v>19.7100</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EY67" s="7" t="n">
-        <x:v>15700.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EZ67" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FA67" s="9" t="n">
-        <x:v>14.0400</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB67" s="7" t="n">
         <x:v>0.0000</x:v>
@@ -59832,67 +59832,67 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FE67" s="7" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>20400.0000</x:v>
       </x:c>
       <x:c r="FF67" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FG67" s="9" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>16.2400</x:v>
       </x:c>
       <x:c r="FH67" s="7" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>17200.0000</x:v>
       </x:c>
       <x:c r="FI67" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FJ67" s="9" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>14.1100</x:v>
       </x:c>
       <x:c r="FK67" s="7" t="n">
-        <x:v>20400.0000</x:v>
+        <x:v>8270.0000</x:v>
       </x:c>
       <x:c r="FL67" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FM67" s="9" t="n">
-        <x:v>16.2400</x:v>
+        <x:v>8.2600</x:v>
       </x:c>
       <x:c r="FN67" s="7" t="n">
-        <x:v>17200.0000</x:v>
+        <x:v>12270.0000</x:v>
       </x:c>
       <x:c r="FO67" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FP67" s="9" t="n">
-        <x:v>14.1100</x:v>
+        <x:v>10.5900</x:v>
       </x:c>
       <x:c r="FQ67" s="7" t="n">
-        <x:v>8270.0000</x:v>
+        <x:v>11750.0000</x:v>
       </x:c>
       <x:c r="FR67" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FS67" s="9" t="n">
-        <x:v>8.2600</x:v>
+        <x:v>10.8100</x:v>
       </x:c>
       <x:c r="FT67" s="7" t="n">
-        <x:v>12270.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FU67" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FV67" s="9" t="n">
-        <x:v>10.5900</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FW67" s="7" t="n">
-        <x:v>11750.0000</x:v>
+        <x:v>5350.0000</x:v>
       </x:c>
       <x:c r="FX67" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FY67" s="9" t="n">
-        <x:v>10.8100</x:v>
+        <x:v>5.5300</x:v>
       </x:c>
       <x:c r="FZ67" s="7" t="n">
         <x:v>0.0000</x:v>
@@ -59904,13 +59904,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GC67" s="7" t="n">
-        <x:v>5350.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GD67" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="GE67" s="9" t="n">
-        <x:v>5.5300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GF67" s="7" t="n">
         <x:v>0.0000</x:v>

--- a/.pm-ai-cache/network-source/task-input-newest.xlsx
+++ b/.pm-ai-cache/network-source/task-input-newest.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工程別生産計画問合せ問合せ" sheetId="1" r:id="R582e56ed637441f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工程別生産計画問合せ問合せ" sheetId="1" r:id="R93e5aaee78e14cbc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -22410,13 +22410,13 @@
         <x:v>3600.0000</x:v>
       </x:c>
       <x:c r="AL28" s="6" t="n">
-        <x:v>2400.0000</x:v>
+        <x:v>4200.0000</x:v>
       </x:c>
       <x:c r="AM28" s="6" t="n">
-        <x:v>1200.0000</x:v>
+        <x:v>-600.0000</x:v>
       </x:c>
       <x:c r="AN28" s="6" t="n">
-        <x:v>1500.0000</x:v>
+        <x:v>2700.0000</x:v>
       </x:c>
       <x:c r="AO28" s="6" t="n">
         <x:v>3600.0000</x:v>

--- a/.pm-ai-cache/network-source/task-input-newest.xlsx
+++ b/.pm-ai-cache/network-source/task-input-newest.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工程別生産計画問合せ問合せ" sheetId="1" r:id="R93e5aaee78e14cbc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工程別生産計画問合せ問合せ" sheetId="1" r:id="Rbbb41e61dc8740dc"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/.pm-ai-cache/network-source/task-input-newest.xlsx
+++ b/.pm-ai-cache/network-source/task-input-newest.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工程別生産計画問合せ問合せ" sheetId="1" r:id="Rbbb41e61dc8740dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工程別生産計画問合せ問合せ" sheetId="1" r:id="R29c2a40cfc444cc4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -10,7 +10,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5">
   <x:si>
-    <x:t xml:space="preserve">表示基準日 : 2026年08月08日 </x:t>
+    <x:t xml:space="preserve">表示基準日 : 2026年08月09日 </x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">S </x:t>
@@ -578,823 +578,823 @@
         <x:v/>
       </x:c>
       <x:c r="AR5" s="2" t="str">
-        <x:v>07/09(木)</x:v>
+        <x:v>07/10(金)</x:v>
       </x:c>
       <x:c r="AS5" s="2" t="str">
-        <x:v>07/09(木)</x:v>
+        <x:v>07/10(金)</x:v>
       </x:c>
       <x:c r="AT5" s="2" t="str">
-        <x:v>07/09(木)</x:v>
+        <x:v>07/10(金)</x:v>
       </x:c>
       <x:c r="AU5" s="2" t="str">
-        <x:v>07/10(金)</x:v>
+        <x:v>07/11(土)</x:v>
       </x:c>
       <x:c r="AV5" s="2" t="str">
-        <x:v>07/10(金)</x:v>
+        <x:v>07/11(土)</x:v>
       </x:c>
       <x:c r="AW5" s="2" t="str">
-        <x:v>07/10(金)</x:v>
+        <x:v>07/11(土)</x:v>
       </x:c>
       <x:c r="AX5" s="2" t="str">
-        <x:v>07/11(土)</x:v>
+        <x:v>07/12(日)</x:v>
       </x:c>
       <x:c r="AY5" s="2" t="str">
-        <x:v>07/11(土)</x:v>
+        <x:v>07/12(日)</x:v>
       </x:c>
       <x:c r="AZ5" s="2" t="str">
-        <x:v>07/11(土)</x:v>
+        <x:v>07/12(日)</x:v>
       </x:c>
       <x:c r="BA5" s="2" t="str">
-        <x:v>07/12(日)</x:v>
+        <x:v>07/13(月)</x:v>
       </x:c>
       <x:c r="BB5" s="2" t="str">
-        <x:v>07/12(日)</x:v>
+        <x:v>07/13(月)</x:v>
       </x:c>
       <x:c r="BC5" s="2" t="str">
-        <x:v>07/12(日)</x:v>
+        <x:v>07/13(月)</x:v>
       </x:c>
       <x:c r="BD5" s="2" t="str">
-        <x:v>07/13(月)</x:v>
+        <x:v>07/14(火)</x:v>
       </x:c>
       <x:c r="BE5" s="2" t="str">
-        <x:v>07/13(月)</x:v>
+        <x:v>07/14(火)</x:v>
       </x:c>
       <x:c r="BF5" s="2" t="str">
-        <x:v>07/13(月)</x:v>
+        <x:v>07/14(火)</x:v>
       </x:c>
       <x:c r="BG5" s="2" t="str">
-        <x:v>07/14(火)</x:v>
+        <x:v>07/15(水)</x:v>
       </x:c>
       <x:c r="BH5" s="2" t="str">
-        <x:v>07/14(火)</x:v>
+        <x:v>07/15(水)</x:v>
       </x:c>
       <x:c r="BI5" s="2" t="str">
-        <x:v>07/14(火)</x:v>
+        <x:v>07/15(水)</x:v>
       </x:c>
       <x:c r="BJ5" s="2" t="str">
-        <x:v>07/15(水)</x:v>
+        <x:v>07/16(木)</x:v>
       </x:c>
       <x:c r="BK5" s="2" t="str">
-        <x:v>07/15(水)</x:v>
+        <x:v>07/16(木)</x:v>
       </x:c>
       <x:c r="BL5" s="2" t="str">
-        <x:v>07/15(水)</x:v>
+        <x:v>07/16(木)</x:v>
       </x:c>
       <x:c r="BM5" s="2" t="str">
-        <x:v>07/16(木)</x:v>
+        <x:v>07/17(金)</x:v>
       </x:c>
       <x:c r="BN5" s="2" t="str">
-        <x:v>07/16(木)</x:v>
+        <x:v>07/17(金)</x:v>
       </x:c>
       <x:c r="BO5" s="2" t="str">
-        <x:v>07/16(木)</x:v>
+        <x:v>07/17(金)</x:v>
       </x:c>
       <x:c r="BP5" s="2" t="str">
-        <x:v>07/17(金)</x:v>
+        <x:v>07/18(土)</x:v>
       </x:c>
       <x:c r="BQ5" s="2" t="str">
-        <x:v>07/17(金)</x:v>
+        <x:v>07/18(土)</x:v>
       </x:c>
       <x:c r="BR5" s="2" t="str">
-        <x:v>07/17(金)</x:v>
+        <x:v>07/18(土)</x:v>
       </x:c>
       <x:c r="BS5" s="2" t="str">
-        <x:v>07/18(土)</x:v>
+        <x:v>07/19(日)</x:v>
       </x:c>
       <x:c r="BT5" s="2" t="str">
-        <x:v>07/18(土)</x:v>
+        <x:v>07/19(日)</x:v>
       </x:c>
       <x:c r="BU5" s="2" t="str">
-        <x:v>07/18(土)</x:v>
+        <x:v>07/19(日)</x:v>
       </x:c>
       <x:c r="BV5" s="2" t="str">
-        <x:v>07/19(日)</x:v>
+        <x:v>07/20(月)</x:v>
       </x:c>
       <x:c r="BW5" s="2" t="str">
-        <x:v>07/19(日)</x:v>
+        <x:v>07/20(月)</x:v>
       </x:c>
       <x:c r="BX5" s="2" t="str">
-        <x:v>07/19(日)</x:v>
+        <x:v>07/20(月)</x:v>
       </x:c>
       <x:c r="BY5" s="2" t="str">
-        <x:v>07/20(月)</x:v>
+        <x:v>07/21(火)</x:v>
       </x:c>
       <x:c r="BZ5" s="2" t="str">
-        <x:v>07/20(月)</x:v>
+        <x:v>07/21(火)</x:v>
       </x:c>
       <x:c r="CA5" s="2" t="str">
-        <x:v>07/20(月)</x:v>
+        <x:v>07/21(火)</x:v>
       </x:c>
       <x:c r="CB5" s="2" t="str">
-        <x:v>07/21(火)</x:v>
+        <x:v>07/22(水)</x:v>
       </x:c>
       <x:c r="CC5" s="2" t="str">
-        <x:v>07/21(火)</x:v>
+        <x:v>07/22(水)</x:v>
       </x:c>
       <x:c r="CD5" s="2" t="str">
-        <x:v>07/21(火)</x:v>
+        <x:v>07/22(水)</x:v>
       </x:c>
       <x:c r="CE5" s="2" t="str">
-        <x:v>07/22(水)</x:v>
+        <x:v>07/23(木)</x:v>
       </x:c>
       <x:c r="CF5" s="2" t="str">
-        <x:v>07/22(水)</x:v>
+        <x:v>07/23(木)</x:v>
       </x:c>
       <x:c r="CG5" s="2" t="str">
-        <x:v>07/22(水)</x:v>
+        <x:v>07/23(木)</x:v>
       </x:c>
       <x:c r="CH5" s="2" t="str">
-        <x:v>07/23(木)</x:v>
+        <x:v>07/24(金)</x:v>
       </x:c>
       <x:c r="CI5" s="2" t="str">
-        <x:v>07/23(木)</x:v>
+        <x:v>07/24(金)</x:v>
       </x:c>
       <x:c r="CJ5" s="2" t="str">
-        <x:v>07/23(木)</x:v>
+        <x:v>07/24(金)</x:v>
       </x:c>
       <x:c r="CK5" s="2" t="str">
-        <x:v>07/24(金)</x:v>
+        <x:v>07/25(土)</x:v>
       </x:c>
       <x:c r="CL5" s="2" t="str">
-        <x:v>07/24(金)</x:v>
+        <x:v>07/25(土)</x:v>
       </x:c>
       <x:c r="CM5" s="2" t="str">
-        <x:v>07/24(金)</x:v>
+        <x:v>07/25(土)</x:v>
       </x:c>
       <x:c r="CN5" s="2" t="str">
-        <x:v>07/25(土)</x:v>
+        <x:v>07/26(日)</x:v>
       </x:c>
       <x:c r="CO5" s="2" t="str">
-        <x:v>07/25(土)</x:v>
+        <x:v>07/26(日)</x:v>
       </x:c>
       <x:c r="CP5" s="2" t="str">
-        <x:v>07/25(土)</x:v>
+        <x:v>07/26(日)</x:v>
       </x:c>
       <x:c r="CQ5" s="2" t="str">
-        <x:v>07/26(日)</x:v>
+        <x:v>07/27(月)</x:v>
       </x:c>
       <x:c r="CR5" s="2" t="str">
-        <x:v>07/26(日)</x:v>
+        <x:v>07/27(月)</x:v>
       </x:c>
       <x:c r="CS5" s="2" t="str">
-        <x:v>07/26(日)</x:v>
+        <x:v>07/27(月)</x:v>
       </x:c>
       <x:c r="CT5" s="2" t="str">
-        <x:v>07/27(月)</x:v>
+        <x:v>07/28(火)</x:v>
       </x:c>
       <x:c r="CU5" s="2" t="str">
-        <x:v>07/27(月)</x:v>
+        <x:v>07/28(火)</x:v>
       </x:c>
       <x:c r="CV5" s="2" t="str">
-        <x:v>07/27(月)</x:v>
+        <x:v>07/28(火)</x:v>
       </x:c>
       <x:c r="CW5" s="2" t="str">
-        <x:v>07/28(火)</x:v>
+        <x:v>07/29(水)</x:v>
       </x:c>
       <x:c r="CX5" s="2" t="str">
-        <x:v>07/28(火)</x:v>
+        <x:v>07/29(水)</x:v>
       </x:c>
       <x:c r="CY5" s="2" t="str">
-        <x:v>07/28(火)</x:v>
+        <x:v>07/29(水)</x:v>
       </x:c>
       <x:c r="CZ5" s="2" t="str">
-        <x:v>07/29(水)</x:v>
+        <x:v>07/30(木)</x:v>
       </x:c>
       <x:c r="DA5" s="2" t="str">
-        <x:v>07/29(水)</x:v>
+        <x:v>07/30(木)</x:v>
       </x:c>
       <x:c r="DB5" s="2" t="str">
-        <x:v>07/29(水)</x:v>
+        <x:v>07/30(木)</x:v>
       </x:c>
       <x:c r="DC5" s="2" t="str">
-        <x:v>07/30(木)</x:v>
+        <x:v>07/31(金)</x:v>
       </x:c>
       <x:c r="DD5" s="2" t="str">
-        <x:v>07/30(木)</x:v>
+        <x:v>07/31(金)</x:v>
       </x:c>
       <x:c r="DE5" s="2" t="str">
-        <x:v>07/30(木)</x:v>
+        <x:v>07/31(金)</x:v>
       </x:c>
       <x:c r="DF5" s="2" t="str">
-        <x:v>07/31(金)</x:v>
+        <x:v>08/01(土)</x:v>
       </x:c>
       <x:c r="DG5" s="2" t="str">
-        <x:v>07/31(金)</x:v>
+        <x:v>08/01(土)</x:v>
       </x:c>
       <x:c r="DH5" s="2" t="str">
-        <x:v>07/31(金)</x:v>
+        <x:v>08/01(土)</x:v>
       </x:c>
       <x:c r="DI5" s="2" t="str">
-        <x:v>08/01(土)</x:v>
+        <x:v>08/02(日)</x:v>
       </x:c>
       <x:c r="DJ5" s="2" t="str">
-        <x:v>08/01(土)</x:v>
+        <x:v>08/02(日)</x:v>
       </x:c>
       <x:c r="DK5" s="2" t="str">
-        <x:v>08/01(土)</x:v>
+        <x:v>08/02(日)</x:v>
       </x:c>
       <x:c r="DL5" s="2" t="str">
-        <x:v>08/02(日)</x:v>
+        <x:v>08/03(月)</x:v>
       </x:c>
       <x:c r="DM5" s="2" t="str">
-        <x:v>08/02(日)</x:v>
+        <x:v>08/03(月)</x:v>
       </x:c>
       <x:c r="DN5" s="2" t="str">
-        <x:v>08/02(日)</x:v>
+        <x:v>08/03(月)</x:v>
       </x:c>
       <x:c r="DO5" s="2" t="str">
-        <x:v>08/03(月)</x:v>
+        <x:v>08/04(火)</x:v>
       </x:c>
       <x:c r="DP5" s="2" t="str">
-        <x:v>08/03(月)</x:v>
+        <x:v>08/04(火)</x:v>
       </x:c>
       <x:c r="DQ5" s="2" t="str">
-        <x:v>08/03(月)</x:v>
+        <x:v>08/04(火)</x:v>
       </x:c>
       <x:c r="DR5" s="2" t="str">
-        <x:v>08/04(火)</x:v>
+        <x:v>08/05(水)</x:v>
       </x:c>
       <x:c r="DS5" s="2" t="str">
-        <x:v>08/04(火)</x:v>
+        <x:v>08/05(水)</x:v>
       </x:c>
       <x:c r="DT5" s="2" t="str">
-        <x:v>08/04(火)</x:v>
+        <x:v>08/05(水)</x:v>
       </x:c>
       <x:c r="DU5" s="2" t="str">
-        <x:v>08/05(水)</x:v>
+        <x:v>08/06(木)</x:v>
       </x:c>
       <x:c r="DV5" s="2" t="str">
-        <x:v>08/05(水)</x:v>
+        <x:v>08/06(木)</x:v>
       </x:c>
       <x:c r="DW5" s="2" t="str">
-        <x:v>08/05(水)</x:v>
+        <x:v>08/06(木)</x:v>
       </x:c>
       <x:c r="DX5" s="2" t="str">
-        <x:v>08/06(木)</x:v>
+        <x:v>08/07(金)</x:v>
       </x:c>
       <x:c r="DY5" s="2" t="str">
-        <x:v>08/06(木)</x:v>
+        <x:v>08/07(金)</x:v>
       </x:c>
       <x:c r="DZ5" s="2" t="str">
-        <x:v>08/06(木)</x:v>
+        <x:v>08/07(金)</x:v>
       </x:c>
       <x:c r="EA5" s="2" t="str">
-        <x:v>08/07(金)</x:v>
+        <x:v>08/08(土)</x:v>
       </x:c>
       <x:c r="EB5" s="2" t="str">
-        <x:v>08/07(金)</x:v>
+        <x:v>08/08(土)</x:v>
       </x:c>
       <x:c r="EC5" s="2" t="str">
-        <x:v>08/07(金)</x:v>
+        <x:v>08/08(土)</x:v>
       </x:c>
       <x:c r="ED5" s="2" t="str">
-        <x:v>08/08(土)</x:v>
+        <x:v>08/09(日)</x:v>
       </x:c>
       <x:c r="EE5" s="2" t="str">
-        <x:v>08/08(土)</x:v>
+        <x:v>08/09(日)</x:v>
       </x:c>
       <x:c r="EF5" s="2" t="str">
-        <x:v>08/08(土)</x:v>
+        <x:v>08/09(日)</x:v>
       </x:c>
       <x:c r="EG5" s="2" t="str">
-        <x:v>08/09(日)</x:v>
+        <x:v>08/10(月)</x:v>
       </x:c>
       <x:c r="EH5" s="2" t="str">
-        <x:v>08/09(日)</x:v>
+        <x:v>08/10(月)</x:v>
       </x:c>
       <x:c r="EI5" s="2" t="str">
-        <x:v>08/09(日)</x:v>
+        <x:v>08/10(月)</x:v>
       </x:c>
       <x:c r="EJ5" s="2" t="str">
-        <x:v>08/10(月)</x:v>
+        <x:v>08/11(火)</x:v>
       </x:c>
       <x:c r="EK5" s="2" t="str">
-        <x:v>08/10(月)</x:v>
+        <x:v>08/11(火)</x:v>
       </x:c>
       <x:c r="EL5" s="2" t="str">
-        <x:v>08/10(月)</x:v>
+        <x:v>08/11(火)</x:v>
       </x:c>
       <x:c r="EM5" s="2" t="str">
-        <x:v>08/11(火)</x:v>
+        <x:v>08/12(水)</x:v>
       </x:c>
       <x:c r="EN5" s="2" t="str">
-        <x:v>08/11(火)</x:v>
+        <x:v>08/12(水)</x:v>
       </x:c>
       <x:c r="EO5" s="2" t="str">
-        <x:v>08/11(火)</x:v>
+        <x:v>08/12(水)</x:v>
       </x:c>
       <x:c r="EP5" s="2" t="str">
-        <x:v>08/12(水)</x:v>
+        <x:v>08/13(木)</x:v>
       </x:c>
       <x:c r="EQ5" s="2" t="str">
-        <x:v>08/12(水)</x:v>
+        <x:v>08/13(木)</x:v>
       </x:c>
       <x:c r="ER5" s="2" t="str">
-        <x:v>08/12(水)</x:v>
+        <x:v>08/13(木)</x:v>
       </x:c>
       <x:c r="ES5" s="2" t="str">
-        <x:v>08/13(木)</x:v>
+        <x:v>08/14(金)</x:v>
       </x:c>
       <x:c r="ET5" s="2" t="str">
-        <x:v>08/13(木)</x:v>
+        <x:v>08/14(金)</x:v>
       </x:c>
       <x:c r="EU5" s="2" t="str">
-        <x:v>08/13(木)</x:v>
+        <x:v>08/14(金)</x:v>
       </x:c>
       <x:c r="EV5" s="2" t="str">
-        <x:v>08/14(金)</x:v>
+        <x:v>08/15(土)</x:v>
       </x:c>
       <x:c r="EW5" s="2" t="str">
-        <x:v>08/14(金)</x:v>
+        <x:v>08/15(土)</x:v>
       </x:c>
       <x:c r="EX5" s="2" t="str">
-        <x:v>08/14(金)</x:v>
+        <x:v>08/15(土)</x:v>
       </x:c>
       <x:c r="EY5" s="2" t="str">
-        <x:v>08/15(土)</x:v>
+        <x:v>08/16(日)</x:v>
       </x:c>
       <x:c r="EZ5" s="2" t="str">
-        <x:v>08/15(土)</x:v>
+        <x:v>08/16(日)</x:v>
       </x:c>
       <x:c r="FA5" s="2" t="str">
-        <x:v>08/15(土)</x:v>
+        <x:v>08/16(日)</x:v>
       </x:c>
       <x:c r="FB5" s="2" t="str">
-        <x:v>08/16(日)</x:v>
+        <x:v>08/17(月)</x:v>
       </x:c>
       <x:c r="FC5" s="2" t="str">
-        <x:v>08/16(日)</x:v>
+        <x:v>08/17(月)</x:v>
       </x:c>
       <x:c r="FD5" s="2" t="str">
-        <x:v>08/16(日)</x:v>
+        <x:v>08/17(月)</x:v>
       </x:c>
       <x:c r="FE5" s="2" t="str">
-        <x:v>08/17(月)</x:v>
+        <x:v>08/18(火)</x:v>
       </x:c>
       <x:c r="FF5" s="2" t="str">
-        <x:v>08/17(月)</x:v>
+        <x:v>08/18(火)</x:v>
       </x:c>
       <x:c r="FG5" s="2" t="str">
-        <x:v>08/17(月)</x:v>
+        <x:v>08/18(火)</x:v>
       </x:c>
       <x:c r="FH5" s="2" t="str">
-        <x:v>08/18(火)</x:v>
+        <x:v>08/19(水)</x:v>
       </x:c>
       <x:c r="FI5" s="2" t="str">
-        <x:v>08/18(火)</x:v>
+        <x:v>08/19(水)</x:v>
       </x:c>
       <x:c r="FJ5" s="2" t="str">
-        <x:v>08/18(火)</x:v>
+        <x:v>08/19(水)</x:v>
       </x:c>
       <x:c r="FK5" s="2" t="str">
-        <x:v>08/19(水)</x:v>
+        <x:v>08/20(木)</x:v>
       </x:c>
       <x:c r="FL5" s="2" t="str">
-        <x:v>08/19(水)</x:v>
+        <x:v>08/20(木)</x:v>
       </x:c>
       <x:c r="FM5" s="2" t="str">
-        <x:v>08/19(水)</x:v>
+        <x:v>08/20(木)</x:v>
       </x:c>
       <x:c r="FN5" s="2" t="str">
-        <x:v>08/20(木)</x:v>
+        <x:v>08/21(金)</x:v>
       </x:c>
       <x:c r="FO5" s="2" t="str">
-        <x:v>08/20(木)</x:v>
+        <x:v>08/21(金)</x:v>
       </x:c>
       <x:c r="FP5" s="2" t="str">
-        <x:v>08/20(木)</x:v>
+        <x:v>08/21(金)</x:v>
       </x:c>
       <x:c r="FQ5" s="2" t="str">
-        <x:v>08/21(金)</x:v>
+        <x:v>08/22(土)</x:v>
       </x:c>
       <x:c r="FR5" s="2" t="str">
-        <x:v>08/21(金)</x:v>
+        <x:v>08/22(土)</x:v>
       </x:c>
       <x:c r="FS5" s="2" t="str">
-        <x:v>08/21(金)</x:v>
+        <x:v>08/22(土)</x:v>
       </x:c>
       <x:c r="FT5" s="2" t="str">
-        <x:v>08/22(土)</x:v>
+        <x:v>08/23(日)</x:v>
       </x:c>
       <x:c r="FU5" s="2" t="str">
-        <x:v>08/22(土)</x:v>
+        <x:v>08/23(日)</x:v>
       </x:c>
       <x:c r="FV5" s="2" t="str">
-        <x:v>08/22(土)</x:v>
+        <x:v>08/23(日)</x:v>
       </x:c>
       <x:c r="FW5" s="2" t="str">
-        <x:v>08/23(日)</x:v>
+        <x:v>08/24(月)</x:v>
       </x:c>
       <x:c r="FX5" s="2" t="str">
-        <x:v>08/23(日)</x:v>
+        <x:v>08/24(月)</x:v>
       </x:c>
       <x:c r="FY5" s="2" t="str">
-        <x:v>08/23(日)</x:v>
+        <x:v>08/24(月)</x:v>
       </x:c>
       <x:c r="FZ5" s="2" t="str">
-        <x:v>08/24(月)</x:v>
+        <x:v>08/25(火)</x:v>
       </x:c>
       <x:c r="GA5" s="2" t="str">
-        <x:v>08/24(月)</x:v>
+        <x:v>08/25(火)</x:v>
       </x:c>
       <x:c r="GB5" s="2" t="str">
-        <x:v>08/24(月)</x:v>
+        <x:v>08/25(火)</x:v>
       </x:c>
       <x:c r="GC5" s="2" t="str">
-        <x:v>08/25(火)</x:v>
+        <x:v>08/26(水)</x:v>
       </x:c>
       <x:c r="GD5" s="2" t="str">
-        <x:v>08/25(火)</x:v>
+        <x:v>08/26(水)</x:v>
       </x:c>
       <x:c r="GE5" s="2" t="str">
-        <x:v>08/25(火)</x:v>
+        <x:v>08/26(水)</x:v>
       </x:c>
       <x:c r="GF5" s="2" t="str">
-        <x:v>08/26(水)</x:v>
+        <x:v>08/27(木)</x:v>
       </x:c>
       <x:c r="GG5" s="2" t="str">
-        <x:v>08/26(水)</x:v>
+        <x:v>08/27(木)</x:v>
       </x:c>
       <x:c r="GH5" s="2" t="str">
-        <x:v>08/26(水)</x:v>
+        <x:v>08/27(木)</x:v>
       </x:c>
       <x:c r="GI5" s="2" t="str">
-        <x:v>08/27(木)</x:v>
+        <x:v>08/28(金)</x:v>
       </x:c>
       <x:c r="GJ5" s="2" t="str">
-        <x:v>08/27(木)</x:v>
+        <x:v>08/28(金)</x:v>
       </x:c>
       <x:c r="GK5" s="2" t="str">
-        <x:v>08/27(木)</x:v>
+        <x:v>08/28(金)</x:v>
       </x:c>
       <x:c r="GL5" s="2" t="str">
-        <x:v>08/28(金)</x:v>
+        <x:v>08/29(土)</x:v>
       </x:c>
       <x:c r="GM5" s="2" t="str">
-        <x:v>08/28(金)</x:v>
+        <x:v>08/29(土)</x:v>
       </x:c>
       <x:c r="GN5" s="2" t="str">
-        <x:v>08/28(金)</x:v>
+        <x:v>08/29(土)</x:v>
       </x:c>
       <x:c r="GO5" s="2" t="str">
-        <x:v>08/29(土)</x:v>
+        <x:v>08/30(日)</x:v>
       </x:c>
       <x:c r="GP5" s="2" t="str">
-        <x:v>08/29(土)</x:v>
+        <x:v>08/30(日)</x:v>
       </x:c>
       <x:c r="GQ5" s="2" t="str">
-        <x:v>08/29(土)</x:v>
+        <x:v>08/30(日)</x:v>
       </x:c>
       <x:c r="GR5" s="2" t="str">
-        <x:v>08/30(日)</x:v>
+        <x:v>08/31(月)</x:v>
       </x:c>
       <x:c r="GS5" s="2" t="str">
-        <x:v>08/30(日)</x:v>
+        <x:v>08/31(月)</x:v>
       </x:c>
       <x:c r="GT5" s="2" t="str">
-        <x:v>08/30(日)</x:v>
+        <x:v>08/31(月)</x:v>
       </x:c>
       <x:c r="GU5" s="2" t="str">
-        <x:v>08/31(月)</x:v>
+        <x:v>09/01(火)</x:v>
       </x:c>
       <x:c r="GV5" s="2" t="str">
-        <x:v>08/31(月)</x:v>
+        <x:v>09/01(火)</x:v>
       </x:c>
       <x:c r="GW5" s="2" t="str">
-        <x:v>08/31(月)</x:v>
+        <x:v>09/01(火)</x:v>
       </x:c>
       <x:c r="GX5" s="2" t="str">
-        <x:v>09/01(火)</x:v>
+        <x:v>09/02(水)</x:v>
       </x:c>
       <x:c r="GY5" s="2" t="str">
-        <x:v>09/01(火)</x:v>
+        <x:v>09/02(水)</x:v>
       </x:c>
       <x:c r="GZ5" s="2" t="str">
-        <x:v>09/01(火)</x:v>
+        <x:v>09/02(水)</x:v>
       </x:c>
       <x:c r="HA5" s="2" t="str">
-        <x:v>09/02(水)</x:v>
+        <x:v>09/03(木)</x:v>
       </x:c>
       <x:c r="HB5" s="2" t="str">
-        <x:v>09/02(水)</x:v>
+        <x:v>09/03(木)</x:v>
       </x:c>
       <x:c r="HC5" s="2" t="str">
-        <x:v>09/02(水)</x:v>
+        <x:v>09/03(木)</x:v>
       </x:c>
       <x:c r="HD5" s="2" t="str">
-        <x:v>09/03(木)</x:v>
+        <x:v>09/04(金)</x:v>
       </x:c>
       <x:c r="HE5" s="2" t="str">
-        <x:v>09/03(木)</x:v>
+        <x:v>09/04(金)</x:v>
       </x:c>
       <x:c r="HF5" s="2" t="str">
-        <x:v>09/03(木)</x:v>
+        <x:v>09/04(金)</x:v>
       </x:c>
       <x:c r="HG5" s="2" t="str">
-        <x:v>09/04(金)</x:v>
+        <x:v>09/05(土)</x:v>
       </x:c>
       <x:c r="HH5" s="2" t="str">
-        <x:v>09/04(金)</x:v>
+        <x:v>09/05(土)</x:v>
       </x:c>
       <x:c r="HI5" s="2" t="str">
-        <x:v>09/04(金)</x:v>
+        <x:v>09/05(土)</x:v>
       </x:c>
       <x:c r="HJ5" s="2" t="str">
-        <x:v>09/05(土)</x:v>
+        <x:v>09/06(日)</x:v>
       </x:c>
       <x:c r="HK5" s="2" t="str">
-        <x:v>09/05(土)</x:v>
+        <x:v>09/06(日)</x:v>
       </x:c>
       <x:c r="HL5" s="2" t="str">
-        <x:v>09/05(土)</x:v>
+        <x:v>09/06(日)</x:v>
       </x:c>
       <x:c r="HM5" s="2" t="str">
-        <x:v>09/06(日)</x:v>
+        <x:v>09/07(月)</x:v>
       </x:c>
       <x:c r="HN5" s="2" t="str">
-        <x:v>09/06(日)</x:v>
+        <x:v>09/07(月)</x:v>
       </x:c>
       <x:c r="HO5" s="2" t="str">
-        <x:v>09/06(日)</x:v>
+        <x:v>09/07(月)</x:v>
       </x:c>
       <x:c r="HP5" s="2" t="str">
-        <x:v>09/07(月)</x:v>
+        <x:v>09/08(火)</x:v>
       </x:c>
       <x:c r="HQ5" s="2" t="str">
-        <x:v>09/07(月)</x:v>
+        <x:v>09/08(火)</x:v>
       </x:c>
       <x:c r="HR5" s="2" t="str">
-        <x:v>09/07(月)</x:v>
+        <x:v>09/08(火)</x:v>
       </x:c>
       <x:c r="HS5" s="2" t="str">
-        <x:v>09/08(火)</x:v>
+        <x:v>09/09(水)</x:v>
       </x:c>
       <x:c r="HT5" s="2" t="str">
-        <x:v>09/08(火)</x:v>
+        <x:v>09/09(水)</x:v>
       </x:c>
       <x:c r="HU5" s="2" t="str">
-        <x:v>09/08(火)</x:v>
+        <x:v>09/09(水)</x:v>
       </x:c>
       <x:c r="HV5" s="2" t="str">
-        <x:v>09/09(水)</x:v>
+        <x:v>09/10(木)</x:v>
       </x:c>
       <x:c r="HW5" s="2" t="str">
-        <x:v>09/09(水)</x:v>
+        <x:v>09/10(木)</x:v>
       </x:c>
       <x:c r="HX5" s="2" t="str">
-        <x:v>09/09(水)</x:v>
+        <x:v>09/10(木)</x:v>
       </x:c>
       <x:c r="HY5" s="2" t="str">
-        <x:v>09/10(木)</x:v>
+        <x:v>09/11(金)</x:v>
       </x:c>
       <x:c r="HZ5" s="2" t="str">
-        <x:v>09/10(木)</x:v>
+        <x:v>09/11(金)</x:v>
       </x:c>
       <x:c r="IA5" s="2" t="str">
-        <x:v>09/10(木)</x:v>
+        <x:v>09/11(金)</x:v>
       </x:c>
       <x:c r="IB5" s="2" t="str">
-        <x:v>09/11(金)</x:v>
+        <x:v>09/12(土)</x:v>
       </x:c>
       <x:c r="IC5" s="2" t="str">
-        <x:v>09/11(金)</x:v>
+        <x:v>09/12(土)</x:v>
       </x:c>
       <x:c r="ID5" s="2" t="str">
-        <x:v>09/11(金)</x:v>
+        <x:v>09/12(土)</x:v>
       </x:c>
       <x:c r="IE5" s="2" t="str">
-        <x:v>09/12(土)</x:v>
+        <x:v>09/13(日)</x:v>
       </x:c>
       <x:c r="IF5" s="2" t="str">
-        <x:v>09/12(土)</x:v>
+        <x:v>09/13(日)</x:v>
       </x:c>
       <x:c r="IG5" s="2" t="str">
-        <x:v>09/12(土)</x:v>
+        <x:v>09/13(日)</x:v>
       </x:c>
       <x:c r="IH5" s="2" t="str">
-        <x:v>09/13(日)</x:v>
+        <x:v>09/14(月)</x:v>
       </x:c>
       <x:c r="II5" s="2" t="str">
-        <x:v>09/13(日)</x:v>
+        <x:v>09/14(月)</x:v>
       </x:c>
       <x:c r="IJ5" s="2" t="str">
-        <x:v>09/13(日)</x:v>
+        <x:v>09/14(月)</x:v>
       </x:c>
       <x:c r="IK5" s="2" t="str">
-        <x:v>09/14(月)</x:v>
+        <x:v>09/15(火)</x:v>
       </x:c>
       <x:c r="IL5" s="2" t="str">
-        <x:v>09/14(月)</x:v>
+        <x:v>09/15(火)</x:v>
       </x:c>
       <x:c r="IM5" s="2" t="str">
-        <x:v>09/14(月)</x:v>
+        <x:v>09/15(火)</x:v>
       </x:c>
       <x:c r="IN5" s="2" t="str">
-        <x:v>09/15(火)</x:v>
+        <x:v>09/16(水)</x:v>
       </x:c>
       <x:c r="IO5" s="2" t="str">
-        <x:v>09/15(火)</x:v>
+        <x:v>09/16(水)</x:v>
       </x:c>
       <x:c r="IP5" s="2" t="str">
-        <x:v>09/15(火)</x:v>
+        <x:v>09/16(水)</x:v>
       </x:c>
       <x:c r="IQ5" s="2" t="str">
-        <x:v>09/16(水)</x:v>
+        <x:v>09/17(木)</x:v>
       </x:c>
       <x:c r="IR5" s="2" t="str">
-        <x:v>09/16(水)</x:v>
+        <x:v>09/17(木)</x:v>
       </x:c>
       <x:c r="IS5" s="2" t="str">
-        <x:v>09/16(水)</x:v>
+        <x:v>09/17(木)</x:v>
       </x:c>
       <x:c r="IT5" s="2" t="str">
-        <x:v>09/17(木)</x:v>
+        <x:v>09/18(金)</x:v>
       </x:c>
       <x:c r="IU5" s="2" t="str">
-        <x:v>09/17(木)</x:v>
+        <x:v>09/18(金)</x:v>
       </x:c>
       <x:c r="IV5" s="2" t="str">
-        <x:v>09/17(木)</x:v>
+        <x:v>09/18(金)</x:v>
       </x:c>
       <x:c r="IW5" s="2" t="str">
-        <x:v>09/18(金)</x:v>
+        <x:v>09/19(土)</x:v>
       </x:c>
       <x:c r="IX5" s="2" t="str">
-        <x:v>09/18(金)</x:v>
+        <x:v>09/19(土)</x:v>
       </x:c>
       <x:c r="IY5" s="2" t="str">
-        <x:v>09/18(金)</x:v>
+        <x:v>09/19(土)</x:v>
       </x:c>
       <x:c r="IZ5" s="2" t="str">
-        <x:v>09/19(土)</x:v>
+        <x:v>09/20(日)</x:v>
       </x:c>
       <x:c r="JA5" s="2" t="str">
-        <x:v>09/19(土)</x:v>
+        <x:v>09/20(日)</x:v>
       </x:c>
       <x:c r="JB5" s="2" t="str">
-        <x:v>09/19(土)</x:v>
+        <x:v>09/20(日)</x:v>
       </x:c>
       <x:c r="JC5" s="2" t="str">
-        <x:v>09/20(日)</x:v>
+        <x:v>09/21(月)</x:v>
       </x:c>
       <x:c r="JD5" s="2" t="str">
-        <x:v>09/20(日)</x:v>
+        <x:v>09/21(月)</x:v>
       </x:c>
       <x:c r="JE5" s="2" t="str">
-        <x:v>09/20(日)</x:v>
+        <x:v>09/21(月)</x:v>
       </x:c>
       <x:c r="JF5" s="2" t="str">
-        <x:v>09/21(月)</x:v>
+        <x:v>09/22(火)</x:v>
       </x:c>
       <x:c r="JG5" s="2" t="str">
-        <x:v>09/21(月)</x:v>
+        <x:v>09/22(火)</x:v>
       </x:c>
       <x:c r="JH5" s="2" t="str">
-        <x:v>09/21(月)</x:v>
+        <x:v>09/22(火)</x:v>
       </x:c>
       <x:c r="JI5" s="2" t="str">
-        <x:v>09/22(火)</x:v>
+        <x:v>09/23(水)</x:v>
       </x:c>
       <x:c r="JJ5" s="2" t="str">
-        <x:v>09/22(火)</x:v>
+        <x:v>09/23(水)</x:v>
       </x:c>
       <x:c r="JK5" s="2" t="str">
-        <x:v>09/22(火)</x:v>
+        <x:v>09/23(水)</x:v>
       </x:c>
       <x:c r="JL5" s="2" t="str">
-        <x:v>09/23(水)</x:v>
+        <x:v>09/24(木)</x:v>
       </x:c>
       <x:c r="JM5" s="2" t="str">
-        <x:v>09/23(水)</x:v>
+        <x:v>09/24(木)</x:v>
       </x:c>
       <x:c r="JN5" s="2" t="str">
-        <x:v>09/23(水)</x:v>
+        <x:v>09/24(木)</x:v>
       </x:c>
       <x:c r="JO5" s="2" t="str">
-        <x:v>09/24(木)</x:v>
+        <x:v>09/25(金)</x:v>
       </x:c>
       <x:c r="JP5" s="2" t="str">
-        <x:v>09/24(木)</x:v>
+        <x:v>09/25(金)</x:v>
       </x:c>
       <x:c r="JQ5" s="2" t="str">
-        <x:v>09/24(木)</x:v>
+        <x:v>09/25(金)</x:v>
       </x:c>
       <x:c r="JR5" s="2" t="str">
-        <x:v>09/25(金)</x:v>
+        <x:v>09/26(土)</x:v>
       </x:c>
       <x:c r="JS5" s="2" t="str">
-        <x:v>09/25(金)</x:v>
+        <x:v>09/26(土)</x:v>
       </x:c>
       <x:c r="JT5" s="2" t="str">
-        <x:v>09/25(金)</x:v>
+        <x:v>09/26(土)</x:v>
       </x:c>
       <x:c r="JU5" s="2" t="str">
-        <x:v>09/26(土)</x:v>
+        <x:v>09/27(日)</x:v>
       </x:c>
       <x:c r="JV5" s="2" t="str">
-        <x:v>09/26(土)</x:v>
+        <x:v>09/27(日)</x:v>
       </x:c>
       <x:c r="JW5" s="2" t="str">
-        <x:v>09/26(土)</x:v>
+        <x:v>09/27(日)</x:v>
       </x:c>
       <x:c r="JX5" s="2" t="str">
-        <x:v>09/27(日)</x:v>
+        <x:v>09/28(月)</x:v>
       </x:c>
       <x:c r="JY5" s="2" t="str">
-        <x:v>09/27(日)</x:v>
+        <x:v>09/28(月)</x:v>
       </x:c>
       <x:c r="JZ5" s="2" t="str">
-        <x:v>09/27(日)</x:v>
+        <x:v>09/28(月)</x:v>
       </x:c>
       <x:c r="KA5" s="2" t="str">
-        <x:v>09/28(月)</x:v>
+        <x:v>09/29(火)</x:v>
       </x:c>
       <x:c r="KB5" s="2" t="str">
-        <x:v>09/28(月)</x:v>
+        <x:v>09/29(火)</x:v>
       </x:c>
       <x:c r="KC5" s="2" t="str">
-        <x:v>09/28(月)</x:v>
+        <x:v>09/29(火)</x:v>
       </x:c>
       <x:c r="KD5" s="2" t="str">
-        <x:v>09/29(火)</x:v>
+        <x:v>09/30(水)</x:v>
       </x:c>
       <x:c r="KE5" s="2" t="str">
-        <x:v>09/29(火)</x:v>
+        <x:v>09/30(水)</x:v>
       </x:c>
       <x:c r="KF5" s="2" t="str">
-        <x:v>09/29(火)</x:v>
+        <x:v>09/30(水)</x:v>
       </x:c>
       <x:c r="KG5" s="2" t="str">
-        <x:v>09/30(水)</x:v>
+        <x:v>10/01(木)</x:v>
       </x:c>
       <x:c r="KH5" s="2" t="str">
-        <x:v>09/30(水)</x:v>
+        <x:v>10/01(木)</x:v>
       </x:c>
       <x:c r="KI5" s="2" t="str">
-        <x:v>09/30(水)</x:v>
+        <x:v>10/01(木)</x:v>
       </x:c>
       <x:c r="KJ5" s="2" t="str">
-        <x:v>10/01(木)</x:v>
+        <x:v>10/02(金)</x:v>
       </x:c>
       <x:c r="KK5" s="2" t="str">
-        <x:v>10/01(木)</x:v>
+        <x:v>10/02(金)</x:v>
       </x:c>
       <x:c r="KL5" s="2" t="str">
-        <x:v>10/01(木)</x:v>
+        <x:v>10/02(金)</x:v>
       </x:c>
       <x:c r="KM5" s="2" t="str">
-        <x:v>10/02(金)</x:v>
+        <x:v>10/03(土)</x:v>
       </x:c>
       <x:c r="KN5" s="2" t="str">
-        <x:v>10/02(金)</x:v>
+        <x:v>10/03(土)</x:v>
       </x:c>
       <x:c r="KO5" s="2" t="str">
-        <x:v>10/02(金)</x:v>
+        <x:v>10/03(土)</x:v>
       </x:c>
       <x:c r="KP5" s="2" t="str">
-        <x:v>10/03(土)</x:v>
+        <x:v>10/04(日)</x:v>
       </x:c>
       <x:c r="KQ5" s="2" t="str">
-        <x:v>10/03(土)</x:v>
+        <x:v>10/04(日)</x:v>
       </x:c>
       <x:c r="KR5" s="2" t="str">
-        <x:v>10/03(土)</x:v>
+        <x:v>10/04(日)</x:v>
       </x:c>
       <x:c r="KS5" s="2" t="str">
-        <x:v>10/04(日)</x:v>
+        <x:v>10/05(月)</x:v>
       </x:c>
       <x:c r="KT5" s="2" t="str">
-        <x:v>10/04(日)</x:v>
+        <x:v>10/05(月)</x:v>
       </x:c>
       <x:c r="KU5" s="2" t="str">
-        <x:v>10/04(日)</x:v>
+        <x:v>10/05(月)</x:v>
       </x:c>
       <x:c r="KV5" s="2" t="str">
-        <x:v>10/05(月)</x:v>
+        <x:v>10/06(火)</x:v>
       </x:c>
       <x:c r="KW5" s="2" t="str">
-        <x:v>10/05(月)</x:v>
+        <x:v>10/06(火)</x:v>
       </x:c>
       <x:c r="KX5" s="2" t="str">
-        <x:v>10/05(月)</x:v>
+        <x:v>10/06(火)</x:v>
       </x:c>
       <x:c r="KY5" s="2" t="str">
-        <x:v>10/06(火)</x:v>
+        <x:v>10/07(水)</x:v>
       </x:c>
       <x:c r="KZ5" s="2" t="str">
-        <x:v>10/06(火)</x:v>
+        <x:v>10/07(水)</x:v>
       </x:c>
       <x:c r="LA5" s="2" t="str">
-        <x:v>10/06(火)</x:v>
+        <x:v>10/07(水)</x:v>
       </x:c>
       <x:c r="LB5" s="2" t="str">
-        <x:v>10/07(水)</x:v>
+        <x:v>10/08(木)</x:v>
       </x:c>
       <x:c r="LC5" s="2" t="str">
-        <x:v>10/07(水)</x:v>
+        <x:v>10/08(木)</x:v>
       </x:c>
       <x:c r="LD5" s="2" t="str">
-        <x:v>10/07(水)</x:v>
+        <x:v>10/08(木)</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2730,22 +2730,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DX7" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4500.0000</x:v>
       </x:c>
       <x:c r="DY7" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="DZ7" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4.1500</x:v>
       </x:c>
       <x:c r="EA7" s="6" t="n">
-        <x:v>4500.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EB7" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EC7" s="8" t="n">
-        <x:v>4.1500</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ED7" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -3680,22 +3680,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DX8" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>900.0000</x:v>
       </x:c>
       <x:c r="DY8" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="DZ8" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.8300</x:v>
       </x:c>
       <x:c r="EA8" s="6" t="n">
-        <x:v>900.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EB8" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EC8" s="8" t="n">
-        <x:v>0.8300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ED8" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -3707,22 +3707,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG8" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3600.0000</x:v>
       </x:c>
       <x:c r="EH8" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EI8" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3.3200</x:v>
       </x:c>
       <x:c r="EJ8" s="6" t="n">
-        <x:v>3600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EK8" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="EL8" s="8" t="n">
-        <x:v>3.3200</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM8" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -4720,22 +4720,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB9" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4500.0000</x:v>
       </x:c>
       <x:c r="FC9" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="FD9" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4.1500</x:v>
       </x:c>
       <x:c r="FE9" s="6" t="n">
-        <x:v>4500.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FF9" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="FG9" s="8" t="n">
-        <x:v>4.1500</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FH9" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -5679,22 +5679,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FE10" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4500.0000</x:v>
       </x:c>
       <x:c r="FF10" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="FG10" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4.1500</x:v>
       </x:c>
       <x:c r="FH10" s="6" t="n">
-        <x:v>4500.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FI10" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="FJ10" s="8" t="n">
-        <x:v>4.1500</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FK10" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -6629,31 +6629,31 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FE11" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2700.0000</x:v>
       </x:c>
       <x:c r="FF11" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="FG11" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.4900</x:v>
       </x:c>
       <x:c r="FH11" s="6" t="n">
-        <x:v>2700.0000</x:v>
+        <x:v>1800.0000</x:v>
       </x:c>
       <x:c r="FI11" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="FJ11" s="8" t="n">
-        <x:v>2.4900</x:v>
+        <x:v>1.6600</x:v>
       </x:c>
       <x:c r="FK11" s="6" t="n">
-        <x:v>1800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FL11" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="FM11" s="8" t="n">
-        <x:v>1.6600</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FN11" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -7588,22 +7588,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FH12" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4500.0000</x:v>
       </x:c>
       <x:c r="FI12" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="FJ12" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4.1500</x:v>
       </x:c>
       <x:c r="FK12" s="6" t="n">
-        <x:v>4500.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FL12" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="FM12" s="8" t="n">
-        <x:v>4.1500</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FN12" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -8547,22 +8547,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FK13" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4500.0000</x:v>
       </x:c>
       <x:c r="FL13" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="FM13" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4.1500</x:v>
       </x:c>
       <x:c r="FN13" s="6" t="n">
-        <x:v>4500.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FO13" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="FP13" s="8" t="n">
-        <x:v>4.1500</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FQ13" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -9506,22 +9506,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FN14" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3300.0000</x:v>
       </x:c>
       <x:c r="FO14" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="FP14" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3.0500</x:v>
       </x:c>
       <x:c r="FQ14" s="6" t="n">
-        <x:v>3300.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FR14" s="8" t="n">
         <x:v>18.0600</x:v>
       </x:c>
       <x:c r="FS14" s="8" t="n">
-        <x:v>3.0500</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FT14" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -10429,22 +10429,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FE15" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>200.0000</x:v>
       </x:c>
       <x:c r="FF15" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="FG15" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.3300</x:v>
       </x:c>
       <x:c r="FH15" s="6" t="n">
-        <x:v>200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FI15" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="FJ15" s="8" t="n">
-        <x:v>0.3300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FK15" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -11379,22 +11379,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FE16" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>950.0000</x:v>
       </x:c>
       <x:c r="FF16" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="FG16" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.5600</x:v>
       </x:c>
       <x:c r="FH16" s="6" t="n">
-        <x:v>950.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FI16" s="8" t="n">
         <x:v>10.1200</x:v>
       </x:c>
       <x:c r="FJ16" s="8" t="n">
-        <x:v>1.5600</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FK16" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -12329,22 +12329,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FE17" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>100.0000</x:v>
       </x:c>
       <x:c r="FF17" s="8" t="n">
         <x:v>14.9900</x:v>
       </x:c>
       <x:c r="FG17" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.1100</x:v>
       </x:c>
       <x:c r="FH17" s="6" t="n">
-        <x:v>100.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FI17" s="8" t="n">
         <x:v>14.9900</x:v>
       </x:c>
       <x:c r="FJ17" s="8" t="n">
-        <x:v>0.1100</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FK17" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -13279,7 +13279,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FE18" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1000.0000</x:v>
       </x:c>
       <x:c r="FF18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -13288,7 +13288,7 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FH18" s="6" t="n">
-        <x:v>1000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FI18" s="8" t="n">
         <x:v>0.0000</x:v>
@@ -14121,31 +14121,31 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DU19" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5000.0000</x:v>
       </x:c>
       <x:c r="DV19" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="DW19" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3.3300</x:v>
       </x:c>
       <x:c r="DX19" s="6" t="n">
-        <x:v>5000.0000</x:v>
+        <x:v>3000.0000</x:v>
       </x:c>
       <x:c r="DY19" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="DZ19" s="8" t="n">
-        <x:v>3.3300</x:v>
+        <x:v>2.0000</x:v>
       </x:c>
       <x:c r="EA19" s="6" t="n">
-        <x:v>3000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EB19" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EC19" s="8" t="n">
-        <x:v>2.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="ED19" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -15107,13 +15107,13 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG20" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5000.0000</x:v>
       </x:c>
       <x:c r="EH20" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EI20" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3.3300</x:v>
       </x:c>
       <x:c r="EJ20" s="6" t="n">
         <x:v>5000.0000</x:v>
@@ -15125,13 +15125,13 @@
         <x:v>3.3300</x:v>
       </x:c>
       <x:c r="EM20" s="6" t="n">
-        <x:v>5000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN20" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EO20" s="8" t="n">
-        <x:v>3.3300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP20" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -16066,22 +16066,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ21" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5000.0000</x:v>
       </x:c>
       <x:c r="EK21" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EL21" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3.3300</x:v>
       </x:c>
       <x:c r="EM21" s="6" t="n">
-        <x:v>5000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN21" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="EO21" s="8" t="n">
-        <x:v>3.3300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP21" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -17070,22 +17070,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB22" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1000.0000</x:v>
       </x:c>
       <x:c r="FC22" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FD22" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.6700</x:v>
       </x:c>
       <x:c r="FE22" s="6" t="n">
-        <x:v>1000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FF22" s="8" t="n">
         <x:v>25.0000</x:v>
       </x:c>
       <x:c r="FG22" s="8" t="n">
-        <x:v>0.6700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FH22" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -18020,22 +18020,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB23" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>600.0000</x:v>
       </x:c>
       <x:c r="FC23" s="8" t="n">
         <x:v>10.0000</x:v>
       </x:c>
       <x:c r="FD23" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.0000</x:v>
       </x:c>
       <x:c r="FE23" s="6" t="n">
-        <x:v>600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FF23" s="8" t="n">
         <x:v>10.0000</x:v>
       </x:c>
       <x:c r="FG23" s="8" t="n">
-        <x:v>1.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FH23" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -18862,31 +18862,31 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DR24" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1200.0000</x:v>
       </x:c>
       <x:c r="DS24" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="DT24" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.3300</x:v>
       </x:c>
       <x:c r="DU24" s="6" t="n">
-        <x:v>1200.0000</x:v>
+        <x:v>1600.0000</x:v>
       </x:c>
       <x:c r="DV24" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="DW24" s="8" t="n">
-        <x:v>1.3300</x:v>
+        <x:v>1.7800</x:v>
       </x:c>
       <x:c r="DX24" s="6" t="n">
-        <x:v>1600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DY24" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="DZ24" s="8" t="n">
-        <x:v>1.7800</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EA24" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -18970,22 +18970,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB24" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>800.0000</x:v>
       </x:c>
       <x:c r="FC24" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FD24" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>0.8900</x:v>
       </x:c>
       <x:c r="FE24" s="6" t="n">
-        <x:v>800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FF24" s="8" t="n">
         <x:v>15.0000</x:v>
       </x:c>
       <x:c r="FG24" s="8" t="n">
-        <x:v>0.8900</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FH24" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -19812,31 +19812,31 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DR25" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1200.0000</x:v>
       </x:c>
       <x:c r="DS25" s="8" t="n">
         <x:v>10.0000</x:v>
       </x:c>
       <x:c r="DT25" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.0000</x:v>
       </x:c>
       <x:c r="DU25" s="6" t="n">
-        <x:v>1200.0000</x:v>
+        <x:v>1600.0000</x:v>
       </x:c>
       <x:c r="DV25" s="8" t="n">
         <x:v>10.0000</x:v>
       </x:c>
       <x:c r="DW25" s="8" t="n">
-        <x:v>2.0000</x:v>
+        <x:v>2.6700</x:v>
       </x:c>
       <x:c r="DX25" s="6" t="n">
-        <x:v>1600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DY25" s="8" t="n">
         <x:v>10.0000</x:v>
       </x:c>
       <x:c r="DZ25" s="8" t="n">
-        <x:v>2.6700</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EA25" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -19920,22 +19920,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB25" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>800.0000</x:v>
       </x:c>
       <x:c r="FC25" s="8" t="n">
         <x:v>10.0000</x:v>
       </x:c>
       <x:c r="FD25" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.3300</x:v>
       </x:c>
       <x:c r="FE25" s="6" t="n">
-        <x:v>800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FF25" s="8" t="n">
         <x:v>10.0000</x:v>
       </x:c>
       <x:c r="FG25" s="8" t="n">
-        <x:v>1.3300</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FH25" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -20807,22 +20807,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG26" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4500.0000</x:v>
       </x:c>
       <x:c r="EH26" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="EI26" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>7.8900</x:v>
       </x:c>
       <x:c r="EJ26" s="6" t="n">
-        <x:v>4500.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EK26" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="EL26" s="8" t="n">
-        <x:v>7.8900</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EM26" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -21766,22 +21766,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EJ27" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4500.0000</x:v>
       </x:c>
       <x:c r="EK27" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="EL27" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>7.8900</x:v>
       </x:c>
       <x:c r="EM27" s="6" t="n">
-        <x:v>4500.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN27" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="EO27" s="8" t="n">
-        <x:v>7.8900</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP27" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -22671,40 +22671,40 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DU28" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1800.0000</x:v>
       </x:c>
       <x:c r="DV28" s="8" t="n">
         <x:v>8.0000</x:v>
       </x:c>
       <x:c r="DW28" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3.7500</x:v>
       </x:c>
       <x:c r="DX28" s="6" t="n">
-        <x:v>1800.0000</x:v>
+        <x:v>600.0000</x:v>
       </x:c>
       <x:c r="DY28" s="8" t="n">
         <x:v>8.0000</x:v>
       </x:c>
       <x:c r="DZ28" s="8" t="n">
-        <x:v>3.7500</x:v>
+        <x:v>1.2500</x:v>
       </x:c>
       <x:c r="EA28" s="6" t="n">
-        <x:v>600.0000</x:v>
+        <x:v>1200.0000</x:v>
       </x:c>
       <x:c r="EB28" s="8" t="n">
         <x:v>8.0000</x:v>
       </x:c>
       <x:c r="EC28" s="8" t="n">
-        <x:v>1.2500</x:v>
+        <x:v>2.5000</x:v>
       </x:c>
       <x:c r="ED28" s="6" t="n">
-        <x:v>1200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EE28" s="8" t="n">
         <x:v>8.0000</x:v>
       </x:c>
       <x:c r="EF28" s="8" t="n">
-        <x:v>2.5000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG28" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -23720,31 +23720,31 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB29" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1500.0000</x:v>
       </x:c>
       <x:c r="FC29" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="FD29" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.6300</x:v>
       </x:c>
       <x:c r="FE29" s="6" t="n">
-        <x:v>1500.0000</x:v>
+        <x:v>3000.0000</x:v>
       </x:c>
       <x:c r="FF29" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="FG29" s="8" t="n">
-        <x:v>2.6300</x:v>
+        <x:v>5.2600</x:v>
       </x:c>
       <x:c r="FH29" s="6" t="n">
-        <x:v>3000.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FI29" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="FJ29" s="8" t="n">
-        <x:v>5.2600</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FK29" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -24679,31 +24679,31 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FE30" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2100.0000</x:v>
       </x:c>
       <x:c r="FF30" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="FG30" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3.6800</x:v>
       </x:c>
       <x:c r="FH30" s="6" t="n">
-        <x:v>2100.0000</x:v>
+        <x:v>2400.0000</x:v>
       </x:c>
       <x:c r="FI30" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="FJ30" s="8" t="n">
-        <x:v>3.6800</x:v>
+        <x:v>4.2100</x:v>
       </x:c>
       <x:c r="FK30" s="6" t="n">
-        <x:v>2400.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FL30" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="FM30" s="8" t="n">
-        <x:v>4.2100</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FN30" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -25656,22 +25656,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FN31" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4500.0000</x:v>
       </x:c>
       <x:c r="FO31" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="FP31" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>7.8900</x:v>
       </x:c>
       <x:c r="FQ31" s="6" t="n">
-        <x:v>4500.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FR31" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="FS31" s="8" t="n">
-        <x:v>7.8900</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FT31" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -26588,31 +26588,31 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FH32" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2700.0000</x:v>
       </x:c>
       <x:c r="FI32" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="FJ32" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>4.7400</x:v>
       </x:c>
       <x:c r="FK32" s="6" t="n">
-        <x:v>2700.0000</x:v>
+        <x:v>1800.0000</x:v>
       </x:c>
       <x:c r="FL32" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="FM32" s="8" t="n">
-        <x:v>4.7400</x:v>
+        <x:v>3.1600</x:v>
       </x:c>
       <x:c r="FN32" s="6" t="n">
-        <x:v>1800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FO32" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="FP32" s="8" t="n">
-        <x:v>3.1600</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FQ32" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -27556,22 +27556,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FN33" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>600.0000</x:v>
       </x:c>
       <x:c r="FO33" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="FP33" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1.0500</x:v>
       </x:c>
       <x:c r="FQ33" s="6" t="n">
-        <x:v>600.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FR33" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="FS33" s="8" t="n">
-        <x:v>1.0500</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FT33" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -27583,22 +27583,22 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FW33" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3900.0000</x:v>
       </x:c>
       <x:c r="FX33" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="FY33" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>6.8400</x:v>
       </x:c>
       <x:c r="FZ33" s="6" t="n">
-        <x:v>3900.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GA33" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="GB33" s="8" t="n">
-        <x:v>6.8400</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GC33" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -28533,31 +28533,31 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FW34" s="6" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>1500.0000</x:v>
       </x:c>
       <x:c r="FX34" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="FY34" s="8" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2.6300</x:v>
       </x:c>
       <x:c r="FZ34" s="6" t="n">
-        <x:v>1500.0000</x:v>
+        <x:v>1800.0000</x:v>
       </x:c>
       <x:c r="GA34" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="GB34" s="8" t="n">
-        <x:v>2.6300</x:v>
+        <x:v>3.1600</x:v>
       </x:c>
       <x:c r="GC34" s="6" t="n">
-        <x:v>1800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GD34" s="8" t="n">
         <x:v>9.5000</x:v>
       </x:c>
       <x:c r="GE34" s="8" t="n">
-        <x:v>3.1600</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GF34" s="6" t="n">
         <x:v>0.0000</x:v>
@@ -29312,76 +29312,76 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="DR35" s="7" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>2400.0000</x:v>
       </x:c>
       <x:c r="DS35" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="DT35" s="9" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>3.3300</x:v>
       </x:c>
       <x:c r="DU35" s="7" t="n">
-        <x:v>2400.0000</x:v>
+        <x:v>10000.0000</x:v>
       </x:c>
       <x:c r="DV35" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="DW35" s="9" t="n">
-        <x:v>3.3300</x:v>
+        <x:v>11.5300</x:v>
       </x:c>
       <x:c r="DX35" s="7" t="n">
-        <x:v>10000.0000</x:v>
+        <x:v>9000.0000</x:v>
       </x:c>
       <x:c r="DY35" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="DZ35" s="9" t="n">
-        <x:v>11.5300</x:v>
+        <x:v>8.2300</x:v>
       </x:c>
       <x:c r="EA35" s="7" t="n">
-        <x:v>9000.0000</x:v>
+        <x:v>1200.0000</x:v>
       </x:c>
       <x:c r="EB35" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="EC35" s="9" t="n">
-        <x:v>8.2300</x:v>
+        <x:v>2.5000</x:v>
       </x:c>
       <x:c r="ED35" s="7" t="n">
-        <x:v>1200.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EE35" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="EF35" s="9" t="n">
-        <x:v>2.5000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EG35" s="7" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>13100.0000</x:v>
       </x:c>
       <x:c r="EH35" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="EI35" s="9" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>14.5400</x:v>
       </x:c>
       <x:c r="EJ35" s="7" t="n">
-        <x:v>13100.0000</x:v>
+        <x:v>14500.0000</x:v>
       </x:c>
       <x:c r="EK35" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="EL35" s="9" t="n">
-        <x:v>14.5400</x:v>
+        <x:v>14.5500</x:v>
       </x:c>
       <x:c r="EM35" s="7" t="n">
-        <x:v>14500.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EN35" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="EO35" s="9" t="n">
-        <x:v>14.5500</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="EP35" s="7" t="n">
         <x:v>0.0000</x:v>
@@ -29420,58 +29420,58 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FB35" s="7" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>9200.0000</x:v>
       </x:c>
       <x:c r="FC35" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FD35" s="9" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>10.6700</x:v>
       </x:c>
       <x:c r="FE35" s="7" t="n">
-        <x:v>9200.0000</x:v>
+        <x:v>14550.0000</x:v>
       </x:c>
       <x:c r="FF35" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FG35" s="9" t="n">
-        <x:v>10.6700</x:v>
+        <x:v>17.5800</x:v>
       </x:c>
       <x:c r="FH35" s="7" t="n">
-        <x:v>14550.0000</x:v>
+        <x:v>11400.0000</x:v>
       </x:c>
       <x:c r="FI35" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FJ35" s="9" t="n">
-        <x:v>17.5800</x:v>
+        <x:v>14.7600</x:v>
       </x:c>
       <x:c r="FK35" s="7" t="n">
-        <x:v>11400.0000</x:v>
+        <x:v>6300.0000</x:v>
       </x:c>
       <x:c r="FL35" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FM35" s="9" t="n">
-        <x:v>14.7600</x:v>
+        <x:v>7.3100</x:v>
       </x:c>
       <x:c r="FN35" s="7" t="n">
-        <x:v>6300.0000</x:v>
+        <x:v>8400.0000</x:v>
       </x:c>
       <x:c r="FO35" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FP35" s="9" t="n">
-        <x:v>7.3100</x:v>
+        <x:v>11.9900</x:v>
       </x:c>
       <x:c r="FQ35" s="7" t="n">
-        <x:v>8400.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FR35" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FS35" s="9" t="n">
-        <x:v>11.9900</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FT35" s="7" t="n">
         <x:v>0.0000</x:v>
@@ -29483,31 +29483,31 @@
         <x:v>0.0000</x:v>
       </x:c>
       <x:c r="FW35" s="7" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>5400.0000</x:v>
       </x:c>
       <x:c r="FX35" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="FY35" s="9" t="n">
-        <x:v>0.0000</x:v>
+        <x:v>9.4700</x:v>
       </x:c>
       <x:c r="FZ35" s="7" t="n">
-        <x:v>5400.0000</x:v>
+        <x:v>1800.0000</x:v>
       </x:c>
       <x:c r="GA35" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="GB35" s="9" t="n">
-        <x:v>9.4700</x:v>
+        <x:v>3.1600</x:v>
       </x:c>
       <x:c r="GC35" s="7" t="n">
-        <x:v>1800.0000</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GD35" s="9" t="str">
         <x:v/>
       </x:c>
       <x:c r="GE35" s="9" t="n">
-        <x:v>3.1600</x:v>
+        <x:v>0.0000</x:v>
       </x:c>
       <x:c r="GF35" s="7" t="n">
         <x:v>0.0000</x:v>

--- a/.pm-ai-cache/network-source/task-input-newest.xlsx
+++ b/.pm-ai-cache/network-source/task-input-newest.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工程別生産計画問合せ問合せ" sheetId="1" r:id="R96e4c7bec70e4dfa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工程別生産計画問合せ問合せ" sheetId="1" r:id="Rdeca38e1507c40e2"/>
   </x:sheets>
 </x:workbook>
 </file>
